--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>20.01053154331047</v>
+        <v>15.448906650814621</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>126.03000000000003</v>
+        <v>93.21000000000004</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>67.86048689138576</v>
+        <v>63.89827961836075</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>29.38972537778437</v>
+        <v>22.000324971691864</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>109.25</v>
+        <v>76.43</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>32.53247290200707</v>
+        <v>22.016675856213674</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>28.37999999999999</v>
+        <v>19.730000000000004</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6.934206163668932</v>
+        <v>7.006532331247617</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.369999999999999</v>
+        <v>2.8599999999999994</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>370.4960835509137</v>
+        <v>257.57180156657967</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         <v>173.01</v>
       </c>
       <c r="H3" s="4">
-        <v>206.33999999999997</v>
+        <v>199.42000000000002</v>
       </c>
       <c r="I3" s="4">
-        <v>247.28000000000003</v>
+        <v>229.88</v>
       </c>
       <c r="J3" s="4">
-        <v>299.04</v>
+        <v>266.22</v>
       </c>
     </row>
     <row r="4">
@@ -1304,13 +1304,13 @@
         <v>4.873613384251674</v>
       </c>
       <c r="H4" s="2">
-        <v>19.26478238252123</v>
+        <v>15.265013583029896</v>
       </c>
       <c r="I4" s="2">
-        <v>19.841039061742794</v>
+        <v>15.27429545682477</v>
       </c>
       <c r="J4" s="2">
-        <v>20.931737301844056</v>
+        <v>15.8082477814512</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>117.65</v>
       </c>
       <c r="H5" s="2">
-        <v>138.97</v>
+        <v>134.3</v>
       </c>
       <c r="I5" s="2">
-        <v>165.63</v>
+        <v>153.98000000000002</v>
       </c>
       <c r="J5" s="2">
-        <v>199.07</v>
+        <v>177.26</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>55.359999999999985</v>
       </c>
       <c r="H7" s="4">
-        <v>67.36999999999998</v>
+        <v>65.12</v>
       </c>
       <c r="I7" s="4">
-        <v>81.65000000000003</v>
+        <v>75.89999999999998</v>
       </c>
       <c r="J7" s="4">
-        <v>99.97000000000003</v>
+        <v>88.96000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>31.998150395930864</v>
       </c>
       <c r="H8" s="2">
-        <v>32.64999515362992</v>
+        <v>32.654698626015445</v>
       </c>
       <c r="I8" s="2">
-        <v>33.019249433840194</v>
+        <v>33.01722637898033</v>
       </c>
       <c r="J8" s="2">
-        <v>33.43031032637775</v>
+        <v>33.415971752685756</v>
       </c>
     </row>
     <row r="9">
@@ -1474,13 +1474,13 @@
         <v>44.22</v>
       </c>
       <c r="H9" s="2">
-        <v>48.489999999999995</v>
+        <v>47.910000000000004</v>
       </c>
       <c r="I9" s="2">
-        <v>53.88</v>
+        <v>52.76</v>
       </c>
       <c r="J9" s="2">
-        <v>60.08</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="10">
@@ -1610,13 +1610,13 @@
         <v>17.09</v>
       </c>
       <c r="H13" s="2">
-        <v>18.19</v>
+        <v>18.200000000000003</v>
       </c>
       <c r="I13" s="2">
-        <v>19.85</v>
+        <v>20.09</v>
       </c>
       <c r="J13" s="2">
-        <v>21.68</v>
+        <v>22.189999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1644,13 +1644,13 @@
         <v>16.240000000000002</v>
       </c>
       <c r="H14" s="2">
-        <v>17.74</v>
+        <v>17.93</v>
       </c>
       <c r="I14" s="2">
-        <v>19.37</v>
+        <v>19.810000000000002</v>
       </c>
       <c r="J14" s="2">
-        <v>21.16</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9199999999999999</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1746,13 +1746,13 @@
         <v>0.81</v>
       </c>
       <c r="H17" s="2">
-        <v>0.97</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="J17" s="2">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="18">
@@ -1780,13 +1780,13 @@
         <v>11.139999999999983</v>
       </c>
       <c r="H18" s="4">
-        <v>18.87999999999998</v>
+        <v>17.21</v>
       </c>
       <c r="I18" s="4">
-        <v>27.77000000000003</v>
+        <v>23.13999999999998</v>
       </c>
       <c r="J18" s="4">
-        <v>39.89000000000003</v>
+        <v>30.730000000000047</v>
       </c>
     </row>
     <row r="19">
@@ -1814,13 +1814,13 @@
         <v>6.438934165655155</v>
       </c>
       <c r="H19" s="2">
-        <v>9.149946689929235</v>
+        <v>8.63002707852773</v>
       </c>
       <c r="I19" s="2">
-        <v>11.230184406341001</v>
+        <v>10.066121454671995</v>
       </c>
       <c r="J19" s="2">
-        <v>13.33935259497058</v>
+        <v>11.543084666816934</v>
       </c>
     </row>
     <row r="20">
@@ -1848,13 +1848,13 @@
         <v>11.139999999999983</v>
       </c>
       <c r="H20" s="4">
-        <v>18.87999999999998</v>
+        <v>17.21</v>
       </c>
       <c r="I20" s="4">
-        <v>27.77000000000003</v>
+        <v>23.13999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>39.89000000000003</v>
+        <v>30.730000000000047</v>
       </c>
     </row>
     <row r="21">
@@ -1986,13 +1986,13 @@
         <v>17.09</v>
       </c>
       <c r="H23" s="2">
-        <v>18.19</v>
+        <v>18.200000000000003</v>
       </c>
       <c r="I23" s="2">
-        <v>19.85</v>
+        <v>20.09</v>
       </c>
       <c r="J23" s="2">
-        <v>21.68</v>
+        <v>22.189999999999998</v>
       </c>
     </row>
     <row r="24">
@@ -2088,13 +2088,13 @@
         <v>35.13999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>44.019999999999975</v>
+        <v>42.36</v>
       </c>
       <c r="I26" s="4">
-        <v>54.61000000000003</v>
+        <v>50.21999999999997</v>
       </c>
       <c r="J26" s="4">
-        <v>68.61000000000003</v>
+        <v>59.96000000000004</v>
       </c>
     </row>
     <row r="27">
@@ -2124,13 +2124,13 @@
         <v>5.241090146750493</v>
       </c>
       <c r="H27" s="2">
-        <v>25.270347182697783</v>
+        <v>20.54638588503137</v>
       </c>
       <c r="I27" s="2">
-        <v>24.057246706042832</v>
+        <v>18.555240793201055</v>
       </c>
       <c r="J27" s="2">
-        <v>25.636330342428117</v>
+        <v>19.394663480685146</v>
       </c>
     </row>
     <row r="28">
@@ -2158,13 +2158,13 @@
         <v>20.310964684122293</v>
       </c>
       <c r="H28" s="2">
-        <v>21.33372104293883</v>
+        <v>21.241600641861396</v>
       </c>
       <c r="I28" s="2">
-        <v>22.08427693303139</v>
+        <v>21.84618061597354</v>
       </c>
       <c r="J28" s="2">
-        <v>22.94341894060996</v>
+        <v>22.522725565321927</v>
       </c>
     </row>
     <row r="29">
@@ -2192,13 +2192,13 @@
         <v>264</v>
       </c>
       <c r="H29" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I29" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J29" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -2260,13 +2260,13 @@
         <v>0.06473484848484848</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06638686131386862</v>
+        <v>0.06594202898550726</v>
       </c>
       <c r="I31" s="2">
-        <v>0.0698943661971831</v>
+        <v>0.06975694444444444</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07374149659863946</v>
+        <v>0.07396666666666665</v>
       </c>
     </row>
     <row r="32">
@@ -2296,13 +2296,13 @@
         <v>2.0211495821252035</v>
       </c>
       <c r="H32" s="2">
-        <v>2.551968325695242</v>
+        <v>1.8648077950492503</v>
       </c>
       <c r="I32" s="2">
-        <v>5.2834323146133455</v>
+        <v>5.785256410256379</v>
       </c>
       <c r="J32" s="2">
-        <v>5.504206720471561</v>
+        <v>6.034843205574902</v>
       </c>
     </row>
     <row r="33">
@@ -2400,13 +2400,13 @@
         <v>0.13063197026022297</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15777777777777768</v>
+        <v>0.1507473309608541</v>
       </c>
       <c r="I35" s="2">
-        <v>0.18896193771626307</v>
+        <v>0.17139931740614325</v>
       </c>
       <c r="J35" s="2">
-        <v>0.2294648829431439</v>
+        <v>0.19659016393442638</v>
       </c>
     </row>
     <row r="36">
@@ -2434,13 +2434,13 @@
         <v>16.939999999999984</v>
       </c>
       <c r="H36" s="4">
-        <v>24.679999999999982</v>
+        <v>23.01</v>
       </c>
       <c r="I36" s="4">
-        <v>33.57000000000003</v>
+        <v>28.93999999999998</v>
       </c>
       <c r="J36" s="4">
-        <v>45.690000000000026</v>
+        <v>36.530000000000044</v>
       </c>
     </row>
     <row r="37">
@@ -2468,13 +2468,13 @@
         <v>9.791341540951382</v>
       </c>
       <c r="H37" s="2">
-        <v>11.960841329843939</v>
+        <v>11.538461538461538</v>
       </c>
       <c r="I37" s="2">
-        <v>13.57570365577484</v>
+        <v>12.589176961893154</v>
       </c>
       <c r="J37" s="2">
-        <v>15.278892455858756</v>
+        <v>13.721733904289701</v>
       </c>
     </row>
     <row r="38">
@@ -2504,13 +2504,13 @@
         <v>3.6719706242349215</v>
       </c>
       <c r="H38" s="2">
-        <v>45.69067296340028</v>
+        <v>35.832349468713254</v>
       </c>
       <c r="I38" s="2">
-        <v>36.02106969205856</v>
+        <v>25.771403737505327</v>
       </c>
       <c r="J38" s="2">
-        <v>36.10366398570149</v>
+        <v>26.22667588113361</v>
       </c>
     </row>
   </sheetData>
@@ -2672,13 +2672,13 @@
         <v>93.68</v>
       </c>
       <c r="H3" s="4">
-        <v>121.21</v>
+        <v>114.29</v>
       </c>
       <c r="I3" s="4">
-        <v>156.83</v>
+        <v>139.43</v>
       </c>
       <c r="J3" s="4">
-        <v>202.93</v>
+        <v>170.11</v>
       </c>
     </row>
     <row r="4">
@@ -2708,13 +2708,13 @@
         <v>5.400540054005409</v>
       </c>
       <c r="H4" s="2">
-        <v>29.387275832621683</v>
+        <v>22.000426985482502</v>
       </c>
       <c r="I4" s="2">
-        <v>29.387014272749788</v>
+        <v>21.996675124682817</v>
       </c>
       <c r="J4" s="2">
-        <v>29.3948861824906</v>
+        <v>22.00387291113821</v>
       </c>
     </row>
     <row r="5">
@@ -2742,13 +2742,13 @@
         <v>54.14715912375008</v>
       </c>
       <c r="H5" s="2">
-        <v>58.74285160414849</v>
+        <v>57.31120248721292</v>
       </c>
       <c r="I5" s="2">
-        <v>63.42203170494985</v>
+        <v>60.653384374456245</v>
       </c>
       <c r="J5" s="2">
-        <v>67.86048689138576</v>
+        <v>63.89827961836075</v>
       </c>
     </row>
     <row r="6">
@@ -2776,13 +2776,13 @@
         <v>29.980000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>39.41999999999999</v>
+        <v>37.17</v>
       </c>
       <c r="I6" s="4">
-        <v>51.81000000000002</v>
+        <v>46.06</v>
       </c>
       <c r="J6" s="4">
-        <v>68.1</v>
+        <v>57.09000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -2810,13 +2810,13 @@
         <v>32.00256191289496</v>
       </c>
       <c r="H7" s="2">
-        <v>32.52206913620987</v>
+        <v>32.522530405109805</v>
       </c>
       <c r="I7" s="2">
-        <v>33.0357712172416</v>
+        <v>33.034497597360684</v>
       </c>
       <c r="J7" s="2">
-        <v>33.55836988123983</v>
+        <v>33.56063723473048</v>
       </c>
     </row>
     <row r="8">
@@ -2844,13 +2844,13 @@
         <v>6.6200000000000045</v>
       </c>
       <c r="H8" s="4">
-        <v>12.929999999999987</v>
+        <v>11.260000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>21.160000000000014</v>
+        <v>16.54</v>
       </c>
       <c r="J8" s="4">
-        <v>32.55</v>
+        <v>23.410000000000018</v>
       </c>
     </row>
     <row r="9">
@@ -2878,13 +2878,13 @@
         <v>7.066609735269005</v>
       </c>
       <c r="H9" s="2">
-        <v>10.667436680141892</v>
+        <v>9.85213054510456</v>
       </c>
       <c r="I9" s="2">
-        <v>13.492316521073782</v>
+        <v>11.862583375170335</v>
       </c>
       <c r="J9" s="2">
-        <v>16.04001379786133</v>
+        <v>13.761683616483461</v>
       </c>
     </row>
     <row r="10">
@@ -2912,13 +2912,13 @@
         <v>7.48</v>
       </c>
       <c r="H10" s="2">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.81</v>
+        <v>9.04</v>
       </c>
       <c r="J10" s="2">
-        <v>9.85</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="11">
@@ -3014,13 +3014,13 @@
         <v>18.870000000000005</v>
       </c>
       <c r="H13" s="4">
-        <v>25.619999999999987</v>
+        <v>23.960000000000004</v>
       </c>
       <c r="I13" s="4">
-        <v>34.79000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="J13" s="4">
-        <v>47.24999999999999</v>
+        <v>38.60000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3050,13 +3050,13 @@
         <v>6.190208216094595</v>
       </c>
       <c r="H14" s="2">
-        <v>35.77106518282977</v>
+        <v>26.974032856385797</v>
       </c>
       <c r="I14" s="2">
-        <v>35.792349726776074</v>
+        <v>26.878130217028364</v>
       </c>
       <c r="J14" s="2">
-        <v>35.81488933601602</v>
+        <v>26.97368421052635</v>
       </c>
     </row>
     <row r="15">
@@ -3084,13 +3084,13 @@
         <v>117</v>
       </c>
       <c r="H15" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I15" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J15" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -3152,13 +3152,13 @@
         <v>0.06393162393162394</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06575</v>
+        <v>0.06475409836065574</v>
       </c>
       <c r="I17" s="2">
-        <v>0.0716260162601626</v>
+        <v>0.07118110236220472</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07817460317460317</v>
+        <v>0.07833333333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3188,13 +3188,13 @@
         <v>2.106622394392188</v>
       </c>
       <c r="H18" s="2">
-        <v>2.8442513368983846</v>
+        <v>1.2864907512930568</v>
       </c>
       <c r="I18" s="2">
-        <v>8.936906859562876</v>
+        <v>9.925246685936395</v>
       </c>
       <c r="J18" s="2">
-        <v>9.142749040592403</v>
+        <v>10.047935103244843</v>
       </c>
     </row>
     <row r="19">
@@ -3292,13 +3292,13 @@
         <v>0.1585714285714286</v>
       </c>
       <c r="H21" s="2">
-        <v>0.20999999999999988</v>
+        <v>0.19322580645161294</v>
       </c>
       <c r="I21" s="2">
-        <v>0.2783200000000001</v>
+        <v>0.23565891472868217</v>
       </c>
       <c r="J21" s="2">
-        <v>0.36914062499999994</v>
+        <v>0.2880597014925374</v>
       </c>
     </row>
     <row r="22">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.26 % / 補助 29.39 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.84 % / 補助 29.39 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.93 % / 補助 29.39 % / 他 6.26 %</t>
+          <t xml:space="preserve">全社 15.81 % / 補助 22 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.98 % / 補助 66.96 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 66.98 % / 補助 66.97 % / 他 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.57 % / 補助 66.44 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.58 % / 補助 66.44 % / 他 66.84 %</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.02 % / 補助 33.04 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 33.02 % / 補助 33.03 % / 他 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.43 % / 補助 33.56 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.42 % / 補助 33.56 % / 他 33.16 %</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.5 % / 補助 21.85 % / 他 25.84 %</t>
+          <t xml:space="preserve">全社 24.02 % / 補助 22.67 % / 他 25.84 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.79 % / 補助 19.54 % / 他 25.68 %</t>
+          <t xml:space="preserve">全社 22.95 % / 補助 21.17 % / 他 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.09 % / 補助 17.52 % / 他 25.52 %</t>
+          <t xml:space="preserve">全社 21.87 % / 補助 19.8 % / 他 25.54 %</t>
         </is>
       </c>
     </row>
@@ -3874,17 +3874,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.15 % / 補助 10.67 % / 他 6.99 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 9.85 % / 他 6.99 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.23 % / 補助 13.49 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.86 % / 他 7.3 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.34 % / 補助 16.04 % / 他 7.64 %</t>
+          <t xml:space="preserve">全社 11.54 % / 補助 13.76 % / 他 7.62 %</t>
         </is>
       </c>
     </row>
@@ -3936,17 +3936,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.96 % / 補助 14.21 % / 他 8.75 %</t>
+          <t xml:space="preserve">全社 11.54 % / 補助 13.61 % / 他 8.75 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.58 % / 補助 16.23 % / 他 8.97 %</t>
+          <t xml:space="preserve">全社 12.59 % / 補助 14.95 % / 他 8.96 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 18.16 % / 他 9.2 %</t>
+          <t xml:space="preserve">全社 13.72 % / 補助 16.29 % / 他 9.18 %</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.51 % / 補助 11.76 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.63 % / 補助 12 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.02 % / 補助 11.03 % / 他 10.99 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / 他 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.47 % / 補助 10.3 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 11 % / 他 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.82 % / 補助 6.51 % / 他 12.1 %</t>
+          <t xml:space="preserve">全社 9.13 % / 補助 6.91 % / 他 12.1 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.03 % / 補助 5.62 % / 他 12.21 %</t>
+          <t xml:space="preserve">全社 8.74 % / 補助 6.48 % / 他 12.22 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.25 % / 補助 4.85 % / 他 12.31 %</t>
+          <t xml:space="preserve">全社 8.34 % / 補助 6.08 % / 他 12.33 %</t>
         </is>
       </c>
     </row>
@@ -4184,17 +4184,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.56 % / 補助 0.41 % / 他 0.76 %</t>
+          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / 他 0.76 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.48 % / 補助 0.33 % / 他 0.74 %</t>
+          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / 他 0.74 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.41 % / 補助 0.27 % / 他 0.72 %</t>
+          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / 他 0.72 %</t>
         </is>
       </c>
     </row>
@@ -4246,17 +4246,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.37 % / 補助 6.92 % / 他 12.86 %</t>
+          <t xml:space="preserve">全社 9.7 % / 補助 7.35 % / 他 12.86 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.51 % / 補助 5.95 % / 他 12.95 %</t>
+          <t xml:space="preserve">全社 9.26 % / 補助 6.86 % / 他 12.96 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.66 % / 補助 5.12 % / 他 13.03 %</t>
+          <t xml:space="preserve">全社 8.8 % / 補助 6.4 % / 他 13.05 %</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.065 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / 他 0.071 億円/人</t>
         </is>
       </c>
     </row>
@@ -4432,17 +4432,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.55 % / 補助 2.84 % / 他 2.31 %</t>
+          <t xml:space="preserve">全社 1.86 % / 補助 1.29 % / 他 2.31 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.28 % / 補助 8.94 % / 他 2.52 %</t>
+          <t xml:space="preserve">全社 5.79 % / 補助 9.93 % / 他 2.62 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.5 % / 補助 9.14 % / 他 2.69 %</t>
+          <t xml:space="preserve">全社 6.03 % / 補助 10.05 % / 他 2.77 %</t>
         </is>
       </c>
     </row>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.93 % / 補助 32.75 % / 他 59.51 %</t>
+          <t xml:space="preserve">全社 45.68 % / 補助 35.06 % / 他 59.51 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.53 % / 補助 26.82 % / 他 59.08 %</t>
+          <t xml:space="preserve">全社 42.37 % / 補助 31.45 % / 他 59.13 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.41 % / 補助 22.01 % / 他 58.61 %</t>
+          <t xml:space="preserve">全社 39.08 % / 補助 28.21 % / 他 58.71 %</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.753 億円/人 / 補助 1.01 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">全社 0.723 億円/人 / 補助 0.937 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.871 億円/人 / 補助 1.275 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">全社 0.798 億円/人 / 補助 1.098 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.611 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.887 億円/人 / 補助 1.289 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4680,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.108 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.092 億円/人 / 他 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.172 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.08 億円/人 / 補助 0.13 億円/人 / 他 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.136 億円/人 / 補助 0.258 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.102 億円/人 / 補助 0.177 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.158 億円/人 / 補助 0.21 億円/人 / 他 0.117 億円/人</t>
+          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / 他 0.117 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.189 億円/人 / 補助 0.278 億円/人 / 他 0.121 億円/人</t>
+          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.236 億円/人 / 他 0.121 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.229 億円/人 / 補助 0.369 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.288 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4804,17 +4804,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.79 % / 補助 2.56 % / 他 4.76 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 4.27 % / 他 4.76 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.65 % / 補助 2.5 % / 他 4.55 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 4.1 % / 他 4.55 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.52 % / 補助 2.44 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.17 % / 補助 3.94 % / 他 4.35 %</t>
         </is>
       </c>
     </row>
@@ -4866,17 +4866,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.48 pt / 補助 26.82 pt / 他 2.55 pt</t>
+          <t xml:space="preserve">全社 10.72 pt / 補助 17.73 pt / 他 2.55 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.19 pt / 補助 26.89 pt / 他 1.7 pt</t>
+          <t xml:space="preserve">全社 10.93 pt / 補助 17.9 pt / 他 1.7 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17.41 pt / 補助 26.96 pt / 他 1.91 pt</t>
+          <t xml:space="preserve">全社 11.64 pt / 補助 18.07 pt / 他 1.91 pt</t>
         </is>
       </c>
     </row>
@@ -4990,17 +4990,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.81 % / 補助 3.55 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / 他 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.35 % / 補助 2.74 % / 他 1.66 %</t>
+          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / 他 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.94 % / 補助 2.12 % / 他 1.56 %</t>
+          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / 他 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.26 倍 / 補助 4.01 倍 / 他 4.97 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.79 倍 / 補助 5.92 倍 / 他 5.41 倍</t>
+          <t xml:space="preserve">全社 4.99 倍 / 補助 4.85 倍 / 他 5.4 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.88 倍 / 補助 8.57 倍 / 他 5.89 倍</t>
+          <t xml:space="preserve">全社 6.3 倍 / 補助 6.44 倍 / 他 5.88 倍</t>
         </is>
       </c>
     </row>
@@ -5362,17 +5362,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 58.74 %</t>
+          <t xml:space="preserve">構成比 57.31 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.42 %</t>
+          <t xml:space="preserve">構成比 60.65 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 67.86 %</t>
+          <t xml:space="preserve">構成比 63.9 %</t>
         </is>
       </c>
     </row>
@@ -5424,17 +5424,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 6.26 %</t>
+          <t xml:space="preserve">補助 22 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.05 pt</t>
+          <t xml:space="preserve">差 -0.04 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.68 pt</t>
+          <t xml:space="preserve">差 2.86 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.18 pt</t>
+          <t xml:space="preserve">差 4.57 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 8.4 pt</t>
+          <t xml:space="preserve">差 6.15 pt</t>
         </is>
       </c>
     </row>
@@ -5610,17 +5610,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.01 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">補助 0.937 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.275 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">補助 1.098 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.611 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.289 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5672,17 +5672,17 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.065 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.072 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.071 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.078 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">補助 0.078 億円/人 / 他 0.071 億円/人</t>
         </is>
       </c>
     </row>
@@ -5734,17 +5734,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 81.52 %</t>
+          <t xml:space="preserve">寄与率 76.44 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 92.58 %</t>
+          <t xml:space="preserve">寄与率 89.04 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 93.98 %</t>
+          <t xml:space="preserve">寄与率 90.51 %</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="B204" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="B206" s="2">
-        <v>133.5</v>
+        <v>82.4</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B223" s="2">
-        <v>76.44</v>
+        <v>74.8</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="B225" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIwLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjEzMy41LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjUsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3Ni40NCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny44OX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MTMzLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjUsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzYuNDQsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwMzY4MDU1NTU1NTU1NCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDczNTk5NDE4MzE4OTE2NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQ0NDg1MzYzMDY3NTMyNzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNzMxNjU4MzkyMjQ5LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDE0OTM3NzcyNDkzMDY0NDYsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yOTM4ODcxNDM5MDA2NTc0LCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU0MDE4NTcwNzI2NTI2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNTU1MDQyNzI1Nzk3NzI4NCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA4ODk0Mzg0MTIyNDYzNTExLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4MTE4MzMyNTM4NjY3ODcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDI2MjQwNzUyNDg1ODkwODkzLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4NzIzNzY5MjEzNjMzOCwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTAzMDAyOTk1NDM3NDEzMjIsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkzMjYxNjQ2NTE2MzY2LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MTkyMzE2Nzk1ODM0OTYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDM2ODA1NTU1NTU1NTQsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjA3MzU5OTQxODMxODkxNjYsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0NDQ4NTM2MzA2NzUzMjc0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA2MDkzMzcwMjc4OTgwNCwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQxNDkzNzc3MjQ5MzA2NDQ2LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTQwMTg1NzA3MjY1MjYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1NTUwNDI3MjU3OTc3Mjg0LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMSwib3RoZXJQYXlHcm93dGgiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4NzIzNzY5MjEzNjMzOCwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkzMjYxNjQ2NTE2MzY2LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MTkyMzE2Nzk1ODM0OTYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.448906650814621</v>
+        <v>15.464691482957393</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>93.21000000000004</v>
+        <v>93.33000000000001</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.0734151154351954</v>
+        <v>2.172559802954921</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.89827961836075</v>
+        <v>63.91350052560445</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.000324971691864</v>
+        <v>22.02271203454029</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>76.43</v>
+        <v>76.54</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>22.016675856213674</v>
+        <v>22.499949660479125</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.730000000000004</v>
+        <v>19.65</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.006532331247617</v>
+        <v>7.027727322388921</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.8599999999999994</v>
+        <v>2.700000000000001</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>257.57180156657967</v>
+        <v>256.5274151436031</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
         <v>150</v>
       </c>
       <c r="E3" s="4">
-        <v>157.3</v>
+        <v>157.31</v>
       </c>
       <c r="F3" s="4">
-        <v>164.97</v>
+        <v>164.98000000000002</v>
       </c>
       <c r="G3" s="4">
-        <v>173.01</v>
+        <v>173.03</v>
       </c>
       <c r="H3" s="4">
-        <v>199.42000000000002</v>
+        <v>199.47</v>
       </c>
       <c r="I3" s="4">
-        <v>229.88</v>
+        <v>229.95999999999998</v>
       </c>
       <c r="J3" s="4">
-        <v>266.22</v>
+        <v>266.36</v>
       </c>
     </row>
     <row r="4">
@@ -1295,22 +1295,22 @@
         <v>4.748603351955305</v>
       </c>
       <c r="E4" s="2">
-        <v>4.866666666666664</v>
+        <v>4.8733333333333295</v>
       </c>
       <c r="F4" s="2">
-        <v>4.876033057851226</v>
+        <v>4.875723094526752</v>
       </c>
       <c r="G4" s="2">
-        <v>4.873613384251674</v>
+        <v>4.879379318705279</v>
       </c>
       <c r="H4" s="2">
-        <v>15.265013583029896</v>
+        <v>15.28058718141363</v>
       </c>
       <c r="I4" s="2">
-        <v>15.27429545682477</v>
+        <v>15.285506592470032</v>
       </c>
       <c r="J4" s="2">
-        <v>15.8082477814512</v>
+        <v>15.828839798225802</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>117.65</v>
       </c>
       <c r="H5" s="2">
-        <v>134.3</v>
+        <v>134.35</v>
       </c>
       <c r="I5" s="2">
-        <v>153.98000000000002</v>
+        <v>154.07999999999998</v>
       </c>
       <c r="J5" s="2">
-        <v>177.26</v>
+        <v>177.44</v>
       </c>
     </row>
     <row r="6">
@@ -1397,22 +1397,22 @@
         <v>48</v>
       </c>
       <c r="E7" s="4">
-        <v>50.33000000000001</v>
+        <v>50.34</v>
       </c>
       <c r="F7" s="4">
-        <v>52.78999999999999</v>
+        <v>52.80000000000001</v>
       </c>
       <c r="G7" s="4">
-        <v>55.359999999999985</v>
+        <v>55.379999999999995</v>
       </c>
       <c r="H7" s="4">
         <v>65.12</v>
       </c>
       <c r="I7" s="4">
-        <v>75.89999999999998</v>
+        <v>75.88</v>
       </c>
       <c r="J7" s="4">
-        <v>88.96000000000004</v>
+        <v>88.92000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>31.996185632549274</v>
+        <v>32.00050854999682</v>
       </c>
       <c r="F8" s="2">
-        <v>31.99975753167242</v>
+        <v>32.00387925809189</v>
       </c>
       <c r="G8" s="2">
-        <v>31.998150395930864</v>
+        <v>32.00601051840721</v>
       </c>
       <c r="H8" s="2">
-        <v>32.654698626015445</v>
+        <v>32.64651326013937</v>
       </c>
       <c r="I8" s="2">
-        <v>33.01722637898033</v>
+        <v>32.99704296399374</v>
       </c>
       <c r="J8" s="2">
-        <v>33.415971752685756</v>
+        <v>33.38339089953447</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.879999999999995</v>
+        <v>38.849999999999994</v>
       </c>
       <c r="F9" s="2">
-        <v>41.48</v>
+        <v>41.43</v>
       </c>
       <c r="G9" s="2">
-        <v>44.22</v>
+        <v>44.14</v>
       </c>
       <c r="H9" s="2">
-        <v>47.910000000000004</v>
+        <v>47.879999999999995</v>
       </c>
       <c r="I9" s="2">
-        <v>52.76</v>
+        <v>52.629999999999995</v>
       </c>
       <c r="J9" s="2">
-        <v>58.23</v>
+        <v>57.980000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -1601,22 +1601,22 @@
         <v>14</v>
       </c>
       <c r="E13" s="2">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
       <c r="F13" s="2">
-        <v>15.989999999999998</v>
+        <v>15.94</v>
       </c>
       <c r="G13" s="2">
-        <v>17.09</v>
+        <v>17.009999999999998</v>
       </c>
       <c r="H13" s="2">
-        <v>18.200000000000003</v>
+        <v>18.16</v>
       </c>
       <c r="I13" s="2">
-        <v>20.09</v>
+        <v>19.95</v>
       </c>
       <c r="J13" s="2">
-        <v>22.189999999999998</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="14">
@@ -1635,22 +1635,22 @@
         <v>13.3</v>
       </c>
       <c r="E14" s="2">
-        <v>14.21</v>
+        <v>14.190000000000001</v>
       </c>
       <c r="F14" s="2">
-        <v>15.19</v>
+        <v>15.14</v>
       </c>
       <c r="G14" s="2">
-        <v>16.240000000000002</v>
+        <v>16.16</v>
       </c>
       <c r="H14" s="2">
-        <v>17.93</v>
+        <v>17.740000000000002</v>
       </c>
       <c r="I14" s="2">
-        <v>19.810000000000002</v>
+        <v>19.509999999999998</v>
       </c>
       <c r="J14" s="2">
-        <v>21.91</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="15">
@@ -1669,7 +1669,7 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="F15" s="2">
         <v>0.8</v>
@@ -1681,10 +1681,10 @@
         <v>0.9299999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1400000000000001</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.45000000000001</v>
+        <v>11.490000000000002</v>
       </c>
       <c r="F18" s="4">
-        <v>11.309999999999995</v>
+        <v>11.370000000000012</v>
       </c>
       <c r="G18" s="4">
-        <v>11.139999999999983</v>
+        <v>11.239999999999995</v>
       </c>
       <c r="H18" s="4">
-        <v>17.21</v>
+        <v>17.24000000000001</v>
       </c>
       <c r="I18" s="4">
-        <v>23.13999999999998</v>
+        <v>23.25</v>
       </c>
       <c r="J18" s="4">
-        <v>30.730000000000047</v>
+        <v>30.94000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.27908455181183</v>
+        <v>7.304049329349693</v>
       </c>
       <c r="F19" s="2">
-        <v>6.855791962174938</v>
+        <v>6.891744453873202</v>
       </c>
       <c r="G19" s="2">
-        <v>6.438934165655155</v>
+        <v>6.495983355487485</v>
       </c>
       <c r="H19" s="2">
-        <v>8.63002707852773</v>
+        <v>8.642903694791201</v>
       </c>
       <c r="I19" s="2">
-        <v>10.066121454671995</v>
+        <v>10.11045399199861</v>
       </c>
       <c r="J19" s="2">
-        <v>11.543084666816934</v>
+        <v>11.615858236972525</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>11.45000000000001</v>
+        <v>11.490000000000002</v>
       </c>
       <c r="F20" s="4">
-        <v>11.309999999999995</v>
+        <v>11.370000000000012</v>
       </c>
       <c r="G20" s="4">
-        <v>11.139999999999983</v>
+        <v>11.239999999999995</v>
       </c>
       <c r="H20" s="4">
-        <v>17.21</v>
+        <v>17.24000000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>23.13999999999998</v>
+        <v>23.25</v>
       </c>
       <c r="J20" s="4">
-        <v>30.730000000000047</v>
+        <v>30.94000000000002</v>
       </c>
     </row>
     <row r="21">
@@ -1977,22 +1977,22 @@
         <v>14</v>
       </c>
       <c r="E23" s="2">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
       <c r="F23" s="2">
-        <v>15.989999999999998</v>
+        <v>15.94</v>
       </c>
       <c r="G23" s="2">
-        <v>17.09</v>
+        <v>17.009999999999998</v>
       </c>
       <c r="H23" s="2">
-        <v>18.200000000000003</v>
+        <v>18.16</v>
       </c>
       <c r="I23" s="2">
-        <v>20.09</v>
+        <v>19.95</v>
       </c>
       <c r="J23" s="2">
-        <v>22.189999999999998</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="24">
@@ -2079,22 +2079,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.71000000000001</v>
+        <v>31.720000000000002</v>
       </c>
       <c r="F26" s="4">
-        <v>33.38999999999999</v>
+        <v>33.400000000000006</v>
       </c>
       <c r="G26" s="4">
-        <v>35.13999999999998</v>
+        <v>35.15999999999999</v>
       </c>
       <c r="H26" s="4">
-        <v>42.36</v>
+        <v>42.35</v>
       </c>
       <c r="I26" s="4">
-        <v>50.21999999999997</v>
+        <v>50.19</v>
       </c>
       <c r="J26" s="4">
-        <v>59.96000000000004</v>
+        <v>59.90000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -2115,22 +2115,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.348837209302348</v>
+        <v>5.382059800664463</v>
       </c>
       <c r="F27" s="2">
-        <v>5.298013245033051</v>
+        <v>5.29634300126105</v>
       </c>
       <c r="G27" s="2">
-        <v>5.241090146750493</v>
+        <v>5.269461077844273</v>
       </c>
       <c r="H27" s="2">
-        <v>20.54638588503137</v>
+        <v>20.449374288964783</v>
       </c>
       <c r="I27" s="2">
-        <v>18.555240793201055</v>
+        <v>18.51239669421487</v>
       </c>
       <c r="J27" s="2">
-        <v>19.394663480685146</v>
+        <v>19.346483363219804</v>
       </c>
     </row>
     <row r="28">
@@ -2149,22 +2149,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.1589319771138</v>
+        <v>20.164007373974954</v>
       </c>
       <c r="F28" s="2">
-        <v>20.24004364429896</v>
+        <v>20.244878167050555</v>
       </c>
       <c r="G28" s="2">
-        <v>20.310964684122293</v>
+        <v>20.32017569207651</v>
       </c>
       <c r="H28" s="2">
-        <v>21.241600641861396</v>
+        <v>21.23126284654334</v>
       </c>
       <c r="I28" s="2">
-        <v>21.84618061597354</v>
+        <v>21.825534875630545</v>
       </c>
       <c r="J28" s="2">
-        <v>22.522725565321927</v>
+        <v>22.488361615858242</v>
       </c>
     </row>
     <row r="29">
@@ -2189,16 +2189,16 @@
         <v>252</v>
       </c>
       <c r="G29" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H29" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30">
@@ -2251,22 +2251,22 @@
         <v>0.06086956521739131</v>
       </c>
       <c r="E31" s="2">
-        <v>0.06233333333333334</v>
+        <v>0.06220833333333333</v>
       </c>
       <c r="F31" s="2">
-        <v>0.06345238095238094</v>
+        <v>0.06325396825396826</v>
       </c>
       <c r="G31" s="2">
-        <v>0.06473484848484848</v>
+        <v>0.0649236641221374</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06594202898550726</v>
+        <v>0.06652014652014653</v>
       </c>
       <c r="I31" s="2">
-        <v>0.06975694444444444</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07396666666666665</v>
+        <v>0.07380471380471382</v>
       </c>
     </row>
     <row r="32">
@@ -2287,22 +2287,22 @@
         <v>1.9901321235802572</v>
       </c>
       <c r="E32" s="2">
-        <v>2.4047619047619095</v>
+        <v>2.199404761904744</v>
       </c>
       <c r="F32" s="2">
-        <v>1.7952635599694178</v>
+        <v>1.680859885816366</v>
       </c>
       <c r="G32" s="2">
-        <v>2.0211495821252035</v>
+        <v>2.6396697539436964</v>
       </c>
       <c r="H32" s="2">
-        <v>1.8648077950492503</v>
+        <v>2.4590146283268055</v>
       </c>
       <c r="I32" s="2">
-        <v>5.785256410256379</v>
+        <v>5.231277533039624</v>
       </c>
       <c r="J32" s="2">
-        <v>6.034843205574902</v>
+        <v>5.43530543530546</v>
       </c>
     </row>
     <row r="33">
@@ -2391,22 +2391,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12942857142857148</v>
+        <v>0.12946938775510206</v>
       </c>
       <c r="F35" s="2">
-        <v>0.12992217898832684</v>
+        <v>0.12996108949416343</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13063197026022297</v>
+        <v>0.13168539325842693</v>
       </c>
       <c r="H35" s="2">
-        <v>0.1507473309608541</v>
+        <v>0.15233812949640288</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17139931740614325</v>
+        <v>0.17306896551724138</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19659016393442638</v>
+        <v>0.1983443708609272</v>
       </c>
     </row>
     <row r="36">
@@ -2425,22 +2425,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.72000000000001</v>
+        <v>15.760000000000002</v>
       </c>
       <c r="F36" s="4">
-        <v>16.339999999999996</v>
+        <v>16.400000000000013</v>
       </c>
       <c r="G36" s="4">
-        <v>16.939999999999984</v>
+        <v>17.039999999999996</v>
       </c>
       <c r="H36" s="4">
-        <v>23.01</v>
+        <v>23.04000000000001</v>
       </c>
       <c r="I36" s="4">
-        <v>28.93999999999998</v>
+        <v>29.05</v>
       </c>
       <c r="J36" s="4">
-        <v>36.530000000000044</v>
+        <v>36.740000000000016</v>
       </c>
     </row>
     <row r="37">
@@ -2459,22 +2459,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>9.993642720915453</v>
+        <v>10.018434937384782</v>
       </c>
       <c r="F37" s="2">
-        <v>9.904831181426923</v>
+        <v>9.940598860467942</v>
       </c>
       <c r="G37" s="2">
-        <v>9.791341540951382</v>
+        <v>9.848003236432985</v>
       </c>
       <c r="H37" s="2">
-        <v>11.538461538461538</v>
+        <v>11.55060911415251</v>
       </c>
       <c r="I37" s="2">
-        <v>12.589176961893154</v>
+        <v>12.632631762045573</v>
       </c>
       <c r="J37" s="2">
-        <v>13.721733904289701</v>
+        <v>13.793362366721734</v>
       </c>
     </row>
     <row r="38">
@@ -2495,22 +2495,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.10596026490071</v>
+        <v>4.370860927152309</v>
       </c>
       <c r="F38" s="2">
-        <v>3.9440203562340015</v>
+        <v>4.060913705583835</v>
       </c>
       <c r="G38" s="2">
-        <v>3.6719706242349215</v>
+        <v>3.9024390243901363</v>
       </c>
       <c r="H38" s="2">
-        <v>35.832349468713254</v>
+        <v>35.21126760563389</v>
       </c>
       <c r="I38" s="2">
-        <v>25.771403737505327</v>
+        <v>26.085069444444397</v>
       </c>
       <c r="J38" s="2">
-        <v>26.22667588113361</v>
+        <v>26.47160068846821</v>
       </c>
     </row>
   </sheetData>
@@ -2663,22 +2663,22 @@
         <v>80</v>
       </c>
       <c r="E3" s="4">
-        <v>84.32</v>
+        <v>84.33</v>
       </c>
       <c r="F3" s="4">
-        <v>88.88</v>
+        <v>88.89</v>
       </c>
       <c r="G3" s="4">
-        <v>93.68</v>
+        <v>93.7</v>
       </c>
       <c r="H3" s="4">
-        <v>114.29</v>
+        <v>114.34</v>
       </c>
       <c r="I3" s="4">
-        <v>139.43</v>
+        <v>139.51</v>
       </c>
       <c r="J3" s="4">
-        <v>170.11</v>
+        <v>170.24</v>
       </c>
     </row>
     <row r="4">
@@ -2699,22 +2699,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E4" s="2">
-        <v>5.399999999999983</v>
+        <v>5.412499999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>5.407969639468702</v>
+        <v>5.407328352899321</v>
       </c>
       <c r="G4" s="2">
-        <v>5.400540054005409</v>
+        <v>5.41118236022049</v>
       </c>
       <c r="H4" s="2">
-        <v>22.000426985482502</v>
+        <v>22.027748132337255</v>
       </c>
       <c r="I4" s="2">
-        <v>21.996675124682817</v>
+        <v>22.01329368549938</v>
       </c>
       <c r="J4" s="2">
-        <v>22.00387291113821</v>
+        <v>22.027094831911697</v>
       </c>
     </row>
     <row r="5">
@@ -2733,22 +2733,22 @@
         <v>53.333333333333336</v>
       </c>
       <c r="E5" s="2">
-        <v>53.60457724094086</v>
+        <v>53.60752653995296</v>
       </c>
       <c r="F5" s="2">
-        <v>53.87646238710069</v>
+        <v>53.87925809188992</v>
       </c>
       <c r="G5" s="2">
-        <v>54.14715912375008</v>
+        <v>54.1524591111368</v>
       </c>
       <c r="H5" s="2">
-        <v>57.31120248721292</v>
+        <v>57.321903043064125</v>
       </c>
       <c r="I5" s="2">
-        <v>60.653384374456245</v>
+        <v>60.66707253435381</v>
       </c>
       <c r="J5" s="2">
-        <v>63.89827961836075</v>
+        <v>63.91350052560445</v>
       </c>
     </row>
     <row r="6">
@@ -2767,22 +2767,22 @@
         <v>25.6</v>
       </c>
       <c r="E6" s="4">
-        <v>26.97999999999999</v>
+        <v>26.989999999999995</v>
       </c>
       <c r="F6" s="4">
-        <v>28.439999999999998</v>
+        <v>28.450000000000003</v>
       </c>
       <c r="G6" s="4">
-        <v>29.980000000000004</v>
+        <v>29.990000000000002</v>
       </c>
       <c r="H6" s="4">
         <v>37.17</v>
       </c>
       <c r="I6" s="4">
-        <v>46.06</v>
+        <v>46.03999999999999</v>
       </c>
       <c r="J6" s="4">
-        <v>57.09000000000002</v>
+        <v>57.040000000000006</v>
       </c>
     </row>
     <row r="7">
@@ -2801,22 +2801,22 @@
         <v>32</v>
       </c>
       <c r="E7" s="2">
-        <v>31.997153700189745</v>
+        <v>32.005217597533495</v>
       </c>
       <c r="F7" s="2">
-        <v>31.998199819982</v>
+        <v>32.00584992687592</v>
       </c>
       <c r="G7" s="2">
-        <v>32.00256191289496</v>
+        <v>32.00640341515475</v>
       </c>
       <c r="H7" s="2">
-        <v>32.522530405109805</v>
+        <v>32.50830855343712</v>
       </c>
       <c r="I7" s="2">
-        <v>33.034497597360684</v>
+        <v>33.001218550641525</v>
       </c>
       <c r="J7" s="2">
-        <v>33.56063723473048</v>
+        <v>33.505639097744364</v>
       </c>
     </row>
     <row r="8">
@@ -2835,22 +2835,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>7.059999999999988</v>
+        <v>7.089999999999989</v>
       </c>
       <c r="F8" s="4">
-        <v>6.849999999999998</v>
+        <v>6.890000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>6.6200000000000045</v>
+        <v>6.680000000000003</v>
       </c>
       <c r="H8" s="4">
-        <v>11.260000000000002</v>
+        <v>11.250000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>16.54</v>
+        <v>16.599999999999987</v>
       </c>
       <c r="J8" s="4">
-        <v>23.410000000000018</v>
+        <v>23.550000000000008</v>
       </c>
     </row>
     <row r="9">
@@ -2869,22 +2869,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>8.372865275142303</v>
+        <v>8.407446934661436</v>
       </c>
       <c r="F9" s="2">
-        <v>7.7070207020702055</v>
+        <v>7.751153110586119</v>
       </c>
       <c r="G9" s="2">
-        <v>7.066609735269005</v>
+        <v>7.129135538954112</v>
       </c>
       <c r="H9" s="2">
-        <v>9.85213054510456</v>
+        <v>9.839076438691622</v>
       </c>
       <c r="I9" s="2">
-        <v>11.862583375170335</v>
+        <v>11.89878861730341</v>
       </c>
       <c r="J9" s="2">
-        <v>13.761683616483461</v>
+        <v>13.833411654135341</v>
       </c>
     </row>
     <row r="10">
@@ -2903,22 +2903,22 @@
         <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
       <c r="F10" s="2">
-        <v>6.95</v>
+        <v>6.92</v>
       </c>
       <c r="G10" s="2">
-        <v>7.48</v>
+        <v>7.43</v>
       </c>
       <c r="H10" s="2">
         <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>9.04</v>
+        <v>8.95</v>
       </c>
       <c r="J10" s="2">
-        <v>10.34</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="11">
@@ -3005,22 +3005,22 @@
         <v>15.700000000000005</v>
       </c>
       <c r="E13" s="4">
-        <v>16.70999999999999</v>
+        <v>16.71999999999999</v>
       </c>
       <c r="F13" s="4">
-        <v>17.769999999999996</v>
+        <v>17.78</v>
       </c>
       <c r="G13" s="4">
-        <v>18.870000000000005</v>
+        <v>18.880000000000003</v>
       </c>
       <c r="H13" s="4">
-        <v>23.960000000000004</v>
+        <v>23.950000000000003</v>
       </c>
       <c r="I13" s="4">
-        <v>30.4</v>
+        <v>30.369999999999987</v>
       </c>
       <c r="J13" s="4">
-        <v>38.60000000000001</v>
+        <v>38.53</v>
       </c>
     </row>
     <row r="14">
@@ -3041,22 +3041,22 @@
         <v>5.2984574111334615</v>
       </c>
       <c r="E14" s="2">
-        <v>6.433121019108179</v>
+        <v>6.496815286624114</v>
       </c>
       <c r="F14" s="2">
-        <v>6.343506882106564</v>
+        <v>6.339712918660356</v>
       </c>
       <c r="G14" s="2">
-        <v>6.190208216094595</v>
+        <v>6.186726659167618</v>
       </c>
       <c r="H14" s="2">
-        <v>26.974032856385797</v>
+        <v>26.853813559322038</v>
       </c>
       <c r="I14" s="2">
-        <v>26.878130217028364</v>
+        <v>26.805845511482175</v>
       </c>
       <c r="J14" s="2">
-        <v>26.97368421052635</v>
+        <v>26.868620349028703</v>
       </c>
     </row>
     <row r="15">
@@ -3081,16 +3081,16 @@
         <v>111</v>
       </c>
       <c r="G15" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H15" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I15" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J15" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -3143,22 +3143,22 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.06152380952380952</v>
+        <v>0.06133333333333334</v>
       </c>
       <c r="F17" s="2">
-        <v>0.06261261261261261</v>
+        <v>0.062342342342342344</v>
       </c>
       <c r="G17" s="2">
-        <v>0.06393162393162394</v>
+        <v>0.06405172413793103</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06475409836065574</v>
+        <v>0.06583333333333334</v>
       </c>
       <c r="I17" s="2">
-        <v>0.07118110236220472</v>
+        <v>0.0716</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07833333333333334</v>
+        <v>0.07852713178294574</v>
       </c>
     </row>
     <row r="18">
@@ -3179,22 +3179,22 @@
         <v>1.9677996422182487</v>
       </c>
       <c r="E18" s="2">
-        <v>2.5396825396825307</v>
+        <v>2.2222222222222365</v>
       </c>
       <c r="F18" s="2">
-        <v>1.7697263827294751</v>
+        <v>1.6451233842538215</v>
       </c>
       <c r="G18" s="2">
-        <v>2.106622394392188</v>
+        <v>2.7419274466812693</v>
       </c>
       <c r="H18" s="2">
-        <v>1.2864907512930568</v>
+        <v>2.7815163750561034</v>
       </c>
       <c r="I18" s="2">
-        <v>9.925246685936395</v>
+        <v>8.759493670886066</v>
       </c>
       <c r="J18" s="2">
-        <v>10.047935103244843</v>
+        <v>9.674765059980084</v>
       </c>
     </row>
     <row r="19">
@@ -3283,22 +3283,22 @@
         <v>0.15392156862745102</v>
       </c>
       <c r="E21" s="2">
-        <v>0.15616822429906532</v>
+        <v>0.15626168224299058</v>
       </c>
       <c r="F21" s="2">
-        <v>0.15725663716814156</v>
+        <v>0.15734513274336284</v>
       </c>
       <c r="G21" s="2">
-        <v>0.1585714285714286</v>
+        <v>0.16000000000000003</v>
       </c>
       <c r="H21" s="2">
-        <v>0.19322580645161294</v>
+        <v>0.1963114754098361</v>
       </c>
       <c r="I21" s="2">
-        <v>0.23565891472868217</v>
+        <v>0.23913385826771644</v>
       </c>
       <c r="J21" s="2">
-        <v>0.2880597014925374</v>
+        <v>0.29412213740458015</v>
       </c>
     </row>
     <row r="22">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.81 % / 補助 22 % / 他 6.26 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / 他 6.27 %</t>
         </is>
       </c>
     </row>
@@ -3673,32 +3673,32 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68.01 %</t>
+          <t xml:space="preserve">全社 67.99 % / 補助 67.99 % / 他 67.99 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.35 % / 補助 67.48 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 67.35 % / 補助 67.49 % / 他 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.98 % / 補助 66.97 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 67 % / 補助 67 % / 他 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.58 % / 補助 66.44 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.62 % / 補助 66.49 % / 他 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3735,32 +3735,32 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 31.99 %</t>
+          <t xml:space="preserve">全社 32.01 % / 補助 32.01 % / 他 32.01 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.65 % / 補助 32.52 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 32.65 % / 補助 32.51 % / 他 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.02 % / 補助 33.03 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 33 % / 補助 33 % / 他 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.42 % / 補助 33.56 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.38 % / 補助 33.51 % / 他 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3797,32 +3797,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.72 % / 補助 23.62 % / 他 25.98 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / 他 25.97 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.14 % / 補助 24.29 % / 他 26.14 %</t>
+          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / 他 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.56 % / 補助 24.94 % / 他 26.3 %</t>
+          <t xml:space="preserve">全社 25.51 % / 補助 24.88 % / 他 26.26 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.02 % / 補助 22.67 % / 他 25.84 %</t>
+          <t xml:space="preserve">全社 24 % / 補助 22.67 % / 他 25.8 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.95 % / 補助 21.17 % / 他 25.69 %</t>
+          <t xml:space="preserve">全社 22.89 % / 補助 21.1 % / 他 25.64 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.87 % / 補助 19.8 % / 他 25.54 %</t>
+          <t xml:space="preserve">全社 21.77 % / 補助 19.67 % / 他 25.48 %</t>
         </is>
       </c>
     </row>
@@ -3859,32 +3859,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.28 % / 補助 8.37 % / 他 6.02 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / 他 6.03 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.86 % / 補助 7.71 % / 他 5.86 %</t>
+          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / 他 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.44 % / 補助 7.07 % / 他 5.7 %</t>
+          <t xml:space="preserve">全社 6.5 % / 補助 7.13 % / 他 5.75 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 9.85 % / 他 6.99 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 9.84 % / 他 7.04 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 11.86 % / 他 7.3 %</t>
+          <t xml:space="preserve">全社 10.11 % / 補助 11.9 % / 他 7.35 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.54 % / 補助 13.76 % / 他 7.62 %</t>
+          <t xml:space="preserve">全社 11.62 % / 補助 13.83 % / 他 7.69 %</t>
         </is>
       </c>
     </row>
@@ -3921,32 +3921,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.99 % / 補助 11.66 % / 他 8.07 %</t>
+          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / 他 8.08 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.9 % / 補助 11.68 % / 他 7.83 %</t>
+          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / 他 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.79 % / 補助 11.66 % / 他 7.59 %</t>
+          <t xml:space="preserve">全社 9.85 % / 補助 11.72 % / 他 7.64 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.54 % / 補助 13.61 % / 他 8.75 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.6 % / 他 8.8 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.59 % / 補助 14.95 % / 他 8.96 %</t>
+          <t xml:space="preserve">全社 12.63 % / 補助 14.98 % / 他 9.01 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.72 % / 補助 16.29 % / 他 9.18 %</t>
+          <t xml:space="preserve">全社 13.79 % / 補助 16.36 % / 他 9.25 %</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.63 % / 補助 12 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.64 % / 補助 12 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 % / 補助 11 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 11 % / 他 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4107,32 +4107,32 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.51 % / 補助 7.66 % / 他 11.65 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 7.64 % / 他 11.63 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.69 % / 補助 7.82 % / 他 11.88 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 7.78 % / 他 11.85 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.88 % / 補助 7.98 % / 他 12.11 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 7.93 % / 他 12.08 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.13 % / 補助 6.91 % / 他 12.1 %</t>
+          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / 他 12.05 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.74 % / 補助 6.48 % / 他 12.22 %</t>
+          <t xml:space="preserve">全社 8.68 % / 補助 6.42 % / 他 12.16 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.34 % / 補助 6.08 % / 他 12.33 %</t>
+          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / 他 12.27 %</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.17 % / 補助 8.16 % / 他 12.48 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / 他 12.47 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.34 % / 補助 8.31 % / 他 12.7 %</t>
+          <t xml:space="preserve">全社 10.3 % / 補助 8.28 % / 他 12.67 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.52 % / 補助 8.49 % / 他 12.92 %</t>
+          <t xml:space="preserve">全社 10.47 % / 補助 8.43 % / 他 12.88 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.7 % / 補助 7.35 % / 他 12.86 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / 他 12.82 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.26 % / 補助 6.86 % / 他 12.96 %</t>
+          <t xml:space="preserve">全社 9.19 % / 補助 6.79 % / 他 12.9 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.8 % / 補助 6.4 % / 他 13.05 %</t>
+          <t xml:space="preserve">全社 8.69 % / 補助 6.27 % / 他 12.98 %</t>
         </is>
       </c>
     </row>
@@ -4293,32 +4293,32 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.062 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / 他 0.063 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.063 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.062 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / 他 0.065 億円/人</t>
+          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / 他 0.066 億円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.065 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.067 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.079 億円/人 / 他 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -4417,32 +4417,32 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.4 % / 補助 2.54 % / 他 2.31 %</t>
+          <t xml:space="preserve">全社 2.2 % / 補助 2.22 % / 他 2.19 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.8 % / 補助 1.77 % / 他 1.83 %</t>
+          <t xml:space="preserve">全社 1.68 % / 補助 1.65 % / 他 1.72 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.02 % / 補助 2.11 % / 他 1.97 %</t>
+          <t xml:space="preserve">全社 2.64 % / 補助 2.74 % / 他 2.57 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.86 % / 補助 1.29 % / 他 2.31 %</t>
+          <t xml:space="preserve">全社 2.46 % / 補助 2.78 % / 他 2.2 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.79 % / 補助 9.93 % / 他 2.62 %</t>
+          <t xml:space="preserve">全社 5.23 % / 補助 8.76 % / 他 2.52 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.03 % / 補助 10.05 % / 他 2.77 %</t>
+          <t xml:space="preserve">全社 5.44 % / 補助 9.67 % / 他 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4479,32 +4479,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.43 % / 補助 41.17 % / 他 60.73 %</t>
+          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / 他 60.67 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.06 % / 補助 41.59 % / 他 61.84 %</t>
+          <t xml:space="preserve">全社 50.9 % / 補助 41.39 % / 他 61.72 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.79 % / 補助 42.13 % / 他 63 %</t>
+          <t xml:space="preserve">全社 51.54 % / 補助 41.84 % / 他 62.78 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.68 % / 補助 35.06 % / 他 59.51 %</t>
+          <t xml:space="preserve">全社 45.6 % / 補助 35.07 % / 他 59.29 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.37 % / 補助 31.45 % / 他 59.13 %</t>
+          <t xml:space="preserve">全社 42.12 % / 補助 31.18 % / 他 58.88 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.08 % / 補助 28.21 % / 他 58.71 %</t>
+          <t xml:space="preserve">全社 38.66 % / 補助 27.72 % / 他 58.4 %</t>
         </is>
       </c>
     </row>
@@ -4613,22 +4613,22 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">全社 0.66 億円/人 / 補助 0.808 億円/人 / 他 0.543 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.723 億円/人 / 補助 0.937 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.798 億円/人 / 補助 1.098 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">全社 0.807 億円/人 / 補助 1.116 億円/人 / 他 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.887 億円/人 / 補助 1.289 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.897 億円/人 / 補助 1.32 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.067 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.068 億円/人 / 他 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -4675,22 +4675,22 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.042 億円/人 / 補助 0.057 億円/人 / 他 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.058 億円/人 / 他 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.092 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / 他 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.08 億円/人 / 補助 0.13 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.133 億円/人 / 他 0.042 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.102 億円/人 / 補助 0.177 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.104 億円/人 / 補助 0.183 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4737,22 +4737,22 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.16 億円/人 / 他 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / 他 0.117 億円/人</t>
+          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / 他 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.236 億円/人 / 他 0.121 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.239 億円/人 / 他 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.288 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.198 億円/人 / 補助 0.294 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4799,22 +4799,22 @@
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.76 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 3.97 % / 補助 4.5 % / 他 3.55 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.55 % / 補助 4.27 % / 他 4.76 %</t>
+          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / 他 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 4.1 % / 他 4.55 %</t>
+          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / 他 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 3.94 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 pt / 補助 0.4 pt / 他 0.41 pt</t>
+          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 pt / 補助 -0 pt / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.91 pt / 補助 0.91 pt / 他 0.71 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.72 pt / 補助 17.73 pt / 他 2.55 pt</t>
+          <t xml:space="preserve">全社 11.08 pt / 補助 18.58 pt / 他 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 pt / 補助 17.9 pt / 他 1.7 pt</t>
+          <t xml:space="preserve">全社 10.89 pt / 補助 17.85 pt / 他 1.67 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.64 pt / 補助 18.07 pt / 他 1.91 pt</t>
+          <t xml:space="preserve">全社 11.62 pt / 補助 18.83 pt / 他 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.29 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.92 倍</t>
+          <t xml:space="preserve">全社 0.91 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.89 倍</t>
+          <t xml:space="preserve">全社 0.88 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.68 倍 / 補助 3.55 倍 / 他 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.25 倍 / 補助 2.94 倍 / 他 3.97 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / 他 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.92 倍 / 補助 2.54 倍 / 他 4.01 倍</t>
+          <t xml:space="preserve">全社 2.94 倍 / 補助 2.55 倍 / 他 4.04 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.97 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.99 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.99 倍 / 補助 4.85 倍 / 他 5.4 倍</t>
+          <t xml:space="preserve">全社 5.01 倍 / 補助 4.86 倍 / 他 5.43 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.3 倍 / 補助 6.44 倍 / 他 5.88 倍</t>
+          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / 他 5.93 倍</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 53.6 %</t>
+          <t xml:space="preserve">構成比 53.61 %</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 57.31 %</t>
+          <t xml:space="preserve">構成比 57.32 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 60.65 %</t>
+          <t xml:space="preserve">構成比 60.67 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.9 %</t>
+          <t xml:space="preserve">構成比 63.91 %</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22.03 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22.01 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 6.26 %</t>
+          <t xml:space="preserve">補助 22.03 % / 他 6.27 %</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5471,32 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">差 -0.01 pt</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 0 pt</t>
-        </is>
-      </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">差 -0 pt</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">差 0.32 pt</t>
+        </is>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">差 -0.01 pt</t>
         </is>
       </c>
-      <c r="J34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 0.31 pt</t>
-        </is>
-      </c>
-      <c r="K34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 -0.04 pt</t>
-        </is>
-      </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.4 pt</t>
+          <t xml:space="preserve">差 -0.34 pt</t>
         </is>
       </c>
     </row>
@@ -5533,27 +5533,27 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.36 pt</t>
+          <t xml:space="preserve">差 2.38 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.85 pt</t>
+          <t xml:space="preserve">差 1.86 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.37 pt</t>
+          <t xml:space="preserve">差 1.38 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.86 pt</t>
+          <t xml:space="preserve">差 2.8 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.57 pt</t>
+          <t xml:space="preserve">差 4.55 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
@@ -5605,22 +5605,22 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">補助 0.808 億円/人 / 他 0.543 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.937 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">補助 0.953 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.098 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">補助 1.116 億円/人 / 他 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.289 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.32 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5657,32 +5657,32 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.062 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">補助 0.061 億円/人 / 他 0.063 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.063 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.062 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.064 億円/人 / 他 0.065 億円/人</t>
+          <t xml:space="preserve">補助 0.064 億円/人 / 他 0.066 億円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.065 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.071 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.072 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.078 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">補助 0.079 億円/人 / 他 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -5719,32 +5719,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 160 %</t>
+          <t xml:space="preserve">寄与率 190.91 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 150 %</t>
+          <t xml:space="preserve">寄与率 166.67 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 135.29 %</t>
+          <t xml:space="preserve">寄与率 161.54 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.44 %</t>
+          <t xml:space="preserve">寄与率 76.17 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.04 %</t>
+          <t xml:space="preserve">寄与率 89.02 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.51 %</t>
+          <t xml:space="preserve">寄与率 90.38 %</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDM2ODA1NTU1NTU1NTQsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjA3MzU5OTQxODMxODkxNjYsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0NDQ4NTM2MzA2NzUzMjc0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA2MDkzMzcwMjc4OTgwNCwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQxNDkzNzc3MjQ5MzA2NDQ2LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTQwMTg1NzA3MjY1MjYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1NTUwNDI3MjU3OTc3Mjg0LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMSwib3RoZXJQYXlHcm93dGgiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4NzIzNzY5MjEzNjMzOCwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkzMjYxNjQ2NTE2MzY2LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MTkyMzE2Nzk1ODM0OTYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTc1NjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAzNzIwNTQ4MjM5NzIwNTA1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -1830,135 +1830,99 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <v>11.000000000000007</v>
+        <v>10.73</v>
       </c>
       <c r="C20" s="4">
-        <v>11.299999999999997</v>
+        <v>11.01</v>
       </c>
       <c r="D20" s="4">
-        <v>11.600000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.490000000000002</v>
+        <v>11.18</v>
       </c>
       <c r="F20" s="4">
-        <v>11.370000000000012</v>
+        <v>11.04</v>
       </c>
       <c r="G20" s="4">
-        <v>11.239999999999995</v>
+        <v>10.89</v>
       </c>
       <c r="H20" s="4">
-        <v>17.24000000000001</v>
+        <v>15.49</v>
       </c>
       <c r="I20" s="4">
-        <v>23.25</v>
+        <v>21.32</v>
       </c>
       <c r="J20" s="4">
-        <v>30.94000000000002</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-19 税引前当期純利益（モデル未対応）（億円）</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>10.73</v>
+      </c>
+      <c r="C21" s="2">
+        <v>11.01</v>
+      </c>
+      <c r="D21" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>11.18</v>
+      </c>
+      <c r="F21" s="2">
+        <v>11.04</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.89</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15.49</v>
+      </c>
+      <c r="I21" s="2">
+        <v>21.32</v>
+      </c>
+      <c r="J21" s="2">
+        <v>28.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-20 当期純利益（モデル未対応）（億円）</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2-20 当期純利益（億円）</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>7.51</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7.71</v>
+      </c>
+      <c r="D22" s="2">
+        <v>7.91</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7.83</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7.73</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7.62</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.84</v>
+      </c>
+      <c r="I22" s="2">
+        <v>14.92</v>
+      </c>
+      <c r="J22" s="2">
+        <v>20.16</v>
       </c>
     </row>
     <row r="23">
@@ -6386,7 +6350,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C244"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6521,11 +6485,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-18</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>92.75</v>
+        <v>10.73</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6536,11 +6500,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-4</t>
+          <t xml:space="preserve">actual:company:2023:2-19</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.73</v>
+        <v>10.73</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6551,11 +6515,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-7</t>
+          <t xml:space="preserve">actual:company:2023:2-20</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>32.65</v>
+        <v>7.51</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6566,11 +6530,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-9</t>
+          <t xml:space="preserve">actual:company:2023:2-27</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.82</v>
+        <v>210</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6581,11 +6545,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-1</t>
+          <t xml:space="preserve">actual:company:2023:2-28</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>143.2</v>
+        <v>5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6596,11 +6560,11 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-10</t>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.1</v>
+        <v>92.75</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -6611,11 +6575,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-12</t>
+          <t xml:space="preserve">actual:company:2023:2-4</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.47</v>
+        <v>0.73</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6626,11 +6590,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-13</t>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0.66</v>
+        <v>32.65</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6641,11 +6605,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-9</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.58</v>
+        <v>0.82</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6656,11 +6620,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.67</v>
+        <v>143.2</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6671,11 +6635,11 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-10</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>97.38</v>
+        <v>0.1</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6686,11 +6650,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-12</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>0.76</v>
+        <v>12.47</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6701,11 +6665,11 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-13</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>34.52</v>
+        <v>0.66</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6716,11 +6680,11 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.86</v>
+        <v>2.58</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6731,11 +6695,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-1</t>
+          <t xml:space="preserve">actual:company:2024:2-15</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>150</v>
+        <v>0.67</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6746,11 +6710,11 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-10</t>
+          <t xml:space="preserve">actual:company:2024:2-18</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.1</v>
+        <v>11.01</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6761,11 +6725,11 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-12</t>
+          <t xml:space="preserve">actual:company:2024:2-19</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>13.3</v>
+        <v>11.01</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6776,11 +6740,11 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-13</t>
+          <t xml:space="preserve">actual:company:2024:2-20</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0.7</v>
+        <v>7.71</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6791,11 +6755,11 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-14</t>
+          <t xml:space="preserve">actual:company:2024:2-27</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>2.7</v>
+        <v>220</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6806,11 +6770,11 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-28</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
@@ -6821,11 +6785,11 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>102</v>
+        <v>97.38</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6836,11 +6800,11 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-4</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6851,11 +6815,11 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>36.4</v>
+        <v>34.52</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6866,11 +6830,11 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-9</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6881,11 +6845,11 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6896,11 +6860,11 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-10</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6911,11 +6875,11 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-12</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>90</v>
+        <v>13.3</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -6926,11 +6890,11 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-13</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6941,11 +6905,11 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>23.04</v>
+        <v>2.7</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
@@ -6956,11 +6920,11 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-15</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>6.78</v>
+        <v>0.7</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6971,11 +6935,11 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-18</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>5.19</v>
+        <v>11.3</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6986,11 +6950,11 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:company:2025:2-19</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>0.36</v>
+        <v>11.3</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -7001,11 +6965,11 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-20</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>76</v>
+        <v>7.91</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -7016,11 +6980,11 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-27</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>1.9</v>
+        <v>230</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
@@ -7031,11 +6995,11 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-28</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
@@ -7046,11 +7010,11 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
@@ -7061,11 +7025,11 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-4</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>24.32</v>
+        <v>0.8</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
@@ -7076,11 +7040,11 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>7.04</v>
+        <v>36.4</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
@@ -7091,11 +7055,11 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-9</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>5.59</v>
+        <v>0.9</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
@@ -7106,11 +7070,11 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>0.38</v>
+        <v>72</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
@@ -7121,11 +7085,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -7136,11 +7100,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -7151,11 +7115,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7166,11 +7130,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>2</v>
+        <v>23.04</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7181,11 +7145,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>25.6</v>
+        <v>6.78</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7196,11 +7160,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>7.3</v>
+        <v>5.19</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7211,11 +7175,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>6</v>
+        <v>0.36</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7226,11 +7190,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>0.4</v>
+        <v>76</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7241,11 +7205,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>132</v>
+        <v>1.9</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7256,11 +7220,11 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
@@ -7271,11 +7235,11 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
@@ -7286,11 +7250,11 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>10</v>
+        <v>24.32</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
@@ -7301,11 +7265,11 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>24</v>
+        <v>7.04</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
@@ -7316,11 +7280,11 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>67</v>
+        <v>5.59</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
@@ -7331,11 +7295,11 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>39</v>
+        <v>0.38</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
@@ -7346,11 +7310,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7361,11 +7325,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7376,11 +7340,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7391,11 +7355,11 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
@@ -7406,11 +7370,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>75</v>
+        <v>25.6</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -7421,11 +7385,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>29</v>
+        <v>7.3</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7436,11 +7400,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7451,11 +7415,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>57</v>
+        <v>0.4</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7466,11 +7430,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7481,11 +7445,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7496,7 +7460,7 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B74" s="2">
@@ -7511,11 +7475,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7526,11 +7490,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7541,11 +7505,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7556,11 +7520,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7571,11 +7535,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7586,11 +7550,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7601,11 +7565,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -7616,11 +7580,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -7631,11 +7595,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -7646,11 +7610,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -7661,11 +7625,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -7676,11 +7640,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -7691,11 +7655,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -7706,11 +7670,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -7721,11 +7685,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -7736,11 +7700,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -7751,11 +7715,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -7766,11 +7730,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -7781,11 +7745,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -7796,11 +7760,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -7811,11 +7775,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -7826,11 +7790,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -7841,11 +7805,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -7856,11 +7820,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -7871,11 +7835,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -7886,11 +7850,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -7901,11 +7865,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -7916,11 +7880,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -7931,11 +7895,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -7946,11 +7910,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -7961,11 +7925,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -7976,11 +7940,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -7991,11 +7955,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8006,11 +7970,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8021,11 +7985,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8036,11 +8000,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8051,11 +8015,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8066,11 +8030,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8081,11 +8045,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8096,11 +8060,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8111,11 +8075,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8126,26 +8090,26 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8156,11 +8120,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>0.005</v>
+        <v>40</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8171,11 +8135,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.0051345755693581975</v>
+        <v>9</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8186,26 +8150,26 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.00013457556935819737</v>
+        <v>83</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8216,11 +8180,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>0.04416666666666668</v>
+        <v>32</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8231,11 +8195,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.04750000000000009</v>
+        <v>32</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8246,11 +8210,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0.03916666666666668</v>
+        <v>73</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8261,11 +8225,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.04250000000000009</v>
+        <v>70</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8276,11 +8240,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>0.024139457023717444</v>
+        <v>11</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8291,11 +8255,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.025553459914763096</v>
+        <v>7</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8306,11 +8270,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>0.019139457023717443</v>
+        <v>64</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8321,11 +8285,11 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.020553459914763095</v>
+        <v>15</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8336,11 +8300,11 @@
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>0.06076086956521719</v>
+        <v>200</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8351,26 +8315,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0.06438405797101453</v>
+        <v>0</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>0.040760869565217184</v>
+        <v>100</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8381,11 +8345,11 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.005</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
@@ -8396,22 +8360,22 @@
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -8426,11 +8390,11 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8441,11 +8405,11 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8456,26 +8420,26 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.03</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
@@ -8486,26 +8450,26 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8516,26 +8480,26 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.08</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -8546,11 +8510,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8561,11 +8525,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8576,11 +8540,11 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>-0.05</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8591,11 +8555,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.3</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -8606,11 +8570,11 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04263157894736836</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8621,41 +8585,41 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.06555555555555558</v>
+        <v>0</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8666,11 +8630,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.05</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8681,26 +8645,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.03</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8711,26 +8675,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.020735994183189166</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.15</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8741,26 +8705,26 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.08</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8771,11 +8735,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8786,41 +8750,41 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8831,11 +8795,11 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.135</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -8846,11 +8810,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>1</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8861,11 +8825,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>50</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -8876,11 +8840,11 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8891,11 +8855,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>20</v>
+        <v>0.05</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8906,11 +8870,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>23</v>
+        <v>0.1</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8921,11 +8885,11 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>23</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8936,11 +8900,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.005</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8951,26 +8915,26 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.3</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8981,11 +8945,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8996,11 +8960,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9011,41 +8975,41 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.01984645846924027</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.06257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9056,26 +9020,26 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.10928571428571428</v>
+        <v>1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9086,11 +9050,11 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.015</v>
+        <v>50</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9101,11 +9065,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>5</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9116,11 +9080,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.04</v>
+        <v>20</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9131,11 +9095,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.05409356725146197</v>
+        <v>23</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9146,11 +9110,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.05</v>
+        <v>23</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9161,11 +9125,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.005</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9176,26 +9140,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.07</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9206,11 +9170,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9221,11 +9185,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.22</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9236,11 +9200,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9251,26 +9215,26 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.11</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9281,26 +9245,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>10</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9311,11 +9275,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>15</v>
+        <v>0.015</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9326,11 +9290,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>15</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9341,11 +9305,11 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9356,56 +9320,56 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>7</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9416,11 +9380,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>3.5</v>
+        <v>0.07</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9431,11 +9395,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>35</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9446,11 +9410,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>15</v>
+        <v>0.22</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9461,11 +9425,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>252.69</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9476,26 +9440,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>82.4</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>10</v>
+        <v>0.11</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9506,11 +9470,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>7</v>
+        <v>7.66</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9521,11 +9485,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>3.74</v>
+        <v>10</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9536,11 +9500,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>2.85</v>
+        <v>15</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9551,11 +9515,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9566,7 +9530,7 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B212" s="2">
@@ -9581,56 +9545,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9641,11 +9605,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9656,11 +9620,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9671,26 +9635,26 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>35</v>
+        <v>252.69</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9701,11 +9665,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>22</v>
+        <v>82.4</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -9716,11 +9680,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>136.84</v>
+        <v>10</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9731,11 +9695,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>74.8</v>
+        <v>7</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9746,11 +9710,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>95</v>
+        <v>3.74</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9761,11 +9725,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>60</v>
+        <v>2.85</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9776,11 +9740,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>33.43</v>
+        <v>70</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9791,11 +9755,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>18.78</v>
+        <v>15</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9806,11 +9770,11 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
@@ -9821,13 +9785,238 @@
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B229" s="2">
+        <v>21</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B230" s="2">
+        <v>40</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B231" s="2">
+        <v>23</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B232" s="2">
+        <v>10</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B233" s="2">
+        <v>6</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B234" s="2">
+        <v>0</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B235" s="2">
+        <v>35</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B236" s="2">
+        <v>22</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B237" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B238" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B239" s="2">
+        <v>95</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B240" s="2">
+        <v>60</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B241" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B242" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B243" s="2">
+        <v>350</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B229" s="2">
+      <c r="B244" s="2">
         <v>213</v>
       </c>
-      <c r="C229" s="0" t="inlineStr">
+      <c r="C244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -9855,7 +10044,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTc1NjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAzNzIwNTQ4MjM5NzIwNTA1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6MTAuNzMsInByZVRheEluY29tZSI6MTAuNzMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjoxMS4wMSwicHJlVGF4SW5jb21lIjoxMS4wMSwibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjoxMS4zLCJwcmVUYXhJbmNvbWUiOjExLjMsIm5ldEluY29tZSI6Ny45MX19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjoxLjksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjIsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDM2MTI4NjY0MjgzMjYzNCwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIxOTI1NTYyMjA0ODMxMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjAyODgzMzQzNzI2OTIwMzUsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.18</v>
+        <v>11.179999999999989</v>
       </c>
       <c r="F20" s="4">
-        <v>11.04</v>
+        <v>11.040000000000001</v>
       </c>
       <c r="G20" s="4">
-        <v>10.89</v>
+        <v>10.890000000000004</v>
       </c>
       <c r="H20" s="4">
-        <v>15.49</v>
+        <v>16</v>
       </c>
       <c r="I20" s="4">
-        <v>21.32</v>
+        <v>21.899999999999988</v>
       </c>
       <c r="J20" s="4">
-        <v>28.8</v>
+        <v>29.460000000000008</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.18</v>
+        <v>11.179999999999989</v>
       </c>
       <c r="F21" s="2">
-        <v>11.04</v>
+        <v>11.040000000000001</v>
       </c>
       <c r="G21" s="2">
-        <v>10.89</v>
+        <v>10.890000000000004</v>
       </c>
       <c r="H21" s="2">
-        <v>15.49</v>
+        <v>16</v>
       </c>
       <c r="I21" s="2">
-        <v>21.32</v>
+        <v>21.899999999999988</v>
       </c>
       <c r="J21" s="2">
-        <v>28.8</v>
+        <v>29.460000000000008</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.83</v>
+        <v>7.832999999999992</v>
       </c>
       <c r="F22" s="2">
-        <v>7.73</v>
+        <v>7.7330000000000005</v>
       </c>
       <c r="G22" s="2">
-        <v>7.62</v>
+        <v>7.616000000000001</v>
       </c>
       <c r="H22" s="2">
-        <v>10.84</v>
+        <v>11.195</v>
       </c>
       <c r="I22" s="2">
-        <v>14.92</v>
+        <v>15.329999999999991</v>
       </c>
       <c r="J22" s="2">
-        <v>20.16</v>
+        <v>20.625000000000004</v>
       </c>
     </row>
     <row r="23">
@@ -10044,7 +10044,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6MTAuNzMsInByZVRheEluY29tZSI6MTAuNzMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjoxMS4wMSwicHJlVGF4SW5jb21lIjoxMS4wMSwibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjoxMS4zLCJwcmVUYXhJbmNvbWUiOjExLjMsIm5ldEluY29tZSI6Ny45MX19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjoxLjksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjIsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDM2MTI4NjY0MjgzMjYzNCwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIxOTI1NTYyMjA0ODMxMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjAyODgzMzQzNzI2OTIwMzUsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMzYxMjg2NjQyODMyNjM0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjE5MjU1NjIyMDQ4MzExLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wOTE3NTYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzcyMDU0ODIzOTcyMDUwNSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI3MjU4OTg3MjEyODIzLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3NzgwNTc2Mjg3MTYzMiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -3560,47 +3560,47 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.99 % / 補助 5.56 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.99 % / 補助 5.56 % / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.75 % / 補助 5.26 % / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.75 % / 補助 5.26 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / 他 6.27 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -3622,47 +3622,47 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68.01 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68.01 %</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / ベース 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / ベース 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.99 % / 補助 67.99 % / 他 67.99 %</t>
+          <t xml:space="preserve">全社 67.99 % / 補助 67.99 % / ベース 67.99 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.35 % / 補助 67.49 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 67.35 % / 補助 67.49 % / ベース 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67 % / 補助 67 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 67 % / 補助 67 % / ベース 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.62 % / 補助 66.49 % / 他 66.83 %</t>
+          <t xml:space="preserve">全社 66.62 % / 補助 66.49 % / ベース 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3684,47 +3684,47 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 31.99 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 31.99 %</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / ベース 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / ベース 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.01 % / 補助 32.01 % / 他 32.01 %</t>
+          <t xml:space="preserve">全社 32.01 % / 補助 32.01 % / ベース 32.01 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.65 % / 補助 32.51 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 32.65 % / 補助 32.51 % / ベース 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33 % / 補助 33 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 33 % / 補助 33 % / ベース 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.38 % / 補助 33.51 % / 他 33.17 %</t>
+          <t xml:space="preserve">全社 33.38 % / 補助 33.51 % / ベース 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3746,47 +3746,47 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.94 % / 補助 22.58 % / 他 25.45 %</t>
+          <t xml:space="preserve">全社 23.94 % / 補助 22.58 % / ベース 25.45 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / 他 25.65 %</t>
+          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / ベース 25.65 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.27 % / 補助 22.88 % / 他 25.86 %</t>
+          <t xml:space="preserve">全社 24.27 % / 補助 22.88 % / ベース 25.86 %</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / 他 25.97 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / ベース 25.97 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / 他 26.11 %</t>
+          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / ベース 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.51 % / 補助 24.88 % / 他 26.26 %</t>
+          <t xml:space="preserve">全社 25.51 % / 補助 24.88 % / ベース 26.26 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24 % / 補助 22.67 % / 他 25.8 %</t>
+          <t xml:space="preserve">全社 24 % / 補助 22.67 % / ベース 25.8 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.89 % / 補助 21.1 % / 他 25.64 %</t>
+          <t xml:space="preserve">全社 22.89 % / 補助 21.1 % / ベース 25.64 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.77 % / 補助 19.67 % / 他 25.48 %</t>
+          <t xml:space="preserve">全社 21.77 % / 補助 19.67 % / ベース 25.48 %</t>
         </is>
       </c>
     </row>
@@ -3808,47 +3808,47 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.06 % / 補助 9.42 % / 他 6.55 %</t>
+          <t xml:space="preserve">全社 8.06 % / 補助 9.42 % / ベース 6.55 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / 他 6.34 %</t>
+          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / ベース 6.34 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.73 % / 補助 9.13 % / 他 6.14 %</t>
+          <t xml:space="preserve">全社 7.73 % / 補助 9.13 % / ベース 6.14 %</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / 他 6.03 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / ベース 6.03 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / 他 5.89 %</t>
+          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / ベース 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.5 % / 補助 7.13 % / 他 5.75 %</t>
+          <t xml:space="preserve">全社 6.5 % / 補助 7.13 % / ベース 5.75 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 9.84 % / 他 7.04 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 9.84 % / ベース 7.04 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.11 % / 補助 11.9 % / 他 7.35 %</t>
+          <t xml:space="preserve">全社 10.11 % / 補助 11.9 % / ベース 7.35 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.62 % / 補助 13.83 % / 他 7.69 %</t>
+          <t xml:space="preserve">全社 11.62 % / 補助 13.83 % / ベース 7.69 %</t>
         </is>
       </c>
     </row>
@@ -3870,47 +3870,47 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / 他 8.7 %</t>
+          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / ベース 8.7 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / 他 8.48 %</t>
+          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / ベース 8.48 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 11.63 % / 他 8.29 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.63 % / ベース 8.29 %</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / 他 8.08 %</t>
+          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / ベース 8.08 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / 他 7.86 %</t>
+          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / ベース 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.85 % / 補助 11.72 % / 他 7.64 %</t>
+          <t xml:space="preserve">全社 9.85 % / 補助 11.72 % / ベース 7.64 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.6 % / 他 8.8 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.6 % / ベース 8.8 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.63 % / 補助 14.98 % / 他 9.01 %</t>
+          <t xml:space="preserve">全社 12.63 % / 補助 14.98 % / ベース 9.01 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.79 % / 補助 16.36 % / 他 9.25 %</t>
+          <t xml:space="preserve">全社 13.79 % / 補助 16.36 % / ベース 9.25 %</t>
         </is>
       </c>
     </row>
@@ -3932,47 +3932,47 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.99 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 11.99 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.64 % / 補助 12 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.64 % / 補助 12 % / ベース 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / 他 10.99 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / ベース 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.94 % / 補助 11 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 11 % / ベース 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4056,47 +4056,47 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.01 % / 補助 7.21 % / 他 11.02 %</t>
+          <t xml:space="preserve">全社 9.01 % / 補助 7.21 % / ベース 11.02 %</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / 他 11.22 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / ベース 11.22 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.33 % / 補助 7.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 9.33 % / 補助 7.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.49 % / 補助 7.64 % / 他 11.63 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 7.64 % / ベース 11.63 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.66 % / 補助 7.78 % / 他 11.85 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 7.78 % / ベース 11.85 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 7.93 % / 他 12.08 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 7.93 % / ベース 12.08 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / 他 12.05 %</t>
+          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / ベース 12.05 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.68 % / 補助 6.42 % / 他 12.16 %</t>
+          <t xml:space="preserve">全社 8.68 % / 補助 6.42 % / ベース 12.16 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / 他 12.27 %</t>
+          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / ベース 12.27 %</t>
         </is>
       </c>
     </row>
@@ -4118,47 +4118,47 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.86 %</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.86 %</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / 他 0.84 %</t>
+          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / ベース 0.84 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / ベース 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / ベース 0.81 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / 他 0.76 %</t>
+          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / ベース 0.76 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / 他 0.74 %</t>
+          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / ベース 0.74 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / 他 0.72 %</t>
+          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / ベース 0.72 %</t>
         </is>
       </c>
     </row>
@@ -4180,47 +4180,47 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.71 % / 他 11.88 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.71 % / ベース 11.88 %</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / 他 12.08 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / ベース 12.08 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 8 % / 他 12.29 %</t>
+          <t xml:space="preserve">全社 10 % / 補助 8 % / ベース 12.29 %</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / 他 12.47 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / ベース 12.47 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.3 % / 補助 8.28 % / 他 12.67 %</t>
+          <t xml:space="preserve">全社 10.3 % / 補助 8.28 % / ベース 12.67 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.47 % / 補助 8.43 % / 他 12.88 %</t>
+          <t xml:space="preserve">全社 10.47 % / 補助 8.43 % / ベース 12.88 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / 他 12.82 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / ベース 12.82 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.19 % / 補助 6.79 % / 他 12.9 %</t>
+          <t xml:space="preserve">全社 9.19 % / 補助 6.79 % / ベース 12.9 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.69 % / 補助 6.27 % / 他 12.98 %</t>
+          <t xml:space="preserve">全社 8.69 % / 補助 6.27 % / ベース 12.98 %</t>
         </is>
       </c>
     </row>
@@ -4242,47 +4242,47 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / 他 0.059 億円/人</t>
+          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / ベース 0.059 億円/人</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / 他 0.06 億円/人</t>
+          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.062 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.062 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / 他 0.066 億円/人</t>
+          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / ベース 0.066 億円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.067 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.067 億円/人 / 補助 0.066 億円/人 / ベース 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.079 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.079 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -4304,47 +4304,47 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.182 億円/人 / 補助 0.18 億円/人 / 他 0.183 億円/人</t>
+          <t xml:space="preserve">全社 0.182 億円/人 / 補助 0.18 億円/人 / ベース 0.183 億円/人</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.19 億円/人 / 他 0.193 億円/人</t>
+          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.19 億円/人 / ベース 0.193 億円/人</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.2 億円/人 / 他 0.2 億円/人</t>
+          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.2 億円/人 / ベース 0.2 億円/人</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / 他 0.203 億円/人</t>
+          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / ベース 0.203 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / 他 0.207 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / ベース 0.207 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / 他 0.213 億円/人</t>
+          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / ベース 0.213 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / 他 0.217 億円/人</t>
+          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / ベース 0.217 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / 他 0.223 億円/人</t>
+          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / ベース 0.223 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / 他 0.23 億円/人</t>
+          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / ベース 0.23 億円/人</t>
         </is>
       </c>
     </row>
@@ -4366,47 +4366,47 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / 他 1.95 %</t>
+          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / ベース 1.95 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / 他 2.02 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / ベース 2.02 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.2 % / 補助 2.22 % / 他 2.19 %</t>
+          <t xml:space="preserve">全社 2.2 % / 補助 2.22 % / ベース 2.19 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.68 % / 補助 1.65 % / 他 1.72 %</t>
+          <t xml:space="preserve">全社 1.68 % / 補助 1.65 % / ベース 1.72 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.64 % / 補助 2.74 % / 他 2.57 %</t>
+          <t xml:space="preserve">全社 2.64 % / 補助 2.74 % / ベース 2.57 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.46 % / 補助 2.78 % / 他 2.2 %</t>
+          <t xml:space="preserve">全社 2.46 % / 補助 2.78 % / ベース 2.2 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.23 % / 補助 8.76 % / 他 2.52 %</t>
+          <t xml:space="preserve">全社 5.23 % / 補助 8.76 % / ベース 2.52 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.44 % / 補助 9.67 % / 他 2.08 %</t>
+          <t xml:space="preserve">全社 5.44 % / 補助 9.67 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4428,47 +4428,47 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.21 % / 補助 39.28 % / 他 57.74 %</t>
+          <t xml:space="preserve">全社 48.21 % / 補助 39.28 % / ベース 57.74 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / 他 58.76 %</t>
+          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / ベース 58.76 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.83 % / 補助 40.76 % / 他 59.72 %</t>
+          <t xml:space="preserve">全社 49.83 % / 補助 40.76 % / ベース 59.72 %</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / 他 60.67 %</t>
+          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / ベース 60.67 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.9 % / 補助 41.39 % / 他 61.72 %</t>
+          <t xml:space="preserve">全社 50.9 % / 補助 41.39 % / ベース 61.72 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.54 % / 補助 41.84 % / 他 62.78 %</t>
+          <t xml:space="preserve">全社 51.54 % / 補助 41.84 % / ベース 62.78 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.6 % / 補助 35.07 % / 他 59.29 %</t>
+          <t xml:space="preserve">全社 45.6 % / 補助 35.07 % / ベース 59.29 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.12 % / 補助 31.18 % / 他 58.88 %</t>
+          <t xml:space="preserve">全社 42.12 % / 補助 31.18 % / ベース 58.88 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.66 % / 補助 27.72 % / 他 58.4 %</t>
+          <t xml:space="preserve">全社 38.66 % / 補助 27.72 % / ベース 58.4 %</t>
         </is>
       </c>
     </row>
@@ -4552,47 +4552,47 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / 他 0.537 億円/人</t>
+          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / ベース 0.537 億円/人</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / 他 0.541 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / ベース 0.541 億円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.66 億円/人 / 補助 0.808 億円/人 / 他 0.543 億円/人</t>
+          <t xml:space="preserve">全社 0.66 億円/人 / 補助 0.808 億円/人 / ベース 0.543 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.807 億円/人 / 補助 1.116 億円/人 / 他 0.565 億円/人</t>
+          <t xml:space="preserve">全社 0.807 億円/人 / 補助 1.116 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.897 億円/人 / 補助 1.32 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.897 億円/人 / 補助 1.32 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4614,47 +4614,47 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / 他 0.035 億円/人</t>
+          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / ベース 0.035 億円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / 他 0.034 億円/人</t>
+          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / ベース 0.034 億円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.068 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.068 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / 他 0.032 億円/人</t>
+          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / ベース 0.032 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.058 億円/人 / 他 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.058 億円/人 / ベース 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / ベース 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.133 億円/人 / 他 0.042 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.133 億円/人 / ベース 0.042 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.104 億円/人 / 補助 0.183 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.104 億円/人 / 補助 0.183 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4676,47 +4676,47 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / 他 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.16 億円/人 / 他 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.16 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / 他 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / ベース 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.239 億円/人 / 他 0.122 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.239 億円/人 / ベース 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.198 億円/人 / 補助 0.294 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.198 億円/人 / 補助 0.294 億円/人 / ベース 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4738,47 +4738,47 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.76 % / 補助 5.56 % / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.76 % / 補助 5.56 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.55 % / 補助 5.26 % / 他 4 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 5.26 % / ベース 4 %</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 5 % / 他 3.85 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 5 % / ベース 3.85 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 % / 補助 5.71 % / 他 4.44 %</t>
+          <t xml:space="preserve">全社 5 % / 補助 5.71 % / ベース 4.44 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 % / 補助 4.5 % / 他 3.55 %</t>
+          <t xml:space="preserve">全社 3.97 % / 補助 4.5 % / ベース 3.55 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / 他 4.79 %</t>
+          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / 他 4.58 %</t>
+          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / 他 5 %</t>
+          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4800,47 +4800,47 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.22 pt / 補助 0 pt / 他 0.18 pt</t>
+          <t xml:space="preserve">全社 0.22 pt / 補助 0 pt / ベース 0.18 pt</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 pt / 補助 0 pt / 他 0.17 pt</t>
+          <t xml:space="preserve">全社 0.2 pt / 補助 0 pt / ベース 0.17 pt</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
+          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / ベース 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / 他 -0.18 pt</t>
+          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / ベース -0.18 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.91 pt / 補助 0.91 pt / 他 0.71 pt</t>
+          <t xml:space="preserve">全社 0.91 pt / 補助 0.91 pt / ベース 0.71 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.08 pt / 補助 18.58 pt / 他 2.52 pt</t>
+          <t xml:space="preserve">全社 11.08 pt / 補助 18.58 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.89 pt / 補助 17.85 pt / 他 1.67 pt</t>
+          <t xml:space="preserve">全社 10.89 pt / 補助 17.85 pt / ベース 1.67 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.62 pt / 補助 18.83 pt / 他 1.27 pt</t>
+          <t xml:space="preserve">全社 11.62 pt / 補助 18.83 pt / ベース 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -4924,47 +4924,47 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / ベース 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / 他 1.97 %</t>
+          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / ベース 1.97 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / 他 1.89 %</t>
+          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / ベース 1.89 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / ベース 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / 他 1.66 %</t>
+          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / ベース 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / 他 1.56 %</t>
+          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / ベース 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5110,47 +5110,47 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.46 倍 / 補助 4.77 倍 / 他 4.06 倍</t>
+          <t xml:space="preserve">全社 4.46 倍 / 補助 4.77 倍 / ベース 4.06 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / 他 3.96 倍</t>
+          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / ベース 3.96 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.31 倍 / 補助 4.65 倍 / 他 3.87 倍</t>
+          <t xml:space="preserve">全社 4.31 倍 / 補助 4.65 倍 / ベース 3.87 倍</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / 他 3.99 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.94 倍 / 補助 2.55 倍 / 他 4.04 倍</t>
+          <t xml:space="preserve">全社 2.94 倍 / 補助 2.55 倍 / ベース 4.04 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.99 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.99 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.01 倍 / 補助 4.86 倍 / 他 5.43 倍</t>
+          <t xml:space="preserve">全社 5.01 倍 / 補助 4.86 倍 / ベース 5.43 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / 他 5.93 倍</t>
+          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / ベース 5.93 倍</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. 補助事業とその他事業の比較</t>
+          <t xml:space="preserve">5. 補助事業とベース事業の比較</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
@@ -5358,47 +5358,47 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 —</t>
+          <t xml:space="preserve">補助 — / ベース —</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.56 % / 他 4.35 %</t>
+          <t xml:space="preserve">補助 5.56 % / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.26 % / 他 4.17 %</t>
+          <t xml:space="preserve">補助 5.26 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.01 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22.01 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / 他 6.27 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業原価率－その他事業原価率</t>
+          <t xml:space="preserve">補助事業原価率－ベース事業原価率</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業営業利益率－その他事業営業利益率</t>
+          <t xml:space="preserve">補助事業営業利益率－ベース事業営業利益率</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -5544,47 +5544,47 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.537 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.537 億円/人</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.803 億円/人 / 他 0.541 億円/人</t>
+          <t xml:space="preserve">補助 0.803 億円/人 / ベース 0.541 億円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.808 億円/人 / 他 0.543 億円/人</t>
+          <t xml:space="preserve">補助 0.808 億円/人 / ベース 0.543 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.953 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">補助 0.953 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.116 億円/人 / 他 0.565 億円/人</t>
+          <t xml:space="preserve">補助 1.116 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.32 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.32 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5606,47 +5606,47 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.058 億円/人 / 他 0.059 億円/人</t>
+          <t xml:space="preserve">補助 0.058 億円/人 / ベース 0.059 億円/人</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.059 億円/人 / 他 0.06 億円/人</t>
+          <t xml:space="preserve">補助 0.059 億円/人 / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.06 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">補助 0.06 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.061 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">補助 0.061 億円/人 / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.062 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.062 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.064 億円/人 / 他 0.066 億円/人</t>
+          <t xml:space="preserve">補助 0.064 億円/人 / ベース 0.066 億円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.066 億円/人 / ベース 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.072 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.072 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.079 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">補助 0.079 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -5957,7 +5957,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -5999,7 +5999,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -6020,7 +6020,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6062,7 +6062,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -6104,7 +6104,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -6146,7 +6146,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -6188,7 +6188,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6230,7 +6230,7 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B24" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.849999999999994</v>
+        <v>38.86</v>
       </c>
       <c r="F9" s="2">
-        <v>41.43</v>
+        <v>41.46</v>
       </c>
       <c r="G9" s="2">
-        <v>44.14</v>
+        <v>44.17</v>
       </c>
       <c r="H9" s="2">
-        <v>47.879999999999995</v>
+        <v>47.94</v>
       </c>
       <c r="I9" s="2">
-        <v>52.629999999999995</v>
+        <v>52.699999999999996</v>
       </c>
       <c r="J9" s="2">
-        <v>57.980000000000004</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="10">
@@ -1499,22 +1499,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="F10" s="2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G10" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="I10" s="2">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="J10" s="2">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="11">
@@ -1533,22 +1533,22 @@
         <v>0.9</v>
       </c>
       <c r="E11" s="2">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="F11" s="2">
-        <v>0.9600000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="H11" s="2">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I11" s="2">
-        <v>1.06</v>
+        <v>1.1300000000000001</v>
       </c>
       <c r="J11" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="12">
@@ -1573,16 +1573,16 @@
         <v>0.1</v>
       </c>
       <c r="G12" s="2">
-        <v>0.11</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="H12" s="2">
-        <v>0.11</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="I12" s="2">
         <v>0.13</v>
       </c>
       <c r="J12" s="2">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.490000000000002</v>
+        <v>11.480000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>11.370000000000012</v>
+        <v>11.34000000000001</v>
       </c>
       <c r="G18" s="4">
-        <v>11.239999999999995</v>
+        <v>11.209999999999997</v>
       </c>
       <c r="H18" s="4">
-        <v>17.24000000000001</v>
+        <v>17.180000000000007</v>
       </c>
       <c r="I18" s="4">
-        <v>23.25</v>
+        <v>23.18</v>
       </c>
       <c r="J18" s="4">
-        <v>30.94000000000002</v>
+        <v>30.86000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.304049329349693</v>
+        <v>7.297692454389424</v>
       </c>
       <c r="F19" s="2">
-        <v>6.891744453873202</v>
+        <v>6.873560431567468</v>
       </c>
       <c r="G19" s="2">
-        <v>6.495983355487485</v>
+        <v>6.478645321620527</v>
       </c>
       <c r="H19" s="2">
-        <v>8.642903694791201</v>
+        <v>8.612823983556428</v>
       </c>
       <c r="I19" s="2">
-        <v>10.11045399199861</v>
+        <v>10.08001391546356</v>
       </c>
       <c r="J19" s="2">
-        <v>11.615858236972525</v>
+        <v>11.585823697251847</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.179999999999989</v>
+        <v>11.16999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>11.040000000000001</v>
+        <v>11.010000000000002</v>
       </c>
       <c r="G20" s="4">
-        <v>10.890000000000004</v>
+        <v>10.860000000000003</v>
       </c>
       <c r="H20" s="4">
-        <v>16</v>
+        <v>15.940000000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>21.899999999999988</v>
+        <v>21.829999999999988</v>
       </c>
       <c r="J20" s="4">
-        <v>29.460000000000008</v>
+        <v>29.38000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.179999999999989</v>
+        <v>11.16999999999999</v>
       </c>
       <c r="F21" s="2">
-        <v>11.040000000000001</v>
+        <v>11.010000000000002</v>
       </c>
       <c r="G21" s="2">
-        <v>10.890000000000004</v>
+        <v>10.860000000000003</v>
       </c>
       <c r="H21" s="2">
-        <v>16</v>
+        <v>15.940000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>21.899999999999988</v>
+        <v>21.829999999999988</v>
       </c>
       <c r="J21" s="2">
-        <v>29.460000000000008</v>
+        <v>29.38000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.832999999999992</v>
+        <v>7.8229999999999915</v>
       </c>
       <c r="F22" s="2">
-        <v>7.7330000000000005</v>
+        <v>7.713000000000001</v>
       </c>
       <c r="G22" s="2">
-        <v>7.616000000000001</v>
+        <v>7.596000000000002</v>
       </c>
       <c r="H22" s="2">
-        <v>11.195</v>
+        <v>11.155000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>15.329999999999991</v>
+        <v>15.27999999999999</v>
       </c>
       <c r="J22" s="2">
-        <v>20.625000000000004</v>
+        <v>20.565000000000005</v>
       </c>
     </row>
     <row r="23">
@@ -1975,22 +1975,22 @@
         <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="F24" s="2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G24" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="H24" s="2">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="I24" s="2">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="J24" s="2">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="25">
@@ -2049,13 +2049,13 @@
         <v>33.400000000000006</v>
       </c>
       <c r="G26" s="4">
-        <v>35.15999999999999</v>
+        <v>35.16</v>
       </c>
       <c r="H26" s="4">
         <v>42.35</v>
       </c>
       <c r="I26" s="4">
-        <v>50.19</v>
+        <v>50.18999999999999</v>
       </c>
       <c r="J26" s="4">
         <v>59.90000000000002</v>
@@ -2088,13 +2088,13 @@
         <v>5.269461077844273</v>
       </c>
       <c r="H27" s="2">
-        <v>20.449374288964783</v>
+        <v>20.44937428896474</v>
       </c>
       <c r="I27" s="2">
-        <v>18.51239669421487</v>
+        <v>18.51239669421485</v>
       </c>
       <c r="J27" s="2">
-        <v>19.346483363219804</v>
+        <v>19.346483363219825</v>
       </c>
     </row>
     <row r="28">
@@ -2119,13 +2119,13 @@
         <v>20.244878167050555</v>
       </c>
       <c r="G28" s="2">
-        <v>20.32017569207651</v>
+        <v>20.320175692076518</v>
       </c>
       <c r="H28" s="2">
         <v>21.23126284654334</v>
       </c>
       <c r="I28" s="2">
-        <v>21.825534875630545</v>
+        <v>21.82553487563054</v>
       </c>
       <c r="J28" s="2">
         <v>22.488361615858242</v>
@@ -2285,22 +2285,22 @@
         <v>0.2</v>
       </c>
       <c r="E33" s="2">
-        <v>0.20600000000000002</v>
+        <v>0.20800000000000002</v>
       </c>
       <c r="F33" s="2">
-        <v>0.21200000000000002</v>
+        <v>0.21800000000000003</v>
       </c>
       <c r="G33" s="2">
-        <v>0.22199999999999998</v>
+        <v>0.22800000000000004</v>
       </c>
       <c r="H33" s="2">
-        <v>0.22999999999999998</v>
+        <v>0.242</v>
       </c>
       <c r="I33" s="2">
-        <v>0.238</v>
+        <v>0.252</v>
       </c>
       <c r="J33" s="2">
-        <v>0.248</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="34">
@@ -2321,22 +2321,22 @@
         <v>4.166666666666674</v>
       </c>
       <c r="E34" s="2">
-        <v>3.0000000000000027</v>
+        <v>4.0000000000000036</v>
       </c>
       <c r="F34" s="2">
-        <v>2.9126213592232997</v>
+        <v>4.807692307692313</v>
       </c>
       <c r="G34" s="2">
-        <v>4.7169811320754595</v>
+        <v>4.587155963302747</v>
       </c>
       <c r="H34" s="2">
-        <v>3.603603603603611</v>
+        <v>6.140350877192957</v>
       </c>
       <c r="I34" s="2">
-        <v>3.4782608695652195</v>
+        <v>4.132231404958686</v>
       </c>
       <c r="J34" s="2">
-        <v>4.201680672268915</v>
+        <v>4.761904761904767</v>
       </c>
     </row>
     <row r="35">
@@ -2361,13 +2361,13 @@
         <v>0.12996108949416343</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13168539325842693</v>
+        <v>0.13168539325842696</v>
       </c>
       <c r="H35" s="2">
         <v>0.15233812949640288</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17306896551724138</v>
+        <v>0.17306896551724135</v>
       </c>
       <c r="J35" s="2">
         <v>0.1983443708609272</v>
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.760000000000002</v>
+        <v>15.750000000000004</v>
       </c>
       <c r="F36" s="4">
-        <v>16.400000000000013</v>
+        <v>16.37000000000001</v>
       </c>
       <c r="G36" s="4">
-        <v>17.039999999999996</v>
+        <v>17.009999999999998</v>
       </c>
       <c r="H36" s="4">
-        <v>23.04000000000001</v>
+        <v>22.980000000000008</v>
       </c>
       <c r="I36" s="4">
-        <v>29.05</v>
+        <v>28.98</v>
       </c>
       <c r="J36" s="4">
-        <v>36.740000000000016</v>
+        <v>36.66000000000002</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.018434937384782</v>
+        <v>10.012078062424514</v>
       </c>
       <c r="F37" s="2">
-        <v>9.940598860467942</v>
+        <v>9.922414838162208</v>
       </c>
       <c r="G37" s="2">
-        <v>9.848003236432985</v>
+        <v>9.830665202566028</v>
       </c>
       <c r="H37" s="2">
-        <v>11.55060911415251</v>
+        <v>11.520529402917736</v>
       </c>
       <c r="I37" s="2">
-        <v>12.632631762045573</v>
+        <v>12.602191685510524</v>
       </c>
       <c r="J37" s="2">
-        <v>13.793362366721734</v>
+        <v>13.763327827001056</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.370860927152309</v>
+        <v>4.304635761589415</v>
       </c>
       <c r="F38" s="2">
-        <v>4.060913705583835</v>
+        <v>3.9365079365079936</v>
       </c>
       <c r="G38" s="2">
-        <v>3.9024390243901363</v>
+        <v>3.9095907147219666</v>
       </c>
       <c r="H38" s="2">
-        <v>35.21126760563389</v>
+        <v>35.0970017636685</v>
       </c>
       <c r="I38" s="2">
-        <v>26.085069444444397</v>
+        <v>26.109660574412487</v>
       </c>
       <c r="J38" s="2">
-        <v>26.47160068846821</v>
+        <v>26.50103519668743</v>
       </c>
     </row>
   </sheetData>
@@ -3761,32 +3761,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / ベース 25.97 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / ベース 25.98 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / ベース 26.11 %</t>
+          <t xml:space="preserve">全社 25.13 % / 補助 24.25 % / ベース 26.15 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.51 % / 補助 24.88 % / ベース 26.26 %</t>
+          <t xml:space="preserve">全社 25.53 % / 補助 24.88 % / ベース 26.3 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24 % / 補助 22.67 % / ベース 25.8 %</t>
+          <t xml:space="preserve">全社 24.03 % / 補助 22.67 % / ベース 25.87 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.89 % / 補助 21.1 % / ベース 25.64 %</t>
+          <t xml:space="preserve">全社 22.92 % / 補助 21.1 % / ベース 25.72 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.77 % / 補助 19.67 % / ベース 25.48 %</t>
+          <t xml:space="preserve">全社 21.8 % / 補助 19.67 % / ベース 25.56 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3823,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / ベース 6.03 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / ベース 6.02 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / ベース 5.89 %</t>
+          <t xml:space="preserve">全社 6.87 % / 補助 7.75 % / ベース 5.85 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.5 % / 補助 7.13 % / ベース 5.75 %</t>
+          <t xml:space="preserve">全社 6.48 % / 補助 7.13 % / ベース 5.71 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 9.84 % / ベース 7.04 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 9.84 % / ベース 6.97 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.11 % / 補助 11.9 % / ベース 7.35 %</t>
+          <t xml:space="preserve">全社 10.08 % / 補助 11.9 % / ベース 7.27 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.62 % / 補助 13.83 % / ベース 7.69 %</t>
+          <t xml:space="preserve">全社 11.59 % / 補助 13.83 % / ベース 7.61 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3885,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / ベース 8.08 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 11.69 % / ベース 8.07 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / ベース 7.86 %</t>
+          <t xml:space="preserve">全社 9.92 % / 補助 11.72 % / ベース 7.82 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.85 % / 補助 11.72 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 11.72 % / ベース 7.6 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.6 % / ベース 8.8 %</t>
+          <t xml:space="preserve">全社 11.52 % / 補助 13.6 % / ベース 8.73 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.63 % / 補助 14.98 % / ベース 9.01 %</t>
+          <t xml:space="preserve">全社 12.6 % / 補助 14.98 % / ベース 8.93 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.79 % / 補助 16.36 % / ベース 9.25 %</t>
+          <t xml:space="preserve">全社 13.76 % / 補助 16.36 % / ベース 9.17 %</t>
         </is>
       </c>
     </row>
@@ -4133,32 +4133,32 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / ベース 0.84 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / ベース 0.81 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.49 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / ベース 0.81 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.84 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / ベース 0.76 %</t>
+          <t xml:space="preserve">全社 0.61 % / 補助 0.44 % / ベース 0.83 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / ベース 0.74 %</t>
+          <t xml:space="preserve">全社 0.55 % / 補助 0.37 % / ベース 0.82 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / ベース 0.72 %</t>
+          <t xml:space="preserve">全社 0.5 % / 補助 0.32 % / ベース 0.8 %</t>
         </is>
       </c>
     </row>
@@ -4195,32 +4195,32 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / ベース 12.47 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / ベース 12.48 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.3 % / 補助 8.28 % / ベース 12.67 %</t>
+          <t xml:space="preserve">全社 10.32 % / 補助 8.28 % / ベース 12.71 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.47 % / 補助 8.43 % / ベース 12.88 %</t>
+          <t xml:space="preserve">全社 10.49 % / 補助 8.43 % / ベース 12.92 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / ベース 12.82 %</t>
+          <t xml:space="preserve">全社 9.71 % / 補助 7.35 % / ベース 12.89 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.19 % / 補助 6.79 % / ベース 12.9 %</t>
+          <t xml:space="preserve">全社 9.22 % / 補助 6.79 % / ベース 12.98 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.69 % / 補助 6.27 % / ベース 12.98 %</t>
+          <t xml:space="preserve">全社 8.73 % / 補助 6.27 % / ベース 13.07 %</t>
         </is>
       </c>
     </row>
@@ -4319,32 +4319,32 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / ベース 0.203 億円/人</t>
+          <t xml:space="preserve">全社 0.208 億円/人 / 補助 0.21 億円/人 / ベース 0.207 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / ベース 0.207 億円/人</t>
+          <t xml:space="preserve">全社 0.218 億円/人 / 補助 0.22 億円/人 / ベース 0.217 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / ベース 0.213 億円/人</t>
+          <t xml:space="preserve">全社 0.228 億円/人 / 補助 0.235 億円/人 / ベース 0.223 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / ベース 0.217 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.25 億円/人 / ベース 0.237 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / ベース 0.223 億円/人</t>
+          <t xml:space="preserve">全社 0.252 億円/人 / 補助 0.26 億円/人 / ベース 0.247 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / ベース 0.23 億円/人</t>
+          <t xml:space="preserve">全社 0.264 億円/人 / 補助 0.275 億円/人 / ベース 0.257 億円/人</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4443,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / ベース 60.67 %</t>
+          <t xml:space="preserve">全社 50.35 % / 補助 41.03 % / ベース 60.73 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.9 % / 補助 41.39 % / ベース 61.72 %</t>
+          <t xml:space="preserve">全社 50.99 % / 補助 41.39 % / ベース 61.91 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.54 % / 補助 41.84 % / ベース 62.78 %</t>
+          <t xml:space="preserve">全社 51.62 % / 補助 41.84 % / ベース 62.96 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.6 % / 補助 35.07 % / ベース 59.29 %</t>
+          <t xml:space="preserve">全社 45.74 % / 補助 35.07 % / ベース 59.62 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.12 % / 補助 31.18 % / ベース 58.88 %</t>
+          <t xml:space="preserve">全社 42.26 % / 補助 31.18 % / ベース 59.23 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.66 % / 補助 27.72 % / ベース 58.4 %</t>
+          <t xml:space="preserve">全社 38.8 % / 補助 27.72 % / ベース 58.77 %</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.133 億円/人 / ベース 0.042 億円/人</t>
+          <t xml:space="preserve">全社 0.081 億円/人 / 補助 0.133 億円/人 / ベース 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.54 %</t>
+          <t xml:space="preserve">全社 4.88 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.09 %</t>
+          <t xml:space="preserve">全社 4.65 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.67 %</t>
+          <t xml:space="preserve">全社 4.43 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.95 倍</t>
+          <t xml:space="preserve">全社 0.49 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.91 倍</t>
+          <t xml:space="preserve">全社 0.47 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.88 倍</t>
+          <t xml:space="preserve">全社 0.45 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5130,27 +5130,27 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / ベース 3.99 倍</t>
+          <t xml:space="preserve">全社 3.25 倍 / 補助 2.95 倍 / ベース 3.97 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.94 倍 / 補助 2.55 倍 / ベース 4.04 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.55 倍 / ベース 4.02 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.99 倍</t>
+          <t xml:space="preserve">全社 3.96 倍 / 補助 3.62 倍 / ベース 4.95 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.01 倍 / 補助 4.86 倍 / ベース 5.43 倍</t>
+          <t xml:space="preserve">全社 5 倍 / 補助 4.86 倍 / ベース 5.39 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / ベース 5.93 倍</t>
+          <t xml:space="preserve">全社 6.32 倍 / 補助 6.48 倍 / ベース 5.87 倍</t>
         </is>
       </c>
     </row>
@@ -5187,17 +5187,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 倍</t>
+          <t xml:space="preserve">全社 0.95 倍</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.51 倍</t>
+          <t xml:space="preserve">全社 1 倍</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 倍</t>
+          <t xml:space="preserve">全社 1.05 倍</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -5497,32 +5497,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.38 pt</t>
+          <t xml:space="preserve">差 2.39 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.86 pt</t>
+          <t xml:space="preserve">差 1.9 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.38 pt</t>
+          <t xml:space="preserve">差 1.42 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.8 pt</t>
+          <t xml:space="preserve">差 2.87 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.55 pt</t>
+          <t xml:space="preserve">差 4.62 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.15 pt</t>
+          <t xml:space="preserve">差 6.23 pt</t>
         </is>
       </c>
     </row>
@@ -5683,12 +5683,12 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 190.91 %</t>
+          <t xml:space="preserve">寄与率 175 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 166.67 %</t>
+          <t xml:space="preserve">寄与率 142.86 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -5698,17 +5698,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.17 %</t>
+          <t xml:space="preserve">寄与率 76.55 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.02 %</t>
+          <t xml:space="preserve">寄与率 89.17 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.38 %</t>
+          <t xml:space="preserve">寄与率 90.49 %</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5810,11 +5810,11 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>5.409356725146197</v>
+        <v>68</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5822,20 +5822,20 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>5.701754385964919</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>68</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5846,34 +5846,34 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>1.6653345369377348e-14</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">実効税率</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>2.0030662342518046</v>
+        <v>30</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>1.9325330501846927</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>2.0735994183189166</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -5894,11 +5894,11 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5909,38 +5909,38 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>5.409356725146197</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>5.116959064327475</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E9" s="2">
-        <v>5.701754385964919</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>4.257246376811585</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <v>4.076086956521719</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E10" s="2">
-        <v>4.438405797101453</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -5972,17 +5972,17 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0.013457556935819737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1.984645846924027</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -5990,20 +5990,20 @@
         </is>
       </c>
       <c r="D12" s="2">
-        <v>1.9139457023717443</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E12" s="2">
-        <v>2.0553459914763095</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4.083333333333339</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <v>3.9166666666666683</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E13" s="2">
-        <v>4.250000000000009</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6035,17 +6035,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6053,20 +6053,20 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6.257246376811586</v>
+        <v>4</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6074,20 +6074,20 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>6.438405797101453</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1.5</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6095,20 +6095,20 @@
         </is>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6116,20 +6116,20 @@
         </is>
       </c>
       <c r="D18" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>0.5134575569358197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.000000000000001</v>
+        <v>22</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6137,20 +6137,20 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>2.484645846924027</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6158,20 +6158,20 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>2.4139457023717443</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E20" s="2">
-        <v>2.5553459914763095</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6182,17 +6182,17 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>4.583333333333338</v>
+        <v>0.5</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6200,20 +6200,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>4.416666666666668</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="2">
-        <v>4.750000000000009</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>11</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6221,20 +6221,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="E23" s="2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10.928571428571427</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6242,20 +6242,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>8.928571428571427</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E24" s="2">
-        <v>11.928571428571427</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>5.380116959064325</v>
+        <v>4.5</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6263,82 +6263,187 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>6.555555555555557</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>23</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D27" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>11</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>10.928571428571427</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
+        <v>8.928571428571427</v>
+      </c>
+      <c r="E29" s="2">
+        <v>11.928571428571427</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E30" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <v>23</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B28" s="2">
+      <c r="B33" s="2">
         <v>7.66</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6350,7 +6455,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C244"/>
+  <dimension ref="A1:C259"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8285,26 +8390,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>200</v>
+        <v>0.6</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8315,26 +8420,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8345,26 +8450,26 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0.0051345755693581975</v>
+        <v>100</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8375,26 +8480,26 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8405,26 +8510,26 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.04416666666666668</v>
+        <v>0</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.04750000000000009</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8435,26 +8540,26 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.03916666666666668</v>
+        <v>0</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.04250000000000009</v>
+        <v>0.99</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8465,11 +8570,11 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8480,11 +8585,11 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.025553459914763096</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8495,11 +8600,11 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.019139457023717443</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -8510,11 +8615,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8525,26 +8630,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.06076086956521719</v>
+        <v>0</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.06438405797101453</v>
+        <v>0.08</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8555,26 +8660,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.040760869565217184</v>
+        <v>0</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.08</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8585,41 +8690,41 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8630,11 +8735,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8645,26 +8750,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.03</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8675,26 +8780,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8705,7 +8810,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -8720,26 +8825,26 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8750,11 +8855,11 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8765,26 +8870,26 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8795,26 +8900,26 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.04263157894736836</v>
+        <v>0</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.06555555555555558</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8825,26 +8930,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.99</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8855,26 +8960,26 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8885,11 +8990,11 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8900,11 +9005,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8915,11 +9020,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -8930,7 +9035,7 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
@@ -8945,11 +9050,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8960,11 +9065,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -8975,41 +9080,41 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9020,11 +9125,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.135</v>
+        <v>0.1</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9035,11 +9140,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9050,11 +9155,11 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>50</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9065,11 +9170,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9080,11 +9185,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9095,11 +9200,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>23</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9110,11 +9215,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>23</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9125,22 +9230,22 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B186" s="2">
@@ -9155,11 +9260,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9170,11 +9275,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.135</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9185,11 +9290,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.02484645846924027</v>
+        <v>1</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9200,11 +9305,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.01984645846924027</v>
+        <v>50</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9215,11 +9320,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.06257246376811586</v>
+        <v>5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9230,11 +9335,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.042572463768115854</v>
+        <v>20</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9245,26 +9350,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>0.10928571428571428</v>
+        <v>23</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9275,11 +9380,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.015</v>
+        <v>23</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9395,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.005</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9305,26 +9410,26 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.68</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9335,11 +9440,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.05</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9350,11 +9455,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9365,11 +9470,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.045</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9380,11 +9485,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9500,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9410,11 +9515,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.22</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9425,11 +9530,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9440,41 +9545,41 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>7.66</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9485,11 +9590,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>10</v>
+        <v>0.015</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9500,11 +9605,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>15</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9515,11 +9620,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9635,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9545,56 +9650,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>7</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9605,11 +9710,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>3.5</v>
+        <v>0.07</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9620,11 +9725,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>35</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9635,11 +9740,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>15</v>
+        <v>0.22</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9650,11 +9755,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>252.69</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9665,26 +9770,26 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>82.4</v>
+        <v>0</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>10</v>
+        <v>0.11</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9695,11 +9800,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>7</v>
+        <v>7.66</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9710,11 +9815,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>3.74</v>
+        <v>10</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9725,11 +9830,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>2.85</v>
+        <v>7.67</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9740,11 +9845,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>70</v>
+        <v>7.67</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9755,11 +9860,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>15</v>
+        <v>7.66</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9770,56 +9875,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -9830,11 +9935,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -9845,11 +9950,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -9860,26 +9965,26 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>35</v>
+        <v>252.69</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -9890,11 +9995,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>22</v>
+        <v>82.4</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -9905,11 +10010,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>136.84</v>
+        <v>10</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -9920,11 +10025,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>74.8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -9935,11 +10040,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>95</v>
+        <v>3.74</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -9950,11 +10055,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>60</v>
+        <v>2.85</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -9965,11 +10070,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>33.43</v>
+        <v>70</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -9980,11 +10085,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>18.78</v>
+        <v>15</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -9995,11 +10100,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10010,13 +10115,238 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B244" s="2">
+        <v>21</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B245" s="2">
+        <v>40</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B246" s="2">
+        <v>23</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B247" s="2">
+        <v>10</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B248" s="2">
+        <v>6</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B249" s="2">
+        <v>0</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B250" s="2">
+        <v>35</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B251" s="2">
+        <v>22</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B252" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B253" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B254" s="2">
+        <v>95</v>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B255" s="2">
+        <v>60</v>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B256" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B257" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B258" s="2">
+        <v>350</v>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B244" s="2">
+      <c r="B259" s="2">
         <v>213</v>
       </c>
-      <c r="C244" s="0" t="inlineStr">
+      <c r="C259" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10044,7 +10374,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMzYxMjg2NjQyODMyNjM0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjE5MjU1NjIyMDQ4MzExLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wOTE3NTYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzcyMDU0ODIzOTcyMDUwNSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI3MjU4OTg3MjEyODIzLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3NzgwNTc2Mjg3MTYzMiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjcsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjgsInZhbHVlIjo3LjY2fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjcuNjcsImZ1dHVyZS1jYXBleDoyMDI3Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyOCI6Ny42NiwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMzYxMjg2NjQyODMyNjM0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjE5MjU1NjIyMDQ4MzExLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTc1NjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAzNzIwNTQ4MjM5NzIwNTA1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>22.499949660479125</v>
+        <v>22.48892448955735</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.65</v>
+        <v>19.649999999999995</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.5274151436031</v>
+        <v>256.52741514360304</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="F9" s="2">
-        <v>41.46</v>
+        <v>41.43</v>
       </c>
       <c r="G9" s="2">
-        <v>44.17</v>
+        <v>44.14</v>
       </c>
       <c r="H9" s="2">
-        <v>47.94</v>
+        <v>47.91</v>
       </c>
       <c r="I9" s="2">
-        <v>52.699999999999996</v>
+        <v>52.67</v>
       </c>
       <c r="J9" s="2">
-        <v>58.06</v>
+        <v>58.02000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1545,10 +1545,10 @@
         <v>1.09</v>
       </c>
       <c r="I11" s="2">
-        <v>1.1300000000000001</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="J11" s="2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>0.12000000000000001</v>
       </c>
       <c r="I12" s="2">
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.13</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -1647,7 +1647,7 @@
         <v>17.740000000000002</v>
       </c>
       <c r="I14" s="2">
-        <v>19.509999999999998</v>
+        <v>19.5</v>
       </c>
       <c r="J14" s="2">
         <v>21.45</v>
@@ -1681,7 +1681,7 @@
         <v>0.9299999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J15" s="2">
         <v>1.13</v>
@@ -1709,16 +1709,16 @@
         <v>3.8499999999999996</v>
       </c>
       <c r="G16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="H16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="I16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="J16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="17">
@@ -1737,22 +1737,22 @@
         <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F17" s="2">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="G17" s="2">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H17" s="2">
-        <v>0.9299999999999999</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J17" s="2">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.480000000000004</v>
+        <v>11.500000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>11.34000000000001</v>
+        <v>11.370000000000012</v>
       </c>
       <c r="G18" s="4">
-        <v>11.209999999999997</v>
+        <v>11.239999999999995</v>
       </c>
       <c r="H18" s="4">
-        <v>17.180000000000007</v>
+        <v>17.210000000000008</v>
       </c>
       <c r="I18" s="4">
-        <v>23.18</v>
+        <v>23.209999999999994</v>
       </c>
       <c r="J18" s="4">
-        <v>30.86000000000002</v>
+        <v>30.90000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.297692454389424</v>
+        <v>7.310406204309963</v>
       </c>
       <c r="F19" s="2">
-        <v>6.873560431567468</v>
+        <v>6.891744453873202</v>
       </c>
       <c r="G19" s="2">
-        <v>6.478645321620527</v>
+        <v>6.495983355487485</v>
       </c>
       <c r="H19" s="2">
-        <v>8.612823983556428</v>
+        <v>8.627863839173814</v>
       </c>
       <c r="I19" s="2">
-        <v>10.08001391546356</v>
+        <v>10.093059662550006</v>
       </c>
       <c r="J19" s="2">
-        <v>11.585823697251847</v>
+        <v>11.600840967112186</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.16999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="F20" s="4">
-        <v>11.010000000000002</v>
+        <v>10.989999999999998</v>
       </c>
       <c r="G20" s="4">
-        <v>10.860000000000003</v>
+        <v>10.84</v>
       </c>
       <c r="H20" s="4">
-        <v>15.940000000000001</v>
+        <v>15.440000000000001</v>
       </c>
       <c r="I20" s="4">
-        <v>21.829999999999988</v>
+        <v>21.29</v>
       </c>
       <c r="J20" s="4">
-        <v>29.38000000000001</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.16999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="F21" s="2">
-        <v>11.010000000000002</v>
+        <v>10.989999999999998</v>
       </c>
       <c r="G21" s="2">
-        <v>10.860000000000003</v>
+        <v>10.84</v>
       </c>
       <c r="H21" s="2">
-        <v>15.940000000000001</v>
+        <v>15.440000000000001</v>
       </c>
       <c r="I21" s="2">
-        <v>21.829999999999988</v>
+        <v>21.29</v>
       </c>
       <c r="J21" s="2">
-        <v>29.38000000000001</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.8229999999999915</v>
+        <v>7.79</v>
       </c>
       <c r="F22" s="2">
-        <v>7.713000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="G22" s="2">
-        <v>7.596000000000002</v>
+        <v>7.59</v>
       </c>
       <c r="H22" s="2">
-        <v>11.155000000000001</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>15.27999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="J22" s="2">
-        <v>20.565000000000005</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.720000000000002</v>
+        <v>31.740000000000002</v>
       </c>
       <c r="F26" s="4">
-        <v>33.400000000000006</v>
+        <v>33.43000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>35.16</v>
+        <v>35.18999999999999</v>
       </c>
       <c r="H26" s="4">
-        <v>42.35</v>
+        <v>42.38</v>
       </c>
       <c r="I26" s="4">
-        <v>50.18999999999999</v>
+        <v>50.21999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>59.90000000000002</v>
+        <v>59.94000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.382059800664463</v>
+        <v>5.448504983388713</v>
       </c>
       <c r="F27" s="2">
-        <v>5.29634300126105</v>
+        <v>5.324511657214881</v>
       </c>
       <c r="G27" s="2">
-        <v>5.269461077844273</v>
+        <v>5.264732276398387</v>
       </c>
       <c r="H27" s="2">
-        <v>20.44937428896474</v>
+        <v>20.431940892298982</v>
       </c>
       <c r="I27" s="2">
-        <v>18.51239669421485</v>
+        <v>18.499292118924004</v>
       </c>
       <c r="J27" s="2">
-        <v>19.346483363219825</v>
+        <v>19.35483870967747</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.164007373974954</v>
+        <v>20.176721123895494</v>
       </c>
       <c r="F28" s="2">
-        <v>20.244878167050555</v>
+        <v>20.263062189356287</v>
       </c>
       <c r="G28" s="2">
-        <v>20.320175692076518</v>
+        <v>20.337513725943474</v>
       </c>
       <c r="H28" s="2">
-        <v>21.23126284654334</v>
+        <v>21.246302702160726</v>
       </c>
       <c r="I28" s="2">
-        <v>21.82553487563054</v>
+        <v>21.838580622716993</v>
       </c>
       <c r="J28" s="2">
-        <v>22.488361615858242</v>
+        <v>22.503378885718583</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12946938775510206</v>
+        <v>0.12955102040816327</v>
       </c>
       <c r="F35" s="2">
-        <v>0.12996108949416343</v>
+        <v>0.13007782101167317</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13168539325842696</v>
+        <v>0.13179775280898873</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15233812949640288</v>
+        <v>0.15244604316546764</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17306896551724135</v>
+        <v>0.1731724137931034</v>
       </c>
       <c r="J35" s="2">
-        <v>0.1983443708609272</v>
+        <v>0.19847682119205304</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.750000000000004</v>
+        <v>15.770000000000003</v>
       </c>
       <c r="F36" s="4">
-        <v>16.37000000000001</v>
+        <v>16.400000000000013</v>
       </c>
       <c r="G36" s="4">
-        <v>17.009999999999998</v>
+        <v>17.039999999999996</v>
       </c>
       <c r="H36" s="4">
-        <v>22.980000000000008</v>
+        <v>23.01000000000001</v>
       </c>
       <c r="I36" s="4">
-        <v>28.98</v>
+        <v>29.009999999999994</v>
       </c>
       <c r="J36" s="4">
-        <v>36.66000000000002</v>
+        <v>36.70000000000002</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.012078062424514</v>
+        <v>10.024791812345054</v>
       </c>
       <c r="F37" s="2">
-        <v>9.922414838162208</v>
+        <v>9.940598860467942</v>
       </c>
       <c r="G37" s="2">
-        <v>9.830665202566028</v>
+        <v>9.848003236432985</v>
       </c>
       <c r="H37" s="2">
-        <v>11.520529402917736</v>
+        <v>11.535569258535123</v>
       </c>
       <c r="I37" s="2">
-        <v>12.602191685510524</v>
+        <v>12.61523743259697</v>
       </c>
       <c r="J37" s="2">
-        <v>13.763327827001056</v>
+        <v>13.778345096861397</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.304635761589415</v>
+        <v>4.437086092715248</v>
       </c>
       <c r="F38" s="2">
-        <v>3.9365079365079936</v>
+        <v>3.9949270767280165</v>
       </c>
       <c r="G38" s="2">
-        <v>3.9095907147219666</v>
+        <v>3.9024390243901363</v>
       </c>
       <c r="H38" s="2">
-        <v>35.0970017636685</v>
+        <v>35.03521126760572</v>
       </c>
       <c r="I38" s="2">
-        <v>26.109660574412487</v>
+        <v>26.07561929595821</v>
       </c>
       <c r="J38" s="2">
-        <v>26.50103519668743</v>
+        <v>26.50810065494664</v>
       </c>
     </row>
   </sheetData>
@@ -2805,16 +2805,16 @@
         <v>6.890000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>6.680000000000003</v>
+        <v>6.690000000000005</v>
       </c>
       <c r="H8" s="4">
-        <v>11.250000000000002</v>
+        <v>11.260000000000003</v>
       </c>
       <c r="I8" s="4">
-        <v>16.599999999999987</v>
+        <v>16.609999999999985</v>
       </c>
       <c r="J8" s="4">
-        <v>23.550000000000008</v>
+        <v>23.560000000000006</v>
       </c>
     </row>
     <row r="9">
@@ -2839,16 +2839,16 @@
         <v>7.751153110586119</v>
       </c>
       <c r="G9" s="2">
-        <v>7.129135538954112</v>
+        <v>7.139807897545363</v>
       </c>
       <c r="H9" s="2">
-        <v>9.839076438691622</v>
+        <v>9.847822284414907</v>
       </c>
       <c r="I9" s="2">
-        <v>11.89878861730341</v>
+        <v>11.905956562253591</v>
       </c>
       <c r="J9" s="2">
-        <v>13.833411654135341</v>
+        <v>13.839285714285717</v>
       </c>
     </row>
     <row r="10">
@@ -2975,16 +2975,16 @@
         <v>17.78</v>
       </c>
       <c r="G13" s="4">
-        <v>18.880000000000003</v>
+        <v>18.890000000000004</v>
       </c>
       <c r="H13" s="4">
-        <v>23.950000000000003</v>
+        <v>23.960000000000004</v>
       </c>
       <c r="I13" s="4">
-        <v>30.369999999999987</v>
+        <v>30.379999999999985</v>
       </c>
       <c r="J13" s="4">
-        <v>38.53</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="14">
@@ -3011,16 +3011,16 @@
         <v>6.339712918660356</v>
       </c>
       <c r="G14" s="2">
-        <v>6.186726659167618</v>
+        <v>6.242969628796424</v>
       </c>
       <c r="H14" s="2">
-        <v>26.853813559322038</v>
+        <v>26.839597670725258</v>
       </c>
       <c r="I14" s="2">
-        <v>26.805845511482175</v>
+        <v>26.794657762938144</v>
       </c>
       <c r="J14" s="2">
-        <v>26.868620349028703</v>
+        <v>26.85977616853199</v>
       </c>
     </row>
     <row r="15">
@@ -3253,16 +3253,16 @@
         <v>0.15734513274336284</v>
       </c>
       <c r="G21" s="2">
-        <v>0.16000000000000003</v>
+        <v>0.1600847457627119</v>
       </c>
       <c r="H21" s="2">
-        <v>0.1963114754098361</v>
+        <v>0.19639344262295086</v>
       </c>
       <c r="I21" s="2">
-        <v>0.23913385826771644</v>
+        <v>0.23921259842519674</v>
       </c>
       <c r="J21" s="2">
-        <v>0.29412213740458015</v>
+        <v>0.29419847328244275</v>
       </c>
     </row>
     <row r="22">
@@ -3761,32 +3761,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.6 % / ベース 25.98 %</t>
+          <t xml:space="preserve">全社 24.69 % / 補助 23.6 % / ベース 25.95 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.13 % / 補助 24.25 % / ベース 26.15 %</t>
+          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / ベース 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.53 % / 補助 24.88 % / ベース 26.3 %</t>
+          <t xml:space="preserve">全社 25.51 % / 補助 24.87 % / ベース 26.27 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.03 % / 補助 22.67 % / ベース 25.87 %</t>
+          <t xml:space="preserve">全社 24.02 % / 補助 22.66 % / ベース 25.84 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.92 % / 補助 21.1 % / ベース 25.72 %</t>
+          <t xml:space="preserve">全社 22.9 % / 補助 21.1 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.8 % / 補助 19.67 % / ベース 25.56 %</t>
+          <t xml:space="preserve">全社 21.78 % / 補助 19.67 % / ベース 25.53 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3823,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.41 % / ベース 6.02 %</t>
+          <t xml:space="preserve">全社 7.31 % / 補助 8.41 % / ベース 6.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.87 % / 補助 7.75 % / ベース 5.85 %</t>
+          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / ベース 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.48 % / 補助 7.13 % / ベース 5.71 %</t>
+          <t xml:space="preserve">全社 6.5 % / 補助 7.14 % / ベース 5.74 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 9.84 % / ベース 6.97 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 9.85 % / ベース 6.99 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.08 % / 補助 11.9 % / ベース 7.27 %</t>
+          <t xml:space="preserve">全社 10.09 % / 補助 11.91 % / ベース 7.3 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.59 % / 補助 13.83 % / ベース 7.61 %</t>
+          <t xml:space="preserve">全社 11.6 % / 補助 13.84 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3885,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 11.69 % / ベース 8.07 %</t>
+          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / ベース 8.1 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.92 % / 補助 11.72 % / ベース 7.82 %</t>
+          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / ベース 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 11.72 % / ベース 7.6 %</t>
+          <t xml:space="preserve">全社 9.85 % / 補助 11.73 % / ベース 7.63 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.52 % / 補助 13.6 % / ベース 8.73 %</t>
+          <t xml:space="preserve">全社 11.54 % / 補助 13.61 % / ベース 8.75 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.6 % / 補助 14.98 % / ベース 8.93 %</t>
+          <t xml:space="preserve">全社 12.62 % / 補助 14.99 % / ベース 8.96 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.76 % / 補助 16.36 % / ベース 9.17 %</t>
+          <t xml:space="preserve">全社 13.78 % / 補助 16.37 % / ベース 9.2 %</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4443,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.35 % / 補助 41.03 % / ベース 60.73 %</t>
+          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / ベース 60.65 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.99 % / 補助 41.39 % / ベース 61.91 %</t>
+          <t xml:space="preserve">全社 50.94 % / 補助 41.39 % / ベース 61.79 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.62 % / 補助 41.84 % / ベース 62.96 %</t>
+          <t xml:space="preserve">全社 51.58 % / 補助 41.82 % / ベース 62.88 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.74 % / 補助 35.07 % / ベース 59.62 %</t>
+          <t xml:space="preserve">全社 45.71 % / 補助 35.06 % / ベース 59.55 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.26 % / 補助 31.18 % / ベース 59.23 %</t>
+          <t xml:space="preserve">全社 42.23 % / 補助 31.17 % / ベース 59.17 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.8 % / 補助 27.72 % / ベース 58.77 %</t>
+          <t xml:space="preserve">全社 38.77 % / 補助 27.71 % / ベース 58.69 %</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
@@ -5125,32 +5125,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.94 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.25 倍 / 補助 2.95 倍 / ベース 3.97 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.55 倍 / ベース 4.02 倍</t>
+          <t xml:space="preserve">全社 2.94 倍 / 補助 2.56 倍 / ベース 4.03 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.96 倍 / 補助 3.62 倍 / ベース 4.95 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 倍 / 補助 4.86 倍 / ベース 5.39 倍</t>
+          <t xml:space="preserve">全社 5 倍 / 補助 4.86 倍 / ベース 5.4 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.32 倍 / 補助 6.48 倍 / ベース 5.87 倍</t>
+          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5497,32 +5497,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.39 pt</t>
+          <t xml:space="preserve">差 2.36 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.9 pt</t>
+          <t xml:space="preserve">差 1.86 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.42 pt</t>
+          <t xml:space="preserve">差 1.4 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.87 pt</t>
+          <t xml:space="preserve">差 2.86 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.62 pt</t>
+          <t xml:space="preserve">差 4.61 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.23 pt</t>
+          <t xml:space="preserve">差 6.2 pt</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5683,17 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 175 %</t>
+          <t xml:space="preserve">寄与率 210 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 142.86 %</t>
+          <t xml:space="preserve">寄与率 153.85 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 161.54 %</t>
+          <t xml:space="preserve">寄与率 153.85 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.49 %</t>
+          <t xml:space="preserve">寄与率 90.38 %</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5821,11 +5821,15 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>99</v>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5842,185 +5846,221 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>99</v>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率</t>
+          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>60</v>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>5.409356725146197</v>
+        <v>95</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D7" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5.701754385964919</v>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>90</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1.6653345369377348e-14</v>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>2.0030662342518046</v>
+        <v>90</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>1.9325330501846927</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2.0735994183189166</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>5.409356725146197</v>
+        <v>25</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D10" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5.701754385964919</v>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>5.409356725146197</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E12" s="2">
-        <v>5.701754385964919</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4.257246376811585</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>4.076086956521719</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4.438405797101453</v>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6031,105 +6071,125 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.013457556935819737</v>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>1.984645846924027</v>
+        <v>-0.5</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D15" s="2">
-        <v>1.9139457023717443</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2.0553459914763095</v>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8</v>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>4.083333333333339</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>3.9166666666666683</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4.250000000000009</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>22</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6137,20 +6197,20 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>15</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E19" s="2">
-        <v>30</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6.257246376811586</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6158,41 +6218,41 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>6.438405797101453</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>1.5</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <v>0</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.5</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6200,20 +6260,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>0.5</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E22" s="2">
-        <v>0.5134575569358197</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6221,20 +6281,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>2.484645846924027</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6242,20 +6302,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>2.4139457023717443</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E24" s="2">
-        <v>2.5553459914763095</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.5</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6263,20 +6323,20 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E25" s="2">
-        <v>8</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6287,17 +6347,17 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>8</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>4.583333333333338</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6305,41 +6365,45 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>4.416666666666668</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E27" s="2">
-        <v>4.750000000000009</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="E28" s="2">
-        <v>13.5</v>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>10.928571428571427</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6347,20 +6411,20 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>8.928571428571427</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E29" s="2">
-        <v>11.928571428571427</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>5.380116959064325</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6368,82 +6432,338 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>6.555555555555557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D31" s="2">
+        <v>15</v>
+      </c>
+      <c r="E31" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>23</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D32" s="2">
+        <v>6.076086956521719</v>
+      </c>
+      <c r="E32" s="2">
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.5134575569358197</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <v>2.484645846924027</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D36" s="2">
+        <v>2.4139457023717443</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.5553459914763095</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <v>4</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <v>4.583333333333338</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4.750000000000009</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B40" s="2">
+        <v>11</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D40" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E40" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <v>10.928571428571427</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>8.928571428571427</v>
+      </c>
+      <c r="E41" s="2">
+        <v>11.928571428571427</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E42" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>10</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>23</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B33" s="2">
+      <c r="B45" s="2">
         <v>7.66</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6455,7 +6775,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C259"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8480,26 +8800,26 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.0051345755693581975</v>
+        <v>1</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8510,26 +8830,26 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8540,7 +8860,7 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
@@ -8555,11 +8875,11 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.99</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8570,26 +8890,26 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.04416666666666668</v>
+        <v>0</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.04750000000000009</v>
+        <v>0.99</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8600,26 +8920,26 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.03916666666666668</v>
+        <v>0</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.04250000000000009</v>
+        <v>1</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8630,26 +8950,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8660,26 +8980,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.08</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8690,11 +9010,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -8705,11 +9025,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.025553459914763096</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -8720,11 +9040,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.019139457023717443</v>
+        <v>-0.5</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8735,11 +9055,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.5</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8750,26 +9070,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.06076086956521719</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.06438405797101453</v>
+        <v>1</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8780,26 +9100,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.040760869565217184</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.08</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8810,7 +9130,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -8825,26 +9145,26 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8855,11 +9175,11 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8870,26 +9190,26 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.03</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8900,7 +9220,7 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -8915,11 +9235,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.3</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8930,26 +9250,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.99</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8960,26 +9280,26 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.08</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8990,41 +9310,41 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.05701754385964919</v>
+        <v>0</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>-0.05</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9035,11 +9355,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.3</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -9050,26 +9370,26 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.04263157894736836</v>
+        <v>0</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.06555555555555558</v>
+        <v>1</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9080,26 +9400,26 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.03</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9110,26 +9430,26 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.1</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9140,26 +9460,26 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.019325330501846927</v>
+        <v>0</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.99</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9170,26 +9490,26 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9200,11 +9520,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.051169590643274754</v>
+        <v>-0.5</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9215,11 +9535,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.5</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9230,7 +9550,7 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B185" s="2">
@@ -9245,26 +9565,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9275,11 +9595,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.135</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9610,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>1</v>
+        <v>-0.05</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9305,11 +9625,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9320,11 +9640,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9335,11 +9655,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9350,26 +9670,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9380,11 +9700,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>23</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9715,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.005</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9410,26 +9730,26 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.68</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9440,11 +9760,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.05</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9455,11 +9775,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.1</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9470,11 +9790,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.045</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9485,11 +9805,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.04</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9500,26 +9820,26 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.02484645846924027</v>
+        <v>0</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.3</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9850,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.15</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9545,11 +9865,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.3</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9560,26 +9880,26 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9590,41 +9910,41 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.68</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9635,11 +9955,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.04</v>
+        <v>0.135</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9650,11 +9970,11 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.05409356725146197</v>
+        <v>1</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -9665,11 +9985,11 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -9680,11 +10000,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.05380116959064325</v>
+        <v>5</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -9695,11 +10015,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>0.05409356725146197</v>
+        <v>20</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9710,11 +10030,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.07</v>
+        <v>0.3</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9725,11 +10045,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0.020030662342518046</v>
+        <v>23</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9740,11 +10060,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0.22</v>
+        <v>23</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9755,11 +10075,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.2</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9770,41 +10090,41 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>7.66</v>
+        <v>0.68</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9815,11 +10135,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>10</v>
+        <v>0.95</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9830,26 +10150,26 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>7.67</v>
+        <v>0</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>7.67</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9860,11 +10180,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>7.66</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9875,56 +10195,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>7</v>
+        <v>0.04</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -9935,11 +10255,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>3.5</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -9950,11 +10270,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>35</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -9965,11 +10285,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>15</v>
+        <v>0.004</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -9980,11 +10300,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>252.69</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -9995,11 +10315,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>82.4</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10010,26 +10330,26 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>7</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10040,11 +10360,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>3.74</v>
+        <v>0.25</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10055,11 +10375,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>2.85</v>
+        <v>0.015</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10070,11 +10390,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>70</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10085,11 +10405,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10100,11 +10420,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>35</v>
+        <v>0.95</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10115,26 +10435,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>40</v>
+        <v>0.04</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10145,11 +10465,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>23</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10160,11 +10480,11 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
@@ -10175,41 +10495,41 @@
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>35</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10220,11 +10540,11 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>22</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
@@ -10235,11 +10555,11 @@
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>136.84</v>
+        <v>0.07</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10250,11 +10570,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>74.8</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10265,11 +10585,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>95</v>
+        <v>0.005</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10280,11 +10600,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>60</v>
+        <v>0.22</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10295,11 +10615,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>33.43</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10310,26 +10630,26 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>18.78</v>
+        <v>0</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>350</v>
+        <v>0.11</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10340,13 +10660,553 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">driver:subsidy</t>
+        </is>
+      </c>
+      <c r="B259" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:usefulLife</t>
+        </is>
+      </c>
+      <c r="B260" s="2">
+        <v>10</v>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2026</t>
+        </is>
+      </c>
+      <c r="B261" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2027</t>
+        </is>
+      </c>
+      <c r="B262" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2028</t>
+        </is>
+      </c>
+      <c r="B263" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2029</t>
+        </is>
+      </c>
+      <c r="B264" s="2">
+        <v>0</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2030</t>
+        </is>
+      </c>
+      <c r="B265" s="2">
+        <v>0</v>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2031</t>
+        </is>
+      </c>
+      <c r="B266" s="2">
+        <v>0</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
+        </is>
+      </c>
+      <c r="B267" s="2">
+        <v>7</v>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
+        </is>
+      </c>
+      <c r="B268" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B269" s="2">
+        <v>35</v>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B270" s="2">
+        <v>15</v>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B271" s="2">
+        <v>252.69</v>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B272" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
+        </is>
+      </c>
+      <c r="B273" s="2">
+        <v>10</v>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
+        </is>
+      </c>
+      <c r="B274" s="2">
+        <v>7</v>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
+        </is>
+      </c>
+      <c r="B275" s="2">
+        <v>3.74</v>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B276" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+        </is>
+      </c>
+      <c r="B277" s="2">
+        <v>70</v>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B278" s="2">
+        <v>15</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B279" s="2">
+        <v>35</v>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B280" s="2">
+        <v>21</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B281" s="2">
+        <v>40</v>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B282" s="2">
+        <v>23</v>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B283" s="2">
+        <v>10</v>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B284" s="2">
+        <v>6</v>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B285" s="2">
+        <v>0</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B286" s="2">
+        <v>35</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B287" s="2">
+        <v>22</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B288" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>95</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>60</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B292" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B293" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B294" s="2">
+        <v>350</v>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B259" s="2">
+      <c r="B295" s="2">
         <v>213</v>
       </c>
-      <c r="C259" s="0" t="inlineStr">
+      <c r="C295" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10374,7 +11234,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjcsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjgsInZhbHVlIjo3LjY2fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjcuNjcsImZ1dHVyZS1jYXBleDoyMDI3Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyOCI6Ny42NiwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMzYxMjg2NjQyODMyNjM0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjE5MjU1NjIyMDQ4MzExLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTc1NjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAzNzIwNTQ4MjM5NzIwNTA1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyNywidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyOCwidmFsdWUiOjcuNjZ9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjcuNjcsImZ1dHVyZS1jYXBleDoyMDI3Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyOCI6Ny42NiwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -5001,17 +5001,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.65 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.43 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.45 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5187,17 +5187,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.95 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.05 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -6697,7 +6697,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -6775,7 +6775,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10690,11 +10690,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10705,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>7.67</v>
+        <v>3.5</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10720,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>7.66</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10735,56 +10735,56 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>0</v>
+        <v>252.69</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>0</v>
+        <v>82.4</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10795,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10810,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>35</v>
+        <v>3.74</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10825,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>15</v>
+        <v>2.85</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10840,11 +10840,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>252.69</v>
+        <v>70</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10855,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>82.4</v>
+        <v>15</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10870,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10885,11 +10885,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10900,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>3.74</v>
+        <v>40</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10915,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>2.85</v>
+        <v>23</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10930,11 +10930,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10945,11 +10945,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10960,26 +10960,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10990,11 +10990,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11005,11 +11005,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>23</v>
+        <v>136.84</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11020,11 +11020,11 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>10</v>
+        <v>74.8</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11035,11 +11035,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11050,26 +11050,26 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>35</v>
+        <v>33.43</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11080,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>22</v>
+        <v>18.78</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11095,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>136.84</v>
+        <v>350</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11110,103 +11110,13 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B289" s="2">
-        <v>74.8</v>
+        <v>213</v>
       </c>
       <c r="C289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
-        </is>
-      </c>
-      <c r="B290" s="2">
-        <v>95</v>
-      </c>
-      <c r="C290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
-        </is>
-      </c>
-      <c r="B291" s="2">
-        <v>60</v>
-      </c>
-      <c r="C291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
-        </is>
-      </c>
-      <c r="B292" s="2">
-        <v>33.43</v>
-      </c>
-      <c r="C292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B293" s="2">
-        <v>18.78</v>
-      </c>
-      <c r="C293" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B294" s="2">
-        <v>350</v>
-      </c>
-      <c r="C294" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B295" s="2">
-        <v>213</v>
-      </c>
-      <c r="C295" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11234,7 +11144,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyNywidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyOCwidmFsdWUiOjcuNjZ9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjcuNjcsImZ1dHVyZS1jYXBleDoyMDI3Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyOCI6Ny42NiwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>22.48892448955735</v>
+        <v>23.144831937435285</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.649999999999995</v>
+        <v>19.65</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.52741514360304</v>
+        <v>256.5274151436031</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="J6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.84</v>
+        <v>38.26</v>
       </c>
       <c r="F9" s="2">
-        <v>41.43</v>
+        <v>40.28</v>
       </c>
       <c r="G9" s="2">
-        <v>44.14</v>
+        <v>42.42</v>
       </c>
       <c r="H9" s="2">
-        <v>47.91</v>
+        <v>46.19</v>
       </c>
       <c r="I9" s="2">
-        <v>52.67</v>
+        <v>50.949999999999996</v>
       </c>
       <c r="J9" s="2">
-        <v>58.02000000000001</v>
+        <v>56.300000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1703,22 @@
         <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>3.2800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="2">
-        <v>3.8499999999999996</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="H16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="I16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="J16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.500000000000004</v>
+        <v>12.080000000000005</v>
       </c>
       <c r="F18" s="4">
-        <v>11.370000000000012</v>
+        <v>12.520000000000007</v>
       </c>
       <c r="G18" s="4">
-        <v>11.239999999999995</v>
+        <v>12.959999999999994</v>
       </c>
       <c r="H18" s="4">
-        <v>17.210000000000008</v>
+        <v>18.930000000000007</v>
       </c>
       <c r="I18" s="4">
-        <v>23.209999999999994</v>
+        <v>24.929999999999993</v>
       </c>
       <c r="J18" s="4">
-        <v>30.90000000000002</v>
+        <v>32.62000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.310406204309963</v>
+        <v>7.679104952005597</v>
       </c>
       <c r="F19" s="2">
-        <v>6.891744453873202</v>
+        <v>7.588798642259671</v>
       </c>
       <c r="G19" s="2">
-        <v>6.495983355487485</v>
+        <v>7.490030630526495</v>
       </c>
       <c r="H19" s="2">
-        <v>8.627863839173814</v>
+        <v>9.490148894570616</v>
       </c>
       <c r="I19" s="2">
-        <v>10.093059662550006</v>
+        <v>10.841015828839797</v>
       </c>
       <c r="J19" s="2">
-        <v>11.600840967112186</v>
+        <v>12.246583571106779</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.14</v>
+        <v>11.719999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>10.989999999999998</v>
+        <v>12.139999999999999</v>
       </c>
       <c r="G20" s="4">
-        <v>10.84</v>
+        <v>12.56</v>
       </c>
       <c r="H20" s="4">
-        <v>15.440000000000001</v>
+        <v>17.16</v>
       </c>
       <c r="I20" s="4">
-        <v>21.29</v>
+        <v>23.009999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>28.81</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.14</v>
+        <v>11.719999999999999</v>
       </c>
       <c r="F21" s="2">
-        <v>10.989999999999998</v>
+        <v>12.139999999999999</v>
       </c>
       <c r="G21" s="2">
-        <v>10.84</v>
+        <v>12.56</v>
       </c>
       <c r="H21" s="2">
-        <v>15.440000000000001</v>
+        <v>17.16</v>
       </c>
       <c r="I21" s="2">
-        <v>21.29</v>
+        <v>23.009999999999998</v>
       </c>
       <c r="J21" s="2">
-        <v>28.81</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.79</v>
+        <v>8.2</v>
       </c>
       <c r="F22" s="2">
-        <v>7.69</v>
+        <v>8.5</v>
       </c>
       <c r="G22" s="2">
-        <v>7.59</v>
+        <v>8.8</v>
       </c>
       <c r="H22" s="2">
-        <v>10.799999999999999</v>
+        <v>12.01</v>
       </c>
       <c r="I22" s="2">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="J22" s="2">
-        <v>20.17</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="23">
@@ -2009,22 +2009,22 @@
         <v>3.5</v>
       </c>
       <c r="E25" s="2">
-        <v>4.27</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="2">
-        <v>5.029999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="G25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="H25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="I25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.740000000000002</v>
+        <v>31.550000000000004</v>
       </c>
       <c r="F26" s="4">
-        <v>33.43000000000001</v>
+        <v>33.05000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>35.18999999999999</v>
+        <v>34.60999999999999</v>
       </c>
       <c r="H26" s="4">
-        <v>42.38</v>
+        <v>41.800000000000004</v>
       </c>
       <c r="I26" s="4">
-        <v>50.21999999999999</v>
+        <v>49.63999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>59.94000000000002</v>
+        <v>59.36000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.448504983388713</v>
+        <v>4.8172757475083205</v>
       </c>
       <c r="F27" s="2">
-        <v>5.324511657214881</v>
+        <v>4.754358161648198</v>
       </c>
       <c r="G27" s="2">
-        <v>5.264732276398387</v>
+        <v>4.720121028744262</v>
       </c>
       <c r="H27" s="2">
-        <v>20.431940892298982</v>
+        <v>20.774342675527336</v>
       </c>
       <c r="I27" s="2">
-        <v>18.499292118924004</v>
+        <v>18.75598086124399</v>
       </c>
       <c r="J27" s="2">
-        <v>19.35483870967747</v>
+        <v>19.580983078162827</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.176721123895494</v>
+        <v>20.055940499650372</v>
       </c>
       <c r="F28" s="2">
-        <v>20.263062189356287</v>
+        <v>20.032731240150326</v>
       </c>
       <c r="G28" s="2">
-        <v>20.337513725943474</v>
+        <v>20.002311737848924</v>
       </c>
       <c r="H28" s="2">
-        <v>21.246302702160726</v>
+        <v>20.955532160224596</v>
       </c>
       <c r="I28" s="2">
-        <v>21.838580622716993</v>
+        <v>21.586362845712298</v>
       </c>
       <c r="J28" s="2">
-        <v>22.503378885718583</v>
+        <v>22.285628472743664</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12955102040816327</v>
+        <v>0.12877551020408165</v>
       </c>
       <c r="F35" s="2">
-        <v>0.13007782101167317</v>
+        <v>0.1285992217898833</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13179775280898873</v>
+        <v>0.12962546816479398</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15244604316546764</v>
+        <v>0.15035971223021585</v>
       </c>
       <c r="I35" s="2">
-        <v>0.1731724137931034</v>
+        <v>0.17117241379310344</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19847682119205304</v>
+        <v>0.19655629139072855</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.770000000000003</v>
+        <v>15.580000000000005</v>
       </c>
       <c r="F36" s="4">
-        <v>16.400000000000013</v>
+        <v>16.020000000000007</v>
       </c>
       <c r="G36" s="4">
-        <v>17.039999999999996</v>
+        <v>16.459999999999994</v>
       </c>
       <c r="H36" s="4">
-        <v>23.01000000000001</v>
+        <v>22.430000000000007</v>
       </c>
       <c r="I36" s="4">
-        <v>29.009999999999994</v>
+        <v>28.429999999999993</v>
       </c>
       <c r="J36" s="4">
-        <v>36.70000000000002</v>
+        <v>36.12000000000002</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.024791812345054</v>
+        <v>9.904011188099933</v>
       </c>
       <c r="F37" s="2">
-        <v>9.940598860467942</v>
+        <v>9.710267911261974</v>
       </c>
       <c r="G37" s="2">
-        <v>9.848003236432985</v>
+        <v>9.512801248338434</v>
       </c>
       <c r="H37" s="2">
-        <v>11.535569258535123</v>
+        <v>11.24479871659899</v>
       </c>
       <c r="I37" s="2">
-        <v>12.61523743259697</v>
+        <v>12.363019655592275</v>
       </c>
       <c r="J37" s="2">
-        <v>13.778345096861397</v>
+        <v>13.560594683886476</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.437086092715248</v>
+        <v>3.1788079470199015</v>
       </c>
       <c r="F38" s="2">
-        <v>3.9949270767280165</v>
+        <v>2.824133504492954</v>
       </c>
       <c r="G38" s="2">
-        <v>3.9024390243901363</v>
+        <v>2.7465667915105296</v>
       </c>
       <c r="H38" s="2">
-        <v>35.03521126760572</v>
+        <v>36.26974483596608</v>
       </c>
       <c r="I38" s="2">
-        <v>26.07561929595821</v>
+        <v>26.749888542131007</v>
       </c>
       <c r="J38" s="2">
-        <v>26.50810065494664</v>
+        <v>27.04889201547671</v>
       </c>
     </row>
   </sheetData>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -2799,22 +2799,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>7.089999999999989</v>
+        <v>7.669999999999991</v>
       </c>
       <c r="F8" s="4">
-        <v>6.890000000000001</v>
+        <v>8.04</v>
       </c>
       <c r="G8" s="4">
-        <v>6.690000000000005</v>
+        <v>8.410000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>11.260000000000003</v>
+        <v>12.980000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>16.609999999999985</v>
+        <v>18.329999999999984</v>
       </c>
       <c r="J8" s="4">
-        <v>23.560000000000006</v>
+        <v>25.280000000000005</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2833,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>8.407446934661436</v>
+        <v>9.095221154986351</v>
       </c>
       <c r="F9" s="2">
-        <v>7.751153110586119</v>
+        <v>9.044886938913264</v>
       </c>
       <c r="G9" s="2">
-        <v>7.139807897545363</v>
+        <v>8.975453575240131</v>
       </c>
       <c r="H9" s="2">
-        <v>9.847822284414907</v>
+        <v>11.352107748819313</v>
       </c>
       <c r="I9" s="2">
-        <v>11.905956562253591</v>
+        <v>13.13884309368503</v>
       </c>
       <c r="J9" s="2">
-        <v>13.839285714285717</v>
+        <v>14.84962406015038</v>
       </c>
     </row>
     <row r="10">
@@ -2922,283 +2922,281 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（億円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
       <c r="C12" s="2">
-        <v>1.9</v>
+        <v>0.47</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="2">
-        <v>2.77</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="2">
-        <v>3.53</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-11 付加価値（億円）</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <v>14.129999999999999</v>
-      </c>
-      <c r="C13" s="4">
-        <v>14.910000000000004</v>
-      </c>
-      <c r="D13" s="4">
-        <v>15.700000000000005</v>
-      </c>
-      <c r="E13" s="4">
-        <v>16.71999999999999</v>
-      </c>
-      <c r="F13" s="4">
-        <v>17.78</v>
-      </c>
-      <c r="G13" s="4">
-        <v>18.890000000000004</v>
-      </c>
-      <c r="H13" s="4">
-        <v>23.960000000000004</v>
-      </c>
-      <c r="I13" s="4">
-        <v>30.379999999999985</v>
-      </c>
-      <c r="J13" s="4">
-        <v>38.54</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（億円）</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.43</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>1.8</v>
       </c>
       <c r="C14" s="2">
-        <v>5.520169851380086</v>
+        <v>1.9</v>
       </c>
       <c r="D14" s="2">
-        <v>5.2984574111334615</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>6.496815286624114</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
-        <v>6.339712918660356</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
-        <v>6.242969628796424</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2">
-        <v>26.839597670725258</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2">
-        <v>26.794657762938144</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>26.85977616853199</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <v>90</v>
-      </c>
-      <c r="C15" s="2">
-        <v>95</v>
-      </c>
-      <c r="D15" s="2">
-        <v>100</v>
-      </c>
-      <c r="E15" s="2">
-        <v>105</v>
-      </c>
-      <c r="F15" s="2">
-        <v>111</v>
-      </c>
-      <c r="G15" s="2">
-        <v>116</v>
-      </c>
-      <c r="H15" s="2">
-        <v>120</v>
-      </c>
-      <c r="I15" s="2">
-        <v>125</v>
-      </c>
-      <c r="J15" s="2">
-        <v>129</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-11 付加価値（億円）</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>14.129999999999999</v>
+      </c>
+      <c r="C15" s="4">
+        <v>14.910000000000004</v>
+      </c>
+      <c r="D15" s="4">
+        <v>15.700000000000005</v>
+      </c>
+      <c r="E15" s="4">
+        <v>16.529999999999994</v>
+      </c>
+      <c r="F15" s="4">
+        <v>17.4</v>
+      </c>
+      <c r="G15" s="4">
+        <v>18.310000000000002</v>
+      </c>
+      <c r="H15" s="4">
+        <v>23.380000000000003</v>
+      </c>
+      <c r="I15" s="4">
+        <v>29.799999999999983</v>
+      </c>
+      <c r="J15" s="4">
+        <v>37.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-14 役員数（人）</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <v>2</v>
+          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>5.520169851380086</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>5.2984574111334615</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>5.286624203821577</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>5.263157894736881</v>
       </c>
       <c r="G16" s="2">
-        <v>2</v>
+        <v>5.229885057471284</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>27.689787001638443</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>27.459366980324983</v>
       </c>
       <c r="J16" s="2">
-        <v>2</v>
+        <v>27.382550335570556</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.05766666666666667</v>
+        <v>90</v>
       </c>
       <c r="C17" s="2">
-        <v>0.05884210526315789</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2">
-        <v>0.06</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2">
-        <v>0.06133333333333334</v>
+        <v>105</v>
       </c>
       <c r="F17" s="2">
-        <v>0.062342342342342344</v>
+        <v>111</v>
       </c>
       <c r="G17" s="2">
-        <v>0.06405172413793103</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06583333333333334</v>
+        <v>120</v>
       </c>
       <c r="I17" s="2">
-        <v>0.0716</v>
+        <v>125</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07852713178294574</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-14 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>2.0383328262853606</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>1.9677996422182487</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>2.2222222222222365</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>1.6451233842538215</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
-        <v>2.7419274466812693</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>2.7815163750561034</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2">
-        <v>8.759493670886066</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>9.674765059980084</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0.18</v>
+        <v>0.05766666666666667</v>
       </c>
       <c r="C19" s="2">
-        <v>0.19</v>
+        <v>0.05884210526315789</v>
       </c>
       <c r="D19" s="2">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E19" s="2">
-        <v>0.21</v>
+        <v>0.06133333333333334</v>
       </c>
       <c r="F19" s="2">
-        <v>0.22</v>
+        <v>0.062342342342342344</v>
       </c>
       <c r="G19" s="2">
-        <v>0.235</v>
+        <v>0.06405172413793103</v>
       </c>
       <c r="H19" s="2">
-        <v>0.25</v>
+        <v>0.06583333333333334</v>
       </c>
       <c r="I19" s="2">
-        <v>0.26</v>
+        <v>0.0716</v>
       </c>
       <c r="J19" s="2">
-        <v>0.275</v>
+        <v>0.07852713178294574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -3207,109 +3205,179 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>5.555555555555558</v>
+        <v>2.0383328262853606</v>
       </c>
       <c r="D20" s="2">
-        <v>5.263157894736836</v>
+        <v>1.9677996422182487</v>
       </c>
       <c r="E20" s="2">
-        <v>4.999999999999982</v>
+        <v>2.2222222222222365</v>
       </c>
       <c r="F20" s="2">
-        <v>4.761904761904767</v>
+        <v>1.6451233842538215</v>
       </c>
       <c r="G20" s="2">
-        <v>6.818181818181812</v>
+        <v>2.7419274466812693</v>
       </c>
       <c r="H20" s="2">
-        <v>6.382978723404253</v>
+        <v>2.7815163750561034</v>
       </c>
       <c r="I20" s="2">
-        <v>4.0000000000000036</v>
+        <v>8.759493670886066</v>
       </c>
       <c r="J20" s="2">
-        <v>5.769230769230771</v>
+        <v>9.674765059980084</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.15358695652173912</v>
+        <v>0.18</v>
       </c>
       <c r="C21" s="2">
-        <v>0.1537113402061856</v>
+        <v>0.19</v>
       </c>
       <c r="D21" s="2">
-        <v>0.15392156862745102</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="2">
-        <v>0.15626168224299058</v>
+        <v>0.21</v>
       </c>
       <c r="F21" s="2">
-        <v>0.15734513274336284</v>
+        <v>0.22</v>
       </c>
       <c r="G21" s="2">
-        <v>0.1600847457627119</v>
+        <v>0.235</v>
       </c>
       <c r="H21" s="2">
-        <v>0.19639344262295086</v>
+        <v>0.25</v>
       </c>
       <c r="I21" s="2">
-        <v>0.23921259842519674</v>
+        <v>0.26</v>
       </c>
       <c r="J21" s="2">
-        <v>0.29419847328244275</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <v>5.555555555555558</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5.263157894736836</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4.999999999999982</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4.761904761904767</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6.818181818181812</v>
+      </c>
+      <c r="H22" s="2">
+        <v>6.382978723404253</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5.769230769230771</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>0.15358695652173912</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.1537113402061856</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.15392156862745102</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.15448598130841115</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.15398230088495574</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.15516949152542375</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.1916393442622951</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.23464566929133845</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.28977099236641224</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">7-20 市場伸び率（年あたり）（%）</t>
         </is>
       </c>
-      <c r="B22" s="2">
+      <c r="B24" s="2">
         <v>5</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3761,32 +3829,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.69 % / 補助 23.6 % / ベース 25.95 %</t>
+          <t xml:space="preserve">全社 24.32 % / 補助 22.91 % / ベース 25.95 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.11 % / 補助 24.25 % / ベース 26.11 %</t>
+          <t xml:space="preserve">全社 24.42 % / 補助 22.96 % / ベース 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.51 % / 補助 24.87 % / ベース 26.27 %</t>
+          <t xml:space="preserve">全社 24.52 % / 補助 23.03 % / ベース 26.27 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.02 % / 補助 22.66 % / ベース 25.84 %</t>
+          <t xml:space="preserve">全社 23.16 % / 補助 21.16 % / ベース 25.84 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.9 % / 補助 21.1 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.16 % / 補助 19.86 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.78 % / 補助 19.67 % / ベース 25.53 %</t>
+          <t xml:space="preserve">全社 21.14 % / 補助 18.66 % / ベース 25.53 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3891,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.31 % / 補助 8.41 % / ベース 6.04 %</t>
+          <t xml:space="preserve">全社 7.68 % / 補助 9.1 % / ベース 6.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.89 % / 補助 7.75 % / ベース 5.89 %</t>
+          <t xml:space="preserve">全社 7.59 % / 補助 9.04 % / ベース 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.5 % / 補助 7.14 % / ベース 5.74 %</t>
+          <t xml:space="preserve">全社 7.49 % / 補助 8.98 % / ベース 5.74 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 9.85 % / ベース 6.99 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 11.35 % / ベース 6.99 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.09 % / 補助 11.91 % / ベース 7.3 %</t>
+          <t xml:space="preserve">全社 10.84 % / 補助 13.14 % / ベース 7.3 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.6 % / 補助 13.84 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 12.25 % / 補助 14.85 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3953,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 11.69 % / ベース 8.1 %</t>
+          <t xml:space="preserve">全社 9.9 % / 補助 11.47 % / ベース 8.1 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.94 % / 補助 11.72 % / ベース 7.86 %</t>
+          <t xml:space="preserve">全社 9.71 % / 補助 11.29 % / ベース 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.85 % / 補助 11.73 % / ベース 7.63 %</t>
+          <t xml:space="preserve">全社 9.51 % / 補助 11.11 % / ベース 7.63 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.54 % / 補助 13.61 % / ベース 8.75 %</t>
+          <t xml:space="preserve">全社 11.24 % / 補助 13.1 % / ベース 8.75 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.62 % / 補助 14.99 % / ベース 8.96 %</t>
+          <t xml:space="preserve">全社 12.36 % / 補助 14.57 % / ベース 8.96 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.78 % / 補助 16.37 % / ベース 9.2 %</t>
+          <t xml:space="preserve">全社 13.56 % / 補助 16.02 % / ベース 9.2 %</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4511,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.32 % / 補助 41.03 % / ベース 60.65 %</t>
+          <t xml:space="preserve">全社 50.62 % / 補助 41.5 % / ベース 60.65 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.94 % / 補助 41.39 % / ベース 61.79 %</t>
+          <t xml:space="preserve">全社 51.53 % / 補助 42.3 % / ベース 61.79 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.58 % / 補助 41.82 % / ベース 62.88 %</t>
+          <t xml:space="preserve">全社 52.44 % / 補助 43.15 % / ベース 62.88 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.71 % / 補助 35.06 % / ベース 59.55 %</t>
+          <t xml:space="preserve">全社 46.34 % / 補助 35.93 % / ベース 59.55 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.23 % / 補助 31.17 % / ベース 59.17 %</t>
+          <t xml:space="preserve">全社 42.73 % / 補助 31.78 % / ベース 59.17 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.77 % / 補助 27.71 % / ベース 58.69 %</t>
+          <t xml:space="preserve">全社 39.15 % / 補助 28.13 % / ベース 58.69 %</t>
         </is>
       </c>
     </row>
@@ -4629,32 +4697,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.068 億円/人 / ベース 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / ベース 0.032 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / ベース 0.032 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.058 億円/人 / ベース 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.049 億円/人 / 補助 0.073 億円/人 / ベース 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / ベース 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.108 億円/人 / ベース 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.081 億円/人 / 補助 0.133 億円/人 / ベース 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.147 億円/人 / ベース 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.104 億円/人 / 補助 0.183 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.11 億円/人 / 補助 0.196 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4691,32 +4759,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.16 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.155 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / ベース 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.15 億円/人 / 補助 0.192 億円/人 / ベース 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.239 億円/人 / ベース 0.122 億円/人</t>
+          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.235 億円/人 / ベース 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.198 億円/人 / 補助 0.294 億円/人 / ベース 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.29 億円/人 / ベース 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4939,32 +5007,32 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / ベース 2.06 %</t>
+          <t xml:space="preserve">全社 2.22 % / 補助 2.37 % / ベース 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / ベース 1.97 %</t>
+          <t xml:space="preserve">全社 2.12 % / 補助 2.25 % / ベース 1.97 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / ベース 1.89 %</t>
+          <t xml:space="preserve">全社 2.02 % / 補助 2.13 % / ベース 1.89 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / ベース 1.76 %</t>
+          <t xml:space="preserve">全社 1.75 % / 補助 1.75 % / ベース 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / ベース 1.66 %</t>
+          <t xml:space="preserve">全社 1.52 % / 補助 1.43 % / ベース 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / ベース 1.56 %</t>
+          <t xml:space="preserve">全社 1.31 % / 補助 1.17 % / ベース 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5125,32 +5193,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.94 倍</t>
+          <t xml:space="preserve">全社 4.45 倍 / 補助 4.83 倍 / ベース 3.94 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / ベース 3.99 倍</t>
+          <t xml:space="preserve">全社 4.58 倍 / 補助 5.02 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.94 倍 / 補助 2.56 倍 / ベース 4.03 倍</t>
+          <t xml:space="preserve">全社 4.7 倍 / 補助 5.21 倍 / ベース 4.03 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.97 倍</t>
+          <t xml:space="preserve">全社 6.41 倍 / 補助 7.49 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 倍 / 補助 4.86 倍 / ベース 5.4 倍</t>
+          <t xml:space="preserve">全社 8.12 倍 / 補助 10.16 倍 / ベース 5.4 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.33 倍 / 補助 6.48 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 10.32 倍 / 補助 13.64 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5497,32 +5565,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.36 pt</t>
+          <t xml:space="preserve">差 3.05 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.86 pt</t>
+          <t xml:space="preserve">差 3.16 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.4 pt</t>
+          <t xml:space="preserve">差 3.24 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.86 pt</t>
+          <t xml:space="preserve">差 4.36 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.61 pt</t>
+          <t xml:space="preserve">差 5.84 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.2 pt</t>
+          <t xml:space="preserve">差 7.21 pt</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5751,17 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 210 %</t>
+          <t xml:space="preserve">寄与率 77.08 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 153.85 %</t>
+          <t xml:space="preserve">寄与率 84.09 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 153.85 %</t>
+          <t xml:space="preserve">寄与率 84.09 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -5718,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5960,11 +6028,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5985,11 +6053,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6010,11 +6078,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6035,11 +6103,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6060,7 +6128,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6085,11 +6153,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6110,11 +6178,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6135,82 +6203,74 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D17" s="2">
+        <v>5.116959064327475</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>5.409356725146197</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D19" s="2">
-        <v>5.116959064327475</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E19" s="2">
-        <v>5.701754385964919</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6218,37 +6278,37 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E20" s="2">
-        <v>1.6653345369377348e-14</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>2.0030662342518046</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <v>1.9325330501846927</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>2.0735994183189166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6269,11 +6329,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6281,20 +6341,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>5.409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6302,20 +6362,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>5.701754385964919</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.257246376811585</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6323,41 +6383,45 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>4.076086956521719</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E25" s="2">
-        <v>4.438405797101453</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.013457556935819737</v>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.984645846924027</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6365,45 +6429,41 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>1.9139457023717443</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E27" s="2">
-        <v>2.0553459914763095</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>4.083333333333339</v>
+        <v>22</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6411,20 +6471,20 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>3.9166666666666683</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2">
-        <v>4.250000000000009</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6432,20 +6492,20 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>22</v>
+        <v>1.5</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6453,20 +6513,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>6.257246376811586</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6474,20 +6534,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>6.076086956521719</v>
+        <v>0.5</v>
       </c>
       <c r="E32" s="2">
-        <v>6.438405797101453</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>1.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6495,20 +6555,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0.5</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6516,41 +6576,45 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <v>0.5</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E34" s="2">
-        <v>0.5134575569358197</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>7.000000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D35" s="2">
-        <v>5</v>
-      </c>
-      <c r="E35" s="2">
-        <v>10</v>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>2.484645846924027</v>
+        <v>4</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6558,45 +6622,41 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>2.4139457023717443</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>2.5553459914763095</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>4.5</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D37" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E37" s="2">
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6604,20 +6664,20 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E38" s="2">
-        <v>8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>4.583333333333338</v>
+        <v>10.928571428571427</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6625,20 +6685,20 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>4.416666666666668</v>
+        <v>8.928571428571427</v>
       </c>
       <c r="E39" s="2">
-        <v>4.750000000000009</v>
+        <v>11.928571428571427</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>11</v>
+        <v>5.380116959064325</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6646,124 +6706,57 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <v>8.5</v>
+        <v>4.263157894736836</v>
       </c>
       <c r="E40" s="2">
-        <v>13.5</v>
+        <v>6.555555555555557</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業投資額</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>10.928571428571427</v>
+        <v>23</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D41" s="2">
-        <v>8.928571428571427</v>
-      </c>
-      <c r="E41" s="2">
-        <v>11.928571428571427</v>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>5.380116959064325</v>
+        <v>7.66</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D42" s="2">
-        <v>4.263157894736836</v>
-      </c>
-      <c r="E42" s="2">
-        <v>6.555555555555557</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
-        </is>
-      </c>
-      <c r="B43" s="2">
-        <v>10</v>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助事業投資額</t>
-        </is>
-      </c>
-      <c r="B44" s="2">
-        <v>23</v>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">申請補助金額</t>
-        </is>
-      </c>
-      <c r="B45" s="2">
-        <v>7.66</v>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6775,7 +6768,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -7510,11 +7503,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>1.8</v>
+        <v>90</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -7525,11 +7518,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -7540,11 +7533,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>2</v>
+        <v>23.04</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7555,11 +7548,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>23.04</v>
+        <v>6.78</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7570,11 +7563,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>6.78</v>
+        <v>5.19</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7585,11 +7578,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>5.19</v>
+        <v>0.36</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7600,11 +7593,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:project:2023:P2-14</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>0.36</v>
+        <v>1.35</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7615,11 +7608,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:project:2023:P2-4</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>76</v>
+        <v>0.45</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7630,11 +7623,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>1.9</v>
+        <v>76</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7735,11 +7728,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2024:P2-14</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>80</v>
+        <v>1.43</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7750,11 +7743,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2024:P2-4</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>2</v>
+        <v>0.47</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7765,11 +7758,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7780,11 +7773,11 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
@@ -7795,11 +7788,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>25.6</v>
+        <v>2</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -7810,11 +7803,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>7.3</v>
+        <v>25.6</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7825,11 +7818,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7840,11 +7833,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7855,11 +7848,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>132</v>
+        <v>0.4</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7870,11 +7863,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2025:P2-14</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>19</v>
+        <v>1.5</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7885,11 +7878,11 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2025:P2-4</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -7900,11 +7893,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7915,11 +7908,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7930,11 +7923,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7945,11 +7938,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7960,11 +7953,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7975,11 +7968,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7990,11 +7983,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -8005,11 +7998,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8020,11 +8013,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8035,11 +8028,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8050,11 +8043,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8065,11 +8058,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8080,11 +8073,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8095,11 +8088,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8110,11 +8103,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8125,11 +8118,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8140,11 +8133,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8155,11 +8148,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8170,11 +8163,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8185,11 +8178,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8200,11 +8193,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8215,11 +8208,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8230,11 +8223,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8245,11 +8238,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8260,11 +8253,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8275,11 +8268,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8290,11 +8283,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8305,11 +8298,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8320,11 +8313,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8335,11 +8328,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8350,11 +8343,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8365,11 +8358,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8380,11 +8373,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8395,11 +8388,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8410,11 +8403,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8425,11 +8418,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8440,11 +8433,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8455,11 +8448,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8470,11 +8463,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8485,11 +8478,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8500,11 +8493,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8515,11 +8508,11 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8530,11 +8523,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8545,11 +8538,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8560,11 +8553,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8575,11 +8568,11 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8590,11 +8583,11 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8605,11 +8598,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8620,11 +8613,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8635,11 +8628,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8650,11 +8643,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8665,11 +8658,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8680,11 +8673,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8695,11 +8688,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8710,26 +8703,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8740,11 +8733,11 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8755,41 +8748,41 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8800,41 +8793,41 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.005</v>
+        <v>100</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8845,41 +8838,41 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.0051345755693581975</v>
+        <v>0</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.005</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8890,71 +8883,71 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8965,26 +8958,26 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.04416666666666668</v>
+        <v>1</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -8995,11 +8988,11 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04750000000000009</v>
+        <v>-0.5</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -9010,11 +9003,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.03916666666666668</v>
+        <v>0.5</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9025,11 +9018,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.04250000000000009</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9040,11 +9033,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>-0.5</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -9055,11 +9048,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.5</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -9070,26 +9063,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -9100,71 +9093,71 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.08</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -9175,26 +9168,26 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.025553459914763096</v>
+        <v>0</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.019139457023717443</v>
+        <v>0.08</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
@@ -9205,11 +9198,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -9220,26 +9213,26 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.3</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -9250,11 +9243,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.06076086956521719</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -9265,26 +9258,26 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.06438405797101453</v>
+        <v>0</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.040760869565217184</v>
+        <v>0.3</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9295,11 +9288,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -9310,41 +9303,41 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9355,22 +9348,22 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.11928571428571427</v>
+        <v>0</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B173" s="2">
@@ -9385,11 +9378,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>1</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9400,131 +9393,131 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9535,41 +9528,41 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.08</v>
+        <v>-0.5</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9580,11 +9573,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.5</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9595,26 +9588,26 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.05701754385964919</v>
+        <v>0</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9625,11 +9618,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.3</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9640,11 +9633,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>-0.5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9655,11 +9648,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9670,26 +9663,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9700,11 +9693,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.04263157894736836</v>
+        <v>0.5</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9715,26 +9708,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.06555555555555558</v>
+        <v>0</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.051169590643274754</v>
+        <v>1</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9745,11 +9738,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9760,11 +9753,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.05</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9775,11 +9768,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.1</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9790,11 +9783,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9805,11 +9798,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9820,26 +9813,26 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.3</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9850,11 +9843,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.15</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9865,26 +9858,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.3</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9895,11 +9888,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.15</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9910,41 +9903,41 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9955,41 +9948,41 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>50</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -10000,11 +9993,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>5</v>
+        <v>0.135</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10015,11 +10008,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -10030,11 +10023,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.3</v>
+        <v>50</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -10045,11 +10038,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10060,11 +10053,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10075,11 +10068,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10090,11 +10083,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0.005</v>
+        <v>23</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10105,26 +10098,26 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.68</v>
+        <v>0.2</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10135,11 +10128,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.95</v>
+        <v>0.005</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10150,7 +10143,7 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B225" s="2">
@@ -10165,11 +10158,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.68</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -10180,11 +10173,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.95</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10195,26 +10188,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.9</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10225,11 +10218,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.045</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10240,11 +10233,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.04</v>
+        <v>-0.005</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10255,11 +10248,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.9</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10270,11 +10263,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.045</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10285,11 +10278,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10300,11 +10293,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10315,11 +10308,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10330,26 +10323,26 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10360,11 +10353,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.25</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10375,26 +10368,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10405,11 +10398,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10420,11 +10413,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.95</v>
+        <v>0.015</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10435,26 +10428,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10465,11 +10458,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.95</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10480,41 +10473,41 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.9</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
@@ -10525,11 +10518,11 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.05</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10540,26 +10533,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.07</v>
+        <v>0.9</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10570,11 +10563,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10585,11 +10578,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.005</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10600,11 +10593,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.22</v>
+        <v>0.07</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10615,11 +10608,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10630,26 +10623,26 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10660,11 +10653,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>7.66</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10675,26 +10668,26 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7</v>
+        <v>0.11</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10698,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>3.5</v>
+        <v>7.66</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10713,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10735,11 +10728,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10750,11 +10743,11 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>252.69</v>
+        <v>3.5</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10765,11 +10758,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>82.4</v>
+        <v>35</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10780,11 +10773,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10788,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>7</v>
+        <v>252.69</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10803,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>3.74</v>
+        <v>82.4</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10818,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>2.85</v>
+        <v>10</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10840,11 +10833,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10848,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>15</v>
+        <v>3.74</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10863,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>35</v>
+        <v>2.85</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10885,11 +10878,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10893,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10908,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10930,11 +10923,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10945,11 +10938,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10960,26 +10953,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10990,11 +10983,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11005,26 +10998,26 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>136.84</v>
+        <v>0</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>74.8</v>
+        <v>35</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11035,11 +11028,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11050,11 +11043,11 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>60</v>
+        <v>136.84</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
@@ -11065,11 +11058,11 @@
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>33.43</v>
+        <v>74.8</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11073,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>18.78</v>
+        <v>95</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11088,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11110,13 +11103,58 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>350</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B289" s="2">
+      <c r="B292" s="2">
         <v>213</v>
       </c>
-      <c r="C289" s="0" t="inlineStr">
+      <c r="C292" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11144,7 +11182,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MC40NSwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MS4zNSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAuNDcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjEuNDMsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MS41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -6768,7 +6768,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10038,11 +10038,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10053,11 +10053,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10068,11 +10068,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.3</v>
+        <v>23</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10083,11 +10083,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>23</v>
+        <v>0.2</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10098,11 +10098,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>23</v>
+        <v>0.005</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10113,26 +10113,26 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.005</v>
+        <v>0.68</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10143,41 +10143,41 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.95</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10188,26 +10188,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.045833333333333386</v>
+        <v>-0.005</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10218,11 +10218,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.9</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10233,11 +10233,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>-0.005</v>
+        <v>0.045</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10248,11 +10248,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10263,11 +10263,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.045</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10278,11 +10278,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.04</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10293,11 +10293,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.004</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10308,11 +10308,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10323,11 +10323,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.004</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10338,26 +10338,26 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.06257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10368,26 +10368,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.015</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10398,11 +10398,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.25</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10413,11 +10413,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.015</v>
+        <v>0.68</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10428,11 +10428,11 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.95</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
@@ -10443,26 +10443,26 @@
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10473,26 +10473,26 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
@@ -10503,26 +10503,26 @@
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10533,26 +10533,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.9</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10563,11 +10563,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.07</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10578,11 +10578,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10593,11 +10593,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.07</v>
+        <v>0.005</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10608,11 +10608,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.22</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10623,11 +10623,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.005</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10638,26 +10638,26 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.11</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10668,26 +10668,26 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>0.11</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10698,11 +10698,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>7.66</v>
+        <v>3.5</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10713,11 +10713,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10728,11 +10728,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10743,11 +10743,11 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>3.5</v>
+        <v>252.69</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10758,11 +10758,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>35</v>
+        <v>82.4</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10773,11 +10773,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10788,11 +10788,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>252.69</v>
+        <v>7</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10803,11 +10803,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>82.4</v>
+        <v>3.74</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10818,11 +10818,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>10</v>
+        <v>2.85</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10833,11 +10833,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10848,11 +10848,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>3.74</v>
+        <v>15</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10863,11 +10863,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>2.85</v>
+        <v>35</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10878,11 +10878,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10893,11 +10893,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10908,11 +10908,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10923,11 +10923,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10938,11 +10938,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10953,26 +10953,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10983,11 +10983,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -10998,26 +10998,26 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>0</v>
+        <v>136.84</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>35</v>
+        <v>74.8</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11028,11 +11028,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11043,11 +11043,11 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>136.84</v>
+        <v>60</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
@@ -11058,11 +11058,11 @@
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>74.8</v>
+        <v>33.43</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11073,11 +11073,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>95</v>
+        <v>18.78</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11088,11 +11088,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11103,58 +11103,13 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B289" s="2">
-        <v>33.43</v>
+        <v>213</v>
       </c>
       <c r="C289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B290" s="2">
-        <v>18.78</v>
-      </c>
-      <c r="C290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B291" s="2">
-        <v>350</v>
-      </c>
-      <c r="C291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B292" s="2">
-        <v>213</v>
-      </c>
-      <c r="C292" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11182,7 +11137,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MC40NSwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MS4zNSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAuNDcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjEuNDMsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MS41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MC40NSwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MS4zNSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAuNDcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjEuNDMsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MS41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>23.144831937435285</v>
+        <v>23.15564454895256</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.65</v>
+        <v>19.660000000000004</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.5274151436031</v>
+        <v>256.6579634464752</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>50.949999999999996</v>
       </c>
       <c r="J9" s="2">
-        <v>56.300000000000004</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="10">
@@ -1786,7 +1786,7 @@
         <v>24.929999999999993</v>
       </c>
       <c r="J18" s="4">
-        <v>32.62000000000002</v>
+        <v>32.630000000000024</v>
       </c>
     </row>
     <row r="19">
@@ -1820,7 +1820,7 @@
         <v>10.841015828839797</v>
       </c>
       <c r="J19" s="2">
-        <v>12.246583571106779</v>
+        <v>12.250337888571867</v>
       </c>
     </row>
     <row r="20">
@@ -1854,7 +1854,7 @@
         <v>23.009999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>30.53</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="21">
@@ -1888,7 +1888,7 @@
         <v>23.009999999999998</v>
       </c>
       <c r="J21" s="2">
-        <v>30.53</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="22">
@@ -1922,7 +1922,7 @@
         <v>16.1</v>
       </c>
       <c r="J22" s="2">
-        <v>21.37</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="23">
@@ -2058,7 +2058,7 @@
         <v>49.63999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>59.36000000000002</v>
+        <v>59.370000000000026</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         <v>18.75598086124399</v>
       </c>
       <c r="J27" s="2">
-        <v>19.580983078162827</v>
+        <v>19.60112812248194</v>
       </c>
     </row>
     <row r="28">
@@ -2128,7 +2128,7 @@
         <v>21.586362845712298</v>
       </c>
       <c r="J28" s="2">
-        <v>22.285628472743664</v>
+        <v>22.289382790208748</v>
       </c>
     </row>
     <row r="29">
@@ -2370,7 +2370,7 @@
         <v>0.17117241379310344</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19655629139072855</v>
+        <v>0.19658940397351002</v>
       </c>
     </row>
     <row r="36">
@@ -2404,7 +2404,7 @@
         <v>28.429999999999993</v>
       </c>
       <c r="J36" s="4">
-        <v>36.12000000000002</v>
+        <v>36.130000000000024</v>
       </c>
     </row>
     <row r="37">
@@ -2438,7 +2438,7 @@
         <v>12.363019655592275</v>
       </c>
       <c r="J37" s="2">
-        <v>13.560594683886476</v>
+        <v>13.564349001351564</v>
       </c>
     </row>
     <row r="38">
@@ -2474,7 +2474,7 @@
         <v>26.749888542131007</v>
       </c>
       <c r="J38" s="2">
-        <v>27.04889201547671</v>
+        <v>27.08406612733041</v>
       </c>
     </row>
   </sheetData>
@@ -2814,7 +2814,7 @@
         <v>18.329999999999984</v>
       </c>
       <c r="J8" s="4">
-        <v>25.280000000000005</v>
+        <v>25.290000000000006</v>
       </c>
     </row>
     <row r="9">
@@ -2848,7 +2848,7 @@
         <v>13.13884309368503</v>
       </c>
       <c r="J9" s="2">
-        <v>14.84962406015038</v>
+        <v>14.855498120300755</v>
       </c>
     </row>
     <row r="10">
@@ -3052,7 +3052,7 @@
         <v>29.799999999999983</v>
       </c>
       <c r="J15" s="4">
-        <v>37.96</v>
+        <v>37.970000000000006</v>
       </c>
     </row>
     <row r="16">
@@ -3088,7 +3088,7 @@
         <v>27.459366980324983</v>
       </c>
       <c r="J16" s="2">
-        <v>27.382550335570556</v>
+        <v>27.416107382550425</v>
       </c>
     </row>
     <row r="17">
@@ -3330,7 +3330,7 @@
         <v>0.23464566929133845</v>
       </c>
       <c r="J23" s="2">
-        <v>0.28977099236641224</v>
+        <v>0.28984732824427484</v>
       </c>
     </row>
     <row r="24">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.14 % / 補助 18.66 % / ベース 25.53 %</t>
+          <t xml:space="preserve">全社 21.13 % / 補助 18.65 % / ベース 25.53 %</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.25 % / 補助 14.85 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 12.25 % / 補助 14.86 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.56 % / 補助 16.02 % / ベース 9.2 %</t>
+          <t xml:space="preserve">全社 13.56 % / 補助 16.03 % / ベース 9.2 %</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.94 % / 補助 11 % / ベース 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 11 % / ベース 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.15 % / 補助 28.13 % / ベース 58.69 %</t>
+          <t xml:space="preserve">全社 39.14 % / 補助 28.13 % / ベース 58.69 %</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.32 倍 / 補助 13.64 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 10.32 倍 / 補助 13.65 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.21 pt</t>
+          <t xml:space="preserve">差 7.22 pt</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.38 %</t>
+          <t xml:space="preserve">寄与率 90.39 %</t>
         </is>
       </c>
     </row>
@@ -6652,11 +6652,11 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6664,20 +6664,20 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>13.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>10.928571428571427</v>
+        <v>0.5</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>8.928571428571427</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>11.928571428571427</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -9382,11 +9382,11 @@
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.08928571428571427</v>
+        <v>0</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.01</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -9982,11 +9982,11 @@
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.08499999999999999</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.135</v>
+        <v>0.03</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.005</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.11</v>
+        <v>0.015</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MC40NSwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MS4zNSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAuNDcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjEuNDMsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MS41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAzNjEyODY2NDI4MzI2MzQsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDUyMTkyNTU2MjIwNDgzMTEsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMjg4MzM0MzcyNjkyMDM1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDkxNzU2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDM3MjA1NDgyMzk3MjA1MDUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwib3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAsMC4wM10sIm90aGVyU2dhUmF0ZUVuZCI6WzAsMC4wMV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAuNDUsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEuMzUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLjQ3LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxLjQzLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjEuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDM2MTI4NjY0MjgzMjYzNCwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIxOTI1NTYyMjA0ODMxMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjAyODgzMzQzNzI2OTIwMzUsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wOTE3NTYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzcyMDU0ODIzOTcyMDUwNSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>23.15564454895256</v>
+        <v>24.42435037017734</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.660000000000004</v>
+        <v>19.650000000000013</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.027727322388921</v>
+        <v>7.006310447953612</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.700000000000001</v>
+        <v>2.380000000000001</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.6579634464752</v>
+        <v>256.5274151436033</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>173.03</v>
       </c>
       <c r="H3" s="4">
-        <v>199.47</v>
+        <v>199.45999999999998</v>
       </c>
       <c r="I3" s="4">
         <v>229.95999999999998</v>
@@ -1304,10 +1304,10 @@
         <v>4.879379318705279</v>
       </c>
       <c r="H4" s="2">
-        <v>15.28058718141363</v>
+        <v>15.274807836791293</v>
       </c>
       <c r="I4" s="2">
-        <v>15.285506592470032</v>
+        <v>15.291286473478394</v>
       </c>
       <c r="J4" s="2">
         <v>15.828839798225802</v>
@@ -1338,13 +1338,13 @@
         <v>117.65</v>
       </c>
       <c r="H5" s="2">
-        <v>134.35</v>
+        <v>134.36</v>
       </c>
       <c r="I5" s="2">
         <v>154.07999999999998</v>
       </c>
       <c r="J5" s="2">
-        <v>177.44</v>
+        <v>177.45</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>55.379999999999995</v>
       </c>
       <c r="H7" s="4">
-        <v>65.12</v>
+        <v>65.09999999999997</v>
       </c>
       <c r="I7" s="4">
         <v>75.88</v>
       </c>
       <c r="J7" s="4">
-        <v>88.92000000000002</v>
+        <v>88.91000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>32.00601051840721</v>
       </c>
       <c r="H8" s="2">
-        <v>32.64651326013937</v>
+        <v>32.63812293191616</v>
       </c>
       <c r="I8" s="2">
         <v>32.99704296399374</v>
       </c>
       <c r="J8" s="2">
-        <v>33.38339089953447</v>
+        <v>33.37963658206939</v>
       </c>
     </row>
     <row r="9">
@@ -1477,10 +1477,10 @@
         <v>46.19</v>
       </c>
       <c r="I9" s="2">
-        <v>50.949999999999996</v>
+        <v>50.8</v>
       </c>
       <c r="J9" s="2">
-        <v>56.29</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="10">
@@ -1613,10 +1613,10 @@
         <v>18.16</v>
       </c>
       <c r="I13" s="2">
-        <v>19.95</v>
+        <v>19.8</v>
       </c>
       <c r="J13" s="2">
-        <v>21.92</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="14">
@@ -1644,13 +1644,13 @@
         <v>16.16</v>
       </c>
       <c r="H14" s="2">
-        <v>17.740000000000002</v>
+        <v>17.62</v>
       </c>
       <c r="I14" s="2">
-        <v>19.5</v>
+        <v>19.21</v>
       </c>
       <c r="J14" s="2">
-        <v>21.45</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9299999999999999</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="J15" s="2">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1780,13 +1780,13 @@
         <v>12.959999999999994</v>
       </c>
       <c r="H18" s="4">
-        <v>18.930000000000007</v>
+        <v>18.909999999999968</v>
       </c>
       <c r="I18" s="4">
-        <v>24.929999999999993</v>
+        <v>25.08</v>
       </c>
       <c r="J18" s="4">
-        <v>32.630000000000024</v>
+        <v>32.94000000000004</v>
       </c>
     </row>
     <row r="19">
@@ -1814,13 +1814,13 @@
         <v>7.490030630526495</v>
       </c>
       <c r="H19" s="2">
-        <v>9.490148894570616</v>
+        <v>9.480597613556588</v>
       </c>
       <c r="I19" s="2">
-        <v>10.841015828839797</v>
+        <v>10.906244564272049</v>
       </c>
       <c r="J19" s="2">
-        <v>12.250337888571867</v>
+        <v>12.366721729989502</v>
       </c>
     </row>
     <row r="20">
@@ -1848,13 +1848,13 @@
         <v>12.56</v>
       </c>
       <c r="H20" s="4">
-        <v>17.16</v>
+        <v>17.27</v>
       </c>
       <c r="I20" s="4">
-        <v>23.009999999999998</v>
+        <v>23.32</v>
       </c>
       <c r="J20" s="4">
-        <v>30.54</v>
+        <v>31.04</v>
       </c>
     </row>
     <row r="21">
@@ -1882,13 +1882,13 @@
         <v>12.56</v>
       </c>
       <c r="H21" s="2">
-        <v>17.16</v>
+        <v>17.27</v>
       </c>
       <c r="I21" s="2">
-        <v>23.009999999999998</v>
+        <v>23.32</v>
       </c>
       <c r="J21" s="2">
-        <v>30.54</v>
+        <v>31.04</v>
       </c>
     </row>
     <row r="22">
@@ -1916,13 +1916,13 @@
         <v>8.8</v>
       </c>
       <c r="H22" s="2">
-        <v>12.01</v>
+        <v>12.09</v>
       </c>
       <c r="I22" s="2">
-        <v>16.1</v>
+        <v>16.32</v>
       </c>
       <c r="J22" s="2">
-        <v>21.38</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="23">
@@ -1953,10 +1953,10 @@
         <v>18.16</v>
       </c>
       <c r="I23" s="2">
-        <v>19.95</v>
+        <v>19.8</v>
       </c>
       <c r="J23" s="2">
-        <v>21.92</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="24">
@@ -2052,13 +2052,13 @@
         <v>34.60999999999999</v>
       </c>
       <c r="H26" s="4">
-        <v>41.800000000000004</v>
+        <v>41.779999999999966</v>
       </c>
       <c r="I26" s="4">
         <v>49.63999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>59.370000000000026</v>
+        <v>59.36000000000004</v>
       </c>
     </row>
     <row r="27">
@@ -2088,13 +2088,13 @@
         <v>4.720121028744262</v>
       </c>
       <c r="H27" s="2">
-        <v>20.774342675527336</v>
+        <v>20.716555908696833</v>
       </c>
       <c r="I27" s="2">
-        <v>18.75598086124399</v>
+        <v>18.812829104834925</v>
       </c>
       <c r="J27" s="2">
-        <v>19.60112812248194</v>
+        <v>19.580983078162873</v>
       </c>
     </row>
     <row r="28">
@@ -2122,13 +2122,13 @@
         <v>20.002311737848924</v>
       </c>
       <c r="H28" s="2">
-        <v>20.955532160224596</v>
+        <v>20.94655570039104</v>
       </c>
       <c r="I28" s="2">
         <v>21.586362845712298</v>
       </c>
       <c r="J28" s="2">
-        <v>22.289382790208748</v>
+        <v>22.28562847274367</v>
       </c>
     </row>
     <row r="29">
@@ -2156,13 +2156,13 @@
         <v>262</v>
       </c>
       <c r="H29" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I29" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J29" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
@@ -2224,13 +2224,13 @@
         <v>0.0649236641221374</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06652014652014653</v>
+        <v>0.06676470588235295</v>
       </c>
       <c r="I31" s="2">
-        <v>0.06999999999999999</v>
+        <v>0.07021276595744681</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07380471380471382</v>
+        <v>0.07372013651877134</v>
       </c>
     </row>
     <row r="32">
@@ -2260,13 +2260,13 @@
         <v>2.6396697539436964</v>
       </c>
       <c r="H32" s="2">
-        <v>2.4590146283268055</v>
+        <v>2.8357021821074246</v>
       </c>
       <c r="I32" s="2">
-        <v>5.231277533039624</v>
+        <v>5.164495266660407</v>
       </c>
       <c r="J32" s="2">
-        <v>5.43530543530546</v>
+        <v>4.995345950977348</v>
       </c>
     </row>
     <row r="33">
@@ -2364,13 +2364,13 @@
         <v>0.12962546816479398</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15035971223021585</v>
+        <v>0.15083032490974718</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17117241379310344</v>
+        <v>0.17296167247386757</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19658940397351002</v>
+        <v>0.19919463087248337</v>
       </c>
     </row>
     <row r="36">
@@ -2398,13 +2398,13 @@
         <v>16.459999999999994</v>
       </c>
       <c r="H36" s="4">
-        <v>22.430000000000007</v>
+        <v>22.409999999999968</v>
       </c>
       <c r="I36" s="4">
-        <v>28.429999999999993</v>
+        <v>28.58</v>
       </c>
       <c r="J36" s="4">
-        <v>36.130000000000024</v>
+        <v>36.44000000000004</v>
       </c>
     </row>
     <row r="37">
@@ -2432,13 +2432,13 @@
         <v>9.512801248338434</v>
       </c>
       <c r="H37" s="2">
-        <v>11.24479871659899</v>
+        <v>11.235335405595091</v>
       </c>
       <c r="I37" s="2">
-        <v>12.363019655592275</v>
+        <v>12.428248391024526</v>
       </c>
       <c r="J37" s="2">
-        <v>13.564349001351564</v>
+        <v>13.6807328427692</v>
       </c>
     </row>
     <row r="38">
@@ -2468,13 +2468,13 @@
         <v>2.7465667915105296</v>
       </c>
       <c r="H38" s="2">
-        <v>36.26974483596608</v>
+        <v>36.14823815309829</v>
       </c>
       <c r="I38" s="2">
-        <v>26.749888542131007</v>
+        <v>27.532351628737352</v>
       </c>
       <c r="J38" s="2">
-        <v>27.08406612733041</v>
+        <v>27.5017494751576</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2636,7 @@
         <v>93.7</v>
       </c>
       <c r="H3" s="4">
-        <v>114.34</v>
+        <v>114.33</v>
       </c>
       <c r="I3" s="4">
         <v>139.51</v>
@@ -2672,10 +2672,10 @@
         <v>5.41118236022049</v>
       </c>
       <c r="H4" s="2">
-        <v>22.027748132337255</v>
+        <v>22.017075773745987</v>
       </c>
       <c r="I4" s="2">
-        <v>22.01329368549938</v>
+        <v>22.02396571328609</v>
       </c>
       <c r="J4" s="2">
         <v>22.027094831911697</v>
@@ -2706,7 +2706,7 @@
         <v>54.1524591111368</v>
       </c>
       <c r="H5" s="2">
-        <v>57.321903043064125</v>
+        <v>57.319763361074905</v>
       </c>
       <c r="I5" s="2">
         <v>60.66707253435381</v>
@@ -2740,13 +2740,13 @@
         <v>29.990000000000002</v>
       </c>
       <c r="H6" s="4">
-        <v>37.17</v>
+        <v>37.14999999999999</v>
       </c>
       <c r="I6" s="4">
         <v>46.03999999999999</v>
       </c>
       <c r="J6" s="4">
-        <v>57.040000000000006</v>
+        <v>57.030000000000015</v>
       </c>
     </row>
     <row r="7">
@@ -2774,13 +2774,13 @@
         <v>32.00640341515475</v>
       </c>
       <c r="H7" s="2">
-        <v>32.50830855343712</v>
+        <v>32.49365870725093</v>
       </c>
       <c r="I7" s="2">
         <v>33.001218550641525</v>
       </c>
       <c r="J7" s="2">
-        <v>33.505639097744364</v>
+        <v>33.499765037593995</v>
       </c>
     </row>
     <row r="8">
@@ -2808,13 +2808,13 @@
         <v>8.410000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>12.980000000000002</v>
+        <v>12.959999999999992</v>
       </c>
       <c r="I8" s="4">
-        <v>18.329999999999984</v>
+        <v>18.47999999999999</v>
       </c>
       <c r="J8" s="4">
-        <v>25.290000000000006</v>
+        <v>25.600000000000016</v>
       </c>
     </row>
     <row r="9">
@@ -2842,13 +2842,13 @@
         <v>8.975453575240131</v>
       </c>
       <c r="H9" s="2">
-        <v>11.352107748819313</v>
+        <v>11.3356074521123</v>
       </c>
       <c r="I9" s="2">
-        <v>13.13884309368503</v>
+        <v>13.246362267937775</v>
       </c>
       <c r="J9" s="2">
-        <v>14.855498120300755</v>
+        <v>15.037593984962413</v>
       </c>
     </row>
     <row r="10">
@@ -2879,10 +2879,10 @@
         <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.95</v>
+        <v>8.8</v>
       </c>
       <c r="J10" s="2">
-        <v>10.13</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="11">
@@ -3046,13 +3046,13 @@
         <v>18.310000000000002</v>
       </c>
       <c r="H15" s="4">
-        <v>23.380000000000003</v>
+        <v>23.359999999999992</v>
       </c>
       <c r="I15" s="4">
-        <v>29.799999999999983</v>
+        <v>29.79999999999999</v>
       </c>
       <c r="J15" s="4">
-        <v>37.970000000000006</v>
+        <v>37.960000000000015</v>
       </c>
     </row>
     <row r="16">
@@ -3082,13 +3082,13 @@
         <v>5.229885057471284</v>
       </c>
       <c r="H16" s="2">
-        <v>27.689787001638443</v>
+        <v>27.580557072637845</v>
       </c>
       <c r="I16" s="2">
-        <v>27.459366980324983</v>
+        <v>27.568493150684926</v>
       </c>
       <c r="J16" s="2">
-        <v>27.416107382550425</v>
+        <v>27.382550335570556</v>
       </c>
     </row>
     <row r="17">
@@ -3116,13 +3116,13 @@
         <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2">
+        <v>122</v>
+      </c>
+      <c r="J17" s="2">
         <v>125</v>
-      </c>
-      <c r="J17" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -3184,13 +3184,13 @@
         <v>0.06405172413793103</v>
       </c>
       <c r="H19" s="2">
-        <v>0.06583333333333334</v>
+        <v>0.06638655462184874</v>
       </c>
       <c r="I19" s="2">
-        <v>0.0716</v>
+        <v>0.07213114754098361</v>
       </c>
       <c r="J19" s="2">
-        <v>0.07852713178294574</v>
+        <v>0.07848000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3220,13 +3220,13 @@
         <v>2.7419274466812693</v>
       </c>
       <c r="H20" s="2">
-        <v>2.7815163750561034</v>
+        <v>3.645226596695217</v>
       </c>
       <c r="I20" s="2">
-        <v>8.759493670886066</v>
+        <v>8.653247561734801</v>
       </c>
       <c r="J20" s="2">
-        <v>9.674765059980084</v>
+        <v>8.801818181818177</v>
       </c>
     </row>
     <row r="21">
@@ -3324,13 +3324,13 @@
         <v>0.15516949152542375</v>
       </c>
       <c r="H23" s="2">
-        <v>0.1916393442622951</v>
+        <v>0.19305785123966937</v>
       </c>
       <c r="I23" s="2">
-        <v>0.23464566929133845</v>
+        <v>0.2403225806451612</v>
       </c>
       <c r="J23" s="2">
-        <v>0.28984732824427484</v>
+        <v>0.29889763779527573</v>
       </c>
     </row>
     <row r="24">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 15.27 % / 補助 22.02 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / ベース 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.02 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.35 % / 補助 67.49 % / ベース 67.17 %</t>
+          <t xml:space="preserve">全社 67.36 % / 補助 67.51 % / ベース 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.62 % / 補助 66.49 % / ベース 66.83 %</t>
+          <t xml:space="preserve">全社 66.62 % / 補助 66.5 % / ベース 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.65 % / 補助 32.51 % / ベース 32.83 %</t>
+          <t xml:space="preserve">全社 32.64 % / 補助 32.49 % / ベース 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.38 % / 補助 33.51 % / ベース 33.17 %</t>
+          <t xml:space="preserve">全社 33.38 % / 補助 33.5 % / ベース 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.16 % / 補助 19.86 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.09 % / 補助 19.75 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.13 % / 補助 18.65 % / ベース 25.53 %</t>
+          <t xml:space="preserve">全社 21.01 % / 補助 18.46 % / ベース 25.53 %</t>
         </is>
       </c>
     </row>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.49 % / 補助 11.35 % / ベース 6.99 %</t>
+          <t xml:space="preserve">全社 9.48 % / 補助 11.34 % / ベース 6.99 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.84 % / 補助 13.14 % / ベース 7.3 %</t>
+          <t xml:space="preserve">全社 10.91 % / 補助 13.25 % / ベース 7.3 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.25 % / 補助 14.86 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 12.37 % / 補助 15.04 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.24 % / 補助 13.1 % / ベース 8.75 %</t>
+          <t xml:space="preserve">全社 11.24 % / 補助 13.08 % / ベース 8.75 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.36 % / 補助 14.57 % / ベース 8.96 %</t>
+          <t xml:space="preserve">全社 12.43 % / 補助 14.68 % / ベース 8.96 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.56 % / 補助 16.03 % / ベース 9.2 %</t>
+          <t xml:space="preserve">全社 13.68 % / 補助 16.21 % / ベース 9.2 %</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.68 % / 補助 6.42 % / ベース 12.16 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 6.31 % / ベース 12.16 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / ベース 12.27 %</t>
+          <t xml:space="preserve">全社 8.11 % / 補助 5.76 % / ベース 12.27 %</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.22 % / 補助 6.79 % / ベース 12.98 %</t>
+          <t xml:space="preserve">全社 9.16 % / 補助 6.68 % / ベース 12.98 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.73 % / 補助 6.27 % / ベース 13.07 %</t>
+          <t xml:space="preserve">全社 8.6 % / 補助 6.09 % / ベース 13.07 %</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.079 億円/人 / ベース 0.07 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.46 % / 補助 2.78 % / ベース 2.2 %</t>
+          <t xml:space="preserve">全社 2.84 % / 補助 3.65 % / ベース 2.2 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.23 % / 補助 8.76 % / ベース 2.52 %</t>
+          <t xml:space="preserve">全社 5.16 % / 補助 8.65 % / ベース 2.52 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.44 % / 補助 9.67 % / ベース 2.08 %</t>
+          <t xml:space="preserve">全社 5 % / 補助 8.8 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4526,17 +4526,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 46.34 % / 補助 35.93 % / ベース 59.55 %</t>
+          <t xml:space="preserve">全社 46.36 % / 補助 35.96 % / ベース 59.55 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.73 % / 補助 31.78 % / ベース 59.17 %</t>
+          <t xml:space="preserve">全社 42.43 % / 補助 31.28 % / ベース 59.17 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.14 % / 補助 28.13 % / ベース 58.69 %</t>
+          <t xml:space="preserve">全社 38.61 % / 補助 27.29 % / ベース 58.69 %</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4650,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">全社 0.733 億円/人 / 補助 0.961 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.807 億円/人 / 補助 1.116 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">全社 0.815 億円/人 / 補助 1.144 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.897 億円/人 / 補助 1.32 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.909 億円/人 / 補助 1.362 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.108 億円/人 / ベース 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.109 億円/人 / ベース 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.147 億円/人 / ベース 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.089 億円/人 / 補助 0.151 億円/人 / ベース 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 億円/人 / 補助 0.196 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.112 億円/人 / 補助 0.205 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.15 億円/人 / 補助 0.192 億円/人 / ベース 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / ベース 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.235 億円/人 / ベース 0.122 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.24 億円/人 / ベース 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.29 億円/人 / ベース 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.199 億円/人 / 補助 0.299 億円/人 / ベース 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4836,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / ベース 4.79 %</t>
+          <t xml:space="preserve">全社 3.82 % / 補助 2.59 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / ベース 4.58 %</t>
+          <t xml:space="preserve">全社 3.68 % / 補助 2.52 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / ベース 5 %</t>
+          <t xml:space="preserve">全社 3.9 % / 補助 2.46 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.08 pt / 補助 18.58 pt / ベース 2.52 pt</t>
+          <t xml:space="preserve">全社 11.46 pt / 補助 19.43 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.89 pt / 補助 17.85 pt / ベース 1.67 pt</t>
+          <t xml:space="preserve">全社 11.61 pt / 補助 19.5 pt / ベース 1.67 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.62 pt / 補助 18.83 pt / ベース 1.27 pt</t>
+          <t xml:space="preserve">全社 11.93 pt / 補助 19.57 pt / ベース 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -5208,17 +5208,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.41 倍 / 補助 7.49 倍 / ベース 4.97 倍</t>
+          <t xml:space="preserve">全社 6.4 倍 / 補助 7.48 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.12 倍 / 補助 10.16 倍 / ベース 5.4 倍</t>
+          <t xml:space="preserve">全社 8.17 倍 / 補助 10.24 倍 / ベース 5.4 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.32 倍 / 補助 13.65 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 10.41 倍 / 補助 13.8 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / ベース 7.31 %</t>
+          <t xml:space="preserve">補助 22.02 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.01 % / ベース 6.25 %</t>
+          <t xml:space="preserve">補助 22.02 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.32 pt</t>
+          <t xml:space="preserve">差 0.34 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.34 pt</t>
+          <t xml:space="preserve">差 -0.33 pt</t>
         </is>
       </c>
     </row>
@@ -5580,17 +5580,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.36 pt</t>
+          <t xml:space="preserve">差 4.35 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.84 pt</t>
+          <t xml:space="preserve">差 5.95 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.22 pt</t>
+          <t xml:space="preserve">差 7.4 pt</t>
         </is>
       </c>
     </row>
@@ -5642,17 +5642,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.953 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">補助 0.961 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.116 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">補助 1.144 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.32 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.362 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.079 億円/人 / ベース 0.07 億円/人</t>
+          <t xml:space="preserve">補助 0.078 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.55 %</t>
+          <t xml:space="preserve">寄与率 76.47 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.17 %</t>
+          <t xml:space="preserve">寄与率 89.47 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.39 %</t>
+          <t xml:space="preserve">寄与率 90.59 %</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率（売上実績が0の場合の開始水準）</t>
+          <t xml:space="preserve">補助事業 原価率</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5889,21 +5889,17 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D4" s="2">
+        <v>66</v>
+      </c>
+      <c r="E4" s="2">
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率（売上実績が0の場合の開始水準）</t>
+          <t xml:space="preserve">ベース事業 原価率</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -5914,15 +5910,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D5" s="2">
+        <v>66</v>
+      </c>
+      <c r="E5" s="2">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -8932,11 +8924,11 @@
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8939,7 @@
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -9502,11 +9494,11 @@
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9509,7 @@
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -11137,7 +11129,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwib3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAsMC4wM10sIm90aGVyU2dhUmF0ZUVuZCI6WzAsMC4wMV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAuNDUsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEuMzUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLjQ3LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxLjQzLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjEuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDM2MTI4NjY0MjgzMjYzNCwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIxOTI1NTYyMjA0ODMxMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjAyODgzMzQzNzI2OTIwMzUsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wOTE3NTYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzcyMDU0ODIzOTcyMDUwNSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwib3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMC42NiwwLjddLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLDAuMDNdLCJvdGhlclNnYVJhdGVFbmQiOlswLDAuMDFdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLjQ1LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjoxLjM1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MC40NywiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MS40MywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MC41LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTE0IjoxLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuNywiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MC42NiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuNywiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNDQ0MTQzOTIyNTI2NjIyLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjEzOTExMTM4MzkwMTg2LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyMDQ4OTQwODMyNzIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg1NTEwOTc4MjMxNjU4MTcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjM2NTE2NTY0MTczNzc1Niwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgzNzkyMDAzMDQ3NjM2LCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.464691482957393</v>
+        <v>15.463873591495837</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,11 +234,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>93.33000000000001</v>
+        <v>9332089.869999997</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.172559802954921</v>
+        <v>2.184711746547996</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.91350052560445</v>
+        <v>63.91256738860758</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.02271203454029</v>
+        <v>22.020887065724626</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,11 +354,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>76.54</v>
+        <v>7653023</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>24.42435037017734</v>
+        <v>25.09060099268099</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,11 +414,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.650000000000013</v>
+        <v>1964757</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.006310447953612</v>
+        <v>7.009252613618577</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,11 +474,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.380000000000001</v>
+        <v>222489.57999999996</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.5274151436033</v>
+        <v>256.4956919060052</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>5.379211308937237</v>
+        <v>5.380301885516814</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.08000000000000007</v>
+        <v>7976</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -712,167 +712,167 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-1 資産総額（億円）</t>
+          <t xml:space="preserve">1-1 資産総額（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C3" s="4">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="D3" s="4">
-        <v>156</v>
+        <v>15600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-2 うち流動資産（億円）</t>
+          <t xml:space="preserve">1-2 うち流動資産（千円）</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>67</v>
+        <v>6700000</v>
       </c>
       <c r="C4" s="2">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="D4" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-3 うち現金及び預金（億円）</t>
+          <t xml:space="preserve">1-3 うち現金及び預金（千円）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C5" s="2">
-        <v>25</v>
+        <v>2500000</v>
       </c>
       <c r="D5" s="2">
-        <v>27</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-4 うち固定資産（億円）</t>
+          <t xml:space="preserve">1-4 うち固定資産（千円）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>65</v>
+        <v>6500000</v>
       </c>
       <c r="C6" s="2">
-        <v>71</v>
+        <v>7100000</v>
       </c>
       <c r="D6" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-5 うち有形固定資産（億円）</t>
+          <t xml:space="preserve">1-5 うち有形固定資産（千円）</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>53</v>
+        <v>5300000</v>
       </c>
       <c r="C7" s="2">
-        <v>58</v>
+        <v>5800000</v>
       </c>
       <c r="D7" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-6 うち建物及び構築物（億円）</t>
+          <t xml:space="preserve">1-6 うち建物及び構築物（千円）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>1900000</v>
       </c>
       <c r="C8" s="2">
-        <v>20</v>
+        <v>2000000</v>
       </c>
       <c r="D8" s="2">
-        <v>22</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-7 うち機械装置等（億円）</t>
+          <t xml:space="preserve">1-7 うち機械装置等（千円）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C9" s="2">
-        <v>28</v>
+        <v>2800000</v>
       </c>
       <c r="D9" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-8 うち土地（億円）</t>
+          <t xml:space="preserve">1-8 うち土地（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="D10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-9 うち無形固定資産（億円）</t>
+          <t xml:space="preserve">1-9 うち無形固定資産（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C11" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="D11" s="2">
-        <v>9</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-10 うちソフトウェア（億円）</t>
+          <t xml:space="preserve">1-10 うちソフトウェア（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C12" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="D12" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-11 その他資産（自動計算）（億円）</t>
+          <t xml:space="preserve">1-11 その他資産（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -888,103 +888,103 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-12 負債及び純資産合計（自動計算）（億円）</t>
+          <t xml:space="preserve">1-12 負債及び純資産合計（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B14" s="4">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C14" s="4">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="D14" s="4">
-        <v>156</v>
+        <v>15600000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-13 負債総額（億円）</t>
+          <t xml:space="preserve">1-13 負債総額（千円）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>75</v>
+        <v>7500000</v>
       </c>
       <c r="C15" s="2">
-        <v>79</v>
+        <v>7900000</v>
       </c>
       <c r="D15" s="2">
-        <v>83</v>
+        <v>8300000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-14 うち流動負債（億円）</t>
+          <t xml:space="preserve">1-14 うち流動負債（千円）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>39</v>
+        <v>3900000</v>
       </c>
       <c r="C16" s="2">
-        <v>41</v>
+        <v>4100000</v>
       </c>
       <c r="D16" s="2">
-        <v>43</v>
+        <v>4300000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-15 うち短期借入金（億円）</t>
+          <t xml:space="preserve">1-15 うち短期借入金（千円）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="D17" s="2">
-        <v>11</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-16 うち固定負債（億円）</t>
+          <t xml:space="preserve">1-16 うち固定負債（千円）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>36</v>
+        <v>3600000</v>
       </c>
       <c r="C18" s="2">
-        <v>38</v>
+        <v>3800000</v>
       </c>
       <c r="D18" s="2">
-        <v>40</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-17 うち長期借入金（億円）</t>
+          <t xml:space="preserve">1-17 うち長期借入金（千円）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>29</v>
+        <v>2900000</v>
       </c>
       <c r="C19" s="2">
-        <v>31</v>
+        <v>3100000</v>
       </c>
       <c r="D19" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-18 その他負債（自動計算）（億円）</t>
+          <t xml:space="preserve">1-18 その他負債（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -1000,65 +1000,65 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-19 純資産総額（億円）</t>
+          <t xml:space="preserve">1-19 純資産総額（千円）</t>
         </is>
       </c>
       <c r="B21" s="4">
-        <v>57</v>
+        <v>5700000</v>
       </c>
       <c r="C21" s="4">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="D21" s="4">
-        <v>73</v>
+        <v>7300000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-20 うち株主資本（億円）</t>
+          <t xml:space="preserve">1-20 うち株主資本（千円）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>54</v>
+        <v>5400000</v>
       </c>
       <c r="C22" s="2">
-        <v>61</v>
+        <v>6100000</v>
       </c>
       <c r="D22" s="2">
-        <v>70</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-21 うち資本金（億円）</t>
+          <t xml:space="preserve">1-21 うち資本金（千円）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="D23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-22 その他純資産（自動計算）（億円）</t>
+          <t xml:space="preserve">1-22 その他純資産（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="25">
@@ -1080,17 +1080,17 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-24 新規設備投資による支出（億円）</t>
+          <t xml:space="preserve">1-24 新規設備投資による支出（千円）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C26" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="D26" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="27">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.198871650211565</v>
+        <v>1.1990551445460977</v>
       </c>
       <c r="C27" s="2">
-        <v>1.2295081967213117</v>
+        <v>1.2283939159014228</v>
       </c>
       <c r="D27" s="2">
-        <v>1.0596026490066224</v>
+        <v>1.0596026490066226</v>
       </c>
     </row>
   </sheetData>
@@ -1246,35 +1246,35 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-1 売上高（億円）</t>
+          <t xml:space="preserve">2-1 売上高（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
-        <v>136.4</v>
+        <v>13640000</v>
       </c>
       <c r="C3" s="4">
-        <v>143.2</v>
+        <v>14320000</v>
       </c>
       <c r="D3" s="4">
-        <v>150</v>
+        <v>15000000</v>
       </c>
       <c r="E3" s="4">
-        <v>157.31</v>
+        <v>15730756</v>
       </c>
       <c r="F3" s="4">
-        <v>164.98000000000002</v>
+        <v>16497607</v>
       </c>
       <c r="G3" s="4">
-        <v>173.03</v>
+        <v>17302362</v>
       </c>
       <c r="H3" s="4">
-        <v>199.45999999999998</v>
+        <v>19946039</v>
       </c>
       <c r="I3" s="4">
-        <v>229.95999999999998</v>
+        <v>22996374.97</v>
       </c>
       <c r="J3" s="4">
-        <v>266.36</v>
+        <v>26634451.869999997</v>
       </c>
     </row>
     <row r="4">
@@ -1295,124 +1295,124 @@
         <v>4.748603351955305</v>
       </c>
       <c r="E4" s="2">
-        <v>4.8733333333333295</v>
+        <v>4.871706666666675</v>
       </c>
       <c r="F4" s="2">
-        <v>4.875723094526752</v>
+        <v>4.874851532882474</v>
       </c>
       <c r="G4" s="2">
-        <v>4.879379318705279</v>
+        <v>4.878010489642537</v>
       </c>
       <c r="H4" s="2">
-        <v>15.274807836791293</v>
+        <v>15.279283834195589</v>
       </c>
       <c r="I4" s="2">
-        <v>15.291286473478394</v>
+        <v>15.292940969382428</v>
       </c>
       <c r="J4" s="2">
-        <v>15.828839798225802</v>
+        <v>15.820219076902609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-3 売上原価（億円）</t>
+          <t xml:space="preserve">2-3 売上原価（千円）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>92.75</v>
+        <v>9275200</v>
       </c>
       <c r="C5" s="2">
-        <v>97.38</v>
+        <v>9737600</v>
       </c>
       <c r="D5" s="2">
-        <v>102</v>
+        <v>10200000</v>
       </c>
       <c r="E5" s="2">
-        <v>106.97</v>
+        <v>10696914</v>
       </c>
       <c r="F5" s="2">
-        <v>112.18</v>
+        <v>11218373</v>
       </c>
       <c r="G5" s="2">
-        <v>117.65</v>
+        <v>11765605</v>
       </c>
       <c r="H5" s="2">
-        <v>134.36</v>
+        <v>13434963</v>
       </c>
       <c r="I5" s="2">
-        <v>154.07999999999998</v>
+        <v>15407469</v>
       </c>
       <c r="J5" s="2">
-        <v>177.45</v>
+        <v>17743999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-4 うち減価償却費（億円）</t>
+          <t xml:space="preserve">2-4 うち減価償却費（千円）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0.73</v>
+        <v>72600</v>
       </c>
       <c r="C6" s="2">
-        <v>0.76</v>
+        <v>76300</v>
       </c>
       <c r="D6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="G6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="H6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="I6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="J6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-5 売上総利益（億円）</t>
+          <t xml:space="preserve">2-5 売上総利益（千円）</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <v>43.650000000000006</v>
+        <v>4364800</v>
       </c>
       <c r="C7" s="4">
-        <v>45.81999999999999</v>
+        <v>4582400</v>
       </c>
       <c r="D7" s="4">
-        <v>48</v>
+        <v>4800000</v>
       </c>
       <c r="E7" s="4">
-        <v>50.34</v>
+        <v>5033842</v>
       </c>
       <c r="F7" s="4">
-        <v>52.80000000000001</v>
+        <v>5279234</v>
       </c>
       <c r="G7" s="4">
-        <v>55.379999999999995</v>
+        <v>5536757</v>
       </c>
       <c r="H7" s="4">
-        <v>65.09999999999997</v>
+        <v>6511076</v>
       </c>
       <c r="I7" s="4">
-        <v>75.88</v>
+        <v>7588905.969999999</v>
       </c>
       <c r="J7" s="4">
-        <v>88.91000000000003</v>
+        <v>8890452.869999997</v>
       </c>
     </row>
     <row r="8">
@@ -1422,371 +1422,371 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>32.00146627565983</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2">
-        <v>31.997206703910614</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2">
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>32.00050854999682</v>
+        <v>32.00000050855788</v>
       </c>
       <c r="F8" s="2">
-        <v>32.00387925809189</v>
+        <v>31.999998545243564</v>
       </c>
       <c r="G8" s="2">
-        <v>32.00601051840721</v>
+        <v>32.00000670428697</v>
       </c>
       <c r="H8" s="2">
-        <v>32.63812293191616</v>
+        <v>32.643453670174814</v>
       </c>
       <c r="I8" s="2">
-        <v>32.99704296399374</v>
+        <v>33.00044454789128</v>
       </c>
       <c r="J8" s="2">
-        <v>33.37963658206939</v>
+        <v>33.37952255745069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-7 販売費及び一般管理費（億円）</t>
+          <t xml:space="preserve">2-7 販売費及び一般管理費（千円）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>32.65</v>
+        <v>3265017</v>
       </c>
       <c r="C9" s="2">
-        <v>34.52</v>
+        <v>3451072</v>
       </c>
       <c r="D9" s="2">
-        <v>36.4</v>
+        <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>38.26</v>
+        <v>3828099</v>
       </c>
       <c r="F9" s="2">
-        <v>40.28</v>
+        <v>4029317</v>
       </c>
       <c r="G9" s="2">
-        <v>42.42</v>
+        <v>4242329</v>
       </c>
       <c r="H9" s="2">
-        <v>46.19</v>
+        <v>4619081</v>
       </c>
       <c r="I9" s="2">
-        <v>50.8</v>
+        <v>5073716.66</v>
       </c>
       <c r="J9" s="2">
-        <v>55.97</v>
+        <v>5583321.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（億円）</t>
+          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.91</v>
+        <v>91200</v>
       </c>
       <c r="C10" s="2">
-        <v>0.96</v>
+        <v>95600</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E10" s="2">
-        <v>1.04</v>
+        <v>104564</v>
       </c>
       <c r="F10" s="2">
-        <v>1.09</v>
+        <v>109341</v>
       </c>
       <c r="G10" s="2">
-        <v>1.1400000000000001</v>
+        <v>114341</v>
       </c>
       <c r="H10" s="2">
-        <v>1.21</v>
+        <v>119899</v>
       </c>
       <c r="I10" s="2">
-        <v>1.26</v>
+        <v>125729</v>
       </c>
       <c r="J10" s="2">
-        <v>1.32</v>
+        <v>131844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-9 うち役員報酬（億円）</t>
+          <t xml:space="preserve">2-9 うち役員報酬（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.8200000000000001</v>
+        <v>82080</v>
       </c>
       <c r="C11" s="2">
-        <v>0.8600000000000001</v>
+        <v>86040</v>
       </c>
       <c r="D11" s="2">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="E11" s="2">
-        <v>0.9400000000000001</v>
+        <v>94108</v>
       </c>
       <c r="F11" s="2">
-        <v>0.99</v>
+        <v>98407</v>
       </c>
       <c r="G11" s="2">
-        <v>1.02</v>
+        <v>102907</v>
       </c>
       <c r="H11" s="2">
-        <v>1.09</v>
+        <v>107909</v>
       </c>
       <c r="I11" s="2">
-        <v>1.1400000000000001</v>
+        <v>113156</v>
       </c>
       <c r="J11" s="2">
-        <v>1.19</v>
+        <v>118660</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-10 うち役員賞与（億円）</t>
+          <t xml:space="preserve">2-10 うち役員賞与（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.09</v>
+        <v>9120</v>
       </c>
       <c r="C12" s="2">
-        <v>0.1</v>
+        <v>9560</v>
       </c>
       <c r="D12" s="2">
-        <v>0.1</v>
+        <v>10000</v>
       </c>
       <c r="E12" s="2">
-        <v>0.1</v>
+        <v>10456</v>
       </c>
       <c r="F12" s="2">
-        <v>0.1</v>
+        <v>10934</v>
       </c>
       <c r="G12" s="2">
-        <v>0.12000000000000001</v>
+        <v>11434</v>
       </c>
       <c r="H12" s="2">
-        <v>0.12000000000000001</v>
+        <v>11990</v>
       </c>
       <c r="I12" s="2">
-        <v>0.12000000000000001</v>
+        <v>12573</v>
       </c>
       <c r="J12" s="2">
-        <v>0.13</v>
+        <v>13184</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（億円）</t>
+          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>12.29</v>
+        <v>1228817</v>
       </c>
       <c r="C13" s="2">
-        <v>13.129999999999999</v>
+        <v>1312972</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>1400000</v>
       </c>
       <c r="E13" s="2">
-        <v>14.93</v>
+        <v>1494027</v>
       </c>
       <c r="F13" s="2">
-        <v>15.94</v>
+        <v>1594417</v>
       </c>
       <c r="G13" s="2">
-        <v>17.009999999999998</v>
+        <v>1701607</v>
       </c>
       <c r="H13" s="2">
-        <v>18.16</v>
+        <v>1817073</v>
       </c>
       <c r="I13" s="2">
-        <v>19.8</v>
+        <v>1974344.6600000001</v>
       </c>
       <c r="J13" s="2">
-        <v>21.6</v>
+        <v>2145739.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-12 うち従業員の給与（億円）</t>
+          <t xml:space="preserve">2-12 うち従業員の給与（千円）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>11.67</v>
+        <v>1167376</v>
       </c>
       <c r="C14" s="2">
-        <v>12.469999999999999</v>
+        <v>1247324</v>
       </c>
       <c r="D14" s="2">
-        <v>13.3</v>
+        <v>1330000</v>
       </c>
       <c r="E14" s="2">
-        <v>14.190000000000001</v>
+        <v>1419325</v>
       </c>
       <c r="F14" s="2">
-        <v>15.14</v>
+        <v>1514696</v>
       </c>
       <c r="G14" s="2">
-        <v>16.16</v>
+        <v>1616526</v>
       </c>
       <c r="H14" s="2">
-        <v>17.62</v>
+        <v>1756553</v>
       </c>
       <c r="I14" s="2">
-        <v>19.21</v>
+        <v>1909168</v>
       </c>
       <c r="J14" s="2">
-        <v>20.97</v>
+        <v>2075539</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-13 うち従業員の賞与（億円）</t>
+          <t xml:space="preserve">2-13 うち従業員の賞与（千円）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0.62</v>
+        <v>61441</v>
       </c>
       <c r="C15" s="2">
-        <v>0.66</v>
+        <v>65648</v>
       </c>
       <c r="D15" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="2">
-        <v>0.74</v>
+        <v>74702</v>
       </c>
       <c r="F15" s="2">
-        <v>0.8</v>
+        <v>79721</v>
       </c>
       <c r="G15" s="2">
-        <v>0.85</v>
+        <v>85081</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9199999999999999</v>
+        <v>92451</v>
       </c>
       <c r="I15" s="2">
-        <v>1.01</v>
+        <v>100483</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1</v>
+        <v>109239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-14 うち減価償却費（億円）</t>
+          <t xml:space="preserve">2-14 うち減価償却費（千円）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>2.45</v>
+        <v>245400</v>
       </c>
       <c r="C16" s="2">
-        <v>2.58</v>
+        <v>257700</v>
       </c>
       <c r="D16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="E16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="F16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="G16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="H16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="I16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="J16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-15 うち研究開発費（億円）</t>
+          <t xml:space="preserve">2-15 うち研究開発費（千円）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.64</v>
+        <v>63600</v>
       </c>
       <c r="C17" s="2">
-        <v>0.6699999999999999</v>
+        <v>66800</v>
       </c>
       <c r="D17" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="E17" s="2">
-        <v>0.71</v>
+        <v>71356</v>
       </c>
       <c r="F17" s="2">
-        <v>0.74</v>
+        <v>74880</v>
       </c>
       <c r="G17" s="2">
-        <v>0.79</v>
+        <v>78579</v>
       </c>
       <c r="H17" s="2">
-        <v>0.9099999999999999</v>
+        <v>90881</v>
       </c>
       <c r="I17" s="2">
-        <v>1.06</v>
+        <v>105579</v>
       </c>
       <c r="J17" s="2">
-        <v>1.23</v>
+        <v>123181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-16 営業利益（億円）</t>
+          <t xml:space="preserve">2-16 営業利益（千円）</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <v>11.000000000000007</v>
+        <v>1099783</v>
       </c>
       <c r="C18" s="4">
-        <v>11.299999999999997</v>
+        <v>1131328</v>
       </c>
       <c r="D18" s="4">
-        <v>11.600000000000001</v>
+        <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>12.080000000000005</v>
+        <v>1205743</v>
       </c>
       <c r="F18" s="4">
-        <v>12.520000000000007</v>
+        <v>1249917</v>
       </c>
       <c r="G18" s="4">
-        <v>12.959999999999994</v>
+        <v>1294428</v>
       </c>
       <c r="H18" s="4">
-        <v>18.909999999999968</v>
+        <v>1891995</v>
       </c>
       <c r="I18" s="4">
-        <v>25.08</v>
+        <v>2515189.3099999987</v>
       </c>
       <c r="J18" s="4">
-        <v>32.94000000000004</v>
+        <v>3307131.2899999972</v>
       </c>
     </row>
     <row r="19">
@@ -1796,269 +1796,269 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>8.064516129032263</v>
+        <v>8.062925219941349</v>
       </c>
       <c r="C19" s="2">
-        <v>7.8910614525139655</v>
+        <v>7.900335195530726</v>
       </c>
       <c r="D19" s="2">
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.679104952005597</v>
+        <v>7.664876373392353</v>
       </c>
       <c r="F19" s="2">
-        <v>7.588798642259671</v>
+        <v>7.576353346276221</v>
       </c>
       <c r="G19" s="2">
-        <v>7.490030630526495</v>
+        <v>7.481221350009901</v>
       </c>
       <c r="H19" s="2">
-        <v>9.480597613556588</v>
+        <v>9.485567535489126</v>
       </c>
       <c r="I19" s="2">
-        <v>10.906244564272049</v>
+        <v>10.937329528159102</v>
       </c>
       <c r="J19" s="2">
-        <v>12.366721729989502</v>
+        <v>12.416742443740771</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-18 経常利益（億円）</t>
+          <t xml:space="preserve">2-18 経常利益（千円）</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <v>10.73</v>
+        <v>1072503</v>
       </c>
       <c r="C20" s="4">
-        <v>11.01</v>
+        <v>1102688</v>
       </c>
       <c r="D20" s="4">
-        <v>11.3</v>
+        <v>1130000</v>
       </c>
       <c r="E20" s="4">
-        <v>11.719999999999999</v>
+        <v>1169253</v>
       </c>
       <c r="F20" s="4">
-        <v>12.139999999999999</v>
+        <v>1211873</v>
       </c>
       <c r="G20" s="4">
-        <v>12.56</v>
+        <v>1254765</v>
       </c>
       <c r="H20" s="4">
-        <v>17.27</v>
+        <v>1733905</v>
       </c>
       <c r="I20" s="4">
-        <v>23.32</v>
+        <v>2345830</v>
       </c>
       <c r="J20" s="4">
-        <v>31.04</v>
+        <v>3125652</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
+          <t xml:space="preserve">2-19 税引前当期純利益（千円）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>10.73</v>
+        <v>1072503</v>
       </c>
       <c r="C21" s="2">
-        <v>11.01</v>
+        <v>1102688</v>
       </c>
       <c r="D21" s="2">
-        <v>11.3</v>
+        <v>1130000</v>
       </c>
       <c r="E21" s="2">
-        <v>11.719999999999999</v>
+        <v>1169253</v>
       </c>
       <c r="F21" s="2">
-        <v>12.139999999999999</v>
+        <v>1211873</v>
       </c>
       <c r="G21" s="2">
-        <v>12.56</v>
+        <v>1254765</v>
       </c>
       <c r="H21" s="2">
-        <v>17.27</v>
+        <v>1733905</v>
       </c>
       <c r="I21" s="2">
-        <v>23.32</v>
+        <v>2345830</v>
       </c>
       <c r="J21" s="2">
-        <v>31.04</v>
+        <v>3125652</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-20 当期純利益（億円）</t>
+          <t xml:space="preserve">2-20 当期純利益（千円）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>7.51</v>
+        <v>750752.1</v>
       </c>
       <c r="C22" s="2">
-        <v>7.71</v>
+        <v>771881.6</v>
       </c>
       <c r="D22" s="2">
-        <v>7.91</v>
+        <v>791000</v>
       </c>
       <c r="E22" s="2">
-        <v>8.2</v>
+        <v>818477</v>
       </c>
       <c r="F22" s="2">
-        <v>8.5</v>
+        <v>848312</v>
       </c>
       <c r="G22" s="2">
-        <v>8.8</v>
+        <v>878336</v>
       </c>
       <c r="H22" s="2">
-        <v>12.09</v>
+        <v>1213734</v>
       </c>
       <c r="I22" s="2">
-        <v>16.32</v>
+        <v>1642081</v>
       </c>
       <c r="J22" s="2">
-        <v>21.73</v>
+        <v>2187957</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（億円）</t>
+          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（千円）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>12.29</v>
+        <v>1228817</v>
       </c>
       <c r="C23" s="2">
-        <v>13.129999999999999</v>
+        <v>1312972</v>
       </c>
       <c r="D23" s="2">
-        <v>14</v>
+        <v>1400000</v>
       </c>
       <c r="E23" s="2">
-        <v>14.93</v>
+        <v>1494027</v>
       </c>
       <c r="F23" s="2">
-        <v>15.94</v>
+        <v>1594417</v>
       </c>
       <c r="G23" s="2">
-        <v>17.009999999999998</v>
+        <v>1701607</v>
       </c>
       <c r="H23" s="2">
-        <v>18.16</v>
+        <v>1817073</v>
       </c>
       <c r="I23" s="2">
-        <v>19.8</v>
+        <v>1974344.6600000001</v>
       </c>
       <c r="J23" s="2">
-        <v>21.6</v>
+        <v>2145739.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-22 給与支給総額（役員）（億円）</t>
+          <t xml:space="preserve">2-22 給与支給総額（役員）（千円）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.91</v>
+        <v>91200</v>
       </c>
       <c r="C24" s="2">
-        <v>0.96</v>
+        <v>95600</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E24" s="2">
-        <v>1.04</v>
+        <v>104564</v>
       </c>
       <c r="F24" s="2">
-        <v>1.09</v>
+        <v>109341</v>
       </c>
       <c r="G24" s="2">
-        <v>1.1400000000000001</v>
+        <v>114341</v>
       </c>
       <c r="H24" s="2">
-        <v>1.21</v>
+        <v>119899</v>
       </c>
       <c r="I24" s="2">
-        <v>1.26</v>
+        <v>125729</v>
       </c>
       <c r="J24" s="2">
-        <v>1.32</v>
+        <v>131844</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-23 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">2-23 減価償却費（合計）（千円）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>3.1799999999999997</v>
+        <v>318000</v>
       </c>
       <c r="C25" s="2">
-        <v>3.34</v>
+        <v>334000</v>
       </c>
       <c r="D25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="E25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="F25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="G25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="H25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="I25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="J25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-24 付加価値額（億円）</t>
+          <t xml:space="preserve">2-24 付加価値額（千円）</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <v>27.380000000000006</v>
+        <v>2737800</v>
       </c>
       <c r="C26" s="4">
-        <v>28.729999999999997</v>
+        <v>2873900</v>
       </c>
       <c r="D26" s="4">
-        <v>30.1</v>
+        <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>31.550000000000004</v>
+        <v>3154334</v>
       </c>
       <c r="F26" s="4">
-        <v>33.05000000000001</v>
+        <v>3303675</v>
       </c>
       <c r="G26" s="4">
-        <v>34.60999999999999</v>
+        <v>3460376</v>
       </c>
       <c r="H26" s="4">
-        <v>41.779999999999966</v>
+        <v>4178967</v>
       </c>
       <c r="I26" s="4">
-        <v>49.63999999999999</v>
+        <v>4965262.969999999</v>
       </c>
       <c r="J26" s="4">
-        <v>59.36000000000004</v>
+        <v>5934714.869999997</v>
       </c>
     </row>
     <row r="27">
@@ -2073,28 +2073,28 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>4.930606281957606</v>
+        <v>4.9711447147344545</v>
       </c>
       <c r="D27" s="2">
-        <v>4.768534632788035</v>
+        <v>4.735724973033162</v>
       </c>
       <c r="E27" s="2">
-        <v>4.8172757475083205</v>
+        <v>4.795149501661133</v>
       </c>
       <c r="F27" s="2">
-        <v>4.754358161648198</v>
+        <v>4.734470097332744</v>
       </c>
       <c r="G27" s="2">
-        <v>4.720121028744262</v>
+        <v>4.743232914859963</v>
       </c>
       <c r="H27" s="2">
-        <v>20.716555908696833</v>
+        <v>20.766269330269303</v>
       </c>
       <c r="I27" s="2">
-        <v>18.812829104834925</v>
+        <v>18.81555824681074</v>
       </c>
       <c r="J27" s="2">
-        <v>19.580983078162873</v>
+        <v>19.524683906117435</v>
       </c>
     </row>
     <row r="28">
@@ -2104,31 +2104,31 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <v>20.073313782991207</v>
+        <v>20.071847507331377</v>
       </c>
       <c r="C28" s="2">
-        <v>20.062849162011172</v>
+        <v>20.069134078212294</v>
       </c>
       <c r="D28" s="2">
-        <v>20.06666666666667</v>
+        <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.055940499650372</v>
+        <v>20.05201784326195</v>
       </c>
       <c r="F28" s="2">
-        <v>20.032731240150326</v>
+        <v>20.025176984759064</v>
       </c>
       <c r="G28" s="2">
-        <v>20.002311737848924</v>
+        <v>19.999442850635074</v>
       </c>
       <c r="H28" s="2">
-        <v>20.94655570039104</v>
+        <v>20.951362824468557</v>
       </c>
       <c r="I28" s="2">
-        <v>21.586362845712298</v>
+        <v>21.59150290633828</v>
       </c>
       <c r="J28" s="2">
-        <v>22.28562847274367</v>
+        <v>22.282098760532882</v>
       </c>
     </row>
     <row r="29">
@@ -2156,13 +2156,13 @@
         <v>262</v>
       </c>
       <c r="H29" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I29" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J29" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30">
@@ -2202,35 +2202,35 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0.05852380952380952</v>
+        <v>5851.509523809524</v>
       </c>
       <c r="C31" s="2">
-        <v>0.059681818181818176</v>
+        <v>5968.054545454545</v>
       </c>
       <c r="D31" s="2">
-        <v>0.06086956521739131</v>
+        <v>6086.95652173913</v>
       </c>
       <c r="E31" s="2">
-        <v>0.06220833333333333</v>
+        <v>6225.1125</v>
       </c>
       <c r="F31" s="2">
-        <v>0.06325396825396826</v>
+        <v>6327.0515873015875</v>
       </c>
       <c r="G31" s="2">
-        <v>0.0649236641221374</v>
+        <v>6494.68320610687</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06676470588235295</v>
+        <v>6705.066420664207</v>
       </c>
       <c r="I31" s="2">
-        <v>0.07021276595744681</v>
+        <v>7026.137580071175</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07372013651877134</v>
+        <v>7373.675532646048</v>
       </c>
     </row>
     <row r="32">
@@ -2245,62 +2245,62 @@
         </is>
       </c>
       <c r="C32" s="2">
-        <v>1.9786966491604385</v>
+        <v>1.9917086551906937</v>
       </c>
       <c r="D32" s="2">
-        <v>1.9901321235802572</v>
+        <v>1.9923071308914908</v>
       </c>
       <c r="E32" s="2">
-        <v>2.199404761904744</v>
+        <v>2.2697053571428594</v>
       </c>
       <c r="F32" s="2">
-        <v>1.680859885816366</v>
+        <v>1.6375461054171758</v>
       </c>
       <c r="G32" s="2">
-        <v>2.6396697539436964</v>
+        <v>2.6494428959883853</v>
       </c>
       <c r="H32" s="2">
-        <v>2.8357021821074246</v>
+        <v>3.2393144958866804</v>
       </c>
       <c r="I32" s="2">
-        <v>5.164495266660407</v>
+        <v>4.788485889080318</v>
       </c>
       <c r="J32" s="2">
-        <v>4.995345950977348</v>
+        <v>4.946358488063551</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0.182</v>
+        <v>18240</v>
       </c>
       <c r="C33" s="2">
-        <v>0.192</v>
+        <v>19120</v>
       </c>
       <c r="D33" s="2">
-        <v>0.2</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="2">
-        <v>0.20800000000000002</v>
+        <v>20912.8</v>
       </c>
       <c r="F33" s="2">
-        <v>0.21800000000000003</v>
+        <v>21868.2</v>
       </c>
       <c r="G33" s="2">
-        <v>0.22800000000000004</v>
+        <v>22868.2</v>
       </c>
       <c r="H33" s="2">
-        <v>0.242</v>
+        <v>23979.8</v>
       </c>
       <c r="I33" s="2">
-        <v>0.252</v>
+        <v>25145.8</v>
       </c>
       <c r="J33" s="2">
-        <v>0.264</v>
+        <v>26368.8</v>
       </c>
     </row>
     <row r="34">
@@ -2315,96 +2315,96 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>5.494505494505497</v>
+        <v>4.824561403508776</v>
       </c>
       <c r="D34" s="2">
-        <v>4.166666666666674</v>
+        <v>4.602510460251041</v>
       </c>
       <c r="E34" s="2">
-        <v>4.0000000000000036</v>
+        <v>4.56399999999999</v>
       </c>
       <c r="F34" s="2">
-        <v>4.807692307692313</v>
+        <v>4.568493936727758</v>
       </c>
       <c r="G34" s="2">
-        <v>4.587155963302747</v>
+        <v>4.572850074537449</v>
       </c>
       <c r="H34" s="2">
-        <v>6.140350877192957</v>
+        <v>4.860898540331116</v>
       </c>
       <c r="I34" s="2">
-        <v>4.132231404958686</v>
+        <v>4.862425875111542</v>
       </c>
       <c r="J34" s="2">
-        <v>4.761904761904767</v>
+        <v>4.863635279052558</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-33 労働生産性（億円/人）</t>
+          <t xml:space="preserve">2-33 労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>0.12734883720930235</v>
+        <v>12733.953488372093</v>
       </c>
       <c r="C35" s="2">
-        <v>0.12768888888888888</v>
+        <v>12772.888888888889</v>
       </c>
       <c r="D35" s="2">
-        <v>0.12808510638297874</v>
+        <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12877551020408165</v>
+        <v>12874.832653061225</v>
       </c>
       <c r="F35" s="2">
-        <v>0.1285992217898833</v>
+        <v>12854.76653696498</v>
       </c>
       <c r="G35" s="2">
-        <v>0.12962546816479398</v>
+        <v>12960.209737827716</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15083032490974718</v>
+        <v>15141.184782608696</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17296167247386757</v>
+        <v>17361.059335664333</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19919463087248337</v>
+        <v>20049.71239864864</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-34 EBITDA（億円）</t>
+          <t xml:space="preserve">2-34 EBITDA（千円）</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <v>14.180000000000007</v>
+        <v>1417783</v>
       </c>
       <c r="C36" s="4">
-        <v>14.639999999999997</v>
+        <v>1465328</v>
       </c>
       <c r="D36" s="4">
-        <v>15.100000000000001</v>
+        <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>15.580000000000005</v>
+        <v>1555743</v>
       </c>
       <c r="F36" s="4">
-        <v>16.020000000000007</v>
+        <v>1599917</v>
       </c>
       <c r="G36" s="4">
-        <v>16.459999999999994</v>
+        <v>1644428</v>
       </c>
       <c r="H36" s="4">
-        <v>22.409999999999968</v>
+        <v>2241995</v>
       </c>
       <c r="I36" s="4">
-        <v>28.58</v>
+        <v>2865189.3099999987</v>
       </c>
       <c r="J36" s="4">
-        <v>36.44000000000004</v>
+        <v>3657131.2899999972</v>
       </c>
     </row>
     <row r="37">
@@ -2414,31 +2414,31 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <v>10.395894428152497</v>
+        <v>10.394303519061584</v>
       </c>
       <c r="C37" s="2">
-        <v>10.223463687150836</v>
+        <v>10.232737430167598</v>
       </c>
       <c r="D37" s="2">
-        <v>10.066666666666668</v>
+        <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>9.904011188099933</v>
+        <v>9.889817120041783</v>
       </c>
       <c r="F37" s="2">
-        <v>9.710267911261974</v>
+        <v>9.697873152148674</v>
       </c>
       <c r="G37" s="2">
-        <v>9.512801248338434</v>
+        <v>9.504066554612601</v>
       </c>
       <c r="H37" s="2">
-        <v>11.235335405595091</v>
+        <v>11.240301896531937</v>
       </c>
       <c r="I37" s="2">
-        <v>12.428248391024526</v>
+        <v>12.45930853770558</v>
       </c>
       <c r="J37" s="2">
-        <v>13.6807328427692</v>
+        <v>13.730829933538999</v>
       </c>
     </row>
     <row r="38">
@@ -2453,28 +2453,28 @@
         </is>
       </c>
       <c r="C38" s="2">
-        <v>3.2440056417488705</v>
+        <v>3.3534751086731873</v>
       </c>
       <c r="D38" s="2">
-        <v>3.1420765027322606</v>
+        <v>3.0486007228415657</v>
       </c>
       <c r="E38" s="2">
-        <v>3.1788079470199015</v>
+        <v>3.029337748344374</v>
       </c>
       <c r="F38" s="2">
-        <v>2.824133504492954</v>
+        <v>2.839414993350453</v>
       </c>
       <c r="G38" s="2">
-        <v>2.7465667915105296</v>
+        <v>2.782081820494442</v>
       </c>
       <c r="H38" s="2">
-        <v>36.14823815309829</v>
+        <v>36.338897172755516</v>
       </c>
       <c r="I38" s="2">
-        <v>27.532351628737352</v>
+        <v>27.79641836846196</v>
       </c>
       <c r="J38" s="2">
-        <v>27.5017494751576</v>
+        <v>27.640127555829764</v>
       </c>
     </row>
   </sheetData>
@@ -2614,35 +2614,35 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-1 売上高（億円）</t>
+          <t xml:space="preserve">7-1 売上高（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="C3" s="4">
-        <v>76</v>
+        <v>7600000</v>
       </c>
       <c r="D3" s="4">
-        <v>80</v>
+        <v>8000000</v>
       </c>
       <c r="E3" s="4">
-        <v>84.33</v>
+        <v>8432749</v>
       </c>
       <c r="F3" s="4">
-        <v>88.89</v>
+        <v>8888906</v>
       </c>
       <c r="G3" s="4">
-        <v>93.7</v>
+        <v>9369739</v>
       </c>
       <c r="H3" s="4">
-        <v>114.33</v>
+        <v>11433039</v>
       </c>
       <c r="I3" s="4">
-        <v>139.51</v>
+        <v>13950695</v>
       </c>
       <c r="J3" s="4">
-        <v>170.24</v>
+        <v>17022762</v>
       </c>
     </row>
     <row r="4">
@@ -2663,22 +2663,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E4" s="2">
-        <v>5.412499999999998</v>
+        <v>5.409362499999992</v>
       </c>
       <c r="F4" s="2">
-        <v>5.407328352899321</v>
+        <v>5.409351090611136</v>
       </c>
       <c r="G4" s="2">
-        <v>5.41118236022049</v>
+        <v>5.409360836980381</v>
       </c>
       <c r="H4" s="2">
-        <v>22.017075773745987</v>
+        <v>22.02089087006587</v>
       </c>
       <c r="I4" s="2">
-        <v>22.02396571328609</v>
+        <v>22.02088176205819</v>
       </c>
       <c r="J4" s="2">
-        <v>22.027094831911697</v>
+        <v>22.02088856504998</v>
       </c>
     </row>
     <row r="5">
@@ -2697,56 +2697,56 @@
         <v>53.333333333333336</v>
       </c>
       <c r="E5" s="2">
-        <v>53.60752653995296</v>
+        <v>53.606762446763526</v>
       </c>
       <c r="F5" s="2">
-        <v>53.87925809188992</v>
+        <v>53.87997180439563</v>
       </c>
       <c r="G5" s="2">
-        <v>54.1524591111368</v>
+        <v>54.15294744151117</v>
       </c>
       <c r="H5" s="2">
-        <v>57.319763361074905</v>
+        <v>57.31984681269299</v>
       </c>
       <c r="I5" s="2">
-        <v>60.66707253435381</v>
+        <v>60.66475702452855</v>
       </c>
       <c r="J5" s="2">
-        <v>63.91350052560445</v>
+        <v>63.91256738860758</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-4 売上総利益（億円）</t>
+          <t xml:space="preserve">7-4 売上総利益（千円）</t>
         </is>
       </c>
       <c r="B6" s="4">
-        <v>23.04</v>
+        <v>2304000</v>
       </c>
       <c r="C6" s="4">
-        <v>24.32</v>
+        <v>2432000</v>
       </c>
       <c r="D6" s="4">
-        <v>25.6</v>
+        <v>2560000</v>
       </c>
       <c r="E6" s="4">
-        <v>26.989999999999995</v>
+        <v>2698480</v>
       </c>
       <c r="F6" s="4">
-        <v>28.450000000000003</v>
+        <v>2844450</v>
       </c>
       <c r="G6" s="4">
-        <v>29.990000000000002</v>
+        <v>2998317</v>
       </c>
       <c r="H6" s="4">
-        <v>37.14999999999999</v>
+        <v>3715738</v>
       </c>
       <c r="I6" s="4">
-        <v>46.03999999999999</v>
+        <v>4603729</v>
       </c>
       <c r="J6" s="4">
-        <v>57.030000000000015</v>
+        <v>5702625</v>
       </c>
     </row>
     <row r="7">
@@ -2765,56 +2765,56 @@
         <v>32</v>
       </c>
       <c r="E7" s="2">
-        <v>32.005217597533495</v>
+        <v>32.00000379472934</v>
       </c>
       <c r="F7" s="2">
-        <v>32.00584992687592</v>
+        <v>32.00000089999826</v>
       </c>
       <c r="G7" s="2">
-        <v>32.00640341515475</v>
+        <v>32.00000554978106</v>
       </c>
       <c r="H7" s="2">
-        <v>32.49365870725093</v>
+        <v>32.50000284263878</v>
       </c>
       <c r="I7" s="2">
-        <v>33.001218550641525</v>
+        <v>32.999997491164414</v>
       </c>
       <c r="J7" s="2">
-        <v>33.499765037593995</v>
+        <v>33.49999841388841</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-6 営業利益（億円）</t>
+          <t xml:space="preserve">7-6 営業利益（千円）</t>
         </is>
       </c>
       <c r="B8" s="4">
-        <v>6.779999999999998</v>
+        <v>677969</v>
       </c>
       <c r="C8" s="4">
-        <v>7.040000000000003</v>
+        <v>704676</v>
       </c>
       <c r="D8" s="4">
-        <v>7.300000000000004</v>
+        <v>730000</v>
       </c>
       <c r="E8" s="4">
-        <v>7.669999999999991</v>
+        <v>765642</v>
       </c>
       <c r="F8" s="4">
-        <v>8.04</v>
+        <v>802328</v>
       </c>
       <c r="G8" s="4">
-        <v>8.410000000000004</v>
+        <v>840048</v>
       </c>
       <c r="H8" s="4">
-        <v>12.959999999999992</v>
+        <v>1297239</v>
       </c>
       <c r="I8" s="4">
-        <v>18.47999999999999</v>
+        <v>1854112.3399999999</v>
       </c>
       <c r="J8" s="4">
-        <v>25.600000000000016</v>
+        <v>2574339.42</v>
       </c>
     </row>
     <row r="9">
@@ -2824,235 +2824,235 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>9.416666666666664</v>
+        <v>9.416236111111111</v>
       </c>
       <c r="C9" s="2">
-        <v>9.263157894736846</v>
+        <v>9.272052631578948</v>
       </c>
       <c r="D9" s="2">
-        <v>9.125000000000005</v>
+        <v>9.125</v>
       </c>
       <c r="E9" s="2">
-        <v>9.095221154986351</v>
+        <v>9.07938799079636</v>
       </c>
       <c r="F9" s="2">
-        <v>9.044886938913264</v>
+        <v>9.026172624617699</v>
       </c>
       <c r="G9" s="2">
-        <v>8.975453575240131</v>
+        <v>8.96554322377603</v>
       </c>
       <c r="H9" s="2">
-        <v>11.3356074521123</v>
+        <v>11.346405798143433</v>
       </c>
       <c r="I9" s="2">
-        <v>13.246362267937775</v>
+        <v>13.290465743821365</v>
       </c>
       <c r="J9" s="2">
-        <v>15.037593984962413</v>
+        <v>15.12292435269905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8 給与支給総額（常時使用する従業員）（億円）</t>
+          <t xml:space="preserve">7-8 給与支給総額（常時使用する従業員）（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>5.19</v>
+        <v>519031</v>
       </c>
       <c r="C10" s="2">
-        <v>5.59</v>
+        <v>558824</v>
       </c>
       <c r="D10" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="E10" s="2">
-        <v>6.44</v>
+        <v>644416</v>
       </c>
       <c r="F10" s="2">
-        <v>6.92</v>
+        <v>692119</v>
       </c>
       <c r="G10" s="2">
-        <v>7.43</v>
+        <v>743354</v>
       </c>
       <c r="H10" s="2">
-        <v>7.9</v>
+        <v>790000</v>
       </c>
       <c r="I10" s="2">
-        <v>8.8</v>
+        <v>873508.66</v>
       </c>
       <c r="J10" s="2">
-        <v>9.81</v>
+        <v>965843.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-9 給与支給総額（役員）（億円）</t>
+          <t xml:space="preserve">7-9 給与支給総額（役員）（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.36</v>
+        <v>36000</v>
       </c>
       <c r="C11" s="2">
-        <v>0.38</v>
+        <v>38000</v>
       </c>
       <c r="D11" s="2">
-        <v>0.4</v>
+        <v>40000</v>
       </c>
       <c r="E11" s="2">
-        <v>0.42</v>
+        <v>42164</v>
       </c>
       <c r="F11" s="2">
-        <v>0.44</v>
+        <v>44445</v>
       </c>
       <c r="G11" s="2">
-        <v>0.47</v>
+        <v>46849</v>
       </c>
       <c r="H11" s="2">
-        <v>0.5</v>
+        <v>49370</v>
       </c>
       <c r="I11" s="2">
-        <v>0.52</v>
+        <v>52026</v>
       </c>
       <c r="J11" s="2">
-        <v>0.55</v>
+        <v>54825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（億円）</t>
+          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.45</v>
+        <v>45000</v>
       </c>
       <c r="C12" s="2">
-        <v>0.47</v>
+        <v>47500</v>
       </c>
       <c r="D12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="E12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="F12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="G12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="H12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="I12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="J12" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（億円）</t>
+          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>1.35</v>
+        <v>135000</v>
       </c>
       <c r="C13" s="2">
-        <v>1.43</v>
+        <v>142500</v>
       </c>
       <c r="D13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="E13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="F13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="G13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="H13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="I13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="J13" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">7-10 減価償却費（合計）（千円）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>1.8</v>
+        <v>180000</v>
       </c>
       <c r="C14" s="2">
-        <v>1.9</v>
+        <v>190000</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="F14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="G14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="I14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
       <c r="J14" s="2">
-        <v>2</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-11 付加価値（億円）</t>
+          <t xml:space="preserve">7-11 付加価値（千円）</t>
         </is>
       </c>
       <c r="B15" s="4">
-        <v>14.129999999999999</v>
+        <v>1413000</v>
       </c>
       <c r="C15" s="4">
-        <v>14.910000000000004</v>
+        <v>1491500</v>
       </c>
       <c r="D15" s="4">
-        <v>15.700000000000005</v>
+        <v>1570000</v>
       </c>
       <c r="E15" s="4">
-        <v>16.529999999999994</v>
+        <v>1652222</v>
       </c>
       <c r="F15" s="4">
-        <v>17.4</v>
+        <v>1738892</v>
       </c>
       <c r="G15" s="4">
-        <v>18.310000000000002</v>
+        <v>1830251</v>
       </c>
       <c r="H15" s="4">
-        <v>23.359999999999992</v>
+        <v>2336609</v>
       </c>
       <c r="I15" s="4">
-        <v>29.79999999999999</v>
+        <v>2979647</v>
       </c>
       <c r="J15" s="4">
-        <v>37.960000000000015</v>
+        <v>3795008</v>
       </c>
     </row>
     <row r="16">
@@ -3067,28 +3067,28 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>5.520169851380086</v>
+        <v>5.555555555555558</v>
       </c>
       <c r="D16" s="2">
-        <v>5.2984574111334615</v>
+        <v>5.263157894736836</v>
       </c>
       <c r="E16" s="2">
-        <v>5.286624203821577</v>
+        <v>5.237070063694271</v>
       </c>
       <c r="F16" s="2">
-        <v>5.263157894736881</v>
+        <v>5.245663113068333</v>
       </c>
       <c r="G16" s="2">
-        <v>5.229885057471284</v>
+        <v>5.253862804590503</v>
       </c>
       <c r="H16" s="2">
-        <v>27.580557072637845</v>
+        <v>27.66604143366129</v>
       </c>
       <c r="I16" s="2">
-        <v>27.568493150684926</v>
+        <v>27.520137087548658</v>
       </c>
       <c r="J16" s="2">
-        <v>27.382550335570556</v>
+        <v>27.364348864143984</v>
       </c>
     </row>
     <row r="17">
@@ -3116,13 +3116,13 @@
         <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I17" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J17" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
@@ -3162,35 +3162,35 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0.05766666666666667</v>
+        <v>5767.011111111111</v>
       </c>
       <c r="C19" s="2">
-        <v>0.05884210526315789</v>
+        <v>5882.357894736842</v>
       </c>
       <c r="D19" s="2">
-        <v>0.06</v>
+        <v>6000</v>
       </c>
       <c r="E19" s="2">
-        <v>0.06133333333333334</v>
+        <v>6137.295238095238</v>
       </c>
       <c r="F19" s="2">
-        <v>0.062342342342342344</v>
+        <v>6235.306306306306</v>
       </c>
       <c r="G19" s="2">
-        <v>0.06405172413793103</v>
+        <v>6408.224137931034</v>
       </c>
       <c r="H19" s="2">
-        <v>0.06638655462184874</v>
+        <v>6694.9152542372885</v>
       </c>
       <c r="I19" s="2">
-        <v>0.07213114754098361</v>
+        <v>7219.079834710744</v>
       </c>
       <c r="J19" s="2">
-        <v>0.07848000000000001</v>
+        <v>7852.386829268293</v>
       </c>
     </row>
     <row r="20">
@@ -3205,62 +3205,62 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>2.0383328262853606</v>
+        <v>2.000113774767942</v>
       </c>
       <c r="D20" s="2">
-        <v>1.9677996422182487</v>
+        <v>1.9999141053354874</v>
       </c>
       <c r="E20" s="2">
-        <v>2.2222222222222365</v>
+        <v>2.2882539682539615</v>
       </c>
       <c r="F20" s="2">
-        <v>1.6451233842538215</v>
+        <v>1.5969749606096206</v>
       </c>
       <c r="G20" s="2">
-        <v>2.7419274466812693</v>
+        <v>2.7732050861694058</v>
       </c>
       <c r="H20" s="2">
-        <v>3.645226596695217</v>
+        <v>4.473799763171438</v>
       </c>
       <c r="I20" s="2">
-        <v>8.653247561734801</v>
+        <v>7.829293733654152</v>
       </c>
       <c r="J20" s="2">
-        <v>8.801818181818177</v>
+        <v>8.772683071220321</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.18</v>
+        <v>18000</v>
       </c>
       <c r="C21" s="2">
-        <v>0.19</v>
+        <v>19000</v>
       </c>
       <c r="D21" s="2">
-        <v>0.2</v>
+        <v>20000</v>
       </c>
       <c r="E21" s="2">
-        <v>0.21</v>
+        <v>21082</v>
       </c>
       <c r="F21" s="2">
-        <v>0.22</v>
+        <v>22222.5</v>
       </c>
       <c r="G21" s="2">
-        <v>0.235</v>
+        <v>23424.5</v>
       </c>
       <c r="H21" s="2">
-        <v>0.25</v>
+        <v>24685</v>
       </c>
       <c r="I21" s="2">
-        <v>0.26</v>
+        <v>26013</v>
       </c>
       <c r="J21" s="2">
-        <v>0.275</v>
+        <v>27412.5</v>
       </c>
     </row>
     <row r="22">
@@ -3281,56 +3281,56 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E22" s="2">
-        <v>4.999999999999982</v>
+        <v>5.410000000000004</v>
       </c>
       <c r="F22" s="2">
-        <v>4.761904761904767</v>
+        <v>5.409828289536089</v>
       </c>
       <c r="G22" s="2">
-        <v>6.818181818181812</v>
+        <v>5.408932388345145</v>
       </c>
       <c r="H22" s="2">
-        <v>6.382978723404253</v>
+        <v>5.381118060150691</v>
       </c>
       <c r="I22" s="2">
-        <v>4.0000000000000036</v>
+        <v>5.379785294713391</v>
       </c>
       <c r="J22" s="2">
-        <v>5.769230769230771</v>
+        <v>5.380002306539033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+          <t xml:space="preserve">7-19 労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0.15358695652173912</v>
+        <v>15358.695652173914</v>
       </c>
       <c r="C23" s="2">
-        <v>0.1537113402061856</v>
+        <v>15376.288659793814</v>
       </c>
       <c r="D23" s="2">
-        <v>0.15392156862745102</v>
+        <v>15392.156862745098</v>
       </c>
       <c r="E23" s="2">
-        <v>0.15448598130841115</v>
+        <v>15441.327102803738</v>
       </c>
       <c r="F23" s="2">
-        <v>0.15398230088495574</v>
+        <v>15388.424778761062</v>
       </c>
       <c r="G23" s="2">
-        <v>0.15516949152542375</v>
+        <v>15510.601694915254</v>
       </c>
       <c r="H23" s="2">
-        <v>0.19305785123966937</v>
+        <v>19471.741666666665</v>
       </c>
       <c r="I23" s="2">
-        <v>0.2403225806451612</v>
+        <v>24224.772357723577</v>
       </c>
       <c r="J23" s="2">
-        <v>0.29889763779527573</v>
+        <v>30360.064</v>
       </c>
     </row>
     <row r="24">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / ベース 4.26 %</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
-        </is>
-      </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.27 % / 補助 22.02 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 15.28 % / 補助 22.02 % / ベース 7.32 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.02 % / ベース 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.02 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / ベース 6.27 %</t>
+          <t xml:space="preserve">全社 15.82 % / 補助 22.02 % / ベース 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68.01 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -3705,27 +3705,27 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / ベース 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / ベース 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.99 % / 補助 67.99 % / ベース 67.99 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.36 % / 補助 67.51 % / ベース 67.17 %</t>
+          <t xml:space="preserve">全社 67.36 % / 補助 67.5 % / ベース 67.16 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67 % / 補助 67 % / ベース 67.01 %</t>
+          <t xml:space="preserve">全社 67 % / 補助 67 % / ベース 67 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 31.99 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -3767,27 +3767,27 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / ベース 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / ベース 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.01 % / 補助 32.01 % / ベース 32.01 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.64 % / 補助 32.49 % / ベース 32.83 %</t>
+          <t xml:space="preserve">全社 32.64 % / 補助 32.5 % / ベース 32.84 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33 % / 補助 33 % / ベース 32.99 %</t>
+          <t xml:space="preserve">全社 33 % / 補助 33 % / ベース 33 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / ベース 25.65 %</t>
+          <t xml:space="preserve">全社 24.1 % / 補助 22.73 % / ベース 25.65 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.32 % / 補助 22.91 % / ベース 25.95 %</t>
+          <t xml:space="preserve">全社 24.34 % / 補助 22.92 % / ベース 25.97 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.42 % / 補助 22.96 % / ベース 26.11 %</t>
+          <t xml:space="preserve">全社 24.42 % / 補助 22.97 % / ベース 26.12 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.16 % / 補助 21.16 % / ベース 25.84 %</t>
+          <t xml:space="preserve">全社 23.16 % / 補助 21.15 % / ベース 25.85 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.09 % / 補助 19.75 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.06 % / 補助 19.71 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.01 % / 補助 18.46 % / ベース 25.53 %</t>
+          <t xml:space="preserve">全社 20.96 % / 補助 18.38 % / ベース 25.54 %</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / ベース 6.34 %</t>
+          <t xml:space="preserve">全社 7.9 % / 補助 9.27 % / ベース 6.35 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.68 % / 補助 9.1 % / ベース 6.04 %</t>
+          <t xml:space="preserve">全社 7.66 % / 補助 9.08 % / ベース 6.03 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.59 % / 補助 9.04 % / ベース 5.89 %</t>
+          <t xml:space="preserve">全社 7.58 % / 補助 9.03 % / ベース 5.88 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.49 % / 補助 8.98 % / ベース 5.74 %</t>
+          <t xml:space="preserve">全社 7.48 % / 補助 8.97 % / ベース 5.73 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.48 % / 補助 11.34 % / ベース 6.99 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 11.35 % / ベース 6.99 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.91 % / 補助 13.25 % / ベース 7.3 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 13.29 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.37 % / 補助 15.04 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 12.42 % / 補助 15.12 % / ベース 7.62 %</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / ベース 8.7 %</t>
+          <t xml:space="preserve">全社 10.39 % / 補助 11.92 % / ベース 8.69 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / ベース 8.48 %</t>
+          <t xml:space="preserve">全社 10.23 % / 補助 11.77 % / ベース 8.49 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -3953,32 +3953,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.9 % / 補助 11.47 % / ベース 8.1 %</t>
+          <t xml:space="preserve">全社 9.89 % / 補助 11.45 % / ベース 8.09 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.71 % / 補助 11.29 % / ベース 7.86 %</t>
+          <t xml:space="preserve">全社 9.7 % / 補助 11.28 % / ベース 7.85 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.51 % / 補助 11.11 % / ベース 7.63 %</t>
+          <t xml:space="preserve">全社 9.5 % / 補助 11.1 % / ベース 7.62 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.24 % / 補助 13.08 % / ベース 8.75 %</t>
+          <t xml:space="preserve">全社 11.24 % / 補助 13.1 % / ベース 8.75 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.43 % / 補助 14.68 % / ベース 8.96 %</t>
+          <t xml:space="preserve">全社 12.46 % / 補助 14.72 % / ベース 8.97 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.68 % / 補助 16.21 % / ベース 9.2 %</t>
+          <t xml:space="preserve">全社 13.73 % / 補助 16.3 % / ベース 9.18 %</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 % / 補助 11 % / ベース 10.82 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 11 % / ベース 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / ベース 11.22 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.35 % / ベース 11.22 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.49 % / 補助 7.64 % / ベース 11.63 %</t>
+          <t xml:space="preserve">全社 9.5 % / 補助 7.64 % / ベース 11.64 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.66 % / 補助 7.78 % / ベース 11.85 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 7.79 % / ベース 11.86 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
@@ -4154,17 +4154,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / ベース 12.05 %</t>
+          <t xml:space="preserve">全社 9.11 % / 補助 6.91 % / ベース 12.06 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 6.31 % / ベース 12.16 %</t>
+          <t xml:space="preserve">全社 8.59 % / 補助 6.26 % / ベース 12.17 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.11 % / 補助 5.76 % / ベース 12.27 %</t>
+          <t xml:space="preserve">全社 8.06 % / 補助 5.67 % / ベース 12.28 %</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.85 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.86 %</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -4201,27 +4201,27 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.86 %</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.66 % / 補助 0.49 % / ベース 0.85 %</t>
-        </is>
-      </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.84 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.61 % / 補助 0.44 % / ベース 0.83 %</t>
+          <t xml:space="preserve">全社 0.6 % / 補助 0.43 % / ベース 0.83 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.55 % / 補助 0.37 % / ベース 0.82 %</t>
+          <t xml:space="preserve">全社 0.55 % / 補助 0.37 % / ベース 0.81 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / ベース 12.08 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.85 % / ベース 12.08 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -4263,39 +4263,39 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / ベース 12.48 %</t>
+          <t xml:space="preserve">全社 10.16 % / 補助 8.14 % / ベース 12.5 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.32 % / 補助 8.28 % / ベース 12.71 %</t>
+          <t xml:space="preserve">全社 10.33 % / 補助 8.29 % / ベース 12.71 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.49 % / 補助 8.43 % / ベース 12.92 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 8.43 % / ベース 12.93 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.71 % / 補助 7.35 % / ベース 12.89 %</t>
+          <t xml:space="preserve">全社 9.71 % / 補助 7.34 % / ベース 12.89 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.16 % / 補助 6.68 % / ベース 12.98 %</t>
+          <t xml:space="preserve">全社 9.13 % / 補助 6.63 % / ベース 12.98 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.6 % / 補助 6.09 % / ベース 13.07 %</t>
+          <t xml:space="preserve">全社 8.55 % / 補助 6 % / ベース 13.08 %</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -4310,54 +4310,54 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / ベース 0.059 億円/人</t>
+          <t xml:space="preserve">全社 5,851.51 千円/人 / 補助 5,767.01 千円/人 / ベース 5,914.88 千円/人</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / ベース 0.06 億円/人</t>
+          <t xml:space="preserve">全社 5,968.05 千円/人 / 補助 5,882.36 千円/人 / ベース 6,033.18 千円/人</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / ベース 0.062 億円/人</t>
+          <t xml:space="preserve">全社 6,086.96 千円/人 / 補助 6,000 千円/人 / ベース 6,153.85 千円/人</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / ベース 0.063 億円/人</t>
+          <t xml:space="preserve">全社 6,225.11 千円/人 / 補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.062 億円/人 / ベース 0.064 億円/人</t>
+          <t xml:space="preserve">全社 6,327.05 千円/人 / 補助 6,235.31 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / ベース 0.066 億円/人</t>
+          <t xml:space="preserve">全社 6,494.68 千円/人 / 補助 6,408.22 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.067 億円/人 / 補助 0.066 億円/人 / ベース 0.067 億円/人</t>
+          <t xml:space="preserve">全社 6,705.07 千円/人 / 補助 6,694.92 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / ベース 0.069 億円/人</t>
+          <t xml:space="preserve">全社 7,026.14 千円/人 / 補助 7,219.08 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / ベース 0.07 億円/人</t>
+          <t xml:space="preserve">全社 7,373.68 千円/人 / 補助 7,852.39 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額（参考）（億円/人）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額（参考）（千円/人）</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -4372,47 +4372,47 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.182 億円/人 / 補助 0.18 億円/人 / ベース 0.183 億円/人</t>
+          <t xml:space="preserve">全社 18,240 千円/人 / 補助 18,000 千円/人 / ベース 18,400 千円/人</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.19 億円/人 / ベース 0.193 億円/人</t>
+          <t xml:space="preserve">全社 19,120 千円/人 / 補助 19,000 千円/人 / ベース 19,200 千円/人</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.2 億円/人 / ベース 0.2 億円/人</t>
+          <t xml:space="preserve">全社 20,000 千円/人 / 補助 20,000 千円/人 / ベース 20,000 千円/人</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.208 億円/人 / 補助 0.21 億円/人 / ベース 0.207 億円/人</t>
+          <t xml:space="preserve">全社 20,912.8 千円/人 / 補助 21,082 千円/人 / ベース 20,800 千円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.218 億円/人 / 補助 0.22 億円/人 / ベース 0.217 億円/人</t>
+          <t xml:space="preserve">全社 21,868.2 千円/人 / 補助 22,222.5 千円/人 / ベース 21,632 千円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.228 億円/人 / 補助 0.235 億円/人 / ベース 0.223 億円/人</t>
+          <t xml:space="preserve">全社 22,868.2 千円/人 / 補助 23,424.5 千円/人 / ベース 22,497.33 千円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.25 億円/人 / ベース 0.237 億円/人</t>
+          <t xml:space="preserve">全社 23,979.8 千円/人 / 補助 24,685 千円/人 / ベース 23,509.67 千円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.252 億円/人 / 補助 0.26 億円/人 / ベース 0.247 億円/人</t>
+          <t xml:space="preserve">全社 25,145.8 千円/人 / 補助 26,013 千円/人 / ベース 24,567.67 千円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.264 億円/人 / 補助 0.275 億円/人 / ベース 0.257 億円/人</t>
+          <t xml:space="preserve">全社 26,368.8 千円/人 / 補助 27,412.5 千円/人 / ベース 25,673 千円/人</t>
         </is>
       </c>
     </row>
@@ -4439,42 +4439,42 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / ベース 1.95 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 2 % / ベース 2 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / ベース 2.02 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 2 % / ベース 2 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.2 % / 補助 2.22 % / ベース 2.19 %</t>
+          <t xml:space="preserve">全社 2.27 % / 補助 2.29 % / ベース 2.27 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.68 % / 補助 1.65 % / ベース 1.72 %</t>
+          <t xml:space="preserve">全社 1.64 % / 補助 1.6 % / ベース 1.68 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.64 % / 補助 2.74 % / ベース 2.57 %</t>
+          <t xml:space="preserve">全社 2.65 % / 補助 2.77 % / ベース 2.56 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.84 % / 補助 3.65 % / ベース 2.2 %</t>
+          <t xml:space="preserve">全社 3.24 % / 補助 4.47 % / ベース 2.28 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.16 % / 補助 8.65 % / ベース 2.52 %</t>
+          <t xml:space="preserve">全社 4.79 % / 補助 7.83 % / ベース 2.49 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 % / 補助 8.8 % / ベース 2.08 %</t>
+          <t xml:space="preserve">全社 4.95 % / 補助 8.77 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / ベース 58.76 %</t>
+          <t xml:space="preserve">全社 49.01 % / 補助 40.02 % / ベース 58.72 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -4511,32 +4511,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.62 % / 補助 41.5 % / ベース 60.65 %</t>
+          <t xml:space="preserve">全社 50.68 % / 補助 41.55 % / ベース 60.72 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.53 % / 補助 42.3 % / ベース 61.79 %</t>
+          <t xml:space="preserve">全社 51.57 % / 補助 42.36 % / ベース 61.81 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 52.44 % / 補助 43.15 % / ベース 62.88 %</t>
+          <t xml:space="preserve">全社 52.48 % / 補助 43.17 % / ベース 62.92 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 46.36 % / 補助 35.96 % / ベース 59.55 %</t>
+          <t xml:space="preserve">全社 46.35 % / 補助 35.92 % / ベース 59.58 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.43 % / 補助 31.28 % / ベース 59.17 %</t>
+          <t xml:space="preserve">全社 42.3 % / 補助 31.06 % / ベース 59.15 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.61 % / 補助 27.29 % / ベース 58.69 %</t>
+          <t xml:space="preserve">全社 38.38 % / 補助 26.9 % / ベース 58.74 %</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">従業員1人当たり売上高（億円/人）</t>
+          <t xml:space="preserve">従業員1人当たり売上高（千円/人）</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -4620,54 +4620,54 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / ベース 0.537 億円/人</t>
+          <t xml:space="preserve">全社 64,952.38 千円/人 / 補助 80,000 千円/人 / ベース 53,666.67 千円/人</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
+          <t xml:space="preserve">全社 65,090.91 千円/人 / 補助 80,000 千円/人 / ベース 53,760 千円/人</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
+          <t xml:space="preserve">全社 65,217.39 千円/人 / 補助 80,000 千円/人 / ベース 53,846.15 千円/人</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / ベース 0.541 億円/人</t>
+          <t xml:space="preserve">全社 65,544.82 千円/人 / 補助 80,311.9 千円/人 / ベース 54,059.31 千円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / ベース 0.54 億円/人</t>
+          <t xml:space="preserve">全社 65,466.69 千円/人 / 補助 80,080.23 千円/人 / ベース 53,962.42 千円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.66 億円/人 / 補助 0.808 億円/人 / ベース 0.543 億円/人</t>
+          <t xml:space="preserve">全社 66,039.55 千円/人 / 補助 80,773.61 千円/人 / ベース 54,333.03 千円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.733 億円/人 / 補助 0.961 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">全社 73,601.62 千円/人 / 補助 96,890.16 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.815 億円/人 / 補助 1.144 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">全社 81,837.63 千円/人 / 補助 115,295 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.909 億円/人 / 補助 1.362 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">全社 91,527.33 千円/人 / 補助 138,396.44 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1人当たり営業利益（億円/人）</t>
+          <t xml:space="preserve">1人当たり営業利益（千円/人）</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -4682,54 +4682,54 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / ベース 0.035 億円/人</t>
+          <t xml:space="preserve">全社 5,237.06 千円/人 / 補助 7,532.99 千円/人 / ベース 3,515.12 千円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / ベース 0.034 億円/人</t>
+          <t xml:space="preserve">全社 5,142.4 千円/人 / 補助 7,417.64 千円/人 / ベース 3,413.22 千円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
+          <t xml:space="preserve">全社 5,043.48 千円/人 / 補助 7,300 千円/人 / ベース 3,307.69 千円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
+          <t xml:space="preserve">全社 5,023.93 千円/人 / 補助 7,291.83 千円/人 / ベース 3,260.01 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / ベース 0.032 億円/人</t>
+          <t xml:space="preserve">全社 4,959.99 千円/人 / 補助 7,228.18 千円/人 / ベース 3,174.39 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.049 億円/人 / 補助 0.073 億円/人 / ベース 0.031 億円/人</t>
+          <t xml:space="preserve">全社 4,940.56 千円/人 / 補助 7,241.79 千円/人 / ベース 3,112.19 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.109 億円/人 / ベース 0.039 億円/人</t>
+          <t xml:space="preserve">全社 6,981.53 千円/人 / 補助 10,993.55 千円/人 / ベース 3,887.29 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.089 億円/人 / 補助 0.151 億円/人 / ベース 0.041 億円/人</t>
+          <t xml:space="preserve">全社 8,950.85 千円/人 / 補助 15,323.24 千円/人 / ベース 4,131.73 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.112 億円/人 / 補助 0.205 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 11,364.71 千円/人 / 補助 20,929.59 千円/人 / ベース 4,361.86 千円/人</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">労働生産性（億円/人）</t>
+          <t xml:space="preserve">労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -4744,47 +4744,47 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
+          <t xml:space="preserve">全社 12,733.95 千円/人 / 補助 15,358.7 千円/人 / ベース 10,770.73 千円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
+          <t xml:space="preserve">全社 12,772.89 千円/人 / 補助 15,376.29 千円/人 / ベース 10,800 千円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
+          <t xml:space="preserve">全社 12,808.51 千円/人 / 補助 15,392.16 千円/人 / ベース 10,827.07 千円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 12,874.83 千円/人 / 補助 15,441.33 千円/人 / ベース 10,884.87 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 12,854.77 千円/人 / 補助 15,388.42 千円/人 / ベース 10,866.55 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.155 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 12,960.21 千円/人 / 補助 15,510.6 千円/人 / ベース 10,940.44 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / ベース 0.118 億円/人</t>
+          <t xml:space="preserve">全社 15,141.18 千円/人 / 補助 19,471.74 千円/人 / ベース 11,809.99 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.24 億円/人 / ベース 0.122 億円/人</t>
+          <t xml:space="preserve">全社 17,361.06 千円/人 / 補助 24,224.77 千円/人 / ベース 12,181.69 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.199 億円/人 / 補助 0.299 億円/人 / ベース 0.125 億円/人</t>
+          <t xml:space="preserve">全社 20,049.71 千円/人 / 補助 30,360.06 千円/人 / ベース 12,512.91 千円/人</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4836,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.82 % / 補助 2.59 % / ベース 4.79 %</t>
+          <t xml:space="preserve">全社 3.44 % / 補助 1.72 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.68 % / 補助 2.52 % / ベース 4.58 %</t>
+          <t xml:space="preserve">全社 3.69 % / 補助 2.54 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.9 % / 補助 2.46 % / ベース 5 %</t>
+          <t xml:space="preserve">全社 3.56 % / 補助 1.65 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4883,32 +4883,32 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / ベース 0.41 pt</t>
+          <t xml:space="preserve">全社 0.52 pt / 補助 0.41 pt / ベース 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / ベース -0.18 pt</t>
+          <t xml:space="preserve">全社 -0.13 pt / 補助 -0.3 pt / ベース -0.19 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.91 pt / 補助 0.91 pt / ベース 0.71 pt</t>
+          <t xml:space="preserve">全社 0.91 pt / 補助 0.9 pt / ベース 0.71 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.46 pt / 補助 19.43 pt / ベース 2.52 pt</t>
+          <t xml:space="preserve">全社 11.84 pt / 補助 20.3 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.61 pt / 補助 19.5 pt / ベース 1.67 pt</t>
+          <t xml:space="preserve">全社 11.6 pt / 補助 19.48 pt / ベース 1.68 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.93 pt / 補助 19.57 pt / ベース 1.27 pt</t>
+          <t xml:space="preserve">全社 12.26 pt / 補助 20.37 pt / ベース 1.26 pt</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / ベース 3.96 倍</t>
+          <t xml:space="preserve">全社 4.39 倍 / 補助 4.71 倍 / ベース 3.96 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -5193,32 +5193,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.45 倍 / 補助 4.83 倍 / ベース 3.94 倍</t>
+          <t xml:space="preserve">全社 4.44 倍 / 補助 4.83 倍 / ベース 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.58 倍 / 補助 5.02 倍 / ベース 3.99 倍</t>
+          <t xml:space="preserve">全社 4.57 倍 / 補助 5.01 倍 / ベース 3.98 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.7 倍 / 補助 5.21 倍 / ベース 4.03 倍</t>
+          <t xml:space="preserve">全社 4.7 倍 / 補助 5.2 倍 / ベース 4.03 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.4 倍 / 補助 7.48 倍 / ベース 4.97 倍</t>
+          <t xml:space="preserve">全社 6.41 倍 / 補助 7.49 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.17 倍 / 補助 10.24 倍 / ベース 5.4 倍</t>
+          <t xml:space="preserve">全社 8.19 倍 / 補助 10.27 倍 / ベース 5.41 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.41 倍 / 補助 13.8 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 10.45 倍 / 補助 13.87 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 60.67 %</t>
+          <t xml:space="preserve">構成比 60.66 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.02 % / ベース 7.31 %</t>
+          <t xml:space="preserve">補助 22.02 % / ベース 7.32 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.02 % / ベース 6.25 %</t>
+          <t xml:space="preserve">補助 22.02 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / ベース 6.27 %</t>
+          <t xml:space="preserve">補助 22.02 % / ベース 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.01 pt</t>
+          <t xml:space="preserve">差 0 pt</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.01 pt</t>
+          <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0 pt</t>
+          <t xml:space="preserve">差 0 pt</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.01 pt</t>
+          <t xml:space="preserve">差 0 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.86 pt</t>
+          <t xml:space="preserve">差 2.87 pt</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.16 pt</t>
+          <t xml:space="preserve">差 3.14 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
@@ -5580,24 +5580,24 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.35 pt</t>
+          <t xml:space="preserve">差 4.36 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.95 pt</t>
+          <t xml:space="preserve">差 5.98 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.4 pt</t>
+          <t xml:space="preserve">差 7.5 pt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">事業別1人当たり売上高（億円/人）</t>
+          <t xml:space="preserve">事業別1人当たり売上高（千円/人）</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -5612,54 +5612,54 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.537 億円/人</t>
+          <t xml:space="preserve">補助 80,000 千円/人 / ベース 53,666.67 千円/人</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
+          <t xml:space="preserve">補助 80,000 千円/人 / ベース 53,760 千円/人</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
+          <t xml:space="preserve">補助 80,000 千円/人 / ベース 53,846.15 千円/人</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.803 億円/人 / ベース 0.541 億円/人</t>
+          <t xml:space="preserve">補助 80,311.9 千円/人 / ベース 54,059.31 千円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / ベース 0.54 億円/人</t>
+          <t xml:space="preserve">補助 80,080.23 千円/人 / ベース 53,962.42 千円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.808 億円/人 / ベース 0.543 億円/人</t>
+          <t xml:space="preserve">補助 80,773.61 千円/人 / ベース 54,333.03 千円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.961 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">補助 96,890.16 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.144 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">補助 115,295 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.362 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">補助 138,396.44 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">事業別従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">事業別従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -5674,47 +5674,47 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.058 億円/人 / ベース 0.059 億円/人</t>
+          <t xml:space="preserve">補助 5,767.01 千円/人 / ベース 5,914.88 千円/人</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.059 億円/人 / ベース 0.06 億円/人</t>
+          <t xml:space="preserve">補助 5,882.36 千円/人 / ベース 6,033.18 千円/人</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.06 億円/人 / ベース 0.062 億円/人</t>
+          <t xml:space="preserve">補助 6,000 千円/人 / ベース 6,153.85 千円/人</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.061 億円/人 / ベース 0.063 億円/人</t>
+          <t xml:space="preserve">補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.062 億円/人 / ベース 0.064 億円/人</t>
+          <t xml:space="preserve">補助 6,235.31 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.064 億円/人 / ベース 0.066 億円/人</t>
+          <t xml:space="preserve">補助 6,408.22 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.066 億円/人 / ベース 0.067 億円/人</t>
+          <t xml:space="preserve">補助 6,694.92 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.072 億円/人 / ベース 0.069 億円/人</t>
+          <t xml:space="preserve">補助 7,219.08 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.078 億円/人 / ベース 0.07 億円/人</t>
+          <t xml:space="preserve">補助 7,852.39 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
@@ -5741,42 +5741,42 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 86.67 %</t>
+          <t xml:space="preserve">寄与率 84.66 %</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 86.67 %</t>
+          <t xml:space="preserve">寄与率 88.32 %</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 77.08 %</t>
+          <t xml:space="preserve">寄与率 77.92 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 84.09 %</t>
+          <t xml:space="preserve">寄与率 83.05 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 84.09 %</t>
+          <t xml:space="preserve">寄与率 84.74 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.47 %</t>
+          <t xml:space="preserve">寄与率 76.51 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.47 %</t>
+          <t xml:space="preserve">寄与率 89.36 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.59 %</t>
+          <t xml:space="preserve">寄与率 90.94 %</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -6216,53 +6216,61 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1.6653345369377348e-14</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>2.0030662342518046</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D19" s="2">
-        <v>1.9325330501846927</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2.0735994183189166</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>5.409356725146197</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6270,37 +6278,37 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>5.701754385964919</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <v>0</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6321,11 +6329,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>4.257246376811585</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6333,20 +6341,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>4.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>4.438405797101453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6354,20 +6362,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E24" s="2">
-        <v>0.013457556935819737</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>1.984645846924027</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6375,45 +6383,41 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>1.9139457023717443</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E25" s="2">
-        <v>2.0553459914763095</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>4.083333333333339</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6421,41 +6425,45 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>3.9166666666666683</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E27" s="2">
-        <v>4.250000000000009</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>22</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6463,20 +6471,20 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>15</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E29" s="2">
-        <v>30</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>6.257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6484,20 +6492,20 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>6.438405797101453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>1.5</v>
+        <v>22</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6505,20 +6513,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.5</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6526,20 +6534,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>0.5</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E32" s="2">
-        <v>0.5134575569358197</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>7.000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6547,20 +6555,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>2.484645846924027</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6568,45 +6576,41 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <v>2.4139457023717443</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="2">
-        <v>2.5553459914763095</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>4.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D35" s="2">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>4</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6614,41 +6618,45 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>0</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E36" s="2">
-        <v>8</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>4.583333333333338</v>
+        <v>4.5</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="2">
-        <v>4.416666666666668</v>
-      </c>
-      <c r="E37" s="2">
-        <v>4.750000000000009</v>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6659,17 +6667,17 @@
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>0.5</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6677,20 +6685,20 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>4.416666666666668</v>
       </c>
       <c r="E39" s="2">
-        <v>1</v>
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>5.380116959064325</v>
+        <v>1.5</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6698,57 +6706,99 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>6.555555555555557</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>23</v>
+        <v>0.5</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E42" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B42" s="2">
-        <v>7.66</v>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="B44" s="2">
+        <v>766000</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.67億円）</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6760,7 +6810,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6809,7 +6859,7 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <v>136.4</v>
+        <v>13640000</v>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
@@ -6824,7 +6874,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>0.09</v>
+        <v>9120</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -6839,7 +6889,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>11.67</v>
+        <v>1167376</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -6854,7 +6904,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0.62</v>
+        <v>61441</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -6869,7 +6919,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>2.45</v>
+        <v>245400</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -6884,7 +6934,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0.64</v>
+        <v>63600</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -6899,7 +6949,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>10.73</v>
+        <v>1072503</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6914,7 +6964,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>10.73</v>
+        <v>1072503</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6929,7 +6979,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>7.51</v>
+        <v>750752.1</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6974,7 +7024,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>92.75</v>
+        <v>9275200</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -6989,7 +7039,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0.73</v>
+        <v>72600</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -7004,7 +7054,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>32.65</v>
+        <v>3265017</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -7019,7 +7069,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.82</v>
+        <v>82080</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -7034,7 +7084,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>143.2</v>
+        <v>14320000</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -7049,7 +7099,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0.1</v>
+        <v>9560</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -7064,7 +7114,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>12.47</v>
+        <v>1247324</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -7079,7 +7129,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.66</v>
+        <v>65648</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -7094,7 +7144,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>2.58</v>
+        <v>257700</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -7109,7 +7159,7 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0.67</v>
+        <v>66800</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -7124,7 +7174,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>11.01</v>
+        <v>1102688</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -7139,7 +7189,7 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>11.01</v>
+        <v>1102688</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7204,7 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <v>7.71</v>
+        <v>771881.6</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -7199,7 +7249,7 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <v>97.38</v>
+        <v>9737600</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -7214,7 +7264,7 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.76</v>
+        <v>76300</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -7229,7 +7279,7 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <v>34.52</v>
+        <v>3451072</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -7244,7 +7294,7 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.86</v>
+        <v>86040</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -7259,7 +7309,7 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <v>150</v>
+        <v>15000000</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -7274,7 +7324,7 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0.1</v>
+        <v>10000</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -7289,7 +7339,7 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <v>13.3</v>
+        <v>1330000</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -7304,7 +7354,7 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -7319,7 +7369,7 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
@@ -7334,7 +7384,7 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -7349,7 +7399,7 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <v>11.3</v>
+        <v>1130000</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -7364,7 +7414,7 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <v>11.3</v>
+        <v>1130000</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -7379,7 +7429,7 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <v>7.91</v>
+        <v>791000</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -7424,7 +7474,7 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <v>102</v>
+        <v>10200000</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
@@ -7439,7 +7489,7 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
@@ -7454,7 +7504,7 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>36.4</v>
+        <v>3640000</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
@@ -7469,7 +7519,7 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
@@ -7484,7 +7534,7 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
@@ -7529,7 +7579,7 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <v>23.04</v>
+        <v>2304000</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7544,7 +7594,7 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <v>6.78</v>
+        <v>677969</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7559,7 +7609,7 @@
         </is>
       </c>
       <c r="B53" s="2">
-        <v>5.19</v>
+        <v>519031</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7574,7 +7624,7 @@
         </is>
       </c>
       <c r="B54" s="2">
-        <v>0.36</v>
+        <v>36000</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7589,7 +7639,7 @@
         </is>
       </c>
       <c r="B55" s="2">
-        <v>1.35</v>
+        <v>135000</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7604,7 +7654,7 @@
         </is>
       </c>
       <c r="B56" s="2">
-        <v>0.45</v>
+        <v>45000</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7619,7 +7669,7 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <v>76</v>
+        <v>7600000</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7664,7 +7714,7 @@
         </is>
       </c>
       <c r="B60" s="2">
-        <v>24.32</v>
+        <v>2432000</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
@@ -7679,7 +7729,7 @@
         </is>
       </c>
       <c r="B61" s="2">
-        <v>7.04</v>
+        <v>704676</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
@@ -7694,7 +7744,7 @@
         </is>
       </c>
       <c r="B62" s="2">
-        <v>5.59</v>
+        <v>558824</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
@@ -7709,7 +7759,7 @@
         </is>
       </c>
       <c r="B63" s="2">
-        <v>0.38</v>
+        <v>38000</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
@@ -7724,7 +7774,7 @@
         </is>
       </c>
       <c r="B64" s="2">
-        <v>1.43</v>
+        <v>142500</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7739,7 +7789,7 @@
         </is>
       </c>
       <c r="B65" s="2">
-        <v>0.47</v>
+        <v>47500</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7754,7 +7804,7 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>80</v>
+        <v>8000000</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7799,7 +7849,7 @@
         </is>
       </c>
       <c r="B69" s="2">
-        <v>25.6</v>
+        <v>2560000</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7814,7 +7864,7 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <v>7.3</v>
+        <v>730000</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7829,7 +7879,7 @@
         </is>
       </c>
       <c r="B71" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7844,7 +7894,7 @@
         </is>
       </c>
       <c r="B72" s="2">
-        <v>0.4</v>
+        <v>40000</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7859,7 +7909,7 @@
         </is>
       </c>
       <c r="B73" s="2">
-        <v>1.5</v>
+        <v>150000</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7874,7 +7924,7 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>0.5</v>
+        <v>50000</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -7889,7 +7939,7 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7904,7 +7954,7 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>19</v>
+        <v>1900000</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7919,7 +7969,7 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7934,7 +7984,7 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7949,7 +7999,7 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7964,7 +8014,7 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>67</v>
+        <v>6700000</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7979,7 +8029,7 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>39</v>
+        <v>3900000</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -7994,7 +8044,7 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>65</v>
+        <v>6500000</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8009,7 +8059,7 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>36</v>
+        <v>3600000</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8024,7 +8074,7 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8039,7 +8089,7 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8054,7 +8104,7 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>75</v>
+        <v>7500000</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8069,7 +8119,7 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>29</v>
+        <v>2900000</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8084,7 +8134,7 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8099,7 +8149,7 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>57</v>
+        <v>5700000</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8114,7 +8164,7 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>54</v>
+        <v>5400000</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8129,7 +8179,7 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8144,7 +8194,7 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8159,7 +8209,7 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>53</v>
+        <v>5300000</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8174,7 +8224,7 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8189,7 +8239,7 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>20</v>
+        <v>2000000</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8204,7 +8254,7 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8219,7 +8269,7 @@
         </is>
       </c>
       <c r="B97" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8234,7 +8284,7 @@
         </is>
       </c>
       <c r="B98" s="2">
-        <v>25</v>
+        <v>2500000</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8249,7 +8299,7 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8264,7 +8314,7 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>41</v>
+        <v>4100000</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8279,7 +8329,7 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>71</v>
+        <v>7100000</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8294,7 +8344,7 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>38</v>
+        <v>3800000</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8309,7 +8359,7 @@
         </is>
       </c>
       <c r="B103" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8324,7 +8374,7 @@
         </is>
       </c>
       <c r="B104" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8339,7 +8389,7 @@
         </is>
       </c>
       <c r="B105" s="2">
-        <v>79</v>
+        <v>7900000</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8354,7 +8404,7 @@
         </is>
       </c>
       <c r="B106" s="2">
-        <v>31</v>
+        <v>3100000</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8369,7 +8419,7 @@
         </is>
       </c>
       <c r="B107" s="2">
-        <v>28</v>
+        <v>2800000</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8384,7 +8434,7 @@
         </is>
       </c>
       <c r="B108" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8399,7 +8449,7 @@
         </is>
       </c>
       <c r="B109" s="2">
-        <v>61</v>
+        <v>6100000</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8414,7 +8464,7 @@
         </is>
       </c>
       <c r="B110" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8429,7 +8479,7 @@
         </is>
       </c>
       <c r="B111" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8444,7 +8494,7 @@
         </is>
       </c>
       <c r="B112" s="2">
-        <v>58</v>
+        <v>5800000</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8459,7 +8509,7 @@
         </is>
       </c>
       <c r="B113" s="2">
-        <v>156</v>
+        <v>15600000</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8474,7 +8524,7 @@
         </is>
       </c>
       <c r="B114" s="2">
-        <v>22</v>
+        <v>2200000</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8489,7 +8539,7 @@
         </is>
       </c>
       <c r="B115" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8504,7 +8554,7 @@
         </is>
       </c>
       <c r="B116" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8519,7 +8569,7 @@
         </is>
       </c>
       <c r="B117" s="2">
-        <v>27</v>
+        <v>2700000</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8534,7 +8584,7 @@
         </is>
       </c>
       <c r="B118" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8549,7 +8599,7 @@
         </is>
       </c>
       <c r="B119" s="2">
-        <v>43</v>
+        <v>4300000</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8564,7 +8614,7 @@
         </is>
       </c>
       <c r="B120" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8579,7 +8629,7 @@
         </is>
       </c>
       <c r="B121" s="2">
-        <v>40</v>
+        <v>4000000</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8594,7 +8644,7 @@
         </is>
       </c>
       <c r="B122" s="2">
-        <v>9</v>
+        <v>900000</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8609,7 +8659,7 @@
         </is>
       </c>
       <c r="B123" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8624,7 +8674,7 @@
         </is>
       </c>
       <c r="B124" s="2">
-        <v>83</v>
+        <v>8300000</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8639,7 +8689,7 @@
         </is>
       </c>
       <c r="B125" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8654,7 +8704,7 @@
         </is>
       </c>
       <c r="B126" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8669,7 +8719,7 @@
         </is>
       </c>
       <c r="B127" s="2">
-        <v>73</v>
+        <v>7300000</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8734,7 @@
         </is>
       </c>
       <c r="B128" s="2">
-        <v>70</v>
+        <v>7000000</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8699,7 +8749,7 @@
         </is>
       </c>
       <c r="B129" s="2">
-        <v>11</v>
+        <v>1100000</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8714,7 +8764,7 @@
         </is>
       </c>
       <c r="B130" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8729,7 +8779,7 @@
         </is>
       </c>
       <c r="B131" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8774,7 +8824,7 @@
         </is>
       </c>
       <c r="B134" s="2">
-        <v>15</v>
+        <v>1500000</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8789,7 +8839,7 @@
         </is>
       </c>
       <c r="B135" s="2">
-        <v>200</v>
+        <v>20000000</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
@@ -9400,7 +9450,7 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
         </is>
       </c>
       <c r="B176" s="2">
@@ -9415,11 +9465,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>1</v>
+        <v>10000000000</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9430,7 +9480,7 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B178" s="2">
@@ -9445,11 +9495,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9460,7 +9510,7 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B180" s="2">
@@ -9475,11 +9525,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.03</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9490,26 +9540,26 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.7</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9520,26 +9570,26 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9550,26 +9600,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9580,26 +9630,26 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9610,26 +9660,26 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.05701754385964919</v>
+        <v>10000000000</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9640,26 +9690,26 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9670,11 +9720,11 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>-0.5</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9685,11 +9735,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9700,26 +9750,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9730,11 +9780,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.04263157894736836</v>
+        <v>-0.5</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9745,11 +9795,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.06555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9760,26 +9810,26 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.05701754385964919</v>
+        <v>1</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9790,11 +9840,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.05</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9805,11 +9855,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.1</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9820,11 +9870,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9835,11 +9885,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9850,26 +9900,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9880,11 +9930,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.15</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9895,11 +9945,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0.3</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9910,26 +9960,26 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.3</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9940,56 +9990,56 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.03</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10000,56 +10050,56 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>23</v>
+        <v>0.03</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10060,11 +10110,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>23</v>
+        <v>100000</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10075,11 +10125,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0.2</v>
+        <v>5000000</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10090,11 +10140,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10105,26 +10155,26 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.68</v>
+        <v>23</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10135,11 +10185,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -10150,41 +10200,41 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.045833333333333386</v>
+        <v>0</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.68</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
@@ -10195,11 +10245,11 @@
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>-0.005</v>
+        <v>0.95</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10210,26 +10260,26 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.045</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10240,11 +10290,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.04</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10255,11 +10305,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.02484645846924027</v>
+        <v>-0.005</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10270,11 +10320,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.9</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10285,11 +10335,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10300,11 +10350,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.04</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10315,11 +10365,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10330,26 +10380,26 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10360,11 +10410,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.25</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10375,11 +10425,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.015</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10390,26 +10440,26 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.68</v>
+        <v>0.005</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10420,41 +10470,41 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectBaseYearSales</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10465,11 +10515,11 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.05409356725146197</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
@@ -10480,11 +10530,11 @@
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
@@ -10495,56 +10545,56 @@
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectFirstYearSales</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.05380116959064325</v>
+        <v>0</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.04</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10555,11 +10605,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.07</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10570,11 +10620,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.05</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10585,26 +10635,26 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10615,11 +10665,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10630,26 +10680,26 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.015</v>
+        <v>0.07</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10660,11 +10710,11 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>7.66</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10675,11 +10725,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7</v>
+        <v>0.005</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10690,11 +10740,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>3.5</v>
+        <v>0.22</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10755,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>35</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10720,26 +10770,26 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>252.69</v>
+        <v>0.015</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10750,11 +10800,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>82.4</v>
+        <v>766000</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10765,11 +10815,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10780,11 +10830,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10845,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>3.74</v>
+        <v>35</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10860,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>2.85</v>
+        <v>15</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10875,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>70</v>
+        <v>25269000</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10840,11 +10890,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>15</v>
+        <v>8240000</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10905,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10920,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10885,11 +10935,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>40</v>
+        <v>374000</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10950,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>23</v>
+        <v>285000</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10965,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10930,11 +10980,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10945,26 +10995,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10975,11 +11025,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -10990,11 +11040,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>136.84</v>
+        <v>23</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11005,11 +11055,11 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>74.8</v>
+        <v>10</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11020,11 +11070,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11035,26 +11085,26 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>33.43</v>
+        <v>35</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11065,11 +11115,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>18.78</v>
+        <v>22</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11130,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>350</v>
+        <v>13684000</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11095,13 +11145,103 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>7480000</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>95</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>60</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B292" s="2">
+        <v>3343000</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B293" s="2">
+        <v>1878000</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B294" s="2">
+        <v>350</v>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B289" s="2">
+      <c r="B295" s="2">
         <v>213</v>
       </c>
-      <c r="C289" s="0" t="inlineStr">
+      <c r="C295" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11113,7 +11253,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
@@ -11129,7 +11269,14 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwib3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMC42NiwwLjddLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLDAuMDNdLCJvdGhlclNnYVJhdGVFbmQiOlswLDAuMDFdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLjQ1LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjoxLjM1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MC40NywiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MS40MywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MC41LCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTE0IjoxLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuNywiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MC42NiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuNywiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNDQ0MTQzOTIyNTI2NjIyLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjEzOTExMTM4MzkwMTg2LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAyMDI4ODMzNDM3MjY5MjAzNSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MjUwMDAwMDAwMDAwNSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyMDQ4OTQwODMyNzIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg1NTEwOTc4MjMxNjU4MTcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjM2NTE2NTY0MTczNzc1Niwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgzNzkyMDAzMDQ3NjM2LCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MjAwMDAwLCJjb2dzIjo0ODk2MDAwLCJlbXBsb3llZVBheSI6NTE5MDMxLCJvZmZpY2VyUGF5IjozNjAwMCwiZGVwcmVjaWF0aW9uIjoxODAwMDAsIm90aGVyU2dhIjo5MDAwMDAsImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQ5MzA3OSwiZW1wbG95ZWVCb251cyI6MjU5NTIsIm9mZmljZXJDb21wZW5zYXRpb24iOjMyNDAwLCJvZmZpY2VyQm9udXMiOjM2MDAsImNvZ3NEZXByZWNpYXRpb24iOjQ1MDAwLCJzZ2FEZXByZWNpYXRpb24iOjEzNTAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzYwMDB9LCJvdGhlciI6eyJzYWxlcyI6NjQ0MDAwMCwiY29ncyI6NDM3OTIwMCwiZW1wbG95ZWVQYXkiOjcwOTc4Niwib2ZmaWNlclBheSI6NTUyMDAsImRlcHJlY2lhdGlvbiI6MTM4MDAwLCJvdGhlclNnYSI6NzM2MDAwLCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Njc0Mjk3LCJlbXBsb3llZUJvbnVzIjozNTQ4OSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NDk2ODAsIm9mZmljZXJCb251cyI6NTUyMCwiY29nc0RlcHJlY2lhdGlvbiI6Mjc2MDAsInNnYURlcHJlY2lhdGlvbiI6MTEwNDAwLCJyZXNlYXJjaERldmVsb3BtZW50IjoyNzYwMCwib3JkaW5hcnlJbmNvbWUiOjM5NDUzNCwicHJlVGF4SW5jb21lIjozOTQ1MzQsIm5ldEluY29tZSI6NzUwNzUyLjF9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2MDAwMDAsImNvZ3MiOjUxNjgwMDAsImVtcGxveWVlUGF5Ijo1NTg4MjQsIm9mZmljZXJQYXkiOjM4MDAwLCJkZXByZWNpYXRpb24iOjE5MDAwMCwib3RoZXJTZ2EiOjk1MDAwMCwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NTMwODgzLCJlbXBsb3llZUJvbnVzIjoyNzk0MSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzQyMDAsIm9mZmljZXJCb251cyI6MzgwMCwiY29nc0RlcHJlY2lhdGlvbiI6NDc1MDAsInNnYURlcHJlY2lhdGlvbiI6MTQyNTAwLCJyZXNlYXJjaERldmVsb3BtZW50IjozODAwMH0sIm90aGVyIjp7InNhbGVzIjo2NzIwMDAwLCJjb2dzIjo0NTY5NjAwLCJlbXBsb3llZVBheSI6NzU0MTQ4LCJvZmZpY2VyUGF5Ijo1NzYwMCwiZGVwcmVjaWF0aW9uIjoxNDQwMDAsIm90aGVyU2dhIjo3NjgwMDAsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3MTY0NDEsImVtcGxveWVlQm9udXMiOjM3NzA3LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo1MTg0MCwib2ZmaWNlckJvbnVzIjo1NzYwLCJjb2dzRGVwcmVjaWF0aW9uIjoyODgwMCwic2dhRGVwcmVjaWF0aW9uIjoxMTUyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjI4ODAwLCJvcmRpbmFyeUluY29tZSI6Mzk4MDEyLCJwcmVUYXhJbmNvbWUiOjM5ODAxMiwibmV0SW5jb21lIjo3NzE4ODEuNn19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwMDAwMDAsImNvZ3MiOjU0NDAwMDAsImVtcGxveWVlUGF5Ijo2MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo1NzAwMDAsImVtcGxveWVlQm9udXMiOjMwMDAwLCJvZmZpY2VyUGF5Ijo0MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzYwMDAsIm9mZmljZXJCb251cyI6NDAwMCwiZGVwcmVjaWF0aW9uIjoyMDAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjUwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjE1MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NDAwMDAsIm90aGVyU2dhIjoxMDAwMDAwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwMDAwMDAsImNvZ3MiOjQ3NjAwMDAsImVtcGxveWVlUGF5Ijo4MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo3NjAwMDAsImVtcGxveWVlQm9udXMiOjQwMDAwLCJvZmZpY2VyUGF5Ijo2MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NTQwMDAsIm9mZmljZXJCb251cyI6NjAwMCwiZGVwcmVjaWF0aW9uIjoxNTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjMwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjEyMDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzAwMDAsIm90aGVyU2dhIjo4MDAwMDAsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjo0MDAwMDAsInByZVRheEluY29tZSI6NDAwMDAwLCJuZXRJbmNvbWUiOjc5MTAwMH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwicHJvamVjdEJhc2VZZWFyU2FsZXMiOjAsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiaW52ZXN0bWVudCI6MjMwMDAwMCwic3Vic2lkeSI6NzY2MDAwLCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMC42NiwwLjddLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RCYXNlWWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAxXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUwMDAwMCwyMDAwMDAwMF0sInN1YnNpZHkiOlsxMDAwMDAsNTAwMDAwMF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4MjQwMDAwLCJtYXgiOjI1MjY5MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0ODAwMDAsIm1heCI6MTM2ODQwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxODc4MDAwLCJtYXgiOjMzNDMwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyODUwMDAsIm1heCI6Mzc0MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1MTMwMDAsIjIwMjk6cHJvamVjdDo3LTgiOjc5MDAwMH0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzY0MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyNzUyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00Ijo3MjYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyNjUwMTcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05Ijo4MjA4MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjo5MTIwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExNjczNzYsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6NjE0NDEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6MjQ1NDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjYzNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwNzI1MDMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTA3MjUwMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3NTA3NTIuMSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyMDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMzA0MDAwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Njc3OTY5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NTE5MDMxLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MzYwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6NDUwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEzNTAwMCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzMjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5NzM3NjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6NzYzMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNDUxMDcyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6ODYwNDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6OTU2MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMjQ3MzI0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjY1NjQ4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjI1NzcwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1Ijo2NjgwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMTAyNjg4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExMDI2ODgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6NzcxODgxLjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NjAwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQzMjAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcwNDY3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjU1ODgyNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjM4MDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjQ3NTAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxNDI1MDAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExMzAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6NzkxMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAwMDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1NjAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3MzAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2MDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05Ijo0MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00Ijo1MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MTUwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLjY2LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RGaXJzdFllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjEiOjEwMDAwMDAwMDAwLCJkcml2ZXI6cHJvamVjdEJhc2VZZWFyU2FsZXMiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEJhc2VZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMDEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6aW52ZXN0bWVudCI6MjMwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwMDAwMDAsImRyaXZlcjpzdWJzaWR5Ijo3NjYwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEwMDAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAwMDAwMCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4MjQwMDAwLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0ODAwMDAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4NzgwMDAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjI4NTAwMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyNjkwMDAsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNjg0MDAwLCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzM0MzAwMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozNzQwMDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjc5OTk5OTk5OTk5OTk5OSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjc5OTk5OTk5OTk5OTk5OSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOjAsInByb2plY3RCYXNlWWVhclNhbGVzIjowLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjE2Mjc2NTUwNTQ1ODU0N2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjIwNzU1OTcxNTYxNTUsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjA4ODc1MDkxMzA3NSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODMwMzczNTU1NDk1ODM0NCwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDIwOTMxMDg1MTAyMTYyMjcsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDQ0MzM1OTE2NTkxMiwiaW52ZXN0bWVudCI6MjMwMDAwMCwi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3Vic2lkeSI6NzY2MDAwLCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.463873591495837</v>
+        <v>15.463655389422492</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>9332089.869999997</v>
+        <v>9331938.869999997</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.184711746547996</v>
+        <v>2.1848118329287347</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.91256738860758</v>
+        <v>63.91236279520185</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.020887065724626</v>
+        <v>22.02052627021196</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>7653023</v>
+        <v>7652872</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>25.09060099268099</v>
+        <v>23.15053074954352</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>1964757</v>
+        <v>1964723</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.009252613618577</v>
+        <v>7.00782348691229</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>222489.57999999996</v>
+        <v>269565.13</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.4956919060052</v>
+        <v>256.49125326370756</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>5.380301885516814</v>
+        <v>5.376457502612597</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>7976</v>
+        <v>7970</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         <v>17302362</v>
       </c>
       <c r="H3" s="4">
-        <v>19946039</v>
+        <v>19946005</v>
       </c>
       <c r="I3" s="4">
-        <v>22996374.97</v>
+        <v>22996292.97</v>
       </c>
       <c r="J3" s="4">
-        <v>26634451.869999997</v>
+        <v>26634300.869999997</v>
       </c>
     </row>
     <row r="4">
@@ -1304,13 +1304,13 @@
         <v>4.878010489642537</v>
       </c>
       <c r="H4" s="2">
-        <v>15.279283834195589</v>
+        <v>15.279087329232844</v>
       </c>
       <c r="I4" s="2">
-        <v>15.292940969382428</v>
+        <v>15.29272638806618</v>
       </c>
       <c r="J4" s="2">
-        <v>15.820219076902609</v>
+        <v>15.81997544015461</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>11765605</v>
       </c>
       <c r="H5" s="2">
-        <v>13434963</v>
+        <v>13434940</v>
       </c>
       <c r="I5" s="2">
-        <v>15407469</v>
+        <v>15407414</v>
       </c>
       <c r="J5" s="2">
-        <v>17743999</v>
+        <v>17743899</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>5536757</v>
       </c>
       <c r="H7" s="4">
-        <v>6511076</v>
+        <v>6511065</v>
       </c>
       <c r="I7" s="4">
-        <v>7588905.969999999</v>
+        <v>7588878.969999999</v>
       </c>
       <c r="J7" s="4">
-        <v>8890452.869999997</v>
+        <v>8890401.869999997</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>32.00000670428697</v>
       </c>
       <c r="H8" s="2">
-        <v>32.643453670174814</v>
+        <v>32.64345416538299</v>
       </c>
       <c r="I8" s="2">
-        <v>33.00044454789128</v>
+        <v>33.00044481038806</v>
       </c>
       <c r="J8" s="2">
-        <v>33.37952255745069</v>
+        <v>33.37952031627702</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>3828099</v>
+        <v>3828100</v>
       </c>
       <c r="F9" s="2">
-        <v>4029317</v>
+        <v>4029320</v>
       </c>
       <c r="G9" s="2">
-        <v>4242329</v>
+        <v>4242334</v>
       </c>
       <c r="H9" s="2">
-        <v>4619081</v>
+        <v>4619075</v>
       </c>
       <c r="I9" s="2">
-        <v>5073716.66</v>
+        <v>5094739.08</v>
       </c>
       <c r="J9" s="2">
-        <v>5583321.58</v>
+        <v>5630379.13</v>
       </c>
     </row>
     <row r="10">
@@ -1508,13 +1508,13 @@
         <v>114341</v>
       </c>
       <c r="H10" s="2">
-        <v>119899</v>
+        <v>119897</v>
       </c>
       <c r="I10" s="2">
-        <v>125729</v>
+        <v>125725</v>
       </c>
       <c r="J10" s="2">
-        <v>131844</v>
+        <v>131838</v>
       </c>
     </row>
     <row r="11">
@@ -1542,13 +1542,13 @@
         <v>102907</v>
       </c>
       <c r="H11" s="2">
-        <v>107909</v>
+        <v>107907</v>
       </c>
       <c r="I11" s="2">
-        <v>113156</v>
+        <v>113153</v>
       </c>
       <c r="J11" s="2">
-        <v>118660</v>
+        <v>118654</v>
       </c>
     </row>
     <row r="12">
@@ -1579,7 +1579,7 @@
         <v>11990</v>
       </c>
       <c r="I12" s="2">
-        <v>12573</v>
+        <v>12572</v>
       </c>
       <c r="J12" s="2">
         <v>13184</v>
@@ -1601,22 +1601,22 @@
         <v>1400000</v>
       </c>
       <c r="E13" s="2">
-        <v>1494027</v>
+        <v>1494028</v>
       </c>
       <c r="F13" s="2">
-        <v>1594417</v>
+        <v>1594420</v>
       </c>
       <c r="G13" s="2">
-        <v>1701607</v>
+        <v>1701612</v>
       </c>
       <c r="H13" s="2">
         <v>1817073</v>
       </c>
       <c r="I13" s="2">
-        <v>1974344.6600000001</v>
+        <v>1995380.08</v>
       </c>
       <c r="J13" s="2">
-        <v>2145739.58</v>
+        <v>2192820.13</v>
       </c>
     </row>
     <row r="14">
@@ -1635,22 +1635,22 @@
         <v>1330000</v>
       </c>
       <c r="E14" s="2">
-        <v>1419325</v>
+        <v>1419326</v>
       </c>
       <c r="F14" s="2">
-        <v>1514696</v>
+        <v>1514699</v>
       </c>
       <c r="G14" s="2">
-        <v>1616526</v>
+        <v>1616531</v>
       </c>
       <c r="H14" s="2">
-        <v>1756553</v>
+        <v>1775364</v>
       </c>
       <c r="I14" s="2">
-        <v>1909168</v>
+        <v>1951260</v>
       </c>
       <c r="J14" s="2">
-        <v>2075539</v>
+        <v>2146192</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>85081</v>
       </c>
       <c r="H15" s="2">
-        <v>92451</v>
+        <v>93441</v>
       </c>
       <c r="I15" s="2">
-        <v>100483</v>
+        <v>102698</v>
       </c>
       <c r="J15" s="2">
-        <v>109239</v>
+        <v>112958</v>
       </c>
     </row>
     <row r="16">
@@ -1752,7 +1752,7 @@
         <v>105579</v>
       </c>
       <c r="J17" s="2">
-        <v>123181</v>
+        <v>123180</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1205743</v>
+        <v>1205742</v>
       </c>
       <c r="F18" s="4">
-        <v>1249917</v>
+        <v>1249914</v>
       </c>
       <c r="G18" s="4">
-        <v>1294428</v>
+        <v>1294423</v>
       </c>
       <c r="H18" s="4">
-        <v>1891995</v>
+        <v>1891990</v>
       </c>
       <c r="I18" s="4">
-        <v>2515189.3099999987</v>
+        <v>2494139.8899999987</v>
       </c>
       <c r="J18" s="4">
-        <v>3307131.2899999972</v>
+        <v>3260022.7399999974</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.664876373392353</v>
+        <v>7.664870016418791</v>
       </c>
       <c r="F19" s="2">
-        <v>7.576353346276221</v>
+        <v>7.576335161820742</v>
       </c>
       <c r="G19" s="2">
-        <v>7.481221350009901</v>
+        <v>7.481192452221263</v>
       </c>
       <c r="H19" s="2">
-        <v>9.485567535489126</v>
+        <v>9.485558636930051</v>
       </c>
       <c r="I19" s="2">
-        <v>10.937329528159102</v>
+        <v>10.84583455800354</v>
       </c>
       <c r="J19" s="2">
-        <v>12.416742443740771</v>
+        <v>12.23994110418712</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>1130000</v>
       </c>
       <c r="E20" s="4">
-        <v>1169253</v>
+        <v>1169252</v>
       </c>
       <c r="F20" s="4">
-        <v>1211873</v>
+        <v>1211870</v>
       </c>
       <c r="G20" s="4">
-        <v>1254765</v>
+        <v>1254760</v>
       </c>
       <c r="H20" s="4">
-        <v>1733905</v>
+        <v>1714099</v>
       </c>
       <c r="I20" s="4">
-        <v>2345830</v>
+        <v>2301509</v>
       </c>
       <c r="J20" s="4">
-        <v>3125652</v>
+        <v>3051252</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>1130000</v>
       </c>
       <c r="E21" s="2">
-        <v>1169253</v>
+        <v>1169252</v>
       </c>
       <c r="F21" s="2">
-        <v>1211873</v>
+        <v>1211870</v>
       </c>
       <c r="G21" s="2">
-        <v>1254765</v>
+        <v>1254760</v>
       </c>
       <c r="H21" s="2">
-        <v>1733905</v>
+        <v>1714099</v>
       </c>
       <c r="I21" s="2">
-        <v>2345830</v>
+        <v>2301509</v>
       </c>
       <c r="J21" s="2">
-        <v>3125652</v>
+        <v>3051252</v>
       </c>
     </row>
     <row r="22">
@@ -1910,19 +1910,19 @@
         <v>818477</v>
       </c>
       <c r="F22" s="2">
-        <v>848312</v>
+        <v>848310</v>
       </c>
       <c r="G22" s="2">
-        <v>878336</v>
+        <v>878332</v>
       </c>
       <c r="H22" s="2">
-        <v>1213734</v>
+        <v>1199869</v>
       </c>
       <c r="I22" s="2">
-        <v>1642081</v>
+        <v>1611057</v>
       </c>
       <c r="J22" s="2">
-        <v>2187957</v>
+        <v>2135877</v>
       </c>
     </row>
     <row r="23">
@@ -1941,22 +1941,22 @@
         <v>1400000</v>
       </c>
       <c r="E23" s="2">
-        <v>1494027</v>
+        <v>1494028</v>
       </c>
       <c r="F23" s="2">
-        <v>1594417</v>
+        <v>1594420</v>
       </c>
       <c r="G23" s="2">
-        <v>1701607</v>
+        <v>1701612</v>
       </c>
       <c r="H23" s="2">
         <v>1817073</v>
       </c>
       <c r="I23" s="2">
-        <v>1974344.6600000001</v>
+        <v>1995380.08</v>
       </c>
       <c r="J23" s="2">
-        <v>2145739.58</v>
+        <v>2192820.13</v>
       </c>
     </row>
     <row r="24">
@@ -1984,13 +1984,13 @@
         <v>114341</v>
       </c>
       <c r="H24" s="2">
-        <v>119899</v>
+        <v>119897</v>
       </c>
       <c r="I24" s="2">
-        <v>125729</v>
+        <v>125725</v>
       </c>
       <c r="J24" s="2">
-        <v>131844</v>
+        <v>131838</v>
       </c>
     </row>
     <row r="25">
@@ -2052,13 +2052,13 @@
         <v>3460376</v>
       </c>
       <c r="H26" s="4">
-        <v>4178967</v>
+        <v>4178960</v>
       </c>
       <c r="I26" s="4">
-        <v>4965262.969999999</v>
+        <v>4965244.969999999</v>
       </c>
       <c r="J26" s="4">
-        <v>5934714.869999997</v>
+        <v>5934680.869999997</v>
       </c>
     </row>
     <row r="27">
@@ -2088,13 +2088,13 @@
         <v>4.743232914859963</v>
       </c>
       <c r="H27" s="2">
-        <v>20.766269330269303</v>
+        <v>20.76606704011357</v>
       </c>
       <c r="I27" s="2">
-        <v>18.81555824681074</v>
+        <v>18.815326540574652</v>
       </c>
       <c r="J27" s="2">
-        <v>19.524683906117435</v>
+        <v>19.52443244708626</v>
       </c>
     </row>
     <row r="28">
@@ -2122,13 +2122,13 @@
         <v>19.999442850635074</v>
       </c>
       <c r="H28" s="2">
-        <v>20.951362824468557</v>
+        <v>20.951363443456472</v>
       </c>
       <c r="I28" s="2">
-        <v>21.59150290633828</v>
+        <v>21.591501623663646</v>
       </c>
       <c r="J28" s="2">
-        <v>22.282098760532882</v>
+        <v>22.282097431303807</v>
       </c>
     </row>
     <row r="29">
@@ -2156,13 +2156,13 @@
         <v>262</v>
       </c>
       <c r="H29" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30">
@@ -2215,22 +2215,22 @@
         <v>6086.95652173913</v>
       </c>
       <c r="E31" s="2">
-        <v>6225.1125</v>
+        <v>6225.116666666667</v>
       </c>
       <c r="F31" s="2">
-        <v>6327.0515873015875</v>
+        <v>6327.063492063492</v>
       </c>
       <c r="G31" s="2">
-        <v>6494.68320610687</v>
+        <v>6494.702290076336</v>
       </c>
       <c r="H31" s="2">
-        <v>6705.066420664207</v>
+        <v>6655.945054945055</v>
       </c>
       <c r="I31" s="2">
-        <v>7026.137580071175</v>
+        <v>7001.333614035088</v>
       </c>
       <c r="J31" s="2">
-        <v>7373.675532646048</v>
+        <v>7383.23276094276</v>
       </c>
     </row>
     <row r="32">
@@ -2251,22 +2251,22 @@
         <v>1.9923071308914908</v>
       </c>
       <c r="E32" s="2">
-        <v>2.2697053571428594</v>
+        <v>2.269773809523823</v>
       </c>
       <c r="F32" s="2">
-        <v>1.6375461054171758</v>
+        <v>1.6376693137771126</v>
       </c>
       <c r="G32" s="2">
-        <v>2.6494428959883853</v>
+        <v>2.6495513791370273</v>
       </c>
       <c r="H32" s="2">
-        <v>3.2393144958866804</v>
+        <v>2.48268138656782</v>
       </c>
       <c r="I32" s="2">
-        <v>4.788485889080318</v>
+        <v>5.1891738323985415</v>
       </c>
       <c r="J32" s="2">
-        <v>4.946358488063551</v>
+        <v>5.45466289653882</v>
       </c>
     </row>
     <row r="33">
@@ -2294,13 +2294,13 @@
         <v>22868.2</v>
       </c>
       <c r="H33" s="2">
-        <v>23979.8</v>
+        <v>23979.4</v>
       </c>
       <c r="I33" s="2">
-        <v>25145.8</v>
+        <v>25145</v>
       </c>
       <c r="J33" s="2">
-        <v>26368.8</v>
+        <v>26367.6</v>
       </c>
     </row>
     <row r="34">
@@ -2330,13 +2330,13 @@
         <v>4.572850074537449</v>
       </c>
       <c r="H34" s="2">
-        <v>4.860898540331116</v>
+        <v>4.859149386484285</v>
       </c>
       <c r="I34" s="2">
-        <v>4.862425875111542</v>
+        <v>4.860838886711094</v>
       </c>
       <c r="J34" s="2">
-        <v>4.863635279052558</v>
+        <v>4.862199244382581</v>
       </c>
     </row>
     <row r="35">
@@ -2364,13 +2364,13 @@
         <v>12960.209737827716</v>
       </c>
       <c r="H35" s="2">
-        <v>15141.184782608696</v>
+        <v>15032.230215827338</v>
       </c>
       <c r="I35" s="2">
-        <v>17361.059335664333</v>
+        <v>17121.534379310342</v>
       </c>
       <c r="J35" s="2">
-        <v>20049.71239864864</v>
+        <v>19651.26115894039</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1555743</v>
+        <v>1555742</v>
       </c>
       <c r="F36" s="4">
-        <v>1599917</v>
+        <v>1599914</v>
       </c>
       <c r="G36" s="4">
-        <v>1644428</v>
+        <v>1644423</v>
       </c>
       <c r="H36" s="4">
-        <v>2241995</v>
+        <v>2241990</v>
       </c>
       <c r="I36" s="4">
-        <v>2865189.3099999987</v>
+        <v>2844139.8899999987</v>
       </c>
       <c r="J36" s="4">
-        <v>3657131.2899999972</v>
+        <v>3610022.7399999974</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>9.889817120041783</v>
+        <v>9.88981076306822</v>
       </c>
       <c r="F37" s="2">
-        <v>9.697873152148674</v>
+        <v>9.697854967693194</v>
       </c>
       <c r="G37" s="2">
-        <v>9.504066554612601</v>
+        <v>9.504037656823964</v>
       </c>
       <c r="H37" s="2">
-        <v>11.240301896531937</v>
+        <v>11.240295989096563</v>
       </c>
       <c r="I37" s="2">
-        <v>12.45930853770558</v>
+        <v>12.36781899461076</v>
       </c>
       <c r="J37" s="2">
-        <v>13.730829933538999</v>
+        <v>13.55403604404803</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.0486007228415657</v>
       </c>
       <c r="E38" s="2">
-        <v>3.029337748344374</v>
+        <v>3.0292715231788003</v>
       </c>
       <c r="F38" s="2">
-        <v>2.839414993350453</v>
+        <v>2.8392882624496796</v>
       </c>
       <c r="G38" s="2">
-        <v>2.782081820494442</v>
+        <v>2.7819620304591286</v>
       </c>
       <c r="H38" s="2">
-        <v>36.338897172755516</v>
+        <v>36.339007664086424</v>
       </c>
       <c r="I38" s="2">
-        <v>27.79641836846196</v>
+        <v>26.8578312124496</v>
       </c>
       <c r="J38" s="2">
-        <v>27.640127555829764</v>
+        <v>26.928452172582794</v>
       </c>
     </row>
   </sheetData>
@@ -2636,13 +2636,13 @@
         <v>9369739</v>
       </c>
       <c r="H3" s="4">
-        <v>11433039</v>
+        <v>11433005</v>
       </c>
       <c r="I3" s="4">
-        <v>13950695</v>
+        <v>13950613</v>
       </c>
       <c r="J3" s="4">
-        <v>17022762</v>
+        <v>17022611</v>
       </c>
     </row>
     <row r="4">
@@ -2672,13 +2672,13 @@
         <v>5.409360836980381</v>
       </c>
       <c r="H4" s="2">
-        <v>22.02089087006587</v>
+        <v>22.02052799976606</v>
       </c>
       <c r="I4" s="2">
-        <v>22.02088176205819</v>
+        <v>22.02052741164724</v>
       </c>
       <c r="J4" s="2">
-        <v>22.02088856504998</v>
+        <v>22.020523399222668</v>
       </c>
     </row>
     <row r="5">
@@ -2706,13 +2706,13 @@
         <v>54.15294744151117</v>
       </c>
       <c r="H5" s="2">
-        <v>57.31984681269299</v>
+        <v>57.31977406001854</v>
       </c>
       <c r="I5" s="2">
-        <v>60.66475702452855</v>
+        <v>60.66461676322956</v>
       </c>
       <c r="J5" s="2">
-        <v>63.91256738860758</v>
+        <v>63.91236279520185</v>
       </c>
     </row>
     <row r="6">
@@ -2740,13 +2740,13 @@
         <v>2998317</v>
       </c>
       <c r="H6" s="4">
-        <v>3715738</v>
+        <v>3715727</v>
       </c>
       <c r="I6" s="4">
-        <v>4603729</v>
+        <v>4603702</v>
       </c>
       <c r="J6" s="4">
-        <v>5702625</v>
+        <v>5702574</v>
       </c>
     </row>
     <row r="7">
@@ -2774,13 +2774,13 @@
         <v>32.00000554978106</v>
       </c>
       <c r="H7" s="2">
-        <v>32.50000284263878</v>
+        <v>32.50000327997758</v>
       </c>
       <c r="I7" s="2">
-        <v>32.999997491164414</v>
+        <v>32.9999979212383</v>
       </c>
       <c r="J7" s="2">
-        <v>33.49999841388841</v>
+        <v>33.49999597594047</v>
       </c>
     </row>
     <row r="8">
@@ -2799,22 +2799,22 @@
         <v>730000</v>
       </c>
       <c r="E8" s="4">
-        <v>765642</v>
+        <v>765641</v>
       </c>
       <c r="F8" s="4">
-        <v>802328</v>
+        <v>802325</v>
       </c>
       <c r="G8" s="4">
-        <v>840048</v>
+        <v>840043</v>
       </c>
       <c r="H8" s="4">
-        <v>1297239</v>
+        <v>1297234</v>
       </c>
       <c r="I8" s="4">
-        <v>1854112.3399999999</v>
+        <v>1833062.92</v>
       </c>
       <c r="J8" s="4">
-        <v>2574339.42</v>
+        <v>2527230.87</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2833,22 @@
         <v>9.125</v>
       </c>
       <c r="E9" s="2">
-        <v>9.07938799079636</v>
+        <v>9.079376132267189</v>
       </c>
       <c r="F9" s="2">
-        <v>9.026172624617699</v>
+        <v>9.026138874682667</v>
       </c>
       <c r="G9" s="2">
-        <v>8.96554322377603</v>
+        <v>8.965489860496648</v>
       </c>
       <c r="H9" s="2">
-        <v>11.346405798143433</v>
+        <v>11.346395807576398</v>
       </c>
       <c r="I9" s="2">
-        <v>13.290465743821365</v>
+        <v>13.139658594213744</v>
       </c>
       <c r="J9" s="2">
-        <v>15.12292435269905</v>
+        <v>14.846317465634385</v>
       </c>
     </row>
     <row r="10">
@@ -2867,22 +2867,22 @@
         <v>600000</v>
       </c>
       <c r="E10" s="2">
-        <v>644416</v>
+        <v>644417</v>
       </c>
       <c r="F10" s="2">
-        <v>692119</v>
+        <v>692122</v>
       </c>
       <c r="G10" s="2">
-        <v>743354</v>
+        <v>743359</v>
       </c>
       <c r="H10" s="2">
         <v>790000</v>
       </c>
       <c r="I10" s="2">
-        <v>873508.66</v>
+        <v>894544.08</v>
       </c>
       <c r="J10" s="2">
-        <v>965843.58</v>
+        <v>1012924.13</v>
       </c>
     </row>
     <row r="11">
@@ -2910,13 +2910,13 @@
         <v>46849</v>
       </c>
       <c r="H11" s="2">
-        <v>49370</v>
+        <v>49368</v>
       </c>
       <c r="I11" s="2">
-        <v>52026</v>
+        <v>52022</v>
       </c>
       <c r="J11" s="2">
-        <v>54825</v>
+        <v>54819</v>
       </c>
     </row>
     <row r="12">
@@ -3046,13 +3046,13 @@
         <v>1830251</v>
       </c>
       <c r="H15" s="4">
-        <v>2336609</v>
+        <v>2336602</v>
       </c>
       <c r="I15" s="4">
-        <v>2979647</v>
+        <v>2979629</v>
       </c>
       <c r="J15" s="4">
-        <v>3795008</v>
+        <v>3794974</v>
       </c>
     </row>
     <row r="16">
@@ -3082,13 +3082,13 @@
         <v>5.253862804590503</v>
       </c>
       <c r="H16" s="2">
-        <v>27.66604143366129</v>
+        <v>27.665658972457873</v>
       </c>
       <c r="I16" s="2">
-        <v>27.520137087548658</v>
+        <v>27.519748763375198</v>
       </c>
       <c r="J16" s="2">
-        <v>27.364348864143984</v>
+        <v>27.36397719313377</v>
       </c>
     </row>
     <row r="17">
@@ -3116,13 +3116,13 @@
         <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I17" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J17" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -3175,22 +3175,22 @@
         <v>6000</v>
       </c>
       <c r="E19" s="2">
-        <v>6137.295238095238</v>
+        <v>6137.304761904762</v>
       </c>
       <c r="F19" s="2">
-        <v>6235.306306306306</v>
+        <v>6235.333333333333</v>
       </c>
       <c r="G19" s="2">
-        <v>6408.224137931034</v>
+        <v>6408.267241379311</v>
       </c>
       <c r="H19" s="2">
-        <v>6694.9152542372885</v>
+        <v>6583.333333333333</v>
       </c>
       <c r="I19" s="2">
-        <v>7219.079834710744</v>
+        <v>7156.35264</v>
       </c>
       <c r="J19" s="2">
-        <v>7852.386829268293</v>
+        <v>7852.12503875969</v>
       </c>
     </row>
     <row r="20">
@@ -3211,22 +3211,22 @@
         <v>1.9999141053354874</v>
       </c>
       <c r="E20" s="2">
-        <v>2.2882539682539615</v>
+        <v>2.2884126984126896</v>
       </c>
       <c r="F20" s="2">
-        <v>1.5969749606096206</v>
+        <v>1.5972576763182866</v>
       </c>
       <c r="G20" s="2">
-        <v>2.7732050861694058</v>
+        <v>2.773450893499052</v>
       </c>
       <c r="H20" s="2">
-        <v>4.473799763171438</v>
+        <v>2.7318787647242493</v>
       </c>
       <c r="I20" s="2">
-        <v>7.829293733654152</v>
+        <v>8.704090734177218</v>
       </c>
       <c r="J20" s="2">
-        <v>8.772683071220321</v>
+        <v>9.722444291952748</v>
       </c>
     </row>
     <row r="21">
@@ -3254,13 +3254,13 @@
         <v>23424.5</v>
       </c>
       <c r="H21" s="2">
-        <v>24685</v>
+        <v>24684</v>
       </c>
       <c r="I21" s="2">
-        <v>26013</v>
+        <v>26011</v>
       </c>
       <c r="J21" s="2">
-        <v>27412.5</v>
+        <v>27409.5</v>
       </c>
     </row>
     <row r="22">
@@ -3290,13 +3290,13 @@
         <v>5.408932388345145</v>
       </c>
       <c r="H22" s="2">
-        <v>5.381118060150691</v>
+        <v>5.376849025592856</v>
       </c>
       <c r="I22" s="2">
-        <v>5.379785294713391</v>
+        <v>5.375952033706044</v>
       </c>
       <c r="J22" s="2">
-        <v>5.380002306539033</v>
+        <v>5.376571450540157</v>
       </c>
     </row>
     <row r="23">
@@ -3324,13 +3324,13 @@
         <v>15510.601694915254</v>
       </c>
       <c r="H23" s="2">
-        <v>19471.741666666665</v>
+        <v>19152.475409836065</v>
       </c>
       <c r="I23" s="2">
-        <v>24224.772357723577</v>
+        <v>23461.645669291338</v>
       </c>
       <c r="J23" s="2">
-        <v>30360.064</v>
+        <v>28969.26717557252</v>
       </c>
     </row>
     <row r="24">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.06 % / 補助 19.71 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.15 % / 補助 19.86 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.96 % / 補助 18.38 % / ベース 25.54 %</t>
+          <t xml:space="preserve">全社 21.14 % / 補助 18.65 % / ベース 25.54 %</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.94 % / 補助 13.29 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 10.85 % / 補助 13.14 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.42 % / 補助 15.12 % / ベース 7.62 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 14.85 % / ベース 7.62 %</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3973,12 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.46 % / 補助 14.72 % / ベース 8.97 %</t>
+          <t xml:space="preserve">全社 12.37 % / 補助 14.57 % / ベース 8.97 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.73 % / 補助 16.3 % / ベース 9.18 %</t>
+          <t xml:space="preserve">全社 13.55 % / 補助 16.02 % / ベース 9.18 %</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.59 % / 補助 6.26 % / ベース 12.17 %</t>
+          <t xml:space="preserve">全社 8.68 % / 補助 6.41 % / ベース 12.17 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.06 % / 補助 5.67 % / ベース 12.28 %</t>
+          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / ベース 12.28 %</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.5 % / 補助 0.32 % / ベース 0.8 %</t>
+          <t xml:space="preserve">全社 0.49 % / 補助 0.32 % / ベース 0.8 %</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.13 % / 補助 6.63 % / ベース 12.98 %</t>
+          <t xml:space="preserve">全社 9.22 % / 補助 6.79 % / ベース 12.98 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.55 % / 補助 6 % / ベース 13.08 %</t>
+          <t xml:space="preserve">全社 8.73 % / 補助 6.27 % / ベース 13.08 %</t>
         </is>
       </c>
     </row>
@@ -4325,32 +4325,32 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,225.11 千円/人 / 補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
+          <t xml:space="preserve">全社 6,225.12 千円/人 / 補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,327.05 千円/人 / 補助 6,235.31 千円/人 / ベース 6,399.28 千円/人</t>
+          <t xml:space="preserve">全社 6,327.06 千円/人 / 補助 6,235.33 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,494.68 千円/人 / 補助 6,408.22 千円/人 / ベース 6,563.38 千円/人</t>
+          <t xml:space="preserve">全社 6,494.7 千円/人 / 補助 6,408.27 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,705.07 千円/人 / 補助 6,694.92 千円/人 / ベース 6,712.9 千円/人</t>
+          <t xml:space="preserve">全社 6,655.95 千円/人 / 補助 6,583.33 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,026.14 千円/人 / 補助 7,219.08 千円/人 / ベース 6,880.23 千円/人</t>
+          <t xml:space="preserve">全社 7,001.33 千円/人 / 補助 7,156.35 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,373.68 千円/人 / 補助 7,852.39 千円/人 / ベース 7,023.19 千円/人</t>
+          <t xml:space="preserve">全社 7,383.23 千円/人 / 補助 7,852.13 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
@@ -4402,17 +4402,17 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23,979.8 千円/人 / 補助 24,685 千円/人 / ベース 23,509.67 千円/人</t>
+          <t xml:space="preserve">全社 23,979.4 千円/人 / 補助 24,684 千円/人 / ベース 23,509.67 千円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25,145.8 千円/人 / 補助 26,013 千円/人 / ベース 24,567.67 千円/人</t>
+          <t xml:space="preserve">全社 25,145 千円/人 / 補助 26,011 千円/人 / ベース 24,567.67 千円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 26,368.8 千円/人 / 補助 27,412.5 千円/人 / ベース 25,673 千円/人</t>
+          <t xml:space="preserve">全社 26,367.6 千円/人 / 補助 27,409.5 千円/人 / ベース 25,673 千円/人</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.24 % / 補助 4.47 % / ベース 2.28 %</t>
+          <t xml:space="preserve">全社 2.48 % / 補助 2.73 % / ベース 2.28 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.79 % / 補助 7.83 % / ベース 2.49 %</t>
+          <t xml:space="preserve">全社 5.19 % / 補助 8.7 % / ベース 2.49 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.95 % / 補助 8.77 % / ベース 2.08 %</t>
+          <t xml:space="preserve">全社 5.45 % / 補助 9.72 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.68 % / 補助 41.55 % / ベース 60.72 %</t>
+          <t xml:space="preserve">全社 50.68 % / 補助 41.56 % / ベース 60.72 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.3 % / 補助 31.06 % / ベース 59.15 %</t>
+          <t xml:space="preserve">全社 42.72 % / 補助 31.77 % / ベース 59.15 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.38 % / 補助 26.9 % / ベース 58.74 %</t>
+          <t xml:space="preserve">全社 39.17 % / 補助 28.14 % / ベース 58.74 %</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4650,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 73,601.62 千円/人 / 補助 96,890.16 千円/人 / ベース 55,640.52 千円/人</t>
+          <t xml:space="preserve">全社 73,062.29 千円/人 / 補助 95,275.04 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 81,837.63 千円/人 / 補助 115,295 千円/人 / ベース 56,535.5 千円/人</t>
+          <t xml:space="preserve">全社 80,688.75 千円/人 / 補助 111,604.9 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 91,527.33 千円/人 / 補助 138,396.44 千円/人 / ベース 57,212.44 千円/人</t>
+          <t xml:space="preserve">全社 89,677.78 千円/人 / 補助 131,958.22 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
@@ -4697,32 +4697,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,023.93 千円/人 / 補助 7,291.83 千円/人 / ベース 3,260.01 千円/人</t>
+          <t xml:space="preserve">全社 5,023.93 千円/人 / 補助 7,291.82 千円/人 / ベース 3,260.01 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,959.99 千円/人 / 補助 7,228.18 千円/人 / ベース 3,174.39 千円/人</t>
+          <t xml:space="preserve">全社 4,959.98 千円/人 / 補助 7,228.15 千円/人 / ベース 3,174.39 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,940.56 千円/人 / 補助 7,241.79 千円/人 / ベース 3,112.19 千円/人</t>
+          <t xml:space="preserve">全社 4,940.55 千円/人 / 補助 7,241.75 千円/人 / ベース 3,112.19 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,981.53 千円/人 / 補助 10,993.55 千円/人 / ベース 3,887.29 千円/人</t>
+          <t xml:space="preserve">全社 6,930.37 千円/人 / 補助 10,810.28 千円/人 / ベース 3,887.29 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8,950.85 千円/人 / 補助 15,323.24 千円/人 / ベース 4,131.73 千円/人</t>
+          <t xml:space="preserve">全社 8,751.37 千円/人 / 補助 14,664.5 千円/人 / ベース 4,131.73 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11,364.71 千円/人 / 補助 20,929.59 千円/人 / ベース 4,361.86 千円/人</t>
+          <t xml:space="preserve">全社 10,976.51 千円/人 / 補助 19,590.94 千円/人 / ベース 4,361.86 千円/人</t>
         </is>
       </c>
     </row>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15,141.18 千円/人 / 補助 19,471.74 千円/人 / ベース 11,809.99 千円/人</t>
+          <t xml:space="preserve">全社 15,032.23 千円/人 / 補助 19,152.48 千円/人 / ベース 11,809.99 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,361.06 千円/人 / 補助 24,224.77 千円/人 / ベース 12,181.69 千円/人</t>
+          <t xml:space="preserve">全社 17,121.53 千円/人 / 補助 23,461.65 千円/人 / ベース 12,181.69 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20,049.71 千円/人 / 補助 30,360.06 千円/人 / ベース 12,512.91 千円/人</t>
+          <t xml:space="preserve">全社 19,651.26 千円/人 / 補助 28,969.27 千円/人 / ベース 12,512.91 千円/人</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4836,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.44 % / 補助 1.72 % / ベース 4.79 %</t>
+          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 % / 補助 2.54 % / ベース 4.58 %</t>
+          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.56 % / 補助 1.65 % / ベース 5 %</t>
+          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.84 pt / 補助 20.3 pt / ベース 2.52 pt</t>
+          <t xml:space="preserve">全社 11.08 pt / 補助 18.57 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.6 pt / 補助 19.48 pt / ベース 1.68 pt</t>
+          <t xml:space="preserve">全社 10.9 pt / 補助 17.85 pt / ベース 1.68 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.26 pt / 補助 20.37 pt / ベース 1.26 pt</t>
+          <t xml:space="preserve">全社 11.61 pt / 補助 18.82 pt / ベース 1.26 pt</t>
         </is>
       </c>
     </row>
@@ -5213,12 +5213,12 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.19 倍 / 補助 10.27 倍 / ベース 5.41 倍</t>
+          <t xml:space="preserve">全社 8.13 倍 / 補助 10.17 倍 / ベース 5.41 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.45 倍 / 補助 13.87 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 10.31 倍 / 補助 13.64 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.98 pt</t>
+          <t xml:space="preserve">差 5.83 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.5 pt</t>
+          <t xml:space="preserve">差 7.22 pt</t>
         </is>
       </c>
     </row>
@@ -5642,17 +5642,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 96,890.16 千円/人 / ベース 55,640.52 千円/人</t>
+          <t xml:space="preserve">補助 95,275.04 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 115,295 千円/人 / ベース 56,535.5 千円/人</t>
+          <t xml:space="preserve">補助 111,604.9 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 138,396.44 千円/人 / ベース 57,212.44 千円/人</t>
+          <t xml:space="preserve">補助 131,958.22 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
@@ -5694,27 +5694,27 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,235.31 千円/人 / ベース 6,399.28 千円/人</t>
+          <t xml:space="preserve">補助 6,235.33 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,408.22 千円/人 / ベース 6,563.38 千円/人</t>
+          <t xml:space="preserve">補助 6,408.27 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,694.92 千円/人 / ベース 6,712.9 千円/人</t>
+          <t xml:space="preserve">補助 6,583.33 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 7,219.08 千円/人 / ベース 6,880.23 千円/人</t>
+          <t xml:space="preserve">補助 7,156.35 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 7,852.39 千円/人 / ベース 7,023.19 千円/人</t>
+          <t xml:space="preserve">補助 7,852.13 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.36 %</t>
+          <t xml:space="preserve">寄与率 88.99 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.94 %</t>
+          <t xml:space="preserve">寄与率 90.64 %</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5920,61 +5920,53 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
+          <t xml:space="preserve">補助事業 原価率（設備導入期間）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D6" s="2">
+        <v>68</v>
+      </c>
+      <c r="E6" s="2">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
+          <t xml:space="preserve">ベース事業 原価率（設備導入期間）</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D7" s="2">
+        <v>68</v>
+      </c>
+      <c r="E7" s="2">
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
+          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5995,11 +5987,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
+          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6020,11 +6012,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.5</v>
+        <v>90</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6045,11 +6037,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.4</v>
+        <v>90</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6070,11 +6062,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6095,11 +6087,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6120,7 +6112,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6145,11 +6137,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6170,11 +6162,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6195,32 +6187,36 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>5.409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5.701754385964919</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6241,78 +6237,82 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D19" s="2">
+        <v>5.116959064327475</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1.6653345369377348e-14</v>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>2.0030662342518046</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D21" s="2">
-        <v>1.9325330501846927</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2.0735994183189166</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>5.409356725146197</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6320,37 +6320,37 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>5.701754385964919</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
@@ -6371,11 +6371,11 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.257246376811585</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6383,20 +6383,20 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>4.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>4.438405797101453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6404,20 +6404,20 @@
         </is>
       </c>
       <c r="D26" s="2">
-        <v>0</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E26" s="2">
-        <v>0.013457556935819737</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.984645846924027</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6425,45 +6425,41 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>1.9139457023717443</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E27" s="2">
-        <v>2.0553459914763095</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>4.083333333333339</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6471,41 +6467,45 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>3.9166666666666683</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E29" s="2">
-        <v>4.250000000000009</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>22</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6513,20 +6513,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>15</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E31" s="2">
-        <v>30</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>6.257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6534,20 +6534,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>6.438405797101453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>1.5</v>
+        <v>22</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6555,20 +6555,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0.5</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6576,20 +6576,20 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <v>0.5</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E34" s="2">
-        <v>0.5134575569358197</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>7.000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -6597,20 +6597,20 @@
         </is>
       </c>
       <c r="D35" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>2.484645846924027</v>
+        <v>0.5</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6618,45 +6618,41 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>2.4139457023717443</v>
+        <v>0.5</v>
       </c>
       <c r="E36" s="2">
-        <v>2.5553459914763095</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>4.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D37" s="2">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6664,41 +6660,45 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E38" s="2">
-        <v>8</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>4.583333333333338</v>
+        <v>4.5</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D39" s="2">
-        <v>4.416666666666668</v>
-      </c>
-      <c r="E39" s="2">
-        <v>4.750000000000009</v>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6709,17 +6709,17 @@
         <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>0.5</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -6727,20 +6727,20 @@
         </is>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>4.416666666666668</v>
       </c>
       <c r="E41" s="2">
-        <v>1</v>
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>5.380116959064325</v>
+        <v>1.5</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
@@ -6748,57 +6748,99 @@
         </is>
       </c>
       <c r="D42" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>6.555555555555557</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>2300000</v>
+        <v>0.5</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D44" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E44" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B45" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B44" s="2">
+      <c r="B46" s="2">
         <v>766000</v>
       </c>
-      <c r="C44" s="0" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.67億円）</t>
         </is>
       </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6810,7 +6852,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8970,11 +9012,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8985,11 +9027,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -9000,26 +9042,26 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -9030,26 +9072,26 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9060,11 +9102,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.04416666666666668</v>
+        <v>-0.5</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9075,11 +9117,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.04750000000000009</v>
+        <v>0.5</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -9090,11 +9132,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.03916666666666668</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -9105,11 +9147,11 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.04250000000000009</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
@@ -9120,11 +9162,11 @@
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>-0.5</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -9135,11 +9177,11 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.5</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
@@ -9150,26 +9192,26 @@
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -9180,7 +9222,7 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B158" s="2">
@@ -9195,11 +9237,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -9210,7 +9252,7 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B160" s="2">
@@ -9225,7 +9267,7 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B161" s="2">
@@ -9240,26 +9282,26 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.024139457023717444</v>
+        <v>0</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.025553459914763096</v>
+        <v>0.08</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -9270,11 +9312,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.019139457023717443</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -9285,11 +9327,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -9300,26 +9342,26 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.3</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9330,26 +9372,26 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.06076086956521719</v>
+        <v>0</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.06438405797101453</v>
+        <v>0.3</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -9360,11 +9402,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.040760869565217184</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -9375,11 +9417,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9390,37 +9432,37 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B174" s="2">
@@ -9435,22 +9477,22 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B176" s="2">
@@ -9465,11 +9507,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>10000000000</v>
+        <v>0.01</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9480,7 +9522,7 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
         </is>
       </c>
       <c r="B178" s="2">
@@ -9495,11 +9537,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>10000000000</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9510,7 +9552,7 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B180" s="2">
@@ -9525,11 +9567,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9540,7 +9582,7 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B182" s="2">
@@ -9555,11 +9597,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.03</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9570,26 +9612,26 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.7</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9600,26 +9642,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateToBase:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateToBase:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9630,11 +9672,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>-0.5</v>
+        <v>0.66</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9645,11 +9687,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9660,7 +9702,7 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B190" s="2">
@@ -9675,11 +9717,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>10000000000</v>
+        <v>1</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9690,26 +9732,26 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9720,26 +9762,26 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.05701754385964919</v>
+        <v>10000000000</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9750,26 +9792,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9780,11 +9822,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>-0.5</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9795,11 +9837,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9810,26 +9852,26 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9840,11 +9882,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.04263157894736836</v>
+        <v>-0.5</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9855,11 +9897,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.06555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9870,26 +9912,26 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.05701754385964919</v>
+        <v>1</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9900,11 +9942,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.05</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9915,11 +9957,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.1</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9930,11 +9972,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9945,11 +9987,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9960,26 +10002,26 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9990,11 +10032,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.15</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -10005,11 +10047,11 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.3</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -10020,26 +10062,26 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.3</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10050,56 +10092,56 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0.03</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10110,56 +10152,56 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>2300000</v>
+        <v>0.03</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10170,11 +10212,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>23</v>
+        <v>100000</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10185,11 +10227,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0.2</v>
+        <v>5000000</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -10200,11 +10242,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -10215,26 +10257,26 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0.68</v>
+        <v>23</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
@@ -10245,11 +10287,11 @@
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10260,41 +10302,41 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.045833333333333386</v>
+        <v>0</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateToBase</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.68</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10305,11 +10347,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>-0.005</v>
+        <v>0.68</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10320,11 +10362,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10335,26 +10377,26 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.04</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10365,11 +10407,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10380,11 +10422,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.01984645846924027</v>
+        <v>-0.005</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10395,11 +10437,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.004</v>
+        <v>0.9</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10410,11 +10452,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.045</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10425,11 +10467,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.04</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10440,26 +10482,26 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.005</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10470,26 +10512,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectBaseYearSales</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.25</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10500,11 +10542,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.015</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10515,26 +10557,26 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.68</v>
+        <v>0.005</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
@@ -10545,56 +10587,56 @@
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectBaseYearSales</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectFirstYearSales</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.04</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10605,11 +10647,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectCogsRateToBase</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.68</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10620,11 +10662,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10635,56 +10677,56 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectFirstYearSales</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.05380116959064325</v>
+        <v>0</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.04</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10695,11 +10737,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.07</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10710,11 +10752,11 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.05</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10725,26 +10767,26 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10755,11 +10797,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10770,26 +10812,26 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>0.015</v>
+        <v>0.07</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10800,11 +10842,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>766000</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10815,11 +10857,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>7</v>
+        <v>0.005</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10830,11 +10872,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>3.5</v>
+        <v>0.22</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10845,11 +10887,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>35</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10860,26 +10902,26 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>25269000</v>
+        <v>0.015</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10890,11 +10932,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>8240000</v>
+        <v>766000</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10905,11 +10947,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10920,11 +10962,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10935,11 +10977,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>374000</v>
+        <v>35</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10950,11 +10992,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>285000</v>
+        <v>15</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10965,11 +11007,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>70</v>
+        <v>25269000</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10980,11 +11022,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>15</v>
+        <v>8240000</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10995,11 +11037,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11010,11 +11052,11 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -11025,11 +11067,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>40</v>
+        <v>374000</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11040,11 +11082,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>23</v>
+        <v>285000</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11055,11 +11097,11 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11070,11 +11112,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11085,26 +11127,26 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11115,11 +11157,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11130,11 +11172,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>13684000</v>
+        <v>23</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11145,11 +11187,11 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B289" s="2">
-        <v>7480000</v>
+        <v>10</v>
       </c>
       <c r="C289" s="0" t="inlineStr">
         <is>
@@ -11160,11 +11202,11 @@
     <row r="290">
       <c r="A290" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B290" s="2">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="C290" s="0" t="inlineStr">
         <is>
@@ -11175,26 +11217,26 @@
     <row r="291">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B291" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C291" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B292" s="2">
-        <v>3343000</v>
+        <v>35</v>
       </c>
       <c r="C292" s="0" t="inlineStr">
         <is>
@@ -11205,11 +11247,11 @@
     <row r="293">
       <c r="A293" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B293" s="2">
-        <v>1878000</v>
+        <v>22</v>
       </c>
       <c r="C293" s="0" t="inlineStr">
         <is>
@@ -11220,11 +11262,11 @@
     <row r="294">
       <c r="A294" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B294" s="2">
-        <v>350</v>
+        <v>13684000</v>
       </c>
       <c r="C294" s="0" t="inlineStr">
         <is>
@@ -11235,13 +11277,103 @@
     <row r="295">
       <c r="A295" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B295" s="2">
+        <v>7480000</v>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B296" s="2">
+        <v>95</v>
+      </c>
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B297" s="2">
+        <v>60</v>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B298" s="2">
+        <v>3343000</v>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B299" s="2">
+        <v>1878000</v>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B300" s="2">
+        <v>350</v>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B295" s="2">
+      <c r="B301" s="2">
         <v>213</v>
       </c>
-      <c r="C295" s="0" t="inlineStr">
+      <c r="C301" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11269,14 +11401,14 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MjAwMDAwLCJjb2dzIjo0ODk2MDAwLCJlbXBsb3llZVBheSI6NTE5MDMxLCJvZmZpY2VyUGF5IjozNjAwMCwiZGVwcmVjaWF0aW9uIjoxODAwMDAsIm90aGVyU2dhIjo5MDAwMDAsImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQ5MzA3OSwiZW1wbG95ZWVCb251cyI6MjU5NTIsIm9mZmljZXJDb21wZW5zYXRpb24iOjMyNDAwLCJvZmZpY2VyQm9udXMiOjM2MDAsImNvZ3NEZXByZWNpYXRpb24iOjQ1MDAwLCJzZ2FEZXByZWNpYXRpb24iOjEzNTAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzYwMDB9LCJvdGhlciI6eyJzYWxlcyI6NjQ0MDAwMCwiY29ncyI6NDM3OTIwMCwiZW1wbG95ZWVQYXkiOjcwOTc4Niwib2ZmaWNlclBheSI6NTUyMDAsImRlcHJlY2lhdGlvbiI6MTM4MDAwLCJvdGhlclNnYSI6NzM2MDAwLCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Njc0Mjk3LCJlbXBsb3llZUJvbnVzIjozNTQ4OSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NDk2ODAsIm9mZmljZXJCb251cyI6NTUyMCwiY29nc0RlcHJlY2lhdGlvbiI6Mjc2MDAsInNnYURlcHJlY2lhdGlvbiI6MTEwNDAwLCJyZXNlYXJjaERldmVsb3BtZW50IjoyNzYwMCwib3JkaW5hcnlJbmNvbWUiOjM5NDUzNCwicHJlVGF4SW5jb21lIjozOTQ1MzQsIm5ldEluY29tZSI6NzUwNzUyLjF9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2MDAwMDAsImNvZ3MiOjUxNjgwMDAsImVtcGxveWVlUGF5Ijo1NTg4MjQsIm9mZmljZXJQYXkiOjM4MDAwLCJkZXByZWNpYXRpb24iOjE5MDAwMCwib3RoZXJTZ2EiOjk1MDAwMCwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NTMwODgzLCJlbXBsb3llZUJvbnVzIjoyNzk0MSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzQyMDAsIm9mZmljZXJCb251cyI6MzgwMCwiY29nc0RlcHJlY2lhdGlvbiI6NDc1MDAsInNnYURlcHJlY2lhdGlvbiI6MTQyNTAwLCJyZXNlYXJjaERldmVsb3BtZW50IjozODAwMH0sIm90aGVyIjp7InNhbGVzIjo2NzIwMDAwLCJjb2dzIjo0NTY5NjAwLCJlbXBsb3llZVBheSI6NzU0MTQ4LCJvZmZpY2VyUGF5Ijo1NzYwMCwiZGVwcmVjaWF0aW9uIjoxNDQwMDAsIm90aGVyU2dhIjo3NjgwMDAsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3MTY0NDEsImVtcGxveWVlQm9udXMiOjM3NzA3LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo1MTg0MCwib2ZmaWNlckJvbnVzIjo1NzYwLCJjb2dzRGVwcmVjaWF0aW9uIjoyODgwMCwic2dhRGVwcmVjaWF0aW9uIjoxMTUyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjI4ODAwLCJvcmRpbmFyeUluY29tZSI6Mzk4MDEyLCJwcmVUYXhJbmNvbWUiOjM5ODAxMiwibmV0SW5jb21lIjo3NzE4ODEuNn19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwMDAwMDAsImNvZ3MiOjU0NDAwMDAsImVtcGxveWVlUGF5Ijo2MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo1NzAwMDAsImVtcGxveWVlQm9udXMiOjMwMDAwLCJvZmZpY2VyUGF5Ijo0MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzYwMDAsIm9mZmljZXJCb251cyI6NDAwMCwiZGVwcmVjaWF0aW9uIjoyMDAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjUwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjE1MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NDAwMDAsIm90aGVyU2dhIjoxMDAwMDAwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwMDAwMDAsImNvZ3MiOjQ3NjAwMDAsImVtcGxveWVlUGF5Ijo4MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo3NjAwMDAsImVtcGxveWVlQm9udXMiOjQwMDAwLCJvZmZpY2VyUGF5Ijo2MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NTQwMDAsIm9mZmljZXJCb251cyI6NjAwMCwiZGVwcmVjaWF0aW9uIjoxNTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjMwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjEyMDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzAwMDAsIm90aGVyU2dhIjo4MDAwMDAsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjo0MDAwMDAsInByZVRheEluY29tZSI6NDAwMDAwLCJuZXRJbmNvbWUiOjc5MTAwMH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwicHJvamVjdEJhc2VZZWFyU2FsZXMiOjAsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiaW52ZXN0bWVudCI6MjMwMDAwMCwic3Vic2lkeSI6NzY2MDAwLCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMC42NiwwLjddLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RCYXNlWWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAxXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUwMDAwMCwyMDAwMDAwMF0sInN1YnNpZHkiOlsxMDAwMDAsNTAwMDAwMF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4MjQwMDAwLCJtYXgiOjI1MjY5MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0ODAwMDAsIm1heCI6MTM2ODQwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxODc4MDAwLCJtYXgiOjMzNDMwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyODUwMDAsIm1heCI6Mzc0MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1MTMwMDAsIjIwMjk6cHJvamVjdDo3LTgiOjc5MDAwMH0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzY0MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyNzUyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00Ijo3MjYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyNjUwMTcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05Ijo4MjA4MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjo5MTIwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExNjczNzYsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6NjE0NDEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6MjQ1NDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjYzNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwNzI1MDMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTA3MjUwMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3NTA3NTIuMSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyMDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMzA0MDAwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Njc3OTY5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NTE5MDMxLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MzYwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6NDUwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEzNTAwMCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzMjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5NzM3NjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6NzYzMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNDUxMDcyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6ODYwNDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6OTU2MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMjQ3MzI0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjY1NjQ4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjI1NzcwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1Ijo2NjgwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMTAyNjg4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExMDI2ODgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6NzcxODgxLjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NjAwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQzMjAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcwNDY3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjU1ODgyNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjM4MDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjQ3NTAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxNDI1MDAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExMzAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6NzkxMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAwMDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1NjAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3MzAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2MDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05Ijo0MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00Ijo1MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MTUwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLjY2LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RGaXJzdFllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjEiOjEwMDAwMDAwMDAwLCJkcml2ZXI6cHJvamVjdEJhc2VZZWFyU2FsZXMiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEJhc2VZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMDEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6aW52ZXN0bWVudCI6MjMwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwMDAwMDAsImRyaXZlcjpzdWJzaWR5Ijo3NjYwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEwMDAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAwMDAwMCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4MjQwMDAwLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0ODAwMDAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4NzgwMDAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjI4NTAwMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyNjkwMDAsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNjg0MDAwLCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzM0MzAwMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozNzQwMDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjc5OTk5OTk5OTk5OTk5OSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjc5OTk5OTk5OTk5OTk5OSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOjAsInByb2plY3RCYXNlWWVhclNhbGVzIjowLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjE2Mjc2NTUwNTQ1ODU0N2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1MjIwNzU1OTcxNTYxNTUsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYyNTAwMDAwMDAwMDA1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjA4ODc1MDkxMzA3NSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODMwMzczNTU1NDk1ODM0NCwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDIwOTMxMDg1MTAyMTYyMjcsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDQ0MzM1OTE2NTkxMiwiaW52ZXN0bWVudCI6MjMwMDAwMCwi</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MjAwMDAwLCJjb2dzIjo0ODk2MDAwLCJlbXBsb3llZVBheSI6NTE5MDMxLCJvZmZpY2VyUGF5IjozNjAwMCwiZGVwcmVjaWF0aW9uIjoxODAwMDAsIm90aGVyU2dhIjo5MDAwMDAsImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQ5MzA3OSwiZW1wbG95ZWVCb251cyI6MjU5NTIsIm9mZmljZXJDb21wZW5zYXRpb24iOjMyNDAwLCJvZmZpY2VyQm9udXMiOjM2MDAsImNvZ3NEZXByZWNpYXRpb24iOjQ1MDAwLCJzZ2FEZXByZWNpYXRpb24iOjEzNTAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzYwMDB9LCJvdGhlciI6eyJzYWxlcyI6NjQ0MDAwMCwiY29ncyI6NDM3OTIwMCwiZW1wbG95ZWVQYXkiOjcwOTc4Niwib2ZmaWNlclBheSI6NTUyMDAsImRlcHJlY2lhdGlvbiI6MTM4MDAwLCJvdGhlclNnYSI6NzM2MDAwLCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Njc0Mjk3LCJlbXBsb3llZUJvbnVzIjozNTQ4OSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NDk2ODAsIm9mZmljZXJCb251cyI6NTUyMCwiY29nc0RlcHJlY2lhdGlvbiI6Mjc2MDAsInNnYURlcHJlY2lhdGlvbiI6MTEwNDAwLCJyZXNlYXJjaERldmVsb3BtZW50IjoyNzYwMCwib3JkaW5hcnlJbmNvbWUiOjM5NDUzNCwicHJlVGF4SW5jb21lIjozOTQ1MzQsIm5ldEluY29tZSI6NzUwNzUyLjF9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2MDAwMDAsImNvZ3MiOjUxNjgwMDAsImVtcGxveWVlUGF5Ijo1NTg4MjQsIm9mZmljZXJQYXkiOjM4MDAwLCJkZXByZWNpYXRpb24iOjE5MDAwMCwib3RoZXJTZ2EiOjk1MDAwMCwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NTMwODgzLCJlbXBsb3llZUJvbnVzIjoyNzk0MSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzQyMDAsIm9mZmljZXJCb251cyI6MzgwMCwiY29nc0RlcHJlY2lhdGlvbiI6NDc1MDAsInNnYURlcHJlY2lhdGlvbiI6MTQyNTAwLCJyZXNlYXJjaERldmVsb3BtZW50IjozODAwMH0sIm90aGVyIjp7InNhbGVzIjo2NzIwMDAwLCJjb2dzIjo0NTY5NjAwLCJlbXBsb3llZVBheSI6NzU0MTQ4LCJvZmZpY2VyUGF5Ijo1NzYwMCwiZGVwcmVjaWF0aW9uIjoxNDQwMDAsIm90aGVyU2dhIjo3NjgwMDAsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3MTY0NDEsImVtcGxveWVlQm9udXMiOjM3NzA3LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo1MTg0MCwib2ZmaWNlckJvbnVzIjo1NzYwLCJjb2dzRGVwcmVjaWF0aW9uIjoyODgwMCwic2dhRGVwcmVjaWF0aW9uIjoxMTUyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjI4ODAwLCJvcmRpbmFyeUluY29tZSI6Mzk4MDEyLCJwcmVUYXhJbmNvbWUiOjM5ODAxMiwibmV0SW5jb21lIjo3NzE4ODEuNn19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwMDAwMDAsImNvZ3MiOjU0NDAwMDAsImVtcGxveWVlUGF5Ijo2MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo1NzAwMDAsImVtcGxveWVlQm9udXMiOjMwMDAwLCJvZmZpY2VyUGF5Ijo0MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzYwMDAsIm9mZmljZXJCb251cyI6NDAwMCwiZGVwcmVjaWF0aW9uIjoyMDAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjUwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjE1MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NDAwMDAsIm90aGVyU2dhIjoxMDAwMDAwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwMDAwMDAsImNvZ3MiOjQ3NjAwMDAsImVtcGxveWVlUGF5Ijo4MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo3NjAwMDAsImVtcGxveWVlQm9udXMiOjQwMDAwLCJvZmZpY2VyUGF5Ijo2MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NTQwMDAsIm9mZmljZXJCb251cyI6NjAwMCwiZGVwcmVjaWF0aW9uIjoxNTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjMwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjEyMDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzAwMDAsIm90aGVyU2dhIjo4MDAwMDAsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjo0MDAwMDAsInByZVRheEluY29tZSI6NDAwMDAwLCJuZXRJbmNvbWUiOjc5MTAwMH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAuNjYsMC43XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sInByb2plY3RDb2dzUmF0ZVRvQmFzZSI6WzAuNjgsMC42OF0sIm90aGVyQ29nc1JhdGVUb0Jhc2UiOlswLjY4LDAuNjhdLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RCYXNlWWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAxXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUwMDAwMCwyMDAwMDAwMF0sInN1YnNpZHkiOlsxMDAwMDAsNTAwMDAwMF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4MjQwMDAwLCJtYXgiOjI1MjY5MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0ODAwMDAsIm1heCI6MTM2ODQwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxODc4MDAwLCJtYXgiOjMzNDMwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyODUwMDAsIm1heCI6Mzc0MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1MTMwMDAsIjIwMjk6cHJvamVjdDo3LTgiOjc5MDAwMH0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzY0MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyNzUyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00Ijo3MjYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyNjUwMTcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05Ijo4MjA4MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjo5MTIwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExNjczNzYsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6NjE0NDEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6MjQ1NDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjYzNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwNzI1MDMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTA3MjUwMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3NTA3NTIuMSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyMDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMzA0MDAwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Njc3OTY5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NTE5MDMxLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MzYwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6NDUwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEzNTAwMCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzMjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5NzM3NjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6NzYzMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNDUxMDcyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6ODYwNDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6OTU2MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMjQ3MzI0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjY1NjQ4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjI1NzcwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1Ijo2NjgwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMTAyNjg4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExMDI2ODgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6NzcxODgxLjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NjAwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQzMjAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcwNDY3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjU1ODgyNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjM4MDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjQ3NTAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxNDI1MDAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExMzAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6NzkxMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAwMDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1NjAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3MzAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2MDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05Ijo0MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00Ijo1MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MTUwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLjY2LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVRvQmFzZToxIjowLjY4LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVRvQmFzZSI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MSI6MC42OCwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Rmlyc3RZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RCYXNlWWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczoxIjoxMDAwMDAwMDAwMCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjppbnZlc3RtZW50IjoyMzAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAwMDAwMCwiZHJpdmVyOnN1YnNpZHkiOjc2NjAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MTAwMDAwLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MDAwMDAwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyNDAwMDAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQ4MDAwMCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTg3ODAwMCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mjg1MDAwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTI2OTAwMCwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2ODQwMDAsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMzQzMDAwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjM3NDAwMH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTk5OTk5OTk5OTk5LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTk5OTk5OTk5OTk5LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Ni41MjgxMTEzODQ3OTU5MjFlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDczNTk5NDE4MzE4OTE2NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIyMDk2NTY4MTE3MDExMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMDUyNzMxMjA2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c3Vic2lkeSI6NzY2MDAwLCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">MDU3LCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTU3MTE4NjI3MjU2NDk4LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzczNDQ0NjQwMjgyMDA2MSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc2NzAyODY1Mzg4MTUxLCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.463655389422492</v>
+        <v>15.470725584050182</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>9331938.869999997</v>
+        <v>9336831.869999997</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.1848118329287347</v>
+        <v>2.1849919879200375</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.91236279520185</v>
+        <v>63.91899125437013</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.02052627021196</v>
+        <v>22.032216393012405</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>7652872</v>
+        <v>7657765</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>23.15053074954352</v>
+        <v>25.231207135866285</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>1964723</v>
+        <v>2221268.9999999995</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.00782348691229</v>
+        <v>7.008665281543802</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>269565.13</v>
+        <v>285297.11</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.49125326370756</v>
+        <v>289.9828981723237</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>5.376457502612597</v>
+        <v>5.3822239717880915</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>7970</v>
+        <v>7979</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         <v>17302362</v>
       </c>
       <c r="H3" s="4">
-        <v>19946005</v>
+        <v>19947100</v>
       </c>
       <c r="I3" s="4">
-        <v>22996292.97</v>
+        <v>22998965.97</v>
       </c>
       <c r="J3" s="4">
-        <v>26634300.869999997</v>
+        <v>26639193.869999997</v>
       </c>
     </row>
     <row r="4">
@@ -1304,13 +1304,13 @@
         <v>4.878010489642537</v>
       </c>
       <c r="H4" s="2">
-        <v>15.279087329232844</v>
+        <v>15.285415944944392</v>
       </c>
       <c r="I4" s="2">
-        <v>15.29272638806618</v>
+        <v>15.299797815221261</v>
       </c>
       <c r="J4" s="2">
-        <v>15.81997544015461</v>
+        <v>15.827789409090553</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>11765605</v>
       </c>
       <c r="H5" s="2">
-        <v>13434940</v>
+        <v>13506861</v>
       </c>
       <c r="I5" s="2">
-        <v>15407414</v>
+        <v>15324465</v>
       </c>
       <c r="J5" s="2">
-        <v>17743899</v>
+        <v>17444099</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>5536757</v>
       </c>
       <c r="H7" s="4">
-        <v>6511065</v>
+        <v>6440239</v>
       </c>
       <c r="I7" s="4">
-        <v>7588878.969999999</v>
+        <v>7674500.969999999</v>
       </c>
       <c r="J7" s="4">
-        <v>8890401.869999997</v>
+        <v>9195094.869999997</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>32.00000670428697</v>
       </c>
       <c r="H8" s="2">
-        <v>32.64345416538299</v>
+        <v>32.286593038587064</v>
       </c>
       <c r="I8" s="2">
-        <v>33.00044481038806</v>
+        <v>33.368895714749385</v>
       </c>
       <c r="J8" s="2">
-        <v>33.37952031627702</v>
+        <v>34.517166378503475</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>3828100</v>
+        <v>3828103</v>
       </c>
       <c r="F9" s="2">
-        <v>4029320</v>
+        <v>4029326</v>
       </c>
       <c r="G9" s="2">
-        <v>4242334</v>
+        <v>4242343</v>
       </c>
       <c r="H9" s="2">
-        <v>4619075</v>
+        <v>4619215</v>
       </c>
       <c r="I9" s="2">
-        <v>5094739.08</v>
+        <v>5101989.01</v>
       </c>
       <c r="J9" s="2">
-        <v>5630379.13</v>
+        <v>5646692.109999999</v>
       </c>
     </row>
     <row r="10">
@@ -1508,13 +1508,13 @@
         <v>114341</v>
       </c>
       <c r="H10" s="2">
-        <v>119897</v>
+        <v>119899</v>
       </c>
       <c r="I10" s="2">
-        <v>125725</v>
+        <v>125731</v>
       </c>
       <c r="J10" s="2">
-        <v>131838</v>
+        <v>131847</v>
       </c>
     </row>
     <row r="11">
@@ -1542,13 +1542,13 @@
         <v>102907</v>
       </c>
       <c r="H11" s="2">
-        <v>107907</v>
+        <v>107909</v>
       </c>
       <c r="I11" s="2">
-        <v>113153</v>
+        <v>113158</v>
       </c>
       <c r="J11" s="2">
-        <v>118654</v>
+        <v>118662</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>11990</v>
       </c>
       <c r="I12" s="2">
-        <v>12572</v>
+        <v>12573</v>
       </c>
       <c r="J12" s="2">
-        <v>13184</v>
+        <v>13185</v>
       </c>
     </row>
     <row r="13">
@@ -1601,22 +1601,22 @@
         <v>1400000</v>
       </c>
       <c r="E13" s="2">
-        <v>1494028</v>
+        <v>1494031</v>
       </c>
       <c r="F13" s="2">
-        <v>1594420</v>
+        <v>1594426</v>
       </c>
       <c r="G13" s="2">
-        <v>1701612</v>
+        <v>1701621</v>
       </c>
       <c r="H13" s="2">
         <v>1817073</v>
       </c>
       <c r="I13" s="2">
-        <v>1995380.08</v>
+        <v>2002304.01</v>
       </c>
       <c r="J13" s="2">
-        <v>2192820.13</v>
+        <v>2208561.11</v>
       </c>
     </row>
     <row r="14">
@@ -1635,22 +1635,22 @@
         <v>1330000</v>
       </c>
       <c r="E14" s="2">
-        <v>1419326</v>
+        <v>1419329</v>
       </c>
       <c r="F14" s="2">
-        <v>1514699</v>
+        <v>1514705</v>
       </c>
       <c r="G14" s="2">
-        <v>1616531</v>
+        <v>1616540</v>
       </c>
       <c r="H14" s="2">
-        <v>1775364</v>
+        <v>1781563</v>
       </c>
       <c r="I14" s="2">
-        <v>1951260</v>
+        <v>1965342</v>
       </c>
       <c r="J14" s="2">
-        <v>2146192</v>
+        <v>2170197</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>85081</v>
       </c>
       <c r="H15" s="2">
-        <v>93441</v>
+        <v>93767</v>
       </c>
       <c r="I15" s="2">
-        <v>102698</v>
+        <v>103439</v>
       </c>
       <c r="J15" s="2">
-        <v>112958</v>
+        <v>114221</v>
       </c>
     </row>
     <row r="16">
@@ -1746,13 +1746,13 @@
         <v>78579</v>
       </c>
       <c r="H17" s="2">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="I17" s="2">
-        <v>105579</v>
+        <v>105592</v>
       </c>
       <c r="J17" s="2">
-        <v>123180</v>
+        <v>123205</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1205742</v>
+        <v>1205739</v>
       </c>
       <c r="F18" s="4">
-        <v>1249914</v>
+        <v>1249908</v>
       </c>
       <c r="G18" s="4">
-        <v>1294423</v>
+        <v>1294414</v>
       </c>
       <c r="H18" s="4">
-        <v>1891990</v>
+        <v>1821024</v>
       </c>
       <c r="I18" s="4">
-        <v>2494139.8899999987</v>
+        <v>2572511.959999999</v>
       </c>
       <c r="J18" s="4">
-        <v>3260022.7399999974</v>
+        <v>3548402.759999998</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.664870016418791</v>
+        <v>7.664850945498106</v>
       </c>
       <c r="F19" s="2">
-        <v>7.576335161820742</v>
+        <v>7.5762987929097845</v>
       </c>
       <c r="G19" s="2">
-        <v>7.481192452221263</v>
+        <v>7.481140436201716</v>
       </c>
       <c r="H19" s="2">
-        <v>9.485558636930051</v>
+        <v>9.129266910979542</v>
       </c>
       <c r="I19" s="2">
-        <v>10.84583455800354</v>
+        <v>11.185337477152672</v>
       </c>
       <c r="J19" s="2">
-        <v>12.23994110418712</v>
+        <v>13.320233252238417</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>1130000</v>
       </c>
       <c r="E20" s="4">
-        <v>1169252</v>
+        <v>1169249</v>
       </c>
       <c r="F20" s="4">
-        <v>1211870</v>
+        <v>1211864</v>
       </c>
       <c r="G20" s="4">
-        <v>1254760</v>
+        <v>1254751</v>
       </c>
       <c r="H20" s="4">
-        <v>1714099</v>
+        <v>1636608</v>
       </c>
       <c r="I20" s="4">
-        <v>2301509</v>
+        <v>2371982</v>
       </c>
       <c r="J20" s="4">
-        <v>3051252</v>
+        <v>3330105</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>1130000</v>
       </c>
       <c r="E21" s="2">
-        <v>1169252</v>
+        <v>1169249</v>
       </c>
       <c r="F21" s="2">
-        <v>1211870</v>
+        <v>1211864</v>
       </c>
       <c r="G21" s="2">
-        <v>1254760</v>
+        <v>1254751</v>
       </c>
       <c r="H21" s="2">
-        <v>1714099</v>
+        <v>1636608</v>
       </c>
       <c r="I21" s="2">
-        <v>2301509</v>
+        <v>2371982</v>
       </c>
       <c r="J21" s="2">
-        <v>3051252</v>
+        <v>3330105</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>791000</v>
       </c>
       <c r="E22" s="2">
-        <v>818477</v>
+        <v>818475</v>
       </c>
       <c r="F22" s="2">
-        <v>848310</v>
+        <v>848305</v>
       </c>
       <c r="G22" s="2">
-        <v>878332</v>
+        <v>878326</v>
       </c>
       <c r="H22" s="2">
-        <v>1199869</v>
+        <v>1145626</v>
       </c>
       <c r="I22" s="2">
-        <v>1611057</v>
+        <v>1660388</v>
       </c>
       <c r="J22" s="2">
-        <v>2135877</v>
+        <v>2331074</v>
       </c>
     </row>
     <row r="23">
@@ -1941,22 +1941,22 @@
         <v>1400000</v>
       </c>
       <c r="E23" s="2">
-        <v>1494028</v>
+        <v>1494031</v>
       </c>
       <c r="F23" s="2">
-        <v>1594420</v>
+        <v>1594426</v>
       </c>
       <c r="G23" s="2">
-        <v>1701612</v>
+        <v>1701621</v>
       </c>
       <c r="H23" s="2">
         <v>1817073</v>
       </c>
       <c r="I23" s="2">
-        <v>1995380.08</v>
+        <v>2002304.01</v>
       </c>
       <c r="J23" s="2">
-        <v>2192820.13</v>
+        <v>2208561.11</v>
       </c>
     </row>
     <row r="24">
@@ -1984,13 +1984,13 @@
         <v>114341</v>
       </c>
       <c r="H24" s="2">
-        <v>119897</v>
+        <v>119899</v>
       </c>
       <c r="I24" s="2">
-        <v>125725</v>
+        <v>125731</v>
       </c>
       <c r="J24" s="2">
-        <v>131838</v>
+        <v>131847</v>
       </c>
     </row>
     <row r="25">
@@ -2052,13 +2052,13 @@
         <v>3460376</v>
       </c>
       <c r="H26" s="4">
-        <v>4178960</v>
+        <v>4107996</v>
       </c>
       <c r="I26" s="4">
-        <v>4965244.969999999</v>
+        <v>5050546.969999999</v>
       </c>
       <c r="J26" s="4">
-        <v>5934680.869999997</v>
+        <v>6238810.869999997</v>
       </c>
     </row>
     <row r="27">
@@ -2088,13 +2088,13 @@
         <v>4.743232914859963</v>
       </c>
       <c r="H27" s="2">
-        <v>20.76606704011357</v>
+        <v>18.71530723828856</v>
       </c>
       <c r="I27" s="2">
-        <v>18.815326540574652</v>
+        <v>22.94430106553167</v>
       </c>
       <c r="J27" s="2">
-        <v>19.52443244708626</v>
+        <v>23.52742994091983</v>
       </c>
     </row>
     <row r="28">
@@ -2122,13 +2122,13 @@
         <v>19.999442850635074</v>
       </c>
       <c r="H28" s="2">
-        <v>20.951363443456472</v>
+        <v>20.59445232640334</v>
       </c>
       <c r="I28" s="2">
-        <v>21.591501623663646</v>
+        <v>21.95988713835207</v>
       </c>
       <c r="J28" s="2">
-        <v>22.282097431303807</v>
+        <v>23.419668404552958</v>
       </c>
     </row>
     <row r="29">
@@ -2156,13 +2156,13 @@
         <v>262</v>
       </c>
       <c r="H29" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I29" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30">
@@ -2215,22 +2215,22 @@
         <v>6086.95652173913</v>
       </c>
       <c r="E31" s="2">
-        <v>6225.116666666667</v>
+        <v>6225.129166666667</v>
       </c>
       <c r="F31" s="2">
-        <v>6327.063492063492</v>
+        <v>6327.087301587301</v>
       </c>
       <c r="G31" s="2">
-        <v>6494.702290076336</v>
+        <v>6494.736641221374</v>
       </c>
       <c r="H31" s="2">
-        <v>6655.945054945055</v>
+        <v>6631.653284671533</v>
       </c>
       <c r="I31" s="2">
-        <v>7001.333614035088</v>
+        <v>7001.062972027972</v>
       </c>
       <c r="J31" s="2">
-        <v>7383.23276094276</v>
+        <v>7386.492006688963</v>
       </c>
     </row>
     <row r="32">
@@ -2251,22 +2251,22 @@
         <v>1.9923071308914908</v>
       </c>
       <c r="E32" s="2">
-        <v>2.269773809523823</v>
+        <v>2.269979166666669</v>
       </c>
       <c r="F32" s="2">
-        <v>1.6376693137771126</v>
+        <v>1.6378477006803838</v>
       </c>
       <c r="G32" s="2">
-        <v>2.6495513791370273</v>
+        <v>2.649708019549757</v>
       </c>
       <c r="H32" s="2">
-        <v>2.48268138656782</v>
+        <v>2.1081169416657053</v>
       </c>
       <c r="I32" s="2">
-        <v>5.1891738323985415</v>
+        <v>5.570401097570898</v>
       </c>
       <c r="J32" s="2">
-        <v>5.45466289653882</v>
+        <v>5.505293070508466</v>
       </c>
     </row>
     <row r="33">
@@ -2294,13 +2294,13 @@
         <v>22868.2</v>
       </c>
       <c r="H33" s="2">
-        <v>23979.4</v>
+        <v>23979.8</v>
       </c>
       <c r="I33" s="2">
-        <v>25145</v>
+        <v>25146.2</v>
       </c>
       <c r="J33" s="2">
-        <v>26367.6</v>
+        <v>26369.4</v>
       </c>
     </row>
     <row r="34">
@@ -2330,13 +2330,13 @@
         <v>4.572850074537449</v>
       </c>
       <c r="H34" s="2">
-        <v>4.859149386484285</v>
+        <v>4.860898540331116</v>
       </c>
       <c r="I34" s="2">
-        <v>4.860838886711094</v>
+        <v>4.86409394573768</v>
       </c>
       <c r="J34" s="2">
-        <v>4.862199244382581</v>
+        <v>4.864353262123111</v>
       </c>
     </row>
     <row r="35">
@@ -2364,13 +2364,13 @@
         <v>12960.209737827716</v>
       </c>
       <c r="H35" s="2">
-        <v>15032.230215827338</v>
+        <v>14724</v>
       </c>
       <c r="I35" s="2">
-        <v>17121.534379310342</v>
+        <v>17355.831512027486</v>
       </c>
       <c r="J35" s="2">
-        <v>19651.26115894039</v>
+        <v>20522.40417763157</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1555742</v>
+        <v>1555739</v>
       </c>
       <c r="F36" s="4">
-        <v>1599914</v>
+        <v>1599908</v>
       </c>
       <c r="G36" s="4">
-        <v>1644423</v>
+        <v>1644414</v>
       </c>
       <c r="H36" s="4">
-        <v>2241990</v>
+        <v>2171024</v>
       </c>
       <c r="I36" s="4">
-        <v>2844139.8899999987</v>
+        <v>2922511.959999999</v>
       </c>
       <c r="J36" s="4">
-        <v>3610022.7399999974</v>
+        <v>3898402.759999998</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>9.88981076306822</v>
+        <v>9.889791692147536</v>
       </c>
       <c r="F37" s="2">
-        <v>9.697854967693194</v>
+        <v>9.697818598782236</v>
       </c>
       <c r="G37" s="2">
-        <v>9.504037656823964</v>
+        <v>9.503985640804418</v>
       </c>
       <c r="H37" s="2">
-        <v>11.240295989096563</v>
+        <v>10.88390793649202</v>
       </c>
       <c r="I37" s="2">
-        <v>12.36781899461076</v>
+        <v>12.707145024746517</v>
       </c>
       <c r="J37" s="2">
-        <v>13.55403604404803</v>
+        <v>14.634086823438844</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.0486007228415657</v>
       </c>
       <c r="E38" s="2">
-        <v>3.0292715231788003</v>
+        <v>3.029072847682124</v>
       </c>
       <c r="F38" s="2">
-        <v>2.8392882624496796</v>
+        <v>2.8391009031720538</v>
       </c>
       <c r="G38" s="2">
-        <v>2.7819620304591286</v>
+        <v>2.7817849526347693</v>
       </c>
       <c r="H38" s="2">
-        <v>36.339007664086424</v>
+        <v>32.02417396105848</v>
       </c>
       <c r="I38" s="2">
-        <v>26.8578312124496</v>
+        <v>34.61444737598474</v>
       </c>
       <c r="J38" s="2">
-        <v>26.928452172582794</v>
+        <v>33.39219183212509</v>
       </c>
     </row>
   </sheetData>
@@ -2636,13 +2636,13 @@
         <v>9369739</v>
       </c>
       <c r="H3" s="4">
-        <v>11433005</v>
+        <v>11434100</v>
       </c>
       <c r="I3" s="4">
-        <v>13950613</v>
+        <v>13953286</v>
       </c>
       <c r="J3" s="4">
-        <v>17022611</v>
+        <v>17027504</v>
       </c>
     </row>
     <row r="4">
@@ -2672,13 +2672,13 @@
         <v>5.409360836980381</v>
       </c>
       <c r="H4" s="2">
-        <v>22.02052799976606</v>
+        <v>22.03221455795086</v>
       </c>
       <c r="I4" s="2">
-        <v>22.02052741164724</v>
+        <v>22.032219413858556</v>
       </c>
       <c r="J4" s="2">
-        <v>22.020523399222668</v>
+        <v>22.03221520722789</v>
       </c>
     </row>
     <row r="5">
@@ -2706,13 +2706,13 @@
         <v>54.15294744151117</v>
       </c>
       <c r="H5" s="2">
-        <v>57.31977406001854</v>
+        <v>57.32211699946358</v>
       </c>
       <c r="I5" s="2">
-        <v>60.66461676322956</v>
+        <v>60.669188424387244</v>
       </c>
       <c r="J5" s="2">
-        <v>63.91236279520185</v>
+        <v>63.91899125437013</v>
       </c>
     </row>
     <row r="6">
@@ -2740,13 +2740,13 @@
         <v>2998317</v>
       </c>
       <c r="H6" s="4">
-        <v>3715727</v>
+        <v>3658950</v>
       </c>
       <c r="I6" s="4">
-        <v>4603702</v>
+        <v>4674397</v>
       </c>
       <c r="J6" s="4">
-        <v>5702574</v>
+        <v>5959683</v>
       </c>
     </row>
     <row r="7">
@@ -2774,13 +2774,13 @@
         <v>32.00000554978106</v>
       </c>
       <c r="H7" s="2">
-        <v>32.50000327997758</v>
+        <v>32.000332339230894</v>
       </c>
       <c r="I7" s="2">
-        <v>32.9999979212383</v>
+        <v>33.500331033134415</v>
       </c>
       <c r="J7" s="2">
-        <v>33.49999597594047</v>
+        <v>35.0003324033869</v>
       </c>
     </row>
     <row r="8">
@@ -2799,22 +2799,22 @@
         <v>730000</v>
       </c>
       <c r="E8" s="4">
-        <v>765641</v>
+        <v>765638</v>
       </c>
       <c r="F8" s="4">
-        <v>802325</v>
+        <v>802319</v>
       </c>
       <c r="G8" s="4">
-        <v>840043</v>
+        <v>840034</v>
       </c>
       <c r="H8" s="4">
-        <v>1297234</v>
+        <v>1240317</v>
       </c>
       <c r="I8" s="4">
-        <v>1833062.92</v>
+        <v>1896507.9900000002</v>
       </c>
       <c r="J8" s="4">
-        <v>2527230.87</v>
+        <v>2768026.8899999997</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2833,22 @@
         <v>9.125</v>
       </c>
       <c r="E9" s="2">
-        <v>9.079376132267189</v>
+        <v>9.079340556679679</v>
       </c>
       <c r="F9" s="2">
-        <v>9.026138874682667</v>
+        <v>9.026071374812604</v>
       </c>
       <c r="G9" s="2">
-        <v>8.965489860496648</v>
+        <v>8.96539380659376</v>
       </c>
       <c r="H9" s="2">
-        <v>11.346395807576398</v>
+        <v>10.847526259172126</v>
       </c>
       <c r="I9" s="2">
-        <v>13.139658594213744</v>
+        <v>13.591837721953096</v>
       </c>
       <c r="J9" s="2">
-        <v>14.846317465634385</v>
+        <v>16.256210481583206</v>
       </c>
     </row>
     <row r="10">
@@ -2867,22 +2867,22 @@
         <v>600000</v>
       </c>
       <c r="E10" s="2">
-        <v>644417</v>
+        <v>644420</v>
       </c>
       <c r="F10" s="2">
-        <v>692122</v>
+        <v>692128</v>
       </c>
       <c r="G10" s="2">
-        <v>743359</v>
+        <v>743368</v>
       </c>
       <c r="H10" s="2">
         <v>790000</v>
       </c>
       <c r="I10" s="2">
-        <v>894544.08</v>
+        <v>901468.01</v>
       </c>
       <c r="J10" s="2">
-        <v>1012924.13</v>
+        <v>1028665.11</v>
       </c>
     </row>
     <row r="11">
@@ -2910,13 +2910,13 @@
         <v>46849</v>
       </c>
       <c r="H11" s="2">
-        <v>49368</v>
+        <v>49370</v>
       </c>
       <c r="I11" s="2">
-        <v>52022</v>
+        <v>52028</v>
       </c>
       <c r="J11" s="2">
-        <v>54819</v>
+        <v>54828</v>
       </c>
     </row>
     <row r="12">
@@ -3046,13 +3046,13 @@
         <v>1830251</v>
       </c>
       <c r="H15" s="4">
-        <v>2336602</v>
+        <v>2279687</v>
       </c>
       <c r="I15" s="4">
-        <v>2979629</v>
+        <v>3050004</v>
       </c>
       <c r="J15" s="4">
-        <v>3794974</v>
+        <v>4051519.9999999995</v>
       </c>
     </row>
     <row r="16">
@@ -3082,13 +3082,13 @@
         <v>5.253862804590503</v>
       </c>
       <c r="H16" s="2">
-        <v>27.665658972457873</v>
+        <v>24.55597620217118</v>
       </c>
       <c r="I16" s="2">
-        <v>27.519748763375198</v>
+        <v>33.79047211305763</v>
       </c>
       <c r="J16" s="2">
-        <v>27.36397719313377</v>
+        <v>32.83654709961035</v>
       </c>
     </row>
     <row r="17">
@@ -3116,13 +3116,13 @@
         <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J17" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -3175,22 +3175,22 @@
         <v>6000</v>
       </c>
       <c r="E19" s="2">
-        <v>6137.304761904762</v>
+        <v>6137.333333333333</v>
       </c>
       <c r="F19" s="2">
-        <v>6235.333333333333</v>
+        <v>6235.387387387387</v>
       </c>
       <c r="G19" s="2">
-        <v>6408.267241379311</v>
+        <v>6408.3448275862065</v>
       </c>
       <c r="H19" s="2">
-        <v>6583.333333333333</v>
+        <v>6528.925619834711</v>
       </c>
       <c r="I19" s="2">
-        <v>7156.35264</v>
+        <v>7154.508015873016</v>
       </c>
       <c r="J19" s="2">
-        <v>7852.12503875969</v>
+        <v>7852.405419847328</v>
       </c>
     </row>
     <row r="20">
@@ -3211,22 +3211,22 @@
         <v>1.9999141053354874</v>
       </c>
       <c r="E20" s="2">
-        <v>2.2884126984126896</v>
+        <v>2.2888888888888737</v>
       </c>
       <c r="F20" s="2">
-        <v>1.5972576763182866</v>
+        <v>1.597665447328711</v>
       </c>
       <c r="G20" s="2">
-        <v>2.773450893499052</v>
+        <v>2.773804247490186</v>
       </c>
       <c r="H20" s="2">
-        <v>2.7318787647242493</v>
+        <v>1.8816214715762003</v>
       </c>
       <c r="I20" s="2">
-        <v>8.704090734177218</v>
+        <v>9.581705053244916</v>
       </c>
       <c r="J20" s="2">
-        <v>9.722444291952748</v>
+        <v>9.754652624973703</v>
       </c>
     </row>
     <row r="21">
@@ -3254,13 +3254,13 @@
         <v>23424.5</v>
       </c>
       <c r="H21" s="2">
-        <v>24684</v>
+        <v>24685</v>
       </c>
       <c r="I21" s="2">
-        <v>26011</v>
+        <v>26014</v>
       </c>
       <c r="J21" s="2">
-        <v>27409.5</v>
+        <v>27414</v>
       </c>
     </row>
     <row r="22">
@@ -3290,13 +3290,13 @@
         <v>5.408932388345145</v>
       </c>
       <c r="H22" s="2">
-        <v>5.376849025592856</v>
+        <v>5.381118060150691</v>
       </c>
       <c r="I22" s="2">
-        <v>5.375952033706044</v>
+        <v>5.383836337856995</v>
       </c>
       <c r="J22" s="2">
-        <v>5.376571450540157</v>
+        <v>5.381717536710995</v>
       </c>
     </row>
     <row r="23">
@@ -3324,13 +3324,13 @@
         <v>15510.601694915254</v>
       </c>
       <c r="H23" s="2">
-        <v>19152.475409836065</v>
+        <v>18534.040650406503</v>
       </c>
       <c r="I23" s="2">
-        <v>23461.645669291338</v>
+        <v>23828.15625</v>
       </c>
       <c r="J23" s="2">
-        <v>28969.26717557252</v>
+        <v>30462.55639097744</v>
       </c>
     </row>
     <row r="24">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 22.02 % / ベース 7.32 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.03 % / ベース 7.32 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.02 % / ベース 6.26 %</t>
+          <t xml:space="preserve">全社 15.3 % / 補助 22.03 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.82 % / 補助 22.02 % / ベース 6.26 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / ベース 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.36 % / 補助 67.5 % / ベース 67.16 %</t>
+          <t xml:space="preserve">全社 67.71 % / 補助 68 % / ベース 67.33 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67 % / 補助 67 % / ベース 67 %</t>
+          <t xml:space="preserve">全社 66.63 % / 補助 66.5 % / ベース 66.83 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.62 % / 補助 66.5 % / ベース 66.83 %</t>
+          <t xml:space="preserve">全社 65.48 % / 補助 65 % / ベース 66.34 %</t>
         </is>
       </c>
     </row>
@@ -3782,17 +3782,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.64 % / 補助 32.5 % / ベース 32.84 %</t>
+          <t xml:space="preserve">全社 32.29 % / 補助 32 % / ベース 32.67 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33 % / 補助 33 % / ベース 33 %</t>
+          <t xml:space="preserve">全社 33.37 % / 補助 33.5 % / ベース 33.17 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.38 % / 補助 33.5 % / ベース 33.17 %</t>
+          <t xml:space="preserve">全社 34.52 % / 補助 35 % / ベース 33.66 %</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.15 % / 補助 19.86 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.18 % / 補助 19.91 % / ベース 25.69 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.14 % / 補助 18.65 % / ベース 25.54 %</t>
+          <t xml:space="preserve">全社 21.2 % / 補助 18.74 % / ベース 25.54 %</t>
         </is>
       </c>
     </row>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.49 % / 補助 11.35 % / ベース 6.99 %</t>
+          <t xml:space="preserve">全社 9.13 % / 補助 10.85 % / ベース 6.82 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.85 % / 補助 13.14 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 11.19 % / 補助 13.59 % / ベース 7.47 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 14.85 % / ベース 7.62 %</t>
+          <t xml:space="preserve">全社 13.32 % / 補助 16.26 % / ベース 8.12 %</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.24 % / 補助 13.1 % / ベース 8.75 %</t>
+          <t xml:space="preserve">全社 10.88 % / 補助 12.6 % / ベース 8.58 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.37 % / 補助 14.57 % / ベース 8.97 %</t>
+          <t xml:space="preserve">全社 12.71 % / 補助 15.03 % / ベース 9.13 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.55 % / 補助 16.02 % / ベース 9.18 %</t>
+          <t xml:space="preserve">全社 14.63 % / 補助 17.43 % / ベース 9.68 %</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.68 % / 補助 6.41 % / ベース 12.17 %</t>
+          <t xml:space="preserve">全社 8.71 % / 補助 6.46 % / ベース 12.17 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.23 % / 補助 5.95 % / ベース 12.28 %</t>
+          <t xml:space="preserve">全社 8.29 % / 補助 6.04 % / ベース 12.28 %</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.22 % / 補助 6.79 % / ベース 12.98 %</t>
+          <t xml:space="preserve">全社 9.25 % / 補助 6.83 % / ベース 12.98 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.73 % / 補助 6.27 % / ベース 13.08 %</t>
+          <t xml:space="preserve">全社 8.79 % / 補助 6.36 % / ベース 13.08 %</t>
         </is>
       </c>
     </row>
@@ -4325,32 +4325,32 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,225.12 千円/人 / 補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
+          <t xml:space="preserve">全社 6,225.13 千円/人 / 補助 6,137.33 千円/人 / ベース 6,293.41 千円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,327.06 千円/人 / 補助 6,235.33 千円/人 / ベース 6,399.28 千円/人</t>
+          <t xml:space="preserve">全社 6,327.09 千円/人 / 補助 6,235.39 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,494.7 千円/人 / 補助 6,408.27 千円/人 / ベース 6,563.38 千円/人</t>
+          <t xml:space="preserve">全社 6,494.74 千円/人 / 補助 6,408.34 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,655.95 千円/人 / 補助 6,583.33 千円/人 / ベース 6,712.9 千円/人</t>
+          <t xml:space="preserve">全社 6,631.65 千円/人 / 補助 6,528.93 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,001.33 千円/人 / 補助 7,156.35 千円/人 / ベース 6,880.23 千円/人</t>
+          <t xml:space="preserve">全社 7,001.06 千円/人 / 補助 7,154.51 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,383.23 千円/人 / 補助 7,852.13 千円/人 / ベース 7,023.19 千円/人</t>
+          <t xml:space="preserve">全社 7,386.49 千円/人 / 補助 7,852.41 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
@@ -4402,17 +4402,17 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23,979.4 千円/人 / 補助 24,684 千円/人 / ベース 23,509.67 千円/人</t>
+          <t xml:space="preserve">全社 23,979.8 千円/人 / 補助 24,685 千円/人 / ベース 23,509.67 千円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25,145 千円/人 / 補助 26,011 千円/人 / ベース 24,567.67 千円/人</t>
+          <t xml:space="preserve">全社 25,146.2 千円/人 / 補助 26,014 千円/人 / ベース 24,567.67 千円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 26,367.6 千円/人 / 補助 27,409.5 千円/人 / ベース 25,673 千円/人</t>
+          <t xml:space="preserve">全社 26,369.4 千円/人 / 補助 27,414 千円/人 / ベース 25,673 千円/人</t>
         </is>
       </c>
     </row>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.48 % / 補助 2.73 % / ベース 2.28 %</t>
+          <t xml:space="preserve">全社 2.11 % / 補助 1.88 % / ベース 2.28 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.19 % / 補助 8.7 % / ベース 2.49 %</t>
+          <t xml:space="preserve">全社 5.57 % / 補助 9.58 % / ベース 2.49 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.45 % / 補助 9.72 % / ベース 2.08 %</t>
+          <t xml:space="preserve">全社 5.51 % / 補助 9.75 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4521,22 @@
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 52.48 % / 補助 43.17 % / ベース 62.92 %</t>
+          <t xml:space="preserve">全社 52.48 % / 補助 43.18 % / ベース 62.92 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 46.35 % / 補助 35.92 % / ベース 59.58 %</t>
+          <t xml:space="preserve">全社 47.15 % / 補助 36.82 % / ベース 60.03 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.72 % / 補助 31.77 % / ベース 59.15 %</t>
+          <t xml:space="preserve">全社 42.13 % / 補助 31.26 % / ベース 58.71 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.17 % / 補助 28.14 % / ベース 58.74 %</t>
+          <t xml:space="preserve">全社 37.51 % / 補助 26.74 % / ベース 57.46 %</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4650,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 73,062.29 千円/人 / 補助 95,275.04 千円/人 / ベース 55,640.52 千円/人</t>
+          <t xml:space="preserve">全社 72,799.64 千円/人 / 補助 94,496.69 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 80,688.75 千円/人 / 補助 111,604.9 千円/人 / ベース 56,535.5 千円/人</t>
+          <t xml:space="preserve">全社 80,415.96 千円/人 / 補助 110,740.37 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 89,677.78 千円/人 / 補助 131,958.22 千円/人 / ベース 57,212.44 千円/人</t>
+          <t xml:space="preserve">全社 89,094.29 千円/人 / 補助 129,980.95 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
@@ -4697,32 +4697,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,023.93 千円/人 / 補助 7,291.82 千円/人 / ベース 3,260.01 千円/人</t>
+          <t xml:space="preserve">全社 5,023.91 千円/人 / 補助 7,291.79 千円/人 / ベース 3,260.01 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,959.98 千円/人 / 補助 7,228.15 千円/人 / ベース 3,174.39 千円/人</t>
+          <t xml:space="preserve">全社 4,959.95 千円/人 / 補助 7,228.1 千円/人 / ベース 3,174.39 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,940.55 千円/人 / 補助 7,241.75 千円/人 / ベース 3,112.19 千円/人</t>
+          <t xml:space="preserve">全社 4,940.51 千円/人 / 補助 7,241.67 千円/人 / ベース 3,112.19 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,930.37 千円/人 / 補助 10,810.28 千円/人 / ベース 3,887.29 千円/人</t>
+          <t xml:space="preserve">全社 6,646.07 千円/人 / 補助 10,250.55 千円/人 / ベース 3,795.47 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8,751.37 千円/人 / 補助 14,664.5 千円/人 / ベース 4,131.73 千円/人</t>
+          <t xml:space="preserve">全社 8,994.8 千円/人 / 補助 15,051.65 千円/人 / ベース 4,225.02 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10,976.51 千円/人 / 補助 19,590.94 千円/人 / ベース 4,361.86 千円/人</t>
+          <t xml:space="preserve">全社 11,867.57 千円/人 / 補助 21,129.98 千円/人 / ベース 4,645.09 千円/人</t>
         </is>
       </c>
     </row>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15,032.23 千円/人 / 補助 19,152.48 千円/人 / ベース 11,809.99 千円/人</t>
+          <t xml:space="preserve">全社 14,724 千円/人 / 補助 18,534.04 千円/人 / ベース 11,719.93 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,121.53 千円/人 / 補助 23,461.65 千円/人 / ベース 12,181.69 千円/人</t>
+          <t xml:space="preserve">全社 17,355.83 千円/人 / 補助 23,828.16 千円/人 / ベース 12,273.27 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19,651.26 千円/人 / 補助 28,969.27 千円/人 / ベース 12,512.91 千円/人</t>
+          <t xml:space="preserve">全社 20,522.4 千円/人 / 補助 30,462.56 千円/人 / ベース 12,791.17 千円/人</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4836,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.2 % / 補助 3.45 % / ベース 4.79 %</t>
+          <t xml:space="preserve">全社 4.58 % / 補助 4.31 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.4 % / 補助 4.17 % / ベース 4.58 %</t>
+          <t xml:space="preserve">全社 4.38 % / 補助 4.13 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.21 % / 補助 3.2 % / ベース 5 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 3.97 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.08 pt / 補助 18.57 pt / ベース 2.52 pt</t>
+          <t xml:space="preserve">全社 10.71 pt / 補助 17.72 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.9 pt / 補助 17.85 pt / ベース 1.68 pt</t>
+          <t xml:space="preserve">全社 10.92 pt / 補助 17.9 pt / ベース 1.68 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.61 pt / 補助 18.82 pt / ベース 1.26 pt</t>
+          <t xml:space="preserve">全社 11.28 pt / 補助 18.06 pt / ベース 1.26 pt</t>
         </is>
       </c>
     </row>
@@ -5208,17 +5208,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.41 倍 / 補助 7.49 倍 / ベース 4.97 倍</t>
+          <t xml:space="preserve">全社 6.2 倍 / 補助 7.2 倍 / ベース 4.87 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.13 倍 / 補助 10.17 倍 / ベース 5.41 倍</t>
+          <t xml:space="preserve">全社 8.35 倍 / 補助 10.48 倍 / ベース 5.51 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.31 倍 / 補助 13.64 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 11.14 倍 / 補助 14.84 倍 / ベース 6.2 倍</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 60.66 %</t>
+          <t xml:space="preserve">構成比 60.67 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.91 %</t>
+          <t xml:space="preserve">構成比 63.92 %</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.02 % / ベース 7.32 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 7.32 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.02 % / ベース 6.26 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.02 % / ベース 6.26 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5518,17 +5518,17 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.34 pt</t>
+          <t xml:space="preserve">差 0.67 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0 pt</t>
+          <t xml:space="preserve">差 -0.33 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.33 pt</t>
+          <t xml:space="preserve">差 -1.34 pt</t>
         </is>
       </c>
     </row>
@@ -5580,17 +5580,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.36 pt</t>
+          <t xml:space="preserve">差 4.03 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.83 pt</t>
+          <t xml:space="preserve">差 6.12 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.22 pt</t>
+          <t xml:space="preserve">差 8.14 pt</t>
         </is>
       </c>
     </row>
@@ -5642,17 +5642,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 95,275.04 千円/人 / ベース 55,640.52 千円/人</t>
+          <t xml:space="preserve">補助 94,496.69 千円/人 / ベース 55,640.52 千円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 111,604.9 千円/人 / ベース 56,535.5 千円/人</t>
+          <t xml:space="preserve">補助 110,740.37 千円/人 / ベース 56,535.5 千円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 131,958.22 千円/人 / ベース 57,212.44 千円/人</t>
+          <t xml:space="preserve">補助 129,980.95 千円/人 / ベース 57,212.44 千円/人</t>
         </is>
       </c>
     </row>
@@ -5689,32 +5689,32 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,137.3 千円/人 / ベース 6,293.41 千円/人</t>
+          <t xml:space="preserve">補助 6,137.33 千円/人 / ベース 6,293.41 千円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,235.33 千円/人 / ベース 6,399.28 千円/人</t>
+          <t xml:space="preserve">補助 6,235.39 千円/人 / ベース 6,399.28 千円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,408.27 千円/人 / ベース 6,563.38 千円/人</t>
+          <t xml:space="preserve">補助 6,408.34 千円/人 / ベース 6,563.38 千円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 6,583.33 千円/人 / ベース 6,712.9 千円/人</t>
+          <t xml:space="preserve">補助 6,528.93 千円/人 / ベース 6,712.9 千円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 7,156.35 千円/人 / ベース 6,880.23 千円/人</t>
+          <t xml:space="preserve">補助 7,154.51 千円/人 / ベース 6,880.23 千円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 7,852.13 千円/人 / ベース 7,023.19 千円/人</t>
+          <t xml:space="preserve">補助 7,852.41 千円/人 / ベース 7,023.19 千円/人</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.51 %</t>
+          <t xml:space="preserve">寄与率 76.01 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 88.99 %</t>
+          <t xml:space="preserve">寄与率 87.32 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.64 %</t>
+          <t xml:space="preserve">寄与率 89.3 %</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率</t>
+          <t xml:space="preserve">補助事業 原価率（基準年後初年度）</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5899,7 +5899,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率</t>
+          <t xml:space="preserve">ベース事業 原価率（基準年後初年度）</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -5920,7 +5920,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率（設備導入期間初年度）</t>
         </is>
       </c>
       <c r="B6" s="2">
@@ -5941,7 +5941,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率（設備導入期間初年度）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -6308,7 +6308,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率 年当たり改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6434,7 +6434,7 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率 年当たり改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -6585,7 +6585,7 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率 年当たり改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B35" s="2">
@@ -6606,7 +6606,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率 年当たり改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -11401,14 +11401,14 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MjAwMDAwLCJjb2dzIjo0ODk2MDAwLCJlbXBsb3llZVBheSI6NTE5MDMxLCJvZmZpY2VyUGF5IjozNjAwMCwiZGVwcmVjaWF0aW9uIjoxODAwMDAsIm90aGVyU2dhIjo5MDAwMDAsImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQ5MzA3OSwiZW1wbG95ZWVCb251cyI6MjU5NTIsIm9mZmljZXJDb21wZW5zYXRpb24iOjMyNDAwLCJvZmZpY2VyQm9udXMiOjM2MDAsImNvZ3NEZXByZWNpYXRpb24iOjQ1MDAwLCJzZ2FEZXByZWNpYXRpb24iOjEzNTAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzYwMDB9LCJvdGhlciI6eyJzYWxlcyI6NjQ0MDAwMCwiY29ncyI6NDM3OTIwMCwiZW1wbG95ZWVQYXkiOjcwOTc4Niwib2ZmaWNlclBheSI6NTUyMDAsImRlcHJlY2lhdGlvbiI6MTM4MDAwLCJvdGhlclNnYSI6NzM2MDAwLCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Njc0Mjk3LCJlbXBsb3llZUJvbnVzIjozNTQ4OSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NDk2ODAsIm9mZmljZXJCb251cyI6NTUyMCwiY29nc0RlcHJlY2lhdGlvbiI6Mjc2MDAsInNnYURlcHJlY2lhdGlvbiI6MTEwNDAwLCJyZXNlYXJjaERldmVsb3BtZW50IjoyNzYwMCwib3JkaW5hcnlJbmNvbWUiOjM5NDUzNCwicHJlVGF4SW5jb21lIjozOTQ1MzQsIm5ldEluY29tZSI6NzUwNzUyLjF9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2MDAwMDAsImNvZ3MiOjUxNjgwMDAsImVtcGxveWVlUGF5Ijo1NTg4MjQsIm9mZmljZXJQYXkiOjM4MDAwLCJkZXByZWNpYXRpb24iOjE5MDAwMCwib3RoZXJTZ2EiOjk1MDAwMCwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NTMwODgzLCJlbXBsb3llZUJvbnVzIjoyNzk0MSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzQyMDAsIm9mZmljZXJCb251cyI6MzgwMCwiY29nc0RlcHJlY2lhdGlvbiI6NDc1MDAsInNnYURlcHJlY2lhdGlvbiI6MTQyNTAwLCJyZXNlYXJjaERldmVsb3BtZW50IjozODAwMH0sIm90aGVyIjp7InNhbGVzIjo2NzIwMDAwLCJjb2dzIjo0NTY5NjAwLCJlbXBsb3llZVBheSI6NzU0MTQ4LCJvZmZpY2VyUGF5Ijo1NzYwMCwiZGVwcmVjaWF0aW9uIjoxNDQwMDAsIm90aGVyU2dhIjo3NjgwMDAsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3MTY0NDEsImVtcGxveWVlQm9udXMiOjM3NzA3LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo1MTg0MCwib2ZmaWNlckJvbnVzIjo1NzYwLCJjb2dzRGVwcmVjaWF0aW9uIjoyODgwMCwic2dhRGVwcmVjaWF0aW9uIjoxMTUyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjI4ODAwLCJvcmRpbmFyeUluY29tZSI6Mzk4MDEyLCJwcmVUYXhJbmNvbWUiOjM5ODAxMiwibmV0SW5jb21lIjo3NzE4ODEuNn19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwMDAwMDAsImNvZ3MiOjU0NDAwMDAsImVtcGxveWVlUGF5Ijo2MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo1NzAwMDAsImVtcGxveWVlQm9udXMiOjMwMDAwLCJvZmZpY2VyUGF5Ijo0MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzYwMDAsIm9mZmljZXJCb251cyI6NDAwMCwiZGVwcmVjaWF0aW9uIjoyMDAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjUwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjE1MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NDAwMDAsIm90aGVyU2dhIjoxMDAwMDAwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwMDAwMDAsImNvZ3MiOjQ3NjAwMDAsImVtcGxveWVlUGF5Ijo4MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo3NjAwMDAsImVtcGxveWVlQm9udXMiOjQwMDAwLCJvZmZpY2VyUGF5Ijo2MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NTQwMDAsIm9mZmljZXJCb251cyI6NjAwMCwiZGVwcmVjaWF0aW9uIjoxNTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjMwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjEyMDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzAwMDAsIm90aGVyU2dhIjo4MDAwMDAsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjo0MDAwMDAsInByZVRheEluY29tZSI6NDAwMDAwLCJuZXRJbmNvbWUiOjc5MTAwMH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAuNjYsMC43XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sInByb2plY3RDb2dzUmF0ZVRvQmFzZSI6WzAuNjgsMC42OF0sIm90aGVyQ29nc1JhdGVUb0Jhc2UiOlswLjY4LDAuNjhdLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RCYXNlWWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAxXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUwMDAwMCwyMDAwMDAwMF0sInN1YnNpZHkiOlsxMDAwMDAsNTAwMDAwMF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4MjQwMDAwLCJtYXgiOjI1MjY5MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0ODAwMDAsIm1heCI6MTM2ODQwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxODc4MDAwLCJtYXgiOjMzNDMwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyODUwMDAsIm1heCI6Mzc0MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1MTMwMDAsIjIwMjk6cHJvamVjdDo3LTgiOjc5MDAwMH0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzY0MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyNzUyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00Ijo3MjYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyNjUwMTcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05Ijo4MjA4MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjo5MTIwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExNjczNzYsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6NjE0NDEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6MjQ1NDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjYzNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwNzI1MDMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTA3MjUwMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3NTA3NTIuMSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyMDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMzA0MDAwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Njc3OTY5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NTE5MDMxLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MzYwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6NDUwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEzNTAwMCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzMjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5NzM3NjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6NzYzMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNDUxMDcyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6ODYwNDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6OTU2MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMjQ3MzI0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjY1NjQ4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjI1NzcwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1Ijo2NjgwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMTAyNjg4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExMDI2ODgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6NzcxODgxLjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NjAwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQzMjAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcwNDY3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjU1ODgyNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjM4MDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjQ3NTAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxNDI1MDAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExMzAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6NzkxMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAwMDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1NjAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3MzAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2MDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05Ijo0MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00Ijo1MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MTUwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLjY2LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVRvQmFzZToxIjowLjY4LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVRvQmFzZSI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MSI6MC42OCwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Rmlyc3RZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RCYXNlWWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczoxIjoxMDAwMDAwMDAwMCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjppbnZlc3RtZW50IjoyMzAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAwMDAwMCwiZHJpdmVyOnN1YnNpZHkiOjc2NjAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MTAwMDAwLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MDAwMDAwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyNDAwMDAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQ4MDAwMCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTg3ODAwMCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mjg1MDAwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTI2OTAwMCwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2ODQwMDAsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMzQzMDAwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjM3NDAwMH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTk5OTk5OTk5OTk5LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTk5OTk5OTk5OTk5LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Ni41MjgxMTEzODQ3OTU5MjFlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDczNTk5NDE4MzE4OTE2NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIyMDk2NTY4MTE3MDExMSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMDUyNzMxMjA2</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOS4gOmDqOebruaomeacqumBlOOCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MjAwMDAwLCJjb2dzIjo0ODk2MDAwLCJlbXBsb3llZVBheSI6NTE5MDMxLCJvZmZpY2VyUGF5IjozNjAwMCwiZGVwcmVjaWF0aW9uIjoxODAwMDAsIm90aGVyU2dhIjo5MDAwMDAsImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQ5MzA3OSwiZW1wbG95ZWVCb251cyI6MjU5NTIsIm9mZmljZXJDb21wZW5zYXRpb24iOjMyNDAwLCJvZmZpY2VyQm9udXMiOjM2MDAsImNvZ3NEZXByZWNpYXRpb24iOjQ1MDAwLCJzZ2FEZXByZWNpYXRpb24iOjEzNTAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzYwMDB9LCJvdGhlciI6eyJzYWxlcyI6NjQ0MDAwMCwiY29ncyI6NDM3OTIwMCwiZW1wbG95ZWVQYXkiOjcwOTc4Niwib2ZmaWNlclBheSI6NTUyMDAsImRlcHJlY2lhdGlvbiI6MTM4MDAwLCJvdGhlclNnYSI6NzM2MDAwLCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Njc0Mjk3LCJlbXBsb3llZUJvbnVzIjozNTQ4OSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NDk2ODAsIm9mZmljZXJCb251cyI6NTUyMCwiY29nc0RlcHJlY2lhdGlvbiI6Mjc2MDAsInNnYURlcHJlY2lhdGlvbiI6MTEwNDAwLCJyZXNlYXJjaERldmVsb3BtZW50IjoyNzYwMCwib3JkaW5hcnlJbmNvbWUiOjM5NDUzNCwicHJlVGF4SW5jb21lIjozOTQ1MzQsIm5ldEluY29tZSI6NzUwNzUyLjF9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2MDAwMDAsImNvZ3MiOjUxNjgwMDAsImVtcGxveWVlUGF5Ijo1NTg4MjQsIm9mZmljZXJQYXkiOjM4MDAwLCJkZXByZWNpYXRpb24iOjE5MDAwMCwib3RoZXJTZ2EiOjk1MDAwMCwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NTMwODgzLCJlbXBsb3llZUJvbnVzIjoyNzk0MSwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzQyMDAsIm9mZmljZXJCb251cyI6MzgwMCwiY29nc0RlcHJlY2lhdGlvbiI6NDc1MDAsInNnYURlcHJlY2lhdGlvbiI6MTQyNTAwLCJyZXNlYXJjaERldmVsb3BtZW50IjozODAwMH0sIm90aGVyIjp7InNhbGVzIjo2NzIwMDAwLCJjb2dzIjo0NTY5NjAwLCJlbXBsb3llZVBheSI6NzU0MTQ4LCJvZmZpY2VyUGF5Ijo1NzYwMCwiZGVwcmVjaWF0aW9uIjoxNDQwMDAsIm90aGVyU2dhIjo3NjgwMDAsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3MTY0NDEsImVtcGxveWVlQm9udXMiOjM3NzA3LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo1MTg0MCwib2ZmaWNlckJvbnVzIjo1NzYwLCJjb2dzRGVwcmVjaWF0aW9uIjoyODgwMCwic2dhRGVwcmVjaWF0aW9uIjoxMTUyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjI4ODAwLCJvcmRpbmFyeUluY29tZSI6Mzk4MDEyLCJwcmVUYXhJbmNvbWUiOjM5ODAxMiwibmV0SW5jb21lIjo3NzE4ODEuNn19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwMDAwMDAsImNvZ3MiOjU0NDAwMDAsImVtcGxveWVlUGF5Ijo2MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo1NzAwMDAsImVtcGxveWVlQm9udXMiOjMwMDAwLCJvZmZpY2VyUGF5Ijo0MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MzYwMDAsIm9mZmljZXJCb251cyI6NDAwMCwiZGVwcmVjaWF0aW9uIjoyMDAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjUwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjE1MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NDAwMDAsIm90aGVyU2dhIjoxMDAwMDAwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwMDAwMDAsImNvZ3MiOjQ3NjAwMDAsImVtcGxveWVlUGF5Ijo4MDAwMDAsImVtcGxveWVlU2FsYXJ5Ijo3NjAwMDAsImVtcGxveWVlQm9udXMiOjQwMDAwLCJvZmZpY2VyUGF5Ijo2MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6NTQwMDAsIm9mZmljZXJCb251cyI6NjAwMCwiZGVwcmVjaWF0aW9uIjoxNTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjMwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjEyMDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6MzAwMDAsIm90aGVyU2dhIjo4MDAwMDAsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjo0MDAwMDAsInByZVRheEluY29tZSI6NDAwMDAwLCJuZXRJbmNvbWUiOjc5MTAwMH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAuNjYsMC43XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLjY2LDAuN10sInByb2plY3RDb2dzUmF0ZVRvQmFzZSI6WzAuNjgsMC42OF0sIm90aGVyQ29nc1JhdGVUb0Jhc2UiOlswLjY4LDAuNjhdLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RCYXNlWWVhclNhbGVzIjpbMCwxMDAwMDAwMDAwMF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAxXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJpbnZlc3RtZW50IjpbMTUwMDAwMCwyMDAwMDAwMF0sInN1YnNpZHkiOlsxMDAwMDAsNTAwMDAwMF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4MjQwMDAwLCJtYXgiOjI1MjY5MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0ODAwMDAsIm1heCI6MTM2ODQwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxODc4MDAwLCJtYXgiOjMzNDMwMDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyODUwMDAsIm1heCI6Mzc0MDAwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1MTMwMDAsIjIwMjk6cHJvamVjdDo3LTgiOjc5MDAwMH0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzY0MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyNzUyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00Ijo3MjYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyNjUwMTcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05Ijo4MjA4MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjo5MTIwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExNjczNzYsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6NjE0NDEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6MjQ1NDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjYzNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwNzI1MDMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTA3MjUwMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3NTA3NTIuMSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyMDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMzA0MDAwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Njc3OTY5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NTE5MDMxLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MzYwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6NDUwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEzNTAwMCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzMjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5NzM3NjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6NzYzMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNDUxMDcyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6ODYwNDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6OTU2MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMjQ3MzI0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjY1NjQ4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjI1NzcwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1Ijo2NjgwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMTAyNjg4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExMDI2ODgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6NzcxODgxLjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NjAwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQzMjAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcwNDY3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjU1ODgyNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjM4MDAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjQ3NTAwLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxNDI1MDAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExMzAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6NzkxMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAwMDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1NjAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3MzAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2MDAwMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05Ijo0MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00Ijo1MDAwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MTUwMDAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLjY2LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAuNjYsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjcsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVRvQmFzZToxIjowLjY4LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVRvQmFzZSI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MCI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVUb0Jhc2U6MSI6MC42OCwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Rmlyc3RZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RCYXNlWWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczoxIjoxMDAwMDAwMDAwMCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjppbnZlc3RtZW50IjoyMzAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAwMDAwMCwiZHJpdmVyOnN1YnNpZHkiOjc2NjAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MTAwMDAwLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MDAwMDAwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyNDAwMDAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQ4MDAwMCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTg3ODAwMCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mjg1MDAwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTI2OTAwMCwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2ODQwMDAsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMzQzMDAwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjM3NDAwMH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTY2ODIwOTMyNzE2LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42Nzk5OTk5OTk5OTk5OTk5LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6MCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4yOTQ5NjQxMzU5MjI3ODNlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDczNTk5NDE4MzE4OTE2NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIyMTQwNTAwMjYxNDIxNywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjI1MDAwMDAwMDAwMDUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAzMjIxNzQxNDgx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDU3LCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5MTU3MTE4NjI3MjU2NDk4LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMzczNDQ0NjQwMjgyMDA2MSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc2NzAyODY1Mzg4MTUxLCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">ODgyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5NjY1LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNDA1MzE5NjYwMzEwODQ3Nywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgyMTUwMTQ2OTU4NDE1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>25.231207135866285</v>
+        <v>25.592329405571277</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>2221268.9999999995</v>
+        <v>2266973.9999999995</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>289.9828981723237</v>
+        <v>295.94960835509136</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>80000</v>
       </c>
       <c r="E6" s="2">
-        <v>80000</v>
+        <v>83982</v>
       </c>
       <c r="F6" s="2">
-        <v>80000</v>
+        <v>88165</v>
       </c>
       <c r="G6" s="2">
-        <v>80000</v>
+        <v>92558</v>
       </c>
       <c r="H6" s="2">
-        <v>80000</v>
+        <v>107587</v>
       </c>
       <c r="I6" s="2">
-        <v>80000</v>
+        <v>123386</v>
       </c>
       <c r="J6" s="2">
-        <v>80000</v>
+        <v>141913</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1465,22 @@
         <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>3828103</v>
+        <v>3843339</v>
       </c>
       <c r="F9" s="2">
-        <v>4029326</v>
+        <v>4060848</v>
       </c>
       <c r="G9" s="2">
-        <v>4242343</v>
+        <v>4291114</v>
       </c>
       <c r="H9" s="2">
-        <v>4619215</v>
+        <v>4704087</v>
       </c>
       <c r="I9" s="2">
-        <v>5101989.01</v>
+        <v>5227551.01</v>
       </c>
       <c r="J9" s="2">
-        <v>5646692.109999999</v>
+        <v>5818076.109999999</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1703,22 @@
         <v>270000</v>
       </c>
       <c r="E16" s="2">
-        <v>270000</v>
+        <v>285236</v>
       </c>
       <c r="F16" s="2">
-        <v>270000</v>
+        <v>301522</v>
       </c>
       <c r="G16" s="2">
-        <v>270000</v>
+        <v>318771</v>
       </c>
       <c r="H16" s="2">
-        <v>270000</v>
+        <v>355441</v>
       </c>
       <c r="I16" s="2">
-        <v>270000</v>
+        <v>396949</v>
       </c>
       <c r="J16" s="2">
-        <v>270000</v>
+        <v>443924</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1771,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1205739</v>
+        <v>1190503</v>
       </c>
       <c r="F18" s="4">
-        <v>1249908</v>
+        <v>1218386</v>
       </c>
       <c r="G18" s="4">
-        <v>1294414</v>
+        <v>1245643</v>
       </c>
       <c r="H18" s="4">
-        <v>1821024</v>
+        <v>1736152</v>
       </c>
       <c r="I18" s="4">
-        <v>2572511.959999999</v>
+        <v>2446949.959999999</v>
       </c>
       <c r="J18" s="4">
-        <v>3548402.759999998</v>
+        <v>3377018.759999998</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.664850945498106</v>
+        <v>7.567996096309675</v>
       </c>
       <c r="F19" s="2">
-        <v>7.5762987929097845</v>
+        <v>7.385228657707751</v>
       </c>
       <c r="G19" s="2">
-        <v>7.481140436201716</v>
+        <v>7.1992656262769215</v>
       </c>
       <c r="H19" s="2">
-        <v>9.129266910979542</v>
+        <v>8.703781502072982</v>
       </c>
       <c r="I19" s="2">
-        <v>11.185337477152672</v>
+        <v>10.63939119346416</v>
       </c>
       <c r="J19" s="2">
-        <v>13.320233252238417</v>
+        <v>12.676880450962377</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>1130000</v>
       </c>
       <c r="E20" s="4">
-        <v>1169249</v>
+        <v>1154013</v>
       </c>
       <c r="F20" s="4">
-        <v>1211864</v>
+        <v>1180342</v>
       </c>
       <c r="G20" s="4">
-        <v>1254751</v>
+        <v>1205980</v>
       </c>
       <c r="H20" s="4">
-        <v>1636608</v>
+        <v>1551736</v>
       </c>
       <c r="I20" s="4">
-        <v>2371982</v>
+        <v>2246420</v>
       </c>
       <c r="J20" s="4">
-        <v>3330105</v>
+        <v>3158721</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>1130000</v>
       </c>
       <c r="E21" s="2">
-        <v>1169249</v>
+        <v>1154013</v>
       </c>
       <c r="F21" s="2">
-        <v>1211864</v>
+        <v>1180342</v>
       </c>
       <c r="G21" s="2">
-        <v>1254751</v>
+        <v>1205980</v>
       </c>
       <c r="H21" s="2">
-        <v>1636608</v>
+        <v>1551736</v>
       </c>
       <c r="I21" s="2">
-        <v>2371982</v>
+        <v>2246420</v>
       </c>
       <c r="J21" s="2">
-        <v>3330105</v>
+        <v>3158721</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>791000</v>
       </c>
       <c r="E22" s="2">
-        <v>818475</v>
+        <v>807809</v>
       </c>
       <c r="F22" s="2">
-        <v>848305</v>
+        <v>826239</v>
       </c>
       <c r="G22" s="2">
-        <v>878326</v>
+        <v>844186</v>
       </c>
       <c r="H22" s="2">
-        <v>1145626</v>
+        <v>1086215</v>
       </c>
       <c r="I22" s="2">
-        <v>1660388</v>
+        <v>1572494</v>
       </c>
       <c r="J22" s="2">
-        <v>2331074</v>
+        <v>2211105</v>
       </c>
     </row>
     <row r="23">
@@ -2009,22 +2009,22 @@
         <v>350000</v>
       </c>
       <c r="E25" s="2">
-        <v>350000</v>
+        <v>369218</v>
       </c>
       <c r="F25" s="2">
-        <v>350000</v>
+        <v>389687</v>
       </c>
       <c r="G25" s="2">
-        <v>350000</v>
+        <v>411329</v>
       </c>
       <c r="H25" s="2">
-        <v>350000</v>
+        <v>463028</v>
       </c>
       <c r="I25" s="2">
-        <v>350000</v>
+        <v>520335</v>
       </c>
       <c r="J25" s="2">
-        <v>350000</v>
+        <v>585837</v>
       </c>
     </row>
     <row r="26">
@@ -2043,22 +2043,22 @@
         <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>3154334</v>
+        <v>3158316</v>
       </c>
       <c r="F26" s="4">
-        <v>3303675</v>
+        <v>3311840</v>
       </c>
       <c r="G26" s="4">
-        <v>3460376</v>
+        <v>3472934</v>
       </c>
       <c r="H26" s="4">
-        <v>4107996</v>
+        <v>4136152</v>
       </c>
       <c r="I26" s="4">
-        <v>5050546.969999999</v>
+        <v>5095319.969999999</v>
       </c>
       <c r="J26" s="4">
-        <v>6238810.869999997</v>
+        <v>6303263.869999997</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.735724973033162</v>
       </c>
       <c r="E27" s="2">
-        <v>4.795149501661133</v>
+        <v>4.9274418604651204</v>
       </c>
       <c r="F27" s="2">
-        <v>4.734470097332744</v>
+        <v>4.8609448832859</v>
       </c>
       <c r="G27" s="2">
-        <v>4.743232914859963</v>
+        <v>4.8641842601091945</v>
       </c>
       <c r="H27" s="2">
-        <v>18.71530723828856</v>
+        <v>19.096763716212294</v>
       </c>
       <c r="I27" s="2">
-        <v>22.94430106553167</v>
+        <v>23.189862703304875</v>
       </c>
       <c r="J27" s="2">
-        <v>23.52742994091983</v>
+        <v>23.706929243150142</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.05201784326195</v>
+        <v>20.07733131198526</v>
       </c>
       <c r="F28" s="2">
-        <v>20.025176984759064</v>
+        <v>20.074669011087487</v>
       </c>
       <c r="G28" s="2">
-        <v>19.999442850635074</v>
+        <v>20.07202253657622</v>
       </c>
       <c r="H28" s="2">
-        <v>20.59445232640334</v>
+        <v>20.735605677015705</v>
       </c>
       <c r="I28" s="2">
-        <v>21.95988713835207</v>
+        <v>22.154561107861838</v>
       </c>
       <c r="J28" s="2">
-        <v>23.419668404552958</v>
+        <v>23.66161641662319</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>12874.832653061225</v>
+        <v>12891.085714285715</v>
       </c>
       <c r="F35" s="2">
-        <v>12854.76653696498</v>
+        <v>12886.536964980545</v>
       </c>
       <c r="G35" s="2">
-        <v>12960.209737827716</v>
+        <v>13007.243445692884</v>
       </c>
       <c r="H35" s="2">
-        <v>14724</v>
+        <v>14824.917562724015</v>
       </c>
       <c r="I35" s="2">
-        <v>17355.831512027486</v>
+        <v>17509.6906185567</v>
       </c>
       <c r="J35" s="2">
-        <v>20522.40417763157</v>
+        <v>20734.42062499999</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1555739</v>
+        <v>1559721</v>
       </c>
       <c r="F36" s="4">
-        <v>1599908</v>
+        <v>1608073</v>
       </c>
       <c r="G36" s="4">
-        <v>1644414</v>
+        <v>1656972</v>
       </c>
       <c r="H36" s="4">
-        <v>2171024</v>
+        <v>2199180</v>
       </c>
       <c r="I36" s="4">
-        <v>2922511.959999999</v>
+        <v>2967284.959999999</v>
       </c>
       <c r="J36" s="4">
-        <v>3898402.759999998</v>
+        <v>3962855.759999998</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>9.889791692147536</v>
+        <v>9.915105160870844</v>
       </c>
       <c r="F37" s="2">
-        <v>9.697818598782236</v>
+        <v>9.747310625110659</v>
       </c>
       <c r="G37" s="2">
-        <v>9.503985640804418</v>
+        <v>9.576565326745563</v>
       </c>
       <c r="H37" s="2">
-        <v>10.88390793649202</v>
+        <v>11.025061287104391</v>
       </c>
       <c r="I37" s="2">
-        <v>12.707145024746517</v>
+        <v>12.901818994256283</v>
       </c>
       <c r="J37" s="2">
-        <v>14.634086823438844</v>
+        <v>14.876034835509074</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.0486007228415657</v>
       </c>
       <c r="E38" s="2">
-        <v>3.029072847682124</v>
+        <v>3.2927814569536418</v>
       </c>
       <c r="F38" s="2">
-        <v>2.8391009031720538</v>
+        <v>3.100041610005899</v>
       </c>
       <c r="G38" s="2">
-        <v>2.7817849526347693</v>
+        <v>3.0408445387740457</v>
       </c>
       <c r="H38" s="2">
-        <v>32.02417396105848</v>
+        <v>32.72282211165909</v>
       </c>
       <c r="I38" s="2">
-        <v>34.61444737598474</v>
+        <v>34.92688001891611</v>
       </c>
       <c r="J38" s="2">
-        <v>33.39219183212509</v>
+        <v>33.55157369179666</v>
       </c>
     </row>
   </sheetData>
@@ -2799,22 +2799,22 @@
         <v>730000</v>
       </c>
       <c r="E8" s="4">
-        <v>765638</v>
+        <v>756456</v>
       </c>
       <c r="F8" s="4">
-        <v>802319</v>
+        <v>783379</v>
       </c>
       <c r="G8" s="4">
-        <v>840034</v>
+        <v>810723</v>
       </c>
       <c r="H8" s="4">
-        <v>1240317</v>
+        <v>1183179</v>
       </c>
       <c r="I8" s="4">
-        <v>1896507.9900000002</v>
+        <v>1807449.9900000002</v>
       </c>
       <c r="J8" s="4">
-        <v>2768026.8899999997</v>
+        <v>2642443.8899999997</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2833,22 @@
         <v>9.125</v>
       </c>
       <c r="E9" s="2">
-        <v>9.079340556679679</v>
+        <v>8.970455541840508</v>
       </c>
       <c r="F9" s="2">
-        <v>9.026071374812604</v>
+        <v>8.81299678498119</v>
       </c>
       <c r="G9" s="2">
-        <v>8.96539380659376</v>
+        <v>8.652567590196481</v>
       </c>
       <c r="H9" s="2">
-        <v>10.847526259172126</v>
+        <v>10.347810496672235</v>
       </c>
       <c r="I9" s="2">
-        <v>13.591837721953096</v>
+        <v>12.953579465080844</v>
       </c>
       <c r="J9" s="2">
-        <v>16.256210481583206</v>
+        <v>15.518680189415898</v>
       </c>
     </row>
     <row r="10">
@@ -2935,22 +2935,22 @@
         <v>50000</v>
       </c>
       <c r="E12" s="2">
-        <v>50000</v>
+        <v>52705</v>
       </c>
       <c r="F12" s="2">
-        <v>50000</v>
+        <v>55556</v>
       </c>
       <c r="G12" s="2">
-        <v>50000</v>
+        <v>58561</v>
       </c>
       <c r="H12" s="2">
-        <v>50000</v>
+        <v>71463</v>
       </c>
       <c r="I12" s="2">
-        <v>50000</v>
+        <v>85284</v>
       </c>
       <c r="J12" s="2">
-        <v>50000</v>
+        <v>101726</v>
       </c>
     </row>
     <row r="13">
@@ -2969,22 +2969,22 @@
         <v>150000</v>
       </c>
       <c r="E13" s="2">
-        <v>150000</v>
+        <v>159182</v>
       </c>
       <c r="F13" s="2">
-        <v>150000</v>
+        <v>168940</v>
       </c>
       <c r="G13" s="2">
-        <v>150000</v>
+        <v>179311</v>
       </c>
       <c r="H13" s="2">
-        <v>150000</v>
+        <v>207707</v>
       </c>
       <c r="I13" s="2">
-        <v>150000</v>
+        <v>240445</v>
       </c>
       <c r="J13" s="2">
-        <v>150000</v>
+        <v>278123</v>
       </c>
     </row>
     <row r="14">
@@ -3003,22 +3003,22 @@
         <v>200000</v>
       </c>
       <c r="E14" s="2">
-        <v>200000</v>
+        <v>211887</v>
       </c>
       <c r="F14" s="2">
-        <v>200000</v>
+        <v>224496</v>
       </c>
       <c r="G14" s="2">
-        <v>200000</v>
+        <v>237872</v>
       </c>
       <c r="H14" s="2">
-        <v>200000</v>
+        <v>279170</v>
       </c>
       <c r="I14" s="2">
-        <v>200000</v>
+        <v>325729</v>
       </c>
       <c r="J14" s="2">
-        <v>200000</v>
+        <v>379849</v>
       </c>
     </row>
     <row r="15">
@@ -3037,22 +3037,22 @@
         <v>1570000</v>
       </c>
       <c r="E15" s="4">
-        <v>1652222</v>
+        <v>1654927</v>
       </c>
       <c r="F15" s="4">
-        <v>1738892</v>
+        <v>1744448</v>
       </c>
       <c r="G15" s="4">
-        <v>1830251</v>
+        <v>1838812</v>
       </c>
       <c r="H15" s="4">
-        <v>2279687</v>
+        <v>2301719</v>
       </c>
       <c r="I15" s="4">
-        <v>3050004</v>
+        <v>3086675</v>
       </c>
       <c r="J15" s="4">
-        <v>4051519.9999999995</v>
+        <v>4105785.9999999995</v>
       </c>
     </row>
     <row r="16">
@@ -3073,22 +3073,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E16" s="2">
-        <v>5.237070063694271</v>
+        <v>5.409363057324845</v>
       </c>
       <c r="F16" s="2">
-        <v>5.245663113068333</v>
+        <v>5.409362467347512</v>
       </c>
       <c r="G16" s="2">
-        <v>5.253862804590503</v>
+        <v>5.409390248376567</v>
       </c>
       <c r="H16" s="2">
-        <v>24.55597620217118</v>
+        <v>25.174242935112456</v>
       </c>
       <c r="I16" s="2">
-        <v>33.79047211305763</v>
+        <v>34.1030334284941</v>
       </c>
       <c r="J16" s="2">
-        <v>32.83654709961035</v>
+        <v>33.01646593826688</v>
       </c>
     </row>
     <row r="17">
@@ -3315,22 +3315,22 @@
         <v>15392.156862745098</v>
       </c>
       <c r="E23" s="2">
-        <v>15441.327102803738</v>
+        <v>15466.607476635514</v>
       </c>
       <c r="F23" s="2">
-        <v>15388.424778761062</v>
+        <v>15437.592920353982</v>
       </c>
       <c r="G23" s="2">
-        <v>15510.601694915254</v>
+        <v>15583.152542372882</v>
       </c>
       <c r="H23" s="2">
-        <v>18534.040650406503</v>
+        <v>18713.162601626016</v>
       </c>
       <c r="I23" s="2">
-        <v>23828.15625</v>
+        <v>24114.6484375</v>
       </c>
       <c r="J23" s="2">
-        <v>30462.55639097744</v>
+        <v>30870.571428571424</v>
       </c>
     </row>
     <row r="24">
@@ -3829,32 +3829,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.34 % / 補助 22.92 % / ベース 25.97 %</t>
+          <t xml:space="preserve">全社 24.43 % / 補助 23.03 % / ベース 26.05 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.42 % / 補助 22.97 % / ベース 26.12 %</t>
+          <t xml:space="preserve">全社 24.61 % / 補助 23.19 % / ベース 26.28 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.52 % / 補助 23.03 % / ベース 26.27 %</t>
+          <t xml:space="preserve">全社 24.8 % / 補助 23.35 % / ベース 26.52 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.16 % / 補助 21.15 % / ベース 25.85 %</t>
+          <t xml:space="preserve">全社 23.58 % / 補助 21.65 % / ベース 26.18 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.18 % / 補助 19.91 % / ベース 25.69 %</t>
+          <t xml:space="preserve">全社 22.73 % / 補助 20.55 % / ベース 26.1 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.2 % / 補助 18.74 % / ベース 25.54 %</t>
+          <t xml:space="preserve">全社 21.84 % / 補助 19.48 % / ベース 26.02 %</t>
         </is>
       </c>
     </row>
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.66 % / 補助 9.08 % / ベース 6.03 %</t>
+          <t xml:space="preserve">全社 7.57 % / 補助 8.97 % / ベース 5.95 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.58 % / 補助 9.03 % / ベース 5.88 %</t>
+          <t xml:space="preserve">全社 7.39 % / 補助 8.81 % / ベース 5.72 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.48 % / 補助 8.97 % / ベース 5.73 %</t>
+          <t xml:space="preserve">全社 7.2 % / 補助 8.65 % / ベース 5.48 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.13 % / 補助 10.85 % / ベース 6.82 %</t>
+          <t xml:space="preserve">全社 8.7 % / 補助 10.35 % / ベース 6.5 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.19 % / 補助 13.59 % / ベース 7.47 %</t>
+          <t xml:space="preserve">全社 10.64 % / 補助 12.95 % / ベース 7.07 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.32 % / 補助 16.26 % / ベース 8.12 %</t>
+          <t xml:space="preserve">全社 12.68 % / 補助 15.52 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3953,32 +3953,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.89 % / 補助 11.45 % / ベース 8.09 %</t>
+          <t xml:space="preserve">全社 9.92 % / 補助 11.48 % / ベース 8.1 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.7 % / 補助 11.28 % / ベース 7.85 %</t>
+          <t xml:space="preserve">全社 9.75 % / 補助 11.34 % / ベース 7.89 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.5 % / 補助 11.1 % / ベース 7.62 %</t>
+          <t xml:space="preserve">全社 9.58 % / 補助 11.19 % / ベース 7.67 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.88 % / 補助 12.6 % / ベース 8.58 %</t>
+          <t xml:space="preserve">全社 11.03 % / 補助 12.79 % / ベース 8.66 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.71 % / 補助 15.03 % / ベース 9.13 %</t>
+          <t xml:space="preserve">全社 12.9 % / 補助 15.29 % / ベース 9.22 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.63 % / 補助 17.43 % / ベース 9.68 %</t>
+          <t xml:space="preserve">全社 14.88 % / 補助 17.75 % / ベース 9.79 %</t>
         </is>
       </c>
     </row>
@@ -4030,17 +4030,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.64 % / 補助 12 % / ベース 11.15 %</t>
+          <t xml:space="preserve">全社 11.63 % / 補助 12 % / ベース 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / ベース 10.99 %</t>
+          <t xml:space="preserve">全社 11.29 % / 補助 11.49 % / ベース 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.94 % / 補助 11 % / ベース 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 10.99 % / ベース 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4511,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.68 % / 補助 41.56 % / ベース 60.72 %</t>
+          <t xml:space="preserve">全社 50.62 % / 補助 41.49 % / ベース 60.66 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.57 % / 補助 42.36 % / ベース 61.81 %</t>
+          <t xml:space="preserve">全社 51.44 % / 補助 42.22 % / ベース 61.71 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 52.48 % / 補助 43.18 % / ベース 62.92 %</t>
+          <t xml:space="preserve">全社 52.29 % / 補助 42.97 % / ベース 62.77 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 47.15 % / 補助 36.82 % / ベース 60.03 %</t>
+          <t xml:space="preserve">全社 46.83 % / 補助 36.47 % / ベース 59.83 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.13 % / 補助 31.26 % / ベース 58.71 %</t>
+          <t xml:space="preserve">全社 41.76 % / 補助 30.89 % / ベース 58.47 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.51 % / 補助 26.74 % / ベース 57.46 %</t>
+          <t xml:space="preserve">全社 37.13 % / 補助 26.39 % / ベース 57.2 %</t>
         </is>
       </c>
     </row>
@@ -4697,32 +4697,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,023.91 千円/人 / 補助 7,291.79 千円/人 / ベース 3,260.01 千円/人</t>
+          <t xml:space="preserve">全社 4,960.43 千円/人 / 補助 7,204.34 千円/人 / ベース 3,215.16 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,959.95 千円/人 / 補助 7,228.1 千円/人 / ベース 3,174.39 千円/人</t>
+          <t xml:space="preserve">全社 4,834.87 千円/人 / 補助 7,057.47 千円/人 / ベース 3,085.16 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,940.51 千円/人 / 補助 7,241.67 千円/人 / ベース 3,112.19 千円/人</t>
+          <t xml:space="preserve">全社 4,754.36 千円/人 / 補助 6,988.99 千円/人 / ベース 2,978.9 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,646.07 千円/人 / 補助 10,250.55 千円/人 / ベース 3,795.47 千円/人</t>
+          <t xml:space="preserve">全社 6,336.32 千円/人 / 補助 9,778.34 千円/人 / ベース 3,614.2 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8,994.8 千円/人 / 補助 15,051.65 千円/人 / ベース 4,225.02 千円/人</t>
+          <t xml:space="preserve">全社 8,555.77 千円/人 / 補助 14,344.84 千円/人 / ベース 3,996.87 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11,867.57 千円/人 / 補助 21,129.98 千円/人 / ベース 4,645.09 千円/人</t>
+          <t xml:space="preserve">全社 11,294.38 千円/人 / 補助 20,171.33 千円/人 / ベース 4,372.47 千円/人</t>
         </is>
       </c>
     </row>
@@ -4759,32 +4759,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12,874.83 千円/人 / 補助 15,441.33 千円/人 / ベース 10,884.87 千円/人</t>
+          <t xml:space="preserve">全社 12,891.09 千円/人 / 補助 15,466.61 千円/人 / ベース 10,894.12 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12,854.77 千円/人 / 補助 15,388.42 千円/人 / ベース 10,866.55 千円/人</t>
+          <t xml:space="preserve">全社 12,886.54 千円/人 / 補助 15,437.59 千円/人 / ベース 10,884.67 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12,960.21 千円/人 / 補助 15,510.6 千円/人 / ベース 10,940.44 千円/人</t>
+          <t xml:space="preserve">全社 13,007.24 千円/人 / 補助 15,583.15 千円/人 / ベース 10,967.26 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14,724 千円/人 / 補助 18,534.04 千円/人 / ベース 11,719.93 千円/人</t>
+          <t xml:space="preserve">全社 14,824.92 千円/人 / 補助 18,713.16 千円/人 / ベース 11,759.19 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,355.83 千円/人 / 補助 23,828.16 千円/人 / ベース 12,273.27 千円/人</t>
+          <t xml:space="preserve">全社 17,509.69 千円/人 / 補助 24,114.65 千円/人 / ベース 12,322.98 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20,522.4 千円/人 / 補助 30,462.56 千円/人 / ベース 12,791.17 千円/人</t>
+          <t xml:space="preserve">全社 20,734.42 千円/人 / 補助 30,870.57 千円/人 / ベース 12,850.75 千円/人</t>
         </is>
       </c>
     </row>
@@ -5007,32 +5007,32 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.22 % / 補助 2.37 % / ベース 2.06 %</t>
+          <t xml:space="preserve">全社 2.35 % / 補助 2.51 % / ベース 2.16 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.12 % / 補助 2.25 % / ベース 1.97 %</t>
+          <t xml:space="preserve">全社 2.36 % / 補助 2.53 % / ベース 2.17 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.02 % / 補助 2.13 % / ベース 1.89 %</t>
+          <t xml:space="preserve">全社 2.38 % / 補助 2.54 % / ベース 2.19 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.75 % / 補助 1.75 % / ベース 1.76 %</t>
+          <t xml:space="preserve">全社 2.32 % / 補助 2.44 % / ベース 2.16 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.52 % / 補助 1.43 % / ベース 1.66 %</t>
+          <t xml:space="preserve">全社 2.26 % / 補助 2.33 % / ベース 2.15 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.31 % / 補助 1.17 % / ベース 1.56 %</t>
+          <t xml:space="preserve">全社 2.2 % / 補助 2.23 % / ベース 2.14 %</t>
         </is>
       </c>
     </row>
@@ -5193,32 +5193,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.44 倍 / 補助 4.83 倍 / ベース 3.93 倍</t>
+          <t xml:space="preserve">全社 4.22 倍 / 補助 4.57 倍 / ベース 3.76 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.57 倍 / 補助 5.01 倍 / ベース 3.98 倍</t>
+          <t xml:space="preserve">全社 4.13 倍 / 補助 4.49 倍 / ベース 3.63 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.7 倍 / 補助 5.2 倍 / ベース 4.03 倍</t>
+          <t xml:space="preserve">全社 4.03 倍 / 補助 4.41 倍 / ベース 3.51 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.2 倍 / 補助 7.2 倍 / ベース 4.87 倍</t>
+          <t xml:space="preserve">全社 4.75 倍 / 補助 5.24 倍 / ベース 4.01 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.35 倍 / 補助 10.48 倍 / ベース 5.51 倍</t>
+          <t xml:space="preserve">全社 5.7 倍 / 補助 6.55 倍 / ベース 4.29 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.14 倍 / 補助 14.84 倍 / ベース 6.2 倍</t>
+          <t xml:space="preserve">全社 6.76 倍 / 補助 7.96 倍 / ベース 4.57 倍</t>
         </is>
       </c>
     </row>
@@ -5565,32 +5565,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.05 pt</t>
+          <t xml:space="preserve">差 3.02 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.14 pt</t>
+          <t xml:space="preserve">差 3.1 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.24 pt</t>
+          <t xml:space="preserve">差 3.17 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.03 pt</t>
+          <t xml:space="preserve">差 3.85 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.12 pt</t>
+          <t xml:space="preserve">差 5.88 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 8.14 pt</t>
+          <t xml:space="preserve">差 7.88 pt</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 77.92 %</t>
+          <t xml:space="preserve">寄与率 86.73 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 83.05 %</t>
+          <t xml:space="preserve">寄与率 96.56 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 84.74 %</t>
+          <t xml:space="preserve">寄与率 100.32 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.01 %</t>
+          <t xml:space="preserve">寄与率 75.93 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 87.32 %</t>
+          <t xml:space="preserve">寄与率 87.83 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.3 %</t>
+          <t xml:space="preserve">寄与率 89.78 %</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">制度下限5.0%/年（基準年→事業化報告3年目）</t>
         </is>
       </c>
       <c r="D37" s="2">
@@ -11408,7 +11408,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODgyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5NjY1LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNDA1MzE5NjYwMzEwODQ3Nywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgyMTUwMTQ2OTU4NDE1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">ODgyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA5NjY1LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNDA1MzE5NjYwMzEwODQ3Nywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUxNDkxNDc4MzQ4NjkzMzUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgyMTUwMTQ2OTU4NDE1LCJpbnZlc3RtZW50IjoyMzAwMDAwLCJzdWJzaWR5Ijo3NjYwMDAsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_一部目標未達.xlsx
@@ -9,10 +9,11 @@
     <sheet name="貸借対照表等" sheetId="2" r:id="rId2"/>
     <sheet name="会社全体PL" sheetId="3" r:id="rId3"/>
     <sheet name="補助事業収支" sheetId="4" r:id="rId4"/>
-    <sheet name="妥当性診断" sheetId="5" r:id="rId5"/>
-    <sheet name="前提・目標" sheetId="6" r:id="rId6"/>
-    <sheet name="入力データ監査" sheetId="7" r:id="rId7"/>
-    <sheet name="モデルデータ" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="ベース事業PL" sheetId="5" r:id="rId5"/>
+    <sheet name="妥当性診断" sheetId="6" r:id="rId6"/>
+    <sheet name="前提・目標" sheetId="7" r:id="rId7"/>
+    <sheet name="入力データ監査" sheetId="8" r:id="rId8"/>
+    <sheet name="モデルデータ" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -94,11 +95,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -165,6 +166,18 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出力内容</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用単位／入力値／自動計算値／最適化結果／未入力／暫定値／診断チャート（HTML出力）／妥当性チェック</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -384,7 +397,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>25.592329405571277</v>
+        <v>25.50269177780311</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +427,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>2266973.9999999995</v>
+        <v>2259302.9999999995</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +547,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>295.94960835509136</v>
+        <v>294.94817232375976</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1376,22 @@
         <v>80000</v>
       </c>
       <c r="E6" s="2">
-        <v>83982</v>
+        <v>84438</v>
       </c>
       <c r="F6" s="2">
-        <v>88165</v>
+        <v>89162</v>
       </c>
       <c r="G6" s="2">
-        <v>92558</v>
+        <v>94159</v>
       </c>
       <c r="H6" s="2">
-        <v>107587</v>
+        <v>106565</v>
       </c>
       <c r="I6" s="2">
-        <v>123386</v>
+        <v>120353</v>
       </c>
       <c r="J6" s="2">
-        <v>141913</v>
+        <v>136160</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1478,22 @@
         <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>3843339</v>
+        <v>3842883</v>
       </c>
       <c r="F9" s="2">
-        <v>4060848</v>
+        <v>4059851</v>
       </c>
       <c r="G9" s="2">
-        <v>4291114</v>
+        <v>4289513</v>
       </c>
       <c r="H9" s="2">
-        <v>4704087</v>
+        <v>4705109</v>
       </c>
       <c r="I9" s="2">
-        <v>5227551.01</v>
+        <v>5230584.01</v>
       </c>
       <c r="J9" s="2">
-        <v>5818076.109999999</v>
+        <v>5823829.109999999</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1716,22 @@
         <v>270000</v>
       </c>
       <c r="E16" s="2">
-        <v>285236</v>
+        <v>284780</v>
       </c>
       <c r="F16" s="2">
-        <v>301522</v>
+        <v>300525</v>
       </c>
       <c r="G16" s="2">
-        <v>318771</v>
+        <v>317170</v>
       </c>
       <c r="H16" s="2">
-        <v>355441</v>
+        <v>356463</v>
       </c>
       <c r="I16" s="2">
-        <v>396949</v>
+        <v>399982</v>
       </c>
       <c r="J16" s="2">
-        <v>443924</v>
+        <v>449677</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1784,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1190503</v>
+        <v>1190959</v>
       </c>
       <c r="F18" s="4">
-        <v>1218386</v>
+        <v>1219383</v>
       </c>
       <c r="G18" s="4">
-        <v>1245643</v>
+        <v>1247244</v>
       </c>
       <c r="H18" s="4">
-        <v>1736152</v>
+        <v>1735130</v>
       </c>
       <c r="I18" s="4">
-        <v>2446949.959999999</v>
+        <v>2443916.959999999</v>
       </c>
       <c r="J18" s="4">
-        <v>3377018.759999998</v>
+        <v>3371265.759999998</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1818,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.567996096309675</v>
+        <v>7.570894876253881</v>
       </c>
       <c r="F19" s="2">
-        <v>7.385228657707751</v>
+        <v>7.391271958411908</v>
       </c>
       <c r="G19" s="2">
-        <v>7.1992656262769215</v>
+        <v>7.208518698198546</v>
       </c>
       <c r="H19" s="2">
-        <v>8.703781502072982</v>
+        <v>8.698657950278486</v>
       </c>
       <c r="I19" s="2">
-        <v>10.63939119346416</v>
+        <v>10.626203644058869</v>
       </c>
       <c r="J19" s="2">
-        <v>12.676880450962377</v>
+        <v>12.65528445211919</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1852,22 @@
         <v>1130000</v>
       </c>
       <c r="E20" s="4">
-        <v>1154013</v>
+        <v>1154469</v>
       </c>
       <c r="F20" s="4">
-        <v>1180342</v>
+        <v>1181339</v>
       </c>
       <c r="G20" s="4">
-        <v>1205980</v>
+        <v>1207581</v>
       </c>
       <c r="H20" s="4">
-        <v>1551736</v>
+        <v>1550714</v>
       </c>
       <c r="I20" s="4">
-        <v>2246420</v>
+        <v>2243387</v>
       </c>
       <c r="J20" s="4">
-        <v>3158721</v>
+        <v>3152968</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1886,22 @@
         <v>1130000</v>
       </c>
       <c r="E21" s="2">
-        <v>1154013</v>
+        <v>1154469</v>
       </c>
       <c r="F21" s="2">
-        <v>1180342</v>
+        <v>1181339</v>
       </c>
       <c r="G21" s="2">
-        <v>1205980</v>
+        <v>1207581</v>
       </c>
       <c r="H21" s="2">
-        <v>1551736</v>
+        <v>1550714</v>
       </c>
       <c r="I21" s="2">
-        <v>2246420</v>
+        <v>2243387</v>
       </c>
       <c r="J21" s="2">
-        <v>3158721</v>
+        <v>3152968</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1920,22 @@
         <v>791000</v>
       </c>
       <c r="E22" s="2">
-        <v>807809</v>
+        <v>808128</v>
       </c>
       <c r="F22" s="2">
-        <v>826239</v>
+        <v>826937</v>
       </c>
       <c r="G22" s="2">
-        <v>844186</v>
+        <v>845307</v>
       </c>
       <c r="H22" s="2">
-        <v>1086215</v>
+        <v>1085499</v>
       </c>
       <c r="I22" s="2">
-        <v>1572494</v>
+        <v>1570371</v>
       </c>
       <c r="J22" s="2">
-        <v>2211105</v>
+        <v>2207078</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2056,22 @@
         <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>3158316</v>
+        <v>3158772</v>
       </c>
       <c r="F26" s="4">
-        <v>3311840</v>
+        <v>3312837</v>
       </c>
       <c r="G26" s="4">
-        <v>3472934</v>
+        <v>3474535</v>
       </c>
       <c r="H26" s="4">
-        <v>4136152</v>
+        <v>4135130</v>
       </c>
       <c r="I26" s="4">
-        <v>5095319.969999999</v>
+        <v>5092286.969999999</v>
       </c>
       <c r="J26" s="4">
-        <v>6303263.869999997</v>
+        <v>6297510.869999997</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2092,22 @@
         <v>4.735724973033162</v>
       </c>
       <c r="E27" s="2">
-        <v>4.9274418604651204</v>
+        <v>4.942591362126247</v>
       </c>
       <c r="F27" s="2">
-        <v>4.8609448832859</v>
+        <v>4.877370066595499</v>
       </c>
       <c r="G27" s="2">
-        <v>4.8641842601091945</v>
+        <v>4.880952488758128</v>
       </c>
       <c r="H27" s="2">
-        <v>19.096763716212294</v>
+        <v>19.012472172535322</v>
       </c>
       <c r="I27" s="2">
-        <v>23.189862703304875</v>
+        <v>23.146962006031213</v>
       </c>
       <c r="J27" s="2">
-        <v>23.706929243150142</v>
+        <v>23.667635133296482</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2126,22 @@
         <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.07733131198526</v>
+        <v>20.080230091929465</v>
       </c>
       <c r="F28" s="2">
-        <v>20.074669011087487</v>
+        <v>20.080712311791643</v>
       </c>
       <c r="G28" s="2">
-        <v>20.07202253657622</v>
+        <v>20.081275608497844</v>
       </c>
       <c r="H28" s="2">
-        <v>20.735605677015705</v>
+        <v>20.73048212522121</v>
       </c>
       <c r="I28" s="2">
-        <v>22.154561107861838</v>
+        <v>22.141373558456547</v>
       </c>
       <c r="J28" s="2">
-        <v>23.66161641662319</v>
+        <v>23.64002041778</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2368,22 @@
         <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>12891.085714285715</v>
+        <v>12892.94693877551</v>
       </c>
       <c r="F35" s="2">
-        <v>12886.536964980545</v>
+        <v>12890.41634241245</v>
       </c>
       <c r="G35" s="2">
-        <v>13007.243445692884</v>
+        <v>13013.239700374532</v>
       </c>
       <c r="H35" s="2">
-        <v>14824.917562724015</v>
+        <v>14821.254480286738</v>
       </c>
       <c r="I35" s="2">
-        <v>17509.6906185567</v>
+        <v>17499.267938144327</v>
       </c>
       <c r="J35" s="2">
-        <v>20734.42062499999</v>
+        <v>20715.49628289473</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2402,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1559721</v>
+        <v>1560177</v>
       </c>
       <c r="F36" s="4">
-        <v>1608073</v>
+        <v>1609070</v>
       </c>
       <c r="G36" s="4">
-        <v>1656972</v>
+        <v>1658573</v>
       </c>
       <c r="H36" s="4">
-        <v>2199180</v>
+        <v>2198158</v>
       </c>
       <c r="I36" s="4">
-        <v>2967284.959999999</v>
+        <v>2964251.959999999</v>
       </c>
       <c r="J36" s="4">
-        <v>3962855.759999998</v>
+        <v>3957102.759999998</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2436,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>9.915105160870844</v>
+        <v>9.918003940815051</v>
       </c>
       <c r="F37" s="2">
-        <v>9.747310625110659</v>
+        <v>9.753353925814817</v>
       </c>
       <c r="G37" s="2">
-        <v>9.576565326745563</v>
+        <v>9.585818398667188</v>
       </c>
       <c r="H37" s="2">
-        <v>11.025061287104391</v>
+        <v>11.019937735309894</v>
       </c>
       <c r="I37" s="2">
-        <v>12.901818994256283</v>
+        <v>12.888631444850992</v>
       </c>
       <c r="J37" s="2">
-        <v>14.876034835509074</v>
+        <v>14.854438836665887</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2472,22 @@
         <v>3.0486007228415657</v>
       </c>
       <c r="E38" s="2">
-        <v>3.2927814569536418</v>
+        <v>3.322980132450337</v>
       </c>
       <c r="F38" s="2">
-        <v>3.100041610005899</v>
+        <v>3.133811099638062</v>
       </c>
       <c r="G38" s="2">
-        <v>3.0408445387740457</v>
+        <v>3.076497604206163</v>
       </c>
       <c r="H38" s="2">
-        <v>32.72282211165909</v>
+        <v>32.533087177953576</v>
       </c>
       <c r="I38" s="2">
-        <v>34.92688001891611</v>
+        <v>34.85163304912564</v>
       </c>
       <c r="J38" s="2">
-        <v>33.55157369179666</v>
+        <v>33.49414332511731</v>
       </c>
     </row>
   </sheetData>
@@ -2799,22 +2812,22 @@
         <v>730000</v>
       </c>
       <c r="E8" s="4">
-        <v>756456</v>
+        <v>756723</v>
       </c>
       <c r="F8" s="4">
-        <v>783379</v>
+        <v>783947</v>
       </c>
       <c r="G8" s="4">
-        <v>810723</v>
+        <v>811630</v>
       </c>
       <c r="H8" s="4">
-        <v>1183179</v>
+        <v>1181509</v>
       </c>
       <c r="I8" s="4">
-        <v>1807449.9900000002</v>
+        <v>1803597.9900000002</v>
       </c>
       <c r="J8" s="4">
-        <v>2642443.8899999997</v>
+        <v>2635679.8899999997</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2846,22 @@
         <v>9.125</v>
       </c>
       <c r="E9" s="2">
-        <v>8.970455541840508</v>
+        <v>8.973621769128904</v>
       </c>
       <c r="F9" s="2">
-        <v>8.81299678498119</v>
+        <v>8.819386772680463</v>
       </c>
       <c r="G9" s="2">
-        <v>8.652567590196481</v>
+        <v>8.662247689076505</v>
       </c>
       <c r="H9" s="2">
-        <v>10.347810496672235</v>
+        <v>10.333205062051233</v>
       </c>
       <c r="I9" s="2">
-        <v>12.953579465080844</v>
+        <v>12.925973064696016</v>
       </c>
       <c r="J9" s="2">
-        <v>15.518680189415898</v>
+        <v>15.478956222826316</v>
       </c>
     </row>
     <row r="10">
@@ -2935,22 +2948,22 @@
         <v>50000</v>
       </c>
       <c r="E12" s="2">
-        <v>52705</v>
+        <v>52972</v>
       </c>
       <c r="F12" s="2">
-        <v>55556</v>
+        <v>56124</v>
       </c>
       <c r="G12" s="2">
-        <v>58561</v>
+        <v>59468</v>
       </c>
       <c r="H12" s="2">
-        <v>71463</v>
+        <v>69793</v>
       </c>
       <c r="I12" s="2">
-        <v>85284</v>
+        <v>81432</v>
       </c>
       <c r="J12" s="2">
-        <v>101726</v>
+        <v>94962</v>
       </c>
     </row>
     <row r="13">
@@ -2969,22 +2982,22 @@
         <v>150000</v>
       </c>
       <c r="E13" s="2">
-        <v>159182</v>
+        <v>158915</v>
       </c>
       <c r="F13" s="2">
-        <v>168940</v>
+        <v>168372</v>
       </c>
       <c r="G13" s="2">
-        <v>179311</v>
+        <v>178404</v>
       </c>
       <c r="H13" s="2">
-        <v>207707</v>
+        <v>209377</v>
       </c>
       <c r="I13" s="2">
-        <v>240445</v>
+        <v>244297</v>
       </c>
       <c r="J13" s="2">
-        <v>278123</v>
+        <v>284887</v>
       </c>
     </row>
     <row r="14">
@@ -3037,22 +3050,22 @@
         <v>1570000</v>
       </c>
       <c r="E15" s="4">
-        <v>1654927</v>
+        <v>1655194</v>
       </c>
       <c r="F15" s="4">
-        <v>1744448</v>
+        <v>1745016</v>
       </c>
       <c r="G15" s="4">
-        <v>1838812</v>
+        <v>1839719</v>
       </c>
       <c r="H15" s="4">
-        <v>2301719</v>
+        <v>2300049</v>
       </c>
       <c r="I15" s="4">
-        <v>3086675</v>
+        <v>3082823</v>
       </c>
       <c r="J15" s="4">
-        <v>4105785.9999999995</v>
+        <v>4099021.9999999995</v>
       </c>
     </row>
     <row r="16">
@@ -3073,22 +3086,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E16" s="2">
-        <v>5.409363057324845</v>
+        <v>5.426369426751587</v>
       </c>
       <c r="F16" s="2">
-        <v>5.409362467347512</v>
+        <v>5.426675060446096</v>
       </c>
       <c r="G16" s="2">
-        <v>5.409390248376567</v>
+        <v>5.4270562562177105</v>
       </c>
       <c r="H16" s="2">
-        <v>25.174242935112456</v>
+        <v>25.021756039916966</v>
       </c>
       <c r="I16" s="2">
-        <v>34.1030334284941</v>
+        <v>34.03292712459604</v>
       </c>
       <c r="J16" s="2">
-        <v>33.01646593826688</v>
+        <v>32.96326127059515</v>
       </c>
     </row>
     <row r="17">
@@ -3315,22 +3328,22 @@
         <v>15392.156862745098</v>
       </c>
       <c r="E23" s="2">
-        <v>15466.607476635514</v>
+        <v>15469.102803738318</v>
       </c>
       <c r="F23" s="2">
-        <v>15437.592920353982</v>
+        <v>15442.61946902655</v>
       </c>
       <c r="G23" s="2">
-        <v>15583.152542372882</v>
+        <v>15590.838983050848</v>
       </c>
       <c r="H23" s="2">
-        <v>18713.162601626016</v>
+        <v>18699.585365853658</v>
       </c>
       <c r="I23" s="2">
-        <v>24114.6484375</v>
+        <v>24084.5546875</v>
       </c>
       <c r="J23" s="2">
-        <v>30870.571428571424</v>
+        <v>30819.714285714283</v>
       </c>
     </row>
     <row r="24">
@@ -3388,6 +3401,1374 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="58" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業にかかる損益計算書（P/L）</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第6次様式項目</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023
+前々期決算期</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024
+前期決算期</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025
+最新決算期</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026
+補助事業期間</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027
+基準年前年／補助事業期間</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028
+基準年（完了年度）</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2029
+事業化報告1年目</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2030
+事業化報告2年目</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2031
+事業化報告3年目</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-1 売上高（千円）</t>
+        </is>
+      </c>
+      <c r="B3" s="4">
+        <v>6440000</v>
+      </c>
+      <c r="C3" s="4">
+        <v>6720000</v>
+      </c>
+      <c r="D3" s="4">
+        <v>7000000</v>
+      </c>
+      <c r="E3" s="4">
+        <v>7298007</v>
+      </c>
+      <c r="F3" s="4">
+        <v>7608701</v>
+      </c>
+      <c r="G3" s="4">
+        <v>7932623</v>
+      </c>
+      <c r="H3" s="4">
+        <v>8513000</v>
+      </c>
+      <c r="I3" s="4">
+        <v>9045679.97</v>
+      </c>
+      <c r="J3" s="4">
+        <v>9611689.87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-2 売上高成長率（%）</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C4" s="2">
+        <v>4.347826086956519</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4.166666666666674</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4.257242857142862</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4.257244477841682</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4.25725757918467</v>
+      </c>
+      <c r="H4" s="2">
+        <v>7.3163315589307665</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.257253259720441</v>
+      </c>
+      <c r="J4" s="2">
+        <v>6.257239940802362</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-3 売上原価（千円）</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>4379200</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4569600</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4760000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4962645</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5173917</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5394183</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5731711</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6045576</v>
+      </c>
+      <c r="J5" s="2">
+        <v>6376278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-4 うち減価償却費（千円）</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>27600</v>
+      </c>
+      <c r="C6" s="2">
+        <v>28800</v>
+      </c>
+      <c r="D6" s="2">
+        <v>30000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>31466</v>
+      </c>
+      <c r="F6" s="2">
+        <v>33038</v>
+      </c>
+      <c r="G6" s="2">
+        <v>34691</v>
+      </c>
+      <c r="H6" s="2">
+        <v>36772</v>
+      </c>
+      <c r="I6" s="2">
+        <v>38921</v>
+      </c>
+      <c r="J6" s="2">
+        <v>41198</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-5 売上総利益（千円）</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <v>2060800</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2150400</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2240000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2335362</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2434784</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2538440</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2781289</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3000103.9700000007</v>
+      </c>
+      <c r="J7" s="4">
+        <v>3235411.869999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-6 売上総利益率（%）</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2">
+        <v>31.999996711430946</v>
+      </c>
+      <c r="F8" s="2">
+        <v>31.999995794288672</v>
+      </c>
+      <c r="G8" s="2">
+        <v>32.000008067949274</v>
+      </c>
+      <c r="H8" s="2">
+        <v>32.67107952543169</v>
+      </c>
+      <c r="I8" s="2">
+        <v>33.1661520189731</v>
+      </c>
+      <c r="J8" s="2">
+        <v>33.66121788946151</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-7 販売費及び一般管理費（千円）</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>1638986</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1723748</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1810000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1901126</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1999348</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2102826</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2227668</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2359785</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2499826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-8 うち役員の人件費（自動計算）（千円）</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>55200</v>
+      </c>
+      <c r="C10" s="2">
+        <v>57600</v>
+      </c>
+      <c r="D10" s="2">
+        <v>60000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>62400</v>
+      </c>
+      <c r="F10" s="2">
+        <v>64896</v>
+      </c>
+      <c r="G10" s="2">
+        <v>67492</v>
+      </c>
+      <c r="H10" s="2">
+        <v>70529</v>
+      </c>
+      <c r="I10" s="2">
+        <v>73703</v>
+      </c>
+      <c r="J10" s="2">
+        <v>77019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-9 うち役員報酬（千円）</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>49680</v>
+      </c>
+      <c r="C11" s="2">
+        <v>51840</v>
+      </c>
+      <c r="D11" s="2">
+        <v>54000</v>
+      </c>
+      <c r="E11" s="2">
+        <v>56160</v>
+      </c>
+      <c r="F11" s="2">
+        <v>58406</v>
+      </c>
+      <c r="G11" s="2">
+        <v>60743</v>
+      </c>
+      <c r="H11" s="2">
+        <v>63476</v>
+      </c>
+      <c r="I11" s="2">
+        <v>66333</v>
+      </c>
+      <c r="J11" s="2">
+        <v>69317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-10 うち役員賞与（千円）</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>5520</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5760</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6240</v>
+      </c>
+      <c r="F12" s="2">
+        <v>6490</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6749</v>
+      </c>
+      <c r="H12" s="2">
+        <v>7053</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7370</v>
+      </c>
+      <c r="J12" s="2">
+        <v>7702</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-11 うち従業員の人件費（自動計算）（千円）</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>709786</v>
+      </c>
+      <c r="C13" s="2">
+        <v>754148</v>
+      </c>
+      <c r="D13" s="2">
+        <v>800000</v>
+      </c>
+      <c r="E13" s="2">
+        <v>849611</v>
+      </c>
+      <c r="F13" s="2">
+        <v>902298</v>
+      </c>
+      <c r="G13" s="2">
+        <v>958253</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1027073</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1100836</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1179896</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-12 うち従業員の給与（千円）</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>674297</v>
+      </c>
+      <c r="C14" s="2">
+        <v>716441</v>
+      </c>
+      <c r="D14" s="2">
+        <v>760000</v>
+      </c>
+      <c r="E14" s="2">
+        <v>807130</v>
+      </c>
+      <c r="F14" s="2">
+        <v>857183</v>
+      </c>
+      <c r="G14" s="2">
+        <v>910340</v>
+      </c>
+      <c r="H14" s="2">
+        <v>975719</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1045794</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1120901</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-13 うち従業員の賞与（千円）</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>35489</v>
+      </c>
+      <c r="C15" s="2">
+        <v>37707</v>
+      </c>
+      <c r="D15" s="2">
+        <v>40000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>42481</v>
+      </c>
+      <c r="F15" s="2">
+        <v>45115</v>
+      </c>
+      <c r="G15" s="2">
+        <v>47913</v>
+      </c>
+      <c r="H15" s="2">
+        <v>51354</v>
+      </c>
+      <c r="I15" s="2">
+        <v>55042</v>
+      </c>
+      <c r="J15" s="2">
+        <v>58995</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-14 うち減価償却費（千円）</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>110400</v>
+      </c>
+      <c r="C16" s="2">
+        <v>115200</v>
+      </c>
+      <c r="D16" s="2">
+        <v>120000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>125865</v>
+      </c>
+      <c r="F16" s="2">
+        <v>132153</v>
+      </c>
+      <c r="G16" s="2">
+        <v>138766</v>
+      </c>
+      <c r="H16" s="2">
+        <v>147086</v>
+      </c>
+      <c r="I16" s="2">
+        <v>155685</v>
+      </c>
+      <c r="J16" s="2">
+        <v>164790</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-15 うち研究開発費（千円）</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>27600</v>
+      </c>
+      <c r="C17" s="2">
+        <v>28800</v>
+      </c>
+      <c r="D17" s="2">
+        <v>30000</v>
+      </c>
+      <c r="E17" s="2">
+        <v>29192</v>
+      </c>
+      <c r="F17" s="2">
+        <v>30435</v>
+      </c>
+      <c r="G17" s="2">
+        <v>31730</v>
+      </c>
+      <c r="H17" s="2">
+        <v>33716</v>
+      </c>
+      <c r="I17" s="2">
+        <v>35826</v>
+      </c>
+      <c r="J17" s="2">
+        <v>38067</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-16 営業利益（千円）</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <v>421814</v>
+      </c>
+      <c r="C18" s="4">
+        <v>426652</v>
+      </c>
+      <c r="D18" s="4">
+        <v>430000</v>
+      </c>
+      <c r="E18" s="4">
+        <v>434236</v>
+      </c>
+      <c r="F18" s="4">
+        <v>435436</v>
+      </c>
+      <c r="G18" s="4">
+        <v>435614</v>
+      </c>
+      <c r="H18" s="4">
+        <v>553621</v>
+      </c>
+      <c r="I18" s="4">
+        <v>640318.9700000007</v>
+      </c>
+      <c r="J18" s="4">
+        <v>735585.8699999992</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-17 営業利益率（%）</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>6.549906832298137</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6.348988095238095</v>
+      </c>
+      <c r="D19" s="2">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5.950062804817809</v>
+      </c>
+      <c r="F19" s="2">
+        <v>5.7228691204977045</v>
+      </c>
+      <c r="G19" s="2">
+        <v>5.491424463257614</v>
+      </c>
+      <c r="H19" s="2">
+        <v>6.503242100317162</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.078726774809839</v>
+      </c>
+      <c r="J19" s="2">
+        <v>7.653033753158322</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-18 経常利益（千円）</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <v>394534</v>
+      </c>
+      <c r="C20" s="4">
+        <v>398012</v>
+      </c>
+      <c r="D20" s="4">
+        <v>400000</v>
+      </c>
+      <c r="E20" s="4">
+        <v>397746</v>
+      </c>
+      <c r="F20" s="4">
+        <v>397392</v>
+      </c>
+      <c r="G20" s="4">
+        <v>395951</v>
+      </c>
+      <c r="H20" s="4">
+        <v>427462</v>
+      </c>
+      <c r="I20" s="4">
+        <v>506266</v>
+      </c>
+      <c r="J20" s="4">
+        <v>593145</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-19 税引前当期純利益（千円）</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>394534</v>
+      </c>
+      <c r="C21" s="2">
+        <v>398012</v>
+      </c>
+      <c r="D21" s="2">
+        <v>400000</v>
+      </c>
+      <c r="E21" s="2">
+        <v>397746</v>
+      </c>
+      <c r="F21" s="2">
+        <v>397392</v>
+      </c>
+      <c r="G21" s="2">
+        <v>395951</v>
+      </c>
+      <c r="H21" s="2">
+        <v>427462</v>
+      </c>
+      <c r="I21" s="2">
+        <v>506266</v>
+      </c>
+      <c r="J21" s="2">
+        <v>593145</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-20 当期純利益（千円）</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>750752.1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>771881.6</v>
+      </c>
+      <c r="D22" s="2">
+        <v>791000</v>
+      </c>
+      <c r="E22" s="2">
+        <v>278422</v>
+      </c>
+      <c r="F22" s="2">
+        <v>278174</v>
+      </c>
+      <c r="G22" s="2">
+        <v>277166</v>
+      </c>
+      <c r="H22" s="2">
+        <v>299223</v>
+      </c>
+      <c r="I22" s="2">
+        <v>354386</v>
+      </c>
+      <c r="J22" s="2">
+        <v>415202</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-21 給与支給総額（常時使用する従業員）（千円）</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>709786</v>
+      </c>
+      <c r="C23" s="2">
+        <v>754148</v>
+      </c>
+      <c r="D23" s="2">
+        <v>800000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>849611</v>
+      </c>
+      <c r="F23" s="2">
+        <v>902298</v>
+      </c>
+      <c r="G23" s="2">
+        <v>958253</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1027073</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1100836</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1179896</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-22 給与支給総額（役員）（千円）</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>55200</v>
+      </c>
+      <c r="C24" s="2">
+        <v>57600</v>
+      </c>
+      <c r="D24" s="2">
+        <v>60000</v>
+      </c>
+      <c r="E24" s="2">
+        <v>62400</v>
+      </c>
+      <c r="F24" s="2">
+        <v>64896</v>
+      </c>
+      <c r="G24" s="2">
+        <v>67492</v>
+      </c>
+      <c r="H24" s="2">
+        <v>70529</v>
+      </c>
+      <c r="I24" s="2">
+        <v>73703</v>
+      </c>
+      <c r="J24" s="2">
+        <v>77019</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-23 減価償却費（合計）（千円）</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>138000</v>
+      </c>
+      <c r="C25" s="2">
+        <v>144000</v>
+      </c>
+      <c r="D25" s="2">
+        <v>150000</v>
+      </c>
+      <c r="E25" s="2">
+        <v>157331</v>
+      </c>
+      <c r="F25" s="2">
+        <v>165191</v>
+      </c>
+      <c r="G25" s="2">
+        <v>173457</v>
+      </c>
+      <c r="H25" s="2">
+        <v>183858</v>
+      </c>
+      <c r="I25" s="2">
+        <v>194606</v>
+      </c>
+      <c r="J25" s="2">
+        <v>205988</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-24 付加価値額（千円）</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <v>1324800</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1382400</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1440000</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1503578</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1567821</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1634816</v>
+      </c>
+      <c r="H26" s="4">
+        <v>1835081</v>
+      </c>
+      <c r="I26" s="4">
+        <v>2009463.9700000007</v>
+      </c>
+      <c r="J26" s="4">
+        <v>2198488.869999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-25 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C27" s="2">
+        <v>4.347826086956519</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4.166666666666674</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4.415138888888892</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4.272674912774721</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4.273128118579872</v>
+      </c>
+      <c r="H27" s="2">
+        <v>12.250002446758534</v>
+      </c>
+      <c r="I27" s="2">
+        <v>9.502739661083126</v>
+      </c>
+      <c r="J27" s="2">
+        <v>9.406732482991398</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-26 売上高付加価値率（%）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>20.57142857142857</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20.57142857142857</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20.57142857142857</v>
+      </c>
+      <c r="E28" s="2">
+        <v>20.602583691684593</v>
+      </c>
+      <c r="F28" s="2">
+        <v>20.60563294575513</v>
+      </c>
+      <c r="G28" s="2">
+        <v>20.608769633953358</v>
+      </c>
+      <c r="H28" s="2">
+        <v>21.556219898978032</v>
+      </c>
+      <c r="I28" s="2">
+        <v>22.214625950336387</v>
+      </c>
+      <c r="J28" s="2">
+        <v>22.8730733069314</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-27 常時使用する従業員数（就業時間換算）（人）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>120</v>
+      </c>
+      <c r="C29" s="2">
+        <v>125</v>
+      </c>
+      <c r="D29" s="2">
+        <v>130</v>
+      </c>
+      <c r="E29" s="2">
+        <v>135</v>
+      </c>
+      <c r="F29" s="2">
+        <v>141</v>
+      </c>
+      <c r="G29" s="2">
+        <v>146</v>
+      </c>
+      <c r="H29" s="2">
+        <v>153</v>
+      </c>
+      <c r="I29" s="2">
+        <v>160</v>
+      </c>
+      <c r="J29" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-28 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3</v>
+      </c>
+      <c r="J30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-29 従業員1人当たり給与支給総額（千円/人）</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>5914.883333333333</v>
+      </c>
+      <c r="C31" s="2">
+        <v>6033.184</v>
+      </c>
+      <c r="D31" s="2">
+        <v>6153.846153846154</v>
+      </c>
+      <c r="E31" s="2">
+        <v>6293.414814814815</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6399.276595744681</v>
+      </c>
+      <c r="G31" s="2">
+        <v>6563.376712328767</v>
+      </c>
+      <c r="H31" s="2">
+        <v>6712.895424836602</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6880.225</v>
+      </c>
+      <c r="J31" s="2">
+        <v>7023.190476190476</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-30 従業員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C32" s="2">
+        <v>2.0000507195126582</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1.9999747040062799</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2.267990740740733</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1.682103977647631</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2.5643541754892585</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2.2780760431894143</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2.4926587496701735</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2.077918617348651</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-31 役員1人当たり給与支給総額（千円/人）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>18400</v>
+      </c>
+      <c r="C33" s="2">
+        <v>19200</v>
+      </c>
+      <c r="D33" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E33" s="2">
+        <v>20800</v>
+      </c>
+      <c r="F33" s="2">
+        <v>21632</v>
+      </c>
+      <c r="G33" s="2">
+        <v>22497.333333333332</v>
+      </c>
+      <c r="H33" s="2">
+        <v>23509.666666666668</v>
+      </c>
+      <c r="I33" s="2">
+        <v>24567.666666666668</v>
+      </c>
+      <c r="J33" s="2">
+        <v>25673</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-32 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>4.347826086956519</v>
+      </c>
+      <c r="D34" s="2">
+        <v>4.166666666666674</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="F34" s="2">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4.000246548323472</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4.499792568008076</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4.500276482014498</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4.499138433985039</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-33 労働生産性（千円/人）</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>10770.731707317073</v>
+      </c>
+      <c r="C35" s="2">
+        <v>10800</v>
+      </c>
+      <c r="D35" s="2">
+        <v>10827.067669172933</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10895.492753623188</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10887.645833333334</v>
+      </c>
+      <c r="G35" s="2">
+        <v>10971.919463087248</v>
+      </c>
+      <c r="H35" s="2">
+        <v>11763.339743589744</v>
+      </c>
+      <c r="I35" s="2">
+        <v>12327.999815950925</v>
+      </c>
+      <c r="J35" s="2">
+        <v>12856.660058479527</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-34 EBITDA（千円）</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <v>559814</v>
+      </c>
+      <c r="C36" s="4">
+        <v>570652</v>
+      </c>
+      <c r="D36" s="4">
+        <v>580000</v>
+      </c>
+      <c r="E36" s="4">
+        <v>591567</v>
+      </c>
+      <c r="F36" s="4">
+        <v>600627</v>
+      </c>
+      <c r="G36" s="4">
+        <v>609071</v>
+      </c>
+      <c r="H36" s="4">
+        <v>737479</v>
+      </c>
+      <c r="I36" s="4">
+        <v>834924.9700000007</v>
+      </c>
+      <c r="J36" s="4">
+        <v>941573.8699999992</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-35 EBITDAマージン（%）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>8.692763975155279</v>
+      </c>
+      <c r="C37" s="2">
+        <v>8.49184523809524</v>
+      </c>
+      <c r="D37" s="2">
+        <v>8.285714285714285</v>
+      </c>
+      <c r="E37" s="2">
+        <v>8.105870547945488</v>
+      </c>
+      <c r="F37" s="2">
+        <v>7.893949308824199</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7.678053022310527</v>
+      </c>
+      <c r="H37" s="2">
+        <v>8.662974274638788</v>
+      </c>
+      <c r="I37" s="2">
+        <v>9.230096275448938</v>
+      </c>
+      <c r="J37" s="2">
+        <v>9.796132446374898</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2-36 EBITDA増加率（%）</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C38" s="2">
+        <v>1.936000171485519</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1.6381262135241714</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1.9943103448275767</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1.5315255921983573</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1.4058642052388493</v>
+      </c>
+      <c r="H38" s="2">
+        <v>21.082599565567882</v>
+      </c>
+      <c r="I38" s="2">
+        <v>13.213389127012531</v>
+      </c>
+      <c r="J38" s="2">
+        <v>12.773471129986502</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -3834,27 +5215,27 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.61 % / 補助 23.19 % / ベース 26.28 %</t>
+          <t xml:space="preserve">全社 24.61 % / 補助 23.18 % / ベース 26.28 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.8 % / 補助 23.35 % / ベース 26.52 %</t>
+          <t xml:space="preserve">全社 24.79 % / 補助 23.34 % / ベース 26.51 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.58 % / 補助 21.65 % / ベース 26.18 %</t>
+          <t xml:space="preserve">全社 23.59 % / 補助 21.67 % / ベース 26.17 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.73 % / 補助 20.55 % / ベース 26.1 %</t>
+          <t xml:space="preserve">全社 22.74 % / 補助 20.57 % / ベース 26.09 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.84 % / 補助 19.48 % / ベース 26.02 %</t>
+          <t xml:space="preserve">全社 21.86 % / 補助 19.52 % / ベース 26.01 %</t>
         </is>
       </c>
     </row>
@@ -3896,27 +5277,27 @@
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.39 % / 補助 8.81 % / ベース 5.72 %</t>
+          <t xml:space="preserve">全社 7.39 % / 補助 8.82 % / ベース 5.72 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.2 % / 補助 8.65 % / ベース 5.48 %</t>
+          <t xml:space="preserve">全社 7.21 % / 補助 8.66 % / ベース 5.49 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.7 % / 補助 10.35 % / ベース 6.5 %</t>
+          <t xml:space="preserve">全社 8.7 % / 補助 10.33 % / ベース 6.5 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.64 % / 補助 12.95 % / ベース 7.07 %</t>
+          <t xml:space="preserve">全社 10.63 % / 補助 12.93 % / ベース 7.08 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.68 % / 補助 15.52 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 12.66 % / 補助 15.48 % / ベース 7.65 %</t>
         </is>
       </c>
     </row>
@@ -3953,7 +5334,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.92 % / 補助 11.48 % / ベース 8.1 %</t>
+          <t xml:space="preserve">全社 9.92 % / 補助 11.49 % / ベース 8.11 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -3963,22 +5344,22 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.58 % / 補助 11.19 % / ベース 7.67 %</t>
+          <t xml:space="preserve">全社 9.59 % / 補助 11.2 % / ベース 7.68 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.03 % / 補助 12.79 % / ベース 8.66 %</t>
+          <t xml:space="preserve">全社 11.02 % / 補助 12.77 % / ベース 8.66 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.9 % / 補助 15.29 % / ベース 9.22 %</t>
+          <t xml:space="preserve">全社 12.89 % / 補助 15.26 % / ベース 9.23 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.88 % / 補助 17.75 % / ベース 9.79 %</t>
+          <t xml:space="preserve">全社 14.85 % / 補助 17.71 % / ベース 9.8 %</t>
         </is>
       </c>
     </row>
@@ -4511,32 +5892,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.62 % / 補助 41.49 % / ベース 60.66 %</t>
+          <t xml:space="preserve">全社 50.61 % / 補助 41.48 % / ベース 60.66 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.44 % / 補助 42.22 % / ベース 61.71 %</t>
+          <t xml:space="preserve">全社 51.43 % / 補助 42.21 % / ベース 61.69 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 52.29 % / 補助 42.97 % / ベース 62.77 %</t>
+          <t xml:space="preserve">全社 52.26 % / 補助 42.95 % / ベース 62.74 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 46.83 % / 補助 36.47 % / ベース 59.83 %</t>
+          <t xml:space="preserve">全社 46.84 % / 補助 36.49 % / ベース 59.81 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.76 % / 補助 30.89 % / ベース 58.47 %</t>
+          <t xml:space="preserve">全社 41.79 % / 補助 30.93 % / ベース 58.45 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.13 % / 補助 26.39 % / ベース 57.2 %</t>
+          <t xml:space="preserve">全社 37.16 % / 補助 26.43 % / ベース 57.17 %</t>
         </is>
       </c>
     </row>
@@ -4697,32 +6078,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,960.43 千円/人 / 補助 7,204.34 千円/人 / ベース 3,215.16 千円/人</t>
+          <t xml:space="preserve">全社 4,962.33 千円/人 / 補助 7,206.89 千円/人 / ベース 3,216.56 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,834.87 千円/人 / 補助 7,057.47 千円/人 / ベース 3,085.16 千円/人</t>
+          <t xml:space="preserve">全社 4,838.82 千円/人 / 補助 7,062.59 千円/人 / ベース 3,088.2 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4,754.36 千円/人 / 補助 6,988.99 千円/人 / ベース 2,978.9 千円/人</t>
+          <t xml:space="preserve">全社 4,760.47 千円/人 / 補助 6,996.81 千円/人 / ベース 2,983.66 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6,336.32 千円/人 / 補助 9,778.34 千円/人 / ベース 3,614.2 千円/人</t>
+          <t xml:space="preserve">全社 6,332.59 千円/人 / 補助 9,764.54 千円/人 / ベース 3,618.44 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8,555.77 千円/人 / 補助 14,344.84 千円/人 / ベース 3,996.87 千円/人</t>
+          <t xml:space="preserve">全社 8,545.16 千円/人 / 補助 14,314.27 千円/人 / ベース 4,001.99 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11,294.38 千円/人 / 補助 20,171.33 千円/人 / ベース 4,372.47 千円/人</t>
+          <t xml:space="preserve">全社 11,275.14 千円/人 / 補助 20,119.69 千円/人 / ベース 4,378.49 千円/人</t>
         </is>
       </c>
     </row>
@@ -4759,32 +6140,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12,891.09 千円/人 / 補助 15,466.61 千円/人 / ベース 10,894.12 千円/人</t>
+          <t xml:space="preserve">全社 12,892.95 千円/人 / 補助 15,469.1 千円/人 / ベース 10,895.49 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12,886.54 千円/人 / 補助 15,437.59 千円/人 / ベース 10,884.67 千円/人</t>
+          <t xml:space="preserve">全社 12,890.42 千円/人 / 補助 15,442.62 千円/人 / ベース 10,887.65 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13,007.24 千円/人 / 補助 15,583.15 千円/人 / ベース 10,967.26 千円/人</t>
+          <t xml:space="preserve">全社 13,013.24 千円/人 / 補助 15,590.84 千円/人 / ベース 10,971.92 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14,824.92 千円/人 / 補助 18,713.16 千円/人 / ベース 11,759.19 千円/人</t>
+          <t xml:space="preserve">全社 14,821.25 千円/人 / 補助 18,699.59 千円/人 / ベース 11,763.34 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,509.69 千円/人 / 補助 24,114.65 千円/人 / ベース 12,322.98 千円/人</t>
+          <t xml:space="preserve">全社 17,499.27 千円/人 / 補助 24,084.55 千円/人 / ベース 12,328 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20,734.42 千円/人 / 補助 30,870.57 千円/人 / ベース 12,850.75 千円/人</t>
+          <t xml:space="preserve">全社 20,715.5 千円/人 / 補助 30,819.71 千円/人 / ベース 12,856.66 千円/人</t>
         </is>
       </c>
     </row>
@@ -5193,12 +6574,12 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.22 倍 / 補助 4.57 倍 / ベース 3.76 倍</t>
+          <t xml:space="preserve">全社 4.23 倍 / 補助 4.57 倍 / ベース 3.76 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.13 倍 / 補助 4.49 倍 / ベース 3.63 倍</t>
+          <t xml:space="preserve">全社 4.13 倍 / 補助 4.49 倍 / ベース 3.64 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -5208,17 +6589,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.75 倍 / 補助 5.24 倍 / ベース 4.01 倍</t>
+          <t xml:space="preserve">全社 4.75 倍 / 補助 5.23 倍 / ベース 4.01 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.7 倍 / 補助 6.55 倍 / ベース 4.29 倍</t>
+          <t xml:space="preserve">全社 5.7 倍 / 補助 6.54 倍 / ベース 4.29 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.76 倍 / 補助 7.96 倍 / ベース 4.57 倍</t>
+          <t xml:space="preserve">全社 6.75 倍 / 補助 7.94 倍 / ベース 4.57 倍</t>
         </is>
       </c>
     </row>
@@ -5580,17 +6961,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.85 pt</t>
+          <t xml:space="preserve">差 3.83 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.88 pt</t>
+          <t xml:space="preserve">差 5.85 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.88 pt</t>
+          <t xml:space="preserve">差 7.83 pt</t>
         </is>
       </c>
     </row>
@@ -5751,32 +7132,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 86.73 %</t>
+          <t xml:space="preserve">寄与率 86.32 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 96.56 %</t>
+          <t xml:space="preserve">寄与率 95.78 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 100.32 %</t>
+          <t xml:space="preserve">寄与率 99.36 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 75.93 %</t>
+          <t xml:space="preserve">寄与率 75.81 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 87.83 %</t>
+          <t xml:space="preserve">寄与率 87.77 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.78 %</t>
+          <t xml:space="preserve">寄与率 89.73 %</t>
         </is>
       </c>
     </row>
@@ -5784,7 +7165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5799,7 +7180,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来予測・調整水準</t>
+          <t xml:space="preserve">調整条件と根拠</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
@@ -6850,9 +8231,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -7587,11 +8968,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>90</v>
+        <v>180000</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -7602,11 +8983,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -7617,11 +8998,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>2304000</v>
+        <v>2</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7632,11 +9013,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>677969</v>
+        <v>2304000</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7647,11 +9028,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>519031</v>
+        <v>677969</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7662,11 +9043,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>36000</v>
+        <v>519031</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7677,11 +9058,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:P2-14</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>135000</v>
+        <v>36000</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7692,11 +9073,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:P2-4</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>45000</v>
+        <v>7600000</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7707,11 +9088,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>7600000</v>
+        <v>190000</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7812,11 +9193,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:P2-14</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>142500</v>
+        <v>8000000</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7827,11 +9208,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:P2-4</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>47500</v>
+        <v>200000</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7842,11 +9223,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>8000000</v>
+        <v>100</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7857,11 +9238,11 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
@@ -7872,11 +9253,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>2</v>
+        <v>2560000</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -7887,11 +9268,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>2560000</v>
+        <v>730000</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7902,11 +9283,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>730000</v>
+        <v>600000</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7917,11 +9298,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>600000</v>
+        <v>40000</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7932,11 +9313,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>40000</v>
+        <v>13200000</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7947,11 +9328,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:P2-14</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>150000</v>
+        <v>1900000</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7962,11 +9343,11 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:P2-4</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -7977,11 +9358,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>13200000</v>
+        <v>1000000</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7992,11 +9373,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>1900000</v>
+        <v>2400000</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -8007,11 +9388,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>500000</v>
+        <v>6700000</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -8022,11 +9403,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>1000000</v>
+        <v>3900000</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -8037,11 +9418,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>2400000</v>
+        <v>6500000</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -8052,11 +9433,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>6700000</v>
+        <v>3600000</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -8067,11 +9448,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>3900000</v>
+        <v>700000</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -8082,11 +9463,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8097,11 +9478,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>3600000</v>
+        <v>7500000</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8112,11 +9493,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>700000</v>
+        <v>2900000</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8127,11 +9508,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>1000000</v>
+        <v>2400000</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8142,11 +9523,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>7500000</v>
+        <v>5700000</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8157,11 +9538,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>2900000</v>
+        <v>5400000</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8172,11 +9553,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>2400000</v>
+        <v>1200000</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8187,11 +9568,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>5700000</v>
+        <v>500000</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8202,11 +9583,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>5400000</v>
+        <v>5300000</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8217,11 +9598,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>1200000</v>
+        <v>14300000</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8232,11 +9613,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8247,11 +9628,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>5300000</v>
+        <v>800000</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8262,11 +9643,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>14300000</v>
+        <v>1000000</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8277,11 +9658,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8292,11 +9673,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>800000</v>
+        <v>7200000</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8307,11 +9688,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8322,11 +9703,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>2500000</v>
+        <v>7100000</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8337,11 +9718,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>7200000</v>
+        <v>3800000</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8352,11 +9733,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>4100000</v>
+        <v>800000</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8367,11 +9748,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>7100000</v>
+        <v>1000000</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8382,11 +9763,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>3800000</v>
+        <v>7900000</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8397,11 +9778,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>800000</v>
+        <v>3100000</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8412,11 +9793,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>1000000</v>
+        <v>2800000</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8427,11 +9808,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>7900000</v>
+        <v>6400000</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8442,11 +9823,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>3100000</v>
+        <v>6100000</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8457,11 +9838,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>2800000</v>
+        <v>1200000</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8472,11 +9853,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>6400000</v>
+        <v>600000</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8487,11 +9868,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>6100000</v>
+        <v>5800000</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8502,11 +9883,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>1200000</v>
+        <v>15600000</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8517,11 +9898,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>600000</v>
+        <v>2200000</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8532,11 +9913,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>5800000</v>
+        <v>1000000</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8547,11 +9928,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>15600000</v>
+        <v>1000000</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8562,11 +9943,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>2200000</v>
+        <v>2700000</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8577,11 +9958,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>1000000</v>
+        <v>7800000</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8592,11 +9973,11 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>1000000</v>
+        <v>4300000</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8607,11 +9988,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>2700000</v>
+        <v>7800000</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8622,11 +10003,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>7800000</v>
+        <v>4000000</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8637,11 +10018,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>4300000</v>
+        <v>900000</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8652,11 +10033,11 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>7800000</v>
+        <v>1000000</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8667,11 +10048,11 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>4000000</v>
+        <v>8300000</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8682,11 +10063,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>900000</v>
+        <v>3200000</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8697,11 +10078,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8712,11 +10093,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>8300000</v>
+        <v>7300000</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8727,11 +10108,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>3200000</v>
+        <v>7000000</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8742,11 +10123,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>3200000</v>
+        <v>1100000</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8757,11 +10138,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>7300000</v>
+        <v>700000</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8772,11 +10153,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>7000000</v>
+        <v>6400000</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8787,26 +10168,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>700000</v>
+        <v>0.6</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8817,11 +10198,11 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>6400000</v>
+        <v>1500000</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8832,41 +10213,41 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>1500000</v>
+        <v>100</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8877,41 +10258,41 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>100</v>
+        <v>0.005</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8922,41 +10303,41 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.005</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8967,11 +10348,11 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.0051345755693581975</v>
+        <v>0.68</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8982,26 +10363,26 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.66</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -9012,11 +10393,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -9027,26 +10408,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateToBase:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -9057,11 +10438,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -9072,26 +10453,26 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>1</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9102,11 +10483,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>-0.5</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9117,11 +10498,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.5</v>
+      